--- a/4 четверть_9_JavaScript_Vue 3 Composition API.xlsx
+++ b/4 четверть_9_JavaScript_Vue 3 Composition API.xlsx
@@ -1,40 +1,51 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Machenike\Desktop\GB_Developer_Workbook\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE4D3AF4-E14E-444B-A58C-9AFD07D8B0AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6668729E-D01C-4774-884C-A8A70824ADC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-13875" yWindow="-21720" windowWidth="51840" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="import require" sheetId="17" r:id="rId1"/>
-    <sheet name="Launch" sheetId="19" r:id="rId2"/>
-    <sheet name="data" sheetId="18" r:id="rId3"/>
-    <sheet name="v-.." sheetId="16" r:id="rId4"/>
-    <sheet name="{{ }}" sheetId="21" r:id="rId5"/>
-    <sheet name="methods" sheetId="22" r:id="rId6"/>
-    <sheet name="watch" sheetId="23" r:id="rId7"/>
-    <sheet name="Теория" sheetId="14" r:id="rId8"/>
-    <sheet name="Vue Css" sheetId="13" r:id="rId9"/>
-    <sheet name="Vue blank template" sheetId="15" r:id="rId10"/>
+    <sheet name="API-&gt;" sheetId="26" r:id="rId1"/>
+    <sheet name="App" sheetId="25" r:id="rId2"/>
+    <sheet name="setup()" sheetId="27" r:id="rId3"/>
+    <sheet name="General API" sheetId="28" r:id="rId4"/>
+    <sheet name="Lifecycle" sheetId="29" r:id="rId5"/>
+    <sheet name="Reactivity" sheetId="30" r:id="rId6"/>
+    <sheet name="Reactivity Core" sheetId="31" r:id="rId7"/>
+    <sheet name="template" sheetId="24" r:id="rId8"/>
+    <sheet name="import require" sheetId="17" r:id="rId9"/>
+    <sheet name="Launch" sheetId="19" r:id="rId10"/>
+    <sheet name="data" sheetId="18" r:id="rId11"/>
+    <sheet name="v-.." sheetId="16" r:id="rId12"/>
+    <sheet name="{{ }}" sheetId="21" r:id="rId13"/>
+    <sheet name="methods" sheetId="22" r:id="rId14"/>
+    <sheet name="watch" sheetId="23" r:id="rId15"/>
+    <sheet name="Теория" sheetId="14" r:id="rId16"/>
+    <sheet name="Vue Css" sheetId="13" r:id="rId17"/>
+    <sheet name="Vue blank template" sheetId="15" r:id="rId18"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="799">
   <si>
     <t>Урок 1 часть 1</t>
   </si>
@@ -9361,17 +9372,3753 @@
   <si>
     <t>@click="counter"</t>
   </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>Описание</t>
+  </si>
+  <si>
+    <t>Детали</t>
+  </si>
+  <si>
+    <t>По умолчанию</t>
+  </si>
+  <si>
+    <t>Пример</t>
+  </si>
+  <si>
+    <t>Ссылки</t>
+  </si>
+  <si>
+    <t>createApp()</t>
+  </si>
+  <si>
+    <t>Создаёт экземпляр приложения Vue.</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>Creating a Vue Application</t>
+  </si>
+  <si>
+    <t>createSSRApp()</t>
+  </si>
+  <si>
+    <t>Создаёт экземпляр приложения в режиме SSR Hydration.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Использование полностью идентично </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>createApp()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>createSSRApp(App)</t>
+  </si>
+  <si>
+    <t>SSR — Client Hydration</t>
+  </si>
+  <si>
+    <t>app.mount()</t>
+  </si>
+  <si>
+    <t>Монтирует экземпляр приложения в DOM-контейнер.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Аргумент — DOM-элемент или CSS-селектор (используется первый найденный). Возвращает экземпляр корневого компонента. При наличии template/render заменяет содержимое контейнера. В SSR-режиме выполняет гидратацию. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>mount()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> можно вызвать только один раз на экземпляр.</t>
+    </r>
+  </si>
+  <si>
+    <t>app.unmount()</t>
+  </si>
+  <si>
+    <t>Размонтирует смонтированное приложение.</t>
+  </si>
+  <si>
+    <t>Вызывает хуки unmount для всех компонентов в дереве приложения.</t>
+  </si>
+  <si>
+    <t>app.onUnmount()</t>
+  </si>
+  <si>
+    <t>Регистрирует callback, вызываемый при размонтировании приложения.</t>
+  </si>
+  <si>
+    <t>app.onUnmount(() =&gt; { /* cleanup */ })</t>
+  </si>
+  <si>
+    <t>app.component()</t>
+  </si>
+  <si>
+    <t>Регистрирует глобальный компонент или возвращает уже зарегистрированный.</t>
+  </si>
+  <si>
+    <t>При передаче только имени — получение компонента. При передаче имени и определения — регистрация.</t>
+  </si>
+  <si>
+    <t>Component Registration</t>
+  </si>
+  <si>
+    <t>app.directive()</t>
+  </si>
+  <si>
+    <t>Регистрирует глобальную директиву или возвращает уже зарегистрированную.</t>
+  </si>
+  <si>
+    <t>Поддерживает объектную директиву и сокращённую функциональную форму.</t>
+  </si>
+  <si>
+    <t>Custom Directives</t>
+  </si>
+  <si>
+    <t>Устанавливает плагин.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Плагин — объект с методом </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>install()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> или функция, используемая как </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>install()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Опции передаются в </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>install()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Повторный вызов с тем же плагином устанавливает его только один раз.</t>
+    </r>
+  </si>
+  <si>
+    <t>app.use(MyPlugin)</t>
+  </si>
+  <si>
+    <t>Plugins</t>
+  </si>
+  <si>
+    <t>app.provide()</t>
+  </si>
+  <si>
+    <t>Предоставляет значение для inject во всех дочерних компонентах приложения.</t>
+  </si>
+  <si>
+    <t>Первый аргумент — ключ инъекции, второй — значение. Возвращает экземпляр приложения.</t>
+  </si>
+  <si>
+    <t>app.runWithContext()</t>
+  </si>
+  <si>
+    <t>Выполняет callback с текущим приложением как контекстом инъекции.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Требует Vue 3.3+. Во время синхронного вызова callback </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>inject()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> может получать значения из текущего app даже без активного экземпляра компонента. Возвращает результат callback.</t>
+    </r>
+  </si>
+  <si>
+    <t>app.version</t>
+  </si>
+  <si>
+    <t>Версия Vue, с которой создано приложение.</t>
+  </si>
+  <si>
+    <t>Полезно в плагинах для условной логики в зависимости от версии Vue.</t>
+  </si>
+  <si>
+    <t>Global API — version</t>
+  </si>
+  <si>
+    <t>app.config</t>
+  </si>
+  <si>
+    <t>Объект конфигурации экземпляра приложения.</t>
+  </si>
+  <si>
+    <t>Свойства следует изменять до монтирования приложения.</t>
+  </si>
+  <si>
+    <t>console.log(app.config)</t>
+  </si>
+  <si>
+    <t>app.config.errorHandler</t>
+  </si>
+  <si>
+    <t>Глобальный обработчик необработанных ошибок приложения.</t>
+  </si>
+  <si>
+    <t>Принимает ошибку, экземпляр компонента и строку с информацией об источнике. Перехватывает ошибки из render, event handlers, lifecycle hooks, setup(), watchers, custom directives, transition hooks. В production 3-й аргумент — сокращённый код.</t>
+  </si>
+  <si>
+    <t>app.config.errorHandler = (err, instance, info) =&gt; { }</t>
+  </si>
+  <si>
+    <t>Production Error Code Reference</t>
+  </si>
+  <si>
+    <t>app.config.warnHandler</t>
+  </si>
+  <si>
+    <t>Пользовательский обработчик runtime-предупреждений Vue.</t>
+  </si>
+  <si>
+    <t>Принимает сообщение, экземпляр компонента и trace иерархии. Рекомендуется только для отладки, удалять после.</t>
+  </si>
+  <si>
+    <t>app.config.warnHandler = (msg, instance, trace) =&gt; { }</t>
+  </si>
+  <si>
+    <t>app.config.performance</t>
+  </si>
+  <si>
+    <t>Включает трассировку производительности init, compile, render и patch.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Работает только в dev-режиме и в браузерах с поддержкой </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>performance.mark</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> API.</t>
+    </r>
+  </si>
+  <si>
+    <t>app.config.performance = true</t>
+  </si>
+  <si>
+    <t>Guide — Performance</t>
+  </si>
+  <si>
+    <t>app.config.compilerOptions</t>
+  </si>
+  <si>
+    <t>Настройки runtime-компилятора шаблонов.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Влияет на все компоненты приложения. Можно переопределить на уровне компонента через </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>compilerOptions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Важно:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> работает только с full build (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>vue.js</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">). При runtime-only build настройки передаются через </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@vue/compiler-dom</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> в конфигурации сборщика (vue-loader, vite plugin).</t>
+    </r>
+  </si>
+  <si>
+    <t>compilerOptions (component)</t>
+  </si>
+  <si>
+    <t>app.config.compilerOptions.isCustomElement</t>
+  </si>
+  <si>
+    <t>Метод проверки, является ли тег нативным custom element.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Возвращает </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, если тег нужно рендерить как нативный элемент, а не Vue-компонент. HTML и SVG теги распознаются автоматически.</t>
+    </r>
+  </si>
+  <si>
+    <t>Vue and Web Components</t>
+  </si>
+  <si>
+    <t>app.config.compilerOptions.whitespace</t>
+  </si>
+  <si>
+    <t>Настройка обработки пробелов в шаблонах.</t>
+  </si>
+  <si>
+    <r>
+      <t>'condense'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: сжимает пробелы в начале/конце элементов, удаляет пробелы между элементами с переносами строк, сжимает последовательные пробелы в text nodes. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>'preserve'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> отключает пункты 2 и 3.</t>
+    </r>
+  </si>
+  <si>
+    <t>app.config.compilerOptions.delimiters</t>
+  </si>
+  <si>
+    <t>Разделители текстовой интерполяции в шаблоне.</t>
+  </si>
+  <si>
+    <t>Обычно используется для избежания конфликтов с серверными фреймворками, использующими mustache-синтаксис.</t>
+  </si>
+  <si>
+    <t>app.config.compilerOptions.comments</t>
+  </si>
+  <si>
+    <t>Обработка HTML-комментариев в шаблонах.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">По умолчанию Vue удаляет комментарии в production. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> сохраняет их даже в production. В dev комментарии всегда сохраняются.</t>
+    </r>
+  </si>
+  <si>
+    <t>Объект для регистрации глобальных свойств, доступных на любом экземпляре компонента.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Замена </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Vue.prototype</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> из Vue 2. Использовать умеренно. При конфликте с собственным свойством компонента приоритет у свойства компонента.</t>
+    </r>
+  </si>
+  <si>
+    <t>Augmenting Global Properties</t>
+  </si>
+  <si>
+    <t>app.config.optionMergeStrategies</t>
+  </si>
+  <si>
+    <t>Стратегии слияния кастомных опций компонентов.</t>
+  </si>
+  <si>
+    <t>Функция стратегии получает значения опции родителя и потомка. Используется плагинами с кастомными опциями через global mixins.</t>
+  </si>
+  <si>
+    <t>Component Instance — $options</t>
+  </si>
+  <si>
+    <t>app.config.idPrefix</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Префикс для всех ID, генерируемых через </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>useId()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> в приложении.</t>
+    </r>
+  </si>
+  <si>
+    <t>useId()</t>
+  </si>
+  <si>
+    <t>app.config.throwUnhandledErrorInProduction</t>
+  </si>
+  <si>
+    <t>Принудительно пробрасывает необработанные ошибки в production.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">По умолчанию в dev ошибки пробрасываются, в prod — только логируются. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> позволяет сервисам мониторинга перехватывать production-ошибки.</t>
+    </r>
+  </si>
+  <si>
+    <t>Первый аргумент — корневой компонент, 
+второй (опционально) — props для корневого компонента.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>С inline-компонентом:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+import { createApp } from 'vue'
+const app = createApp(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>{
+  /* root component options */
+}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>С импортированным компонентом:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+import { createApp } from 'vue'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>import App from './App.vue'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+const app = createApp(App)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">import { createApp } from 'vue'
+const app = createApp(/* ... */)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>app.mount('#app')</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+// или DOM-элемент:
+app.mount(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>document.body.firstChild</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">import { createApp } from 'vue'
+const app = createApp({})
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>// регистрация</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve">
+app.component(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>'MyComponent', {
+  /* ... */
+}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve">)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>// получение зарегистрированного компонента</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve">
+const </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>MyComponent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve"> = app.component(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>'MyComponent'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">import { createApp } from 'vue'
+const app = createApp({ /* ... */ })
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>// объектная директива</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve">
+app.directive(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>'myDirective'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> {
+  /* custom directive hooks */
+}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve">)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>// функциональная форма</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve">
+app.directive(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>'myDirective', () =&gt; {
+  /* ... */
+}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve">)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>// получение зарегистрированной директивы</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve">
+const </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>myDirective</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve"> = app.directive(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>'myDirective'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Внутри компонента (Options API):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+export default {
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  inject: ['message'],</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  created() {
+    console.log(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>this.message</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) // 'hello'
+  }
+}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>Инициализация переменной</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve">
+import { createApp } from 'vue'
+const app = createApp(/* ... */)
+app.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>provide('message', 'hello'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve">)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>Внутри компонента (Composition API):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve">
+import { </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>inject</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve"> } from 'vue'
+export default {
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>setup</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>() {
+    console.log</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(inject('message')</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>) // 'hello'
+  }
+}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">import { </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>inject</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> } from 'vue'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>app.provide('id', 1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">
+const injected = app.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>runWithContext</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">(() =&gt; {
+  return </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>inject('id')</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">
+})
+console.log(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>injected</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>) // 1</t>
+    </r>
+  </si>
+  <si>
+    <t>Для тестирования</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>// все теги, начинающиеся с 'ion-', считаются custom elements</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">
+app.config.compilerOptions.isCustomElement = (tag) =&gt; {
+  return tag.startsWith('ion-')
+}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>Проверка версии внутри плагина:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">
+export default {
+  install(app) {
+    const version = Number(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>app.version.split('.')[0]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>)
+    if (version &lt; 3) {
+      console.warn('This plugin requires Vue 3')
+    }
+  }
+}</t>
+    </r>
+  </si>
+  <si>
+    <t>Для отладки и логирования</t>
+  </si>
+  <si>
+    <t>Для сборки проектов</t>
+  </si>
+  <si>
+    <t>Не понятно</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">app.config.compilerOptions.delimiters = ['${', '}']
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>//по умолчанию ['{{', '}}']</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">app.config.compilerOptions.whitespace = 'preserve'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>//по умолчанию 'condense'</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">app.config.compilerOptions.comments = true
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>//по умолчанию false</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">app.config.globalProperties.msg = 'hello'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>//по умолчанию {}</t>
+    </r>
+  </si>
+  <si>
+    <t>Глобальная переменная</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Глобальная переменная
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>Главное отличие от app.config.globalProperties</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>Четкая иерархия. Потомок знает, откуда пришли данные (не "глобальная свалка", как в globalProperties).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">import { </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>ref, onMounted, getCurrentInstance</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>} from 'vue';
+const app = createApp({
+  setup() {
+    // В Composition API нет прямого доступа к $options
+    // Придется использовать getCurrentInstance()
+    const instance = getCurrentInstance();
+    // Но стратегии слияния для кастомных свойств работают и здесь
+    onMounted(() =&gt; {
+      console.log(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>instance?.proxy?.$options?.msg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve">); // 'Hello Vue'
+    });
+    return {};
+  }
+});
+// Стратегия слияния все равно применяется к $options
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>app.config.optionMergeStrategies.msg = (parent, child) =&gt; {
+  return (parent || '') + (child || '');
+};</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve">
+app.mount('#app');
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>//по умолчанию {}</t>
+    </r>
+  </si>
+  <si>
+    <t>Для mixins</t>
+  </si>
+  <si>
+    <r>
+      <t>app.config.idPrefix = 'myApp'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>'myApp:0'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve">'myApp:1'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>//по умолчанию undefined</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Для получения уникального значения в рамках одной пользовательской сессии
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>Свой совет:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve"> использовать snapshot даты</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">app.config.throwUnhandledErrorInProduction = true
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="204"/>
+      </rPr>
+      <t>//по умолчанию false</t>
+    </r>
+  </si>
+  <si>
+    <t>Не понятно, нужно разобраться</t>
+  </si>
+  <si>
+    <t>Для создания приложения</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Для создания приложения </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>server side rendering</t>
+    </r>
+  </si>
+  <si>
+    <t>Глобальный компонент</t>
+  </si>
+  <si>
+    <t>Глобальная директива</t>
+  </si>
+  <si>
+    <t>Для проверки версии приложения</t>
+  </si>
+  <si>
+    <t>Для отладки
+По умолчанию false</t>
+  </si>
+  <si>
+    <t>Для отладки</t>
+  </si>
+  <si>
+    <t>Для mixins merge strategy</t>
+  </si>
+  <si>
+    <t>Для получения уникального значения</t>
+  </si>
+  <si>
+    <t>Глобальные значения</t>
+  </si>
+  <si>
+    <t>Для плагинов</t>
+  </si>
+  <si>
+    <t>Для настройки параметров ниже</t>
+  </si>
+  <si>
+    <t>Для сборки</t>
+  </si>
+  <si>
+    <t>Основы setup()</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Правило!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Актуально, если без &lt;script setup&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>setup()</t>
+  </si>
+  <si>
+    <t>Точка входа Composition API в компоненте.</t>
+  </si>
+  <si>
+    <t>Точка входа Composition API</t>
+  </si>
+  <si>
+    <t>import { ref } from 'vue'
+export default {
+  setup() {
+    const count = ref(0)
+    return { count }
+  },
+  mounted() {
+    console.log(this.count) // 0
+  }
+}</t>
+  </si>
+  <si>
+    <t>Используется без SFC/build step или для интеграции Composition API в Options API компонент. Возвращает объект — свойства доступны в template и на this (Options API). Внутри setup() this === undefined. Refs из return автоматически unwrap в template и на this. Рекомендуется script setup в SFC.</t>
+  </si>
+  <si>
+    <t>Composition API — setup()</t>
+  </si>
+  <si>
+    <t>setup(props)</t>
+  </si>
+  <si>
+    <t>Первый аргумент setup — реактивные props компонента.</t>
+  </si>
+  <si>
+    <t>Доступ к props</t>
+  </si>
+  <si>
+    <t>export default {
+  props: { title: String },
+  setup(props) {
+    console.log(props.title)
+  }
+}</t>
+  </si>
+  <si>
+    <t>props реактивны и обновляются при новых значениях. Деструктуризация props теряет reactivity — обращаться как props.xxx.</t>
+  </si>
+  <si>
+    <t>toRefs(props) / toRef(props, key)</t>
+  </si>
+  <si>
+    <t>Утилиты для деструктуризации props с сохранением reactivity.</t>
+  </si>
+  <si>
+    <t>Деструктуризация props</t>
+  </si>
+  <si>
+    <t>import { toRefs, toRef } from 'vue'
+setup(props) {
+  const { title } = toRefs(props)
+  console.log(title.value)
+  const titleRef = toRef(props, 'title')
+}</t>
+  </si>
+  <si>
+    <t>toRefs(props) превращает props в объект refs. toRef(props, 'title') — ref для одного свойства. Нужны при деструктуризации или передаче prop во внешнюю функцию.</t>
+  </si>
+  <si>
+    <t>toRefs()
+toRef() (https://vuejs.org/api/reactivity-utilities#toref)</t>
+  </si>
+  <si>
+    <t>async setup()</t>
+  </si>
+  <si>
+    <t>Асинхронная форма setup с top-level await.</t>
+  </si>
+  <si>
+    <t>Асинхронный setup (Suspense)</t>
+  </si>
+  <si>
+    <t>export default {
+  async setup() {
+    const data = await fetchData()
+    return { data }
+  }
+}</t>
+  </si>
+  <si>
+    <t>Допустима только если компонент — потомок Suspense. Иначе setup() должен возвращать объект синхронно.</t>
+  </si>
+  <si>
+    <t>Setup Context</t>
+  </si>
+  <si>
+    <t>setup(props, context)</t>
+  </si>
+  <si>
+    <t>Второй аргумент — объект Setup Context.</t>
+  </si>
+  <si>
+    <t>setup(props, context) {
+  console.log(context.attrs)
+  console.log(context.slots)
+  console.log(context.emit)
+  console.log(context.expose)
+}</t>
+  </si>
+  <si>
+    <t>context не реактивен, можно безопасно деструктурировать: { attrs, slots, emit, expose }.</t>
+  </si>
+  <si>
+    <t>context.attrs</t>
+  </si>
+  <si>
+    <t>Атрибуты компонента (не-props).</t>
+  </si>
+  <si>
+    <t>Fallthrough attributes</t>
+  </si>
+  <si>
+    <t>setup(props, { attrs }) {
+  console.log(attrs.class)
+}</t>
+  </si>
+  <si>
+    <t>Не реактивный объект, аналог $attrs. Не деструктурировать — использовать attrs.x. Обновляется при обновлении компонента; для side effects — onBeforeUpdate.</t>
+  </si>
+  <si>
+    <t>Fallthrough Attributes</t>
+  </si>
+  <si>
+    <t>context.slots</t>
+  </si>
+  <si>
+    <t>Слоты компонента.</t>
+  </si>
+  <si>
+    <t>Слоты</t>
+  </si>
+  <si>
+    <t>setup(props, { slots }) {
+  console.log(slots.default)
+}</t>
+  </si>
+  <si>
+    <t>Не реактивный объект, аналог $slots. Не деструктурировать — использовать slots.x. Свойства slots не реактивны; side effects — onBeforeUpdate.</t>
+  </si>
+  <si>
+    <t>Slots</t>
+  </si>
+  <si>
+    <t>context.emit</t>
+  </si>
+  <si>
+    <t>Функция для emit событий.</t>
+  </si>
+  <si>
+    <t>Emit событий</t>
+  </si>
+  <si>
+    <t>setup(props, { emit }) {
+  emit('submit', payload)
+}</t>
+  </si>
+  <si>
+    <t>Аналог $emit.</t>
+  </si>
+  <si>
+    <t>Component Events</t>
+  </si>
+  <si>
+    <t>context.expose()</t>
+  </si>
+  <si>
+    <t>Явно ограничивает свойства, доступные родителю через template ref.</t>
+  </si>
+  <si>
+    <t>Expose для template refs</t>
+  </si>
+  <si>
+    <t>setup(props, { expose }) {
+  const publicCount = ref(0)
+  const privateCount = ref(0)
+  expose({ count: publicCount })
+  // expose() без аргументов — ничего не открывает
+}</t>
+  </si>
+  <si>
+    <t>expose() без аргументов делает instance «закрытым». expose({ ... }) выборочно открывает refs/methods родителю.</t>
+  </si>
+  <si>
+    <t>Render functions</t>
+  </si>
+  <si>
+    <t>setup() → render function</t>
+  </si>
+  <si>
+    <t>setup может вернуть render function вместо объекта.</t>
+  </si>
+  <si>
+    <t>Render function из setup</t>
+  </si>
+  <si>
+    <t>import { h, ref } from 'vue'
+export default {
+  setup(props, { expose }) {
+    const count = ref(0)
+    const increment = () =&gt; ++count.value
+    expose({ increment })
+    return () =&gt; h('div', count.value)
+  }
+}</t>
+  </si>
+  <si>
+    <t>Return render function (h/JSX) использует reactive state из setup. При return render function нельзя вернуть объект — для expose методов родителю вызывайте expose() до return.</t>
+  </si>
+  <si>
+    <t>Render Functions</t>
+  </si>
+  <si>
+    <t>Общие утилиты</t>
+  </si>
+  <si>
+    <t>Определение компонентов</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>Возвращает текущую версию Vue.</t>
+  </si>
+  <si>
+    <t>Для проверки версии Vue</t>
+  </si>
+  <si>
+    <t>import { version } from 'vue'
+console.log(version)</t>
+  </si>
+  <si>
+    <t>Тип: string. Полезно для проверки версии при установке плагинов или условной логики.</t>
+  </si>
+  <si>
+    <t>nextTick()</t>
+  </si>
+  <si>
+    <t>Утилита для ожидания следующего цикла обновления DOM.</t>
+  </si>
+  <si>
+    <t>Для работы с DOM после обновления</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">import { ref, nextTick } from 'vue'
+const count = ref(0)
+async function increment() {
+  count.value++
+  // DOM ещё не обновлён
+  console.log(document.getElementById('counter').textContent)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">  await nextTick()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">
+  // DOM обновлён
+  console.log(document.getElementById('counter').textContent)
+}</t>
+    </r>
+  </si>
+  <si>
+    <t>После изменения реактивного состояния Vue буферизует обновления DOM до «next tick». Можно передать callback или await Promise.</t>
+  </si>
+  <si>
+    <t>Component Instance — $nextTick</t>
+  </si>
+  <si>
+    <t>defineComponent()</t>
+  </si>
+  <si>
+    <t>Type helper для определения компонента Vue с выводом типов.</t>
+  </si>
+  <si>
+    <t>Для TypeScript и определения компонентов</t>
+  </si>
+  <si>
+    <t>import { defineComponent } from 'vue'
+const Foo = defineComponent({
+  /* options */
+})
+type FooInstance = InstanceType&lt;typeof Foo&gt;
+// function syntax (3.3+):
+const Comp = defineComponent(
+  (props) =&gt; {
+    const count = ref(0)
+    return () =&gt; h('div', count.value)
+  },
+  { props: { /* ... */ } }
+)</t>
+  </si>
+  <si>
+    <t>Options syntax: первый аргумент — объект опций, возвращает constructor с inferred instance type. Function syntax (3.3+): функция как setup(), возвращает render function (h/JSX); поддерживает generics в TSX. Для webpack treeshaking добавьте /*#__PURE__*/ перед вызовом (для Vite не требуется).</t>
+  </si>
+  <si>
+    <t>Using Vue with TypeScript</t>
+  </si>
+  <si>
+    <t>defineAsyncComponent()</t>
+  </si>
+  <si>
+    <t>Определяет асинхронный компонент с ленивой загрузкой при рендере.</t>
+  </si>
+  <si>
+    <t>Для ленивой загрузки компонентов</t>
+  </si>
+  <si>
+    <t>import { defineAsyncComponent } from 'vue'
+const AsyncComp = defineAsyncComponent(
+  () =&gt; import('./components/AsyncComponent.vue')
+)
+// с опциями:
+defineAsyncComponent({
+  loader: () =&gt; import('./Comp.vue'),
+  loadingComponent: LoadingComp,
+  errorComponent: ErrorComp,
+  delay: 200,
+  timeout: 3000,
+  suspensible: false,
+  onError(error, retry, fail, attempts) { /* ... */ }
+})</t>
+  </si>
+  <si>
+    <t>Аргумент — loader-функция () =&gt; Promise&lt;Component&gt; или объект AsyncComponentOptions с полями loader, loadingComponent, errorComponent, delay, timeout, suspensible, onError.</t>
+  </si>
+  <si>
+    <t>Async Components</t>
+  </si>
+  <si>
+    <t>onBeforeMount()</t>
+  </si>
+  <si>
+    <t>Регистрирует хук непосредственно перед первым монтированием компонента.</t>
+  </si>
+  <si>
+    <t>Монтирование (Composition API)</t>
+  </si>
+  <si>
+    <t>import { onBeforeMount } from 'vue'
+onBeforeMount(() =&gt; {
+  // reactive state готов, DOM ещё не создан
+})</t>
+  </si>
+  <si>
+    <t>Composition API. Вызывать синхронно в setup(). Reactive state уже настроен, DOM-узлы ещё не созданы. Не вызывается при SSR.</t>
+  </si>
+  <si>
+    <t>Lifecycle Hooks</t>
+  </si>
+  <si>
+    <t>onMounted()</t>
+  </si>
+  <si>
+    <t>Регистрирует callback после монтирования компонента.</t>
+  </si>
+  <si>
+    <t>import { ref, onMounted } from 'vue'
+const el = ref()
+onMounted(() =&gt; {
+  console.log(el.value)
+})</t>
+  </si>
+  <si>
+    <t>Composition API. Компонент смонтирован: DOM создан и вставлен, синхронные дочерние компоненты смонтированы. Для side effects с доступом к DOM. Не вызывается при SSR.</t>
+  </si>
+  <si>
+    <t>onBeforeUpdate()</t>
+  </si>
+  <si>
+    <t>Регистрирует хук перед обновлением DOM из-за изменения реактивного состояния.</t>
+  </si>
+  <si>
+    <t>Обновление DOM (Composition API)</t>
+  </si>
+  <si>
+    <t>import { onBeforeUpdate } from 'vue'
+onBeforeUpdate(() =&gt; {
+  // доступ к DOM до обновления Vue
+})</t>
+  </si>
+  <si>
+    <t>Composition API. Можно безопасно изменять state. Не вызывается при SSR.</t>
+  </si>
+  <si>
+    <t>onUpdated()</t>
+  </si>
+  <si>
+    <t>Регистрирует callback после обновления DOM из-за изменения реактивного состояния.</t>
+  </si>
+  <si>
+    <t>import { ref, onUpdated } from 'vue'
+const count = ref(0)
+onUpdated(() =&gt; {
+  console.log(document.getElementById('count').textContent)
+})</t>
+  </si>
+  <si>
+    <t>Composition API. Хук родителя вызывается после дочерних. Не мутировать state в updated — риск бесконечного цикла. Для конкретного изменения DOM используйте nextTick(). Не вызывается при SSR.</t>
+  </si>
+  <si>
+    <t>onBeforeUnmount()</t>
+  </si>
+  <si>
+    <t>Регистрирует хук непосредственно перед размонтированием экземпляра.</t>
+  </si>
+  <si>
+    <t>Размонтирование (Composition API)</t>
+  </si>
+  <si>
+    <t>import { onBeforeUnmount } from 'vue'
+onBeforeUnmount(() =&gt; {
+  // экземпляр ещё полностью функционален
+})</t>
+  </si>
+  <si>
+    <t>Composition API. Экземпляр ещё полностью функционален. Не вызывается при SSR.</t>
+  </si>
+  <si>
+    <t>onUnmounted()</t>
+  </si>
+  <si>
+    <t>Регистрирует callback после размонтирования компонента.</t>
+  </si>
+  <si>
+    <t>import { onMounted, onUnmounted } from 'vue'
+let intervalId
+onMounted(() =&gt; { intervalId = setInterval(() =&gt; {}) })
+onUnmounted(() =&gt; clearInterval(intervalId))</t>
+  </si>
+  <si>
+    <t>Composition API. Все дочерние компоненты размонтированы, reactive effects остановлены. Для очистки таймеров, listeners, соединений. Не вызывается при SSR.</t>
+  </si>
+  <si>
+    <t>onErrorCaptured()</t>
+  </si>
+  <si>
+    <t>Регистрирует хук при перехвате ошибки от descendant-компонента.</t>
+  </si>
+  <si>
+    <t>Обработка ошибок (Composition API)</t>
+  </si>
+  <si>
+    <t>import { onErrorCaptured } from 'vue'
+onErrorCaptured((err, instance, info) =&gt; {
+  console.error(err, info)
+  return false // остановить propagation
+})</t>
+  </si>
+  <si>
+    <t>Composition API. Аргументы: err, instance, info. Перехватывает ошибки из render, handlers, lifecycle, setup, watchers, directives, transitions. return false останавливает propagation. В production info — сокращённый код.</t>
+  </si>
+  <si>
+    <t>Lifecycle Hooks
+Production Error Code Reference (https://vuejs.org/error-reference/)</t>
+  </si>
+  <si>
+    <t>onRenderTracked()</t>
+  </si>
+  <si>
+    <t>Debug-хук при отслеживании reactive dependency render effect.</t>
+  </si>
+  <si>
+    <t>Отладка реактивности (Composition API, dev)</t>
+  </si>
+  <si>
+    <t>import { onRenderTracked } from 'vue'
+onRenderTracked((e) =&gt; {
+  console.log(e.key, e.type, e.target)
+})</t>
+  </si>
+  <si>
+    <t>Composition API. Только dev-режим. Не вызывается при SSR. DebuggerEvent: effect, target, type ('get'/'has'/'iterate'), key.</t>
+  </si>
+  <si>
+    <t>Reactivity in Depth</t>
+  </si>
+  <si>
+    <t>onRenderTriggered()</t>
+  </si>
+  <si>
+    <t>Debug-хук при повторном запуске render effect из-за dependency.</t>
+  </si>
+  <si>
+    <t>import { onRenderTriggered } from 'vue'
+onRenderTriggered((e) =&gt; {
+  console.log(e.key, e.type, e.newValue)
+})</t>
+  </si>
+  <si>
+    <t>Composition API. Только dev-режим. Не вызывается при SSR. DebuggerEvent: type ('set'/'add'/'delete'/'clear'), key, newValue, oldValue.</t>
+  </si>
+  <si>
+    <t>onActivated()</t>
+  </si>
+  <si>
+    <t>Callback после вставки экземпляра в DOM из кэша KeepAlive.</t>
+  </si>
+  <si>
+    <t>KeepAlive (Composition API)</t>
+  </si>
+  <si>
+    <t>import { onActivated } from 'vue'
+onActivated(() =&gt; {
+  // компонент снова активен
+})</t>
+  </si>
+  <si>
+    <t>Composition API. Не вызывается при SSR.</t>
+  </si>
+  <si>
+    <t>Lifecycle of Cached Instance</t>
+  </si>
+  <si>
+    <t>onDeactivated()</t>
+  </si>
+  <si>
+    <t>Callback после удаления экземпляра из DOM в кэш KeepAlive.</t>
+  </si>
+  <si>
+    <t>import { onDeactivated } from 'vue'
+onDeactivated(() =&gt; {
+  // компонент деактивирован, но не уничтожен
+})</t>
+  </si>
+  <si>
+    <t>onServerPrefetch()</t>
+  </si>
+  <si>
+    <t>Регистрирует async-функцию, выполняемую до SSR-рендера компонента.</t>
+  </si>
+  <si>
+    <t>SSR (Composition API)</t>
+  </si>
+  <si>
+    <t>import { ref, onServerPrefetch, onMounted } from 'vue'
+const data = ref(null)
+onServerPrefetch(async () =&gt; {
+  data.value = await fetchOnServer()
+})
+onMounted(async () =&gt; {
+  if (!data.value) data.value = await fetchOnClient()
+})</t>
+  </si>
+  <si>
+    <t>Composition API. Если возвращает Promise, сервер ждёт resolve. Только SSR. Для prefetch данных на сервере.</t>
+  </si>
+  <si>
+    <t>Server-Side Rendering</t>
+  </si>
+  <si>
+    <t>Нормализация ref и value</t>
+  </si>
+  <si>
+    <t>isRef()</t>
+  </si>
+  <si>
+    <t>Проверяет, является ли значение ref-объектом.</t>
+  </si>
+  <si>
+    <t>Проверка ref</t>
+  </si>
+  <si>
+    <t>import { isRef, ref } from 'vue'
+const foo = ref(1)
+if (isRef(foo)) {
+  console.log(foo.value) // 1
+}</t>
+  </si>
+  <si>
+    <t>Возвращает true/false. В runtime позволяет безопасно обращаться к .value только у ref.</t>
+  </si>
+  <si>
+    <t>unref()</t>
+  </si>
+  <si>
+    <t>Возвращает inner value, если аргумент — ref, иначе сам аргумент.</t>
+  </si>
+  <si>
+    <t>Разворачивание ref</t>
+  </si>
+  <si>
+    <t>import { unref, ref } from 'vue'
+function useFoo(x) {
+  const unwrapped = unref(x)
+  // число, даже если x был ref(число)
+  console.log(unwrapped)
+}</t>
+  </si>
+  <si>
+    <t>Синтаксический сахар: val = isRef(val) ? val.value : val.</t>
+  </si>
+  <si>
+    <t>toRef()</t>
+  </si>
+  <si>
+    <t>Нормализует value/ref/getter в ref или создаёт ref для свойства reactive-объекта.</t>
+  </si>
+  <si>
+    <t>Создание/нормализация ref</t>
+  </si>
+  <si>
+    <t>import { reactive, toRef, ref } from 'vue'
+// normalization (3.3+):
+toRef(existingRef)
+toRef(() =&gt; props.foo)
+toRef(1)
+// свойство reactive-объекта:
+const state = reactive({ foo: 1, bar: 2 })
+const fooRef = toRef(state, 'foo')
+fooRef.value++
+console.log(state.foo) // 2</t>
+  </si>
+  <si>
+    <t>Normalization (3.3+): value/ref/getter → ref. Свойство объекта: двусторонний ref, синхронизирован с source. ref(state.foo) не синхронизирован — ref() получает plain value. Для props: toRef(props, 'foo') или toRef(() =&gt; props.foo). Мутация ref prop запрещена; для v-model — computed get/set. Работает с optional properties.</t>
+  </si>
+  <si>
+    <t>Reactivity Utilities</t>
+  </si>
+  <si>
+    <t>toValue()</t>
+  </si>
+  <si>
+    <t>Нормализует value/ref/getter в plain value.</t>
+  </si>
+  <si>
+    <t>Нормализация value/ref/getter (3.3+)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">import { ref, toValue, watch } from 'vue'
+toValue(1) // 1
+toValue(ref(1)) // 1
+toValue(() =&gt; 1) // 1
+function useFeature(id) {
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>watch</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>() =&gt; toValue(id), (value)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> =&gt; {
+    console.log(value)
+  })
+}
+useFeature(1)
+useFeature(ref(1))
+useFeature(() =&gt; 1)</t>
+    </r>
+  </si>
+  <si>
+    <t>Требует Vue 3.3+. Похож на unref(), но также вызывает getter. Удобно в composables, когда аргумент может быть value, ref или функцией-getter.</t>
+  </si>
+  <si>
+    <t>toRefs()</t>
+  </si>
+  <si>
+    <t>Преобразует reactive-объект в plain object, где каждое свойство — ref.</t>
+  </si>
+  <si>
+    <t>Деструктуризация reactive</t>
+  </si>
+  <si>
+    <t>import { reactive, toRefs } from 'vue'
+const state = reactive({ foo: 1, bar: 2 })
+const stateAsRefs = toRefs(state)
+state.foo++
+console.log(stateAsRefs.foo.value) // 2
+stateAsRefs.foo.value++
+console.log(state.foo) // 3</t>
+  </si>
+  <si>
+    <t>Каждый ref создаётся через toRef(). Полезно при return state из composable — деструктуризация без потери reactivity. Только enumerable свойства; для optional — toRef.</t>
+  </si>
+  <si>
+    <t>Проверки proxy</t>
+  </si>
+  <si>
+    <t>isProxy()</t>
+  </si>
+  <si>
+    <t>Проверяет, является ли объект proxy от reactive/readonly/shallowReactive/shallowReadonly.</t>
+  </si>
+  <si>
+    <t>Проверка proxy</t>
+  </si>
+  <si>
+    <t>import { reactive, isProxy } from 'vue'
+const state = reactive({ count: 0 })
+console.log(isProxy(state)) // true
+console.log(isProxy({ count: 0 })) // false</t>
+  </si>
+  <si>
+    <t>isReactive()</t>
+  </si>
+  <si>
+    <t>Проверяет, является ли объект proxy от reactive() или shallowReactive().</t>
+  </si>
+  <si>
+    <t>Проверка reactive proxy</t>
+  </si>
+  <si>
+    <t>import { reactive, readonly, isReactive } from 'vue'
+console.log(isReactive(reactive({}))) // true
+console.log(isReactive(readonly({}))) // false</t>
+  </si>
+  <si>
+    <t>Не включает readonly proxy.</t>
+  </si>
+  <si>
+    <t>isReadonly()</t>
+  </si>
+  <si>
+    <t>Проверяет, является ли значение readonly-объектом.</t>
+  </si>
+  <si>
+    <t>Проверка readonly</t>
+  </si>
+  <si>
+    <t>import { readonly, computed, isReadonly } from 'vue'
+console.log(isReadonly(readonly({}))) // true
+console.log(isReadonly(computed(() =&gt; 1))) // true</t>
+  </si>
+  <si>
+    <t>Свойства readonly могут меняться, но не через прямое присвоение объекту. readonly/shallowReadonly и computed без set считаются readonly.</t>
+  </si>
+  <si>
+    <t>Базовые реактивные примитивы</t>
+  </si>
+  <si>
+    <t>Отслеживание изменений (watchers)</t>
+  </si>
+  <si>
+    <t>ref()</t>
+  </si>
+  <si>
+    <t>Создаёт реактивный и изменяемый ref-объект с единственным свойством .value.</t>
+  </si>
+  <si>
+    <t>Примитивная реактивность</t>
+  </si>
+  <si>
+    <t>import { ref } from 'vue'
+const count = ref(0)
+console.log(count.value) // 0
+count.value = 1
+console.log(count.value) // 1</t>
+  </si>
+  <si>
+    <t>Ref изменяемый и реактивный: чтение/запись .value отслеживаются. Если в .value записан объект — он становится deeply reactive через reactive(). Вложенные refs глубоко разворачиваются. Для shallow — shallowRef().</t>
+  </si>
+  <si>
+    <t>Reactivity Fundamentals</t>
+  </si>
+  <si>
+    <t>computed()</t>
+  </si>
+  <si>
+    <t>Принимает getter и возвращает readonly computed ref; либо объект { get, set } для writable computed.</t>
+  </si>
+  <si>
+    <t>Вычисляемые значения</t>
+  </si>
+  <si>
+    <t>import { ref, computed } from 'vue'
+const count = ref(1)
+const plusOne = computed(() =&gt; count.value + 1)
+console.log(plusOne.value) // 2
+const writable = computed({
+  get: () =&gt; count.value + 1,
+  set: (val) =&gt; { count.value = val - 1 }
+})
+writable.value = 1
+console.log(count.value) // 0</t>
+  </si>
+  <si>
+    <t>Readonly computed нельзя присваивать напрямую. Writable — через get/set. Опционально debuggerOptions: onTrack, onTrigger.</t>
+  </si>
+  <si>
+    <t>Computed Properties</t>
+  </si>
+  <si>
+    <t>reactive()</t>
+  </si>
+  <si>
+    <t>Возвращает reactive proxy объекта.</t>
+  </si>
+  <si>
+    <t>Реактивный объект</t>
+  </si>
+  <si>
+    <t>import { ref, reactive } from 'vue'
+const obj = reactive({ count: 0 })
+obj.count++
+const count = ref(1)
+const state = reactive({ count })
+count.value++ // обновит state.count
+state.count++ // обновит count.value
+const books = reactive([ref('Vue 3 Guide')])
+console.log(books[0].value) // .value в массиве</t>
+  </si>
+  <si>
+    <t>Глубокая реактивность для всех вложенных свойств. Refs внутри объекта разворачиваются, кроме элементов массива/Map/Set — там нужен .value. Proxy не равен исходному объекту — работайте с proxy. Для shallow — shallowReactive().</t>
+  </si>
+  <si>
+    <t>readonly()</t>
+  </si>
+  <si>
+    <t>Принимает reactive/plain object или ref и возвращает readonly proxy.</t>
+  </si>
+  <si>
+    <t>Только чтение</t>
+  </si>
+  <si>
+    <t>import { reactive, readonly, watchEffect } from 'vue'
+const original = reactive({ count: 0 })
+const copy = readonly(original)
+watchEffect(() =&gt; {
+  console.log(copy.count)
+})
+original.count++ // ok, watcher сработает
+copy.count++ // warning, мутация запрещена</t>
+  </si>
+  <si>
+    <t>Readonly proxy глубокий: вложенные свойства тоже readonly. Ref-unwrapping как у reactive(), но значения тоже readonly. Для shallow — shallowReadonly().</t>
+  </si>
+  <si>
+    <t>watchEffect()</t>
+  </si>
+  <si>
+    <t>Немедленно запускает функцию, отслеживает зависимости и перезапускает при их изменении.</t>
+  </si>
+  <si>
+    <t>Автоматическое отслеживание зависимостей</t>
+  </si>
+  <si>
+    <t>import { ref, watchEffect } from 'vue'
+const count = ref(0)
+watchEffect(() =&gt; console.log(count.value))
+// -&gt; 0
+count.value++
+// -&gt; 1
+const stop = watchEffect(() =&gt; {})
+stop() // остановить watcher|Первый аргумент — effect. Второй — options: flush ('pre'|'post'
+//по умолчанию flush: 'pre'</t>
+  </si>
+  <si>
+    <t>Watchers</t>
+  </si>
+  <si>
+    <t>watchPostEffect()</t>
+  </si>
+  <si>
+    <t>Псевдоним watchEffect() с flush: 'post'.</t>
+  </si>
+  <si>
+    <t>watchEffect после render</t>
+  </si>
+  <si>
+    <t>Эквивалент watchEffect(fn, { flush: 'post' }). Удобен, когда side effect должен читать обновлённый DOM.</t>
+  </si>
+  <si>
+    <t>Callback Flush Timing</t>
+  </si>
+  <si>
+    <t>watchSyncEffect()</t>
+  </si>
+  <si>
+    <t>Псевдоним watchEffect() с flush: 'sync'.</t>
+  </si>
+  <si>
+    <t>Синхронный watchEffect</t>
+  </si>
+  <si>
+    <t>Эквивалент watchEffect(fn, { flush: 'sync' }). Может влиять на производительность и согласованность данных при пакетных обновлениях — использовать осторожно.</t>
+  </si>
+  <si>
+    <t>watch()</t>
+  </si>
+  <si>
+    <t>Отслеживает один или несколько reactive-источников и вызывает callback при изменении.</t>
+  </si>
+  <si>
+    <t>Явное отслеживание источников</t>
+  </si>
+  <si>
+    <t>Lazy по умолчанию — callback только при изменении. Источник: getter, ref, reactive object или массив. Options: immediate, deep (или max depth в 3.5+), flush, onTrack/onTrigger, once (3.4+). При прямом watch reactive object — deep mode автоматически. Возвращает handle: stop(), pause(), resume(). Cleanup: onCleanup в callback или onWatcherCleanup().</t>
+  </si>
+  <si>
+    <t>onWatcherCleanup()</t>
+  </si>
+  <si>
+    <t>Регистрирует cleanup при следующем перезапуске текущего watcher.</t>
+  </si>
+  <si>
+    <t>Cleanup watcher (3.5+)</t>
+  </si>
+  <si>
+    <t>import { ref, watch, onWatcherCleanup } from 'vue'
+const id = ref(1)
+watch(id, async (newId) =&gt; {
+  const { response, cancel } = doAsyncWork(newId)
+  onWatcherCleanup(cancel)
+  data.value = await response
+})</t>
+  </si>
+  <si>
+    <t>Только Vue 3.5+. Вызывать синхронно внутри watchEffect или watch callback — не после await в async. Альтернатива onCleanup в watchEffect/watch. failSilently — не бросать ошибку вне watcher.</t>
+  </si>
+  <si>
+    <t>Reactivity Core</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">const state = reactive({ count: 0, name: 'Vue' })
+const user = ref({ name: 'John', age: 30 })
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">// ❌ Деструктуризация ломает реактивность
+const { count, name } = state
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">// ✅ Правильно: использовать toRefs
+const { count, name } = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>toRefs(state)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Деструктуризация реактивных объектов ломает их реактивность, если не использовать toRef()</t>
+  </si>
+  <si>
+    <t>Про деструктуризацию</t>
+  </si>
+  <si>
+    <t>Про замену всего объекта</t>
+  </si>
+  <si>
+    <t>Однако если объект реактивен через reactive, то его замена приведет к потере его реактивности.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">const user = ref({ name: 'John' })
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">// ❌ Деструктуризация ломает реактивность
+state =  { name: 'Jane' } </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">const user = ref({ name: 'John' })
+// Позже...
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>user.value = { name: 'Jane' } // ✅ Реактивность сохраняется</t>
+    </r>
+  </si>
+  <si>
+    <t>sync'), onTrack, onTrigger. Возвращает handle: stop(), pause(), resume(). 
+Cleanup через onCleanup в callback или onWatcherCleanup() (3.5+). 
+flush: 'post' — после render; 'sync' — синхронно (осторожно).</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">import { ref, reactive, watch } from 'vue'
+const state = reactive({ count: 0 })
+watch(() =&gt; state.count, (count, prevCount) =&gt; {
+  console.log(count, prevCount)
+})
+const count = ref(0)
+watch(count, (value, oldValue) =&gt; {
+  console.log(value, oldValue)
+})
+watch([ref(0), ref('')], ([foo, bar], [prevFoo, prevBar]) =&gt; {})
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>//по умолчанию immediate: false, deep: false, flush: 'pre', once: false</t>
+    </r>
+  </si>
+  <si>
+    <t>import { ref, watchPostEffect } from 'vue'
+const count = ref(0)
+watchPostEffect(() =&gt; {
+  // выполняется после обновления DOM
+  console.log(count.value)
+})</t>
+  </si>
+  <si>
+    <t>import { ref, watchSyncEffect } from 'vue'
+const count = ref(0)
+watchSyncEffect(() =&gt; {
+  // синхронно при каждом изменении зависимости
+  console.log(count.value)
+})</t>
+  </si>
+  <si>
+    <t>1 Использовать только с Object и Array
+2 Почти аналог data() в Options API
+3 Требуется работа только со свойствами
+4 Не требуется полная замена Object</t>
+  </si>
+  <si>
+    <t>`https://vuejs.org/guide/essentials/watchers.html#watch-source-types</t>
+  </si>
+  <si>
+    <t>Деструктуризация массива параметров функции</t>
+  </si>
+  <si>
+    <t>watch([x, () =&gt; y.value], ([newX, newY]) =&gt; {
+  console.log(`x is ${newX} and y is ${newY}`)
+})</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>several refs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -&gt; getter -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>link</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">single ref </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">-&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>reactive</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">watch(
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>() =&gt; x.value + y.value,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  (sum) =&gt; {
+    console.log(`sum of x + y is: ${sum}`)
+  }
+)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Важно! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Getter всегда возвращает лишь </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ссылку на объект</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, поэтому если в getter положить объект со свойствами, то</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> при изменении свойств watcher не сработает,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> а при присвоении нового объекта срабатывает</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Важно! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Так как здесь </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>не ссылка на объект</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, а </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>реактивный объект/значение, то watcher срабатывает всегда - и когда изменяются свойства, и когда присваивается новый объект</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Важно!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Если </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>изменяются свойства</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, то </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>newX = oldX</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, так как </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ссылка на объект не поменялась</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Важно! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Если </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>присваивается новый объект</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, то </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>newX != oldX</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>так как поменялась ссылка на объект</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">const x = ref(0)
+const y = ref(0)
+watch(
+   </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>x</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>//</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>reactive object</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+   (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>newX, oldX</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) =&gt; {
+  console.log(`x is ${newX}`)
+})</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">watch(
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  () =&gt; state.someObject</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, //</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>link</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  () =&gt; {
+    // fires only when state.someObject is replaced
+  }
+)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">watch(
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  () =&gt; state.someObject, //</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>link</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  () =&gt; {
+    // fires only when state.someObject is replaced
+  },
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>{ deep: true }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Но!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">При указании { deep: true } </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>отслеживание происходит точно также как и при реактивном объекте</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Важно!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Если изменяются свойства, то newX = oldX, так как ссылка на объект не поменялась
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Важно!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Если присваивается новый объект, то newX != oldX, так как поменялась ссылка на объект</t>
+    </r>
+  </si>
+  <si>
+    <t>Агрегация отслеживания</t>
+  </si>
+  <si>
+    <t>создай отдельный xls с содержимым про Composition API Reactivity: Core из https://vuejs.org/api/</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="48" x14ac:knownFonts="1">
+  <fonts count="63">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -9756,8 +13503,88 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Arial Unicode MS"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF00B050"/>
+      <name val="Arial Unicode MS"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -9836,6 +13663,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -9846,13 +13679,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -9863,20 +13697,20 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="28" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -9885,7 +13719,60 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="6" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="49" fontId="21" fillId="7" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="7" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -9894,51 +13781,10 @@
     <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="6" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="2" applyFill="1"/>
-    <xf numFmtId="49" fontId="17" fillId="7" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="7" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -9950,99 +13796,169 @@
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="49" fontId="37" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="36" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="33" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="36" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="51" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="58" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="32" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="33" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="29" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="32" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="Гиперссылка" xfId="3" builtinId="8"/>
+    <cellStyle name="Гиперссылка 2" xfId="4" xr:uid="{C34F8B78-A62E-4E4D-AC99-81334F44B07F}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{141A142D-D8A7-43F9-B8D2-54AA311FA1CB}"/>
     <cellStyle name="Обычный 2 2" xfId="2" xr:uid="{6AED7C1E-16D4-4B27-9CDE-4556C8555CBE}"/>
@@ -10454,526 +14370,49 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B7CAD42-95E0-4E20-A7EA-DF3B831CFF68}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A053E7E8-304F-43A3-ADB5-1EB2FE3D5F8D}">
   <sheetPr>
+    <tabColor rgb="FF7030A0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:V33"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A2:E3"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="46.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="62.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="81.08984375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="56.453125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.36328125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="43.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.08984375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="67.90625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="64.453125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="7.90625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="39.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.90625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="72.54296875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="43.90625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7.90625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="56.90625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="46.6328125" style="2" customWidth="1"/>
-    <col min="18" max="18" width="62.90625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="49.08984375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="67.6328125" style="2" customWidth="1"/>
-    <col min="22" max="22" width="68.453125" style="1" customWidth="1"/>
-    <col min="23" max="24" width="59.453125" style="1" customWidth="1"/>
-    <col min="25" max="25" width="59.54296875" style="1" customWidth="1"/>
-    <col min="26" max="26" width="99.453125" style="1" customWidth="1"/>
-    <col min="27" max="27" width="41.36328125" style="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.6328125" style="1"/>
+    <col min="1" max="1" width="36" style="2" customWidth="1"/>
+    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="71.21875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="65" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="2"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="2" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="2" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="2" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="2" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
-      <c r="G2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="5"/>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C3" s="43" t="s">
-        <v>278</v>
-      </c>
-      <c r="D3" s="41" t="s">
-        <v>309</v>
-      </c>
-      <c r="P3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="2"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B4" s="58" t="s">
-        <v>261</v>
-      </c>
-      <c r="C4" s="58" t="s">
-        <v>260</v>
-      </c>
-      <c r="D4" s="41" t="s">
-        <v>310</v>
-      </c>
-      <c r="P4" s="1"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="2"/>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A5" s="57" t="s">
-        <v>377</v>
-      </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-    </row>
-    <row r="6" spans="1:22" ht="116" x14ac:dyDescent="0.35">
-      <c r="A6" s="56" t="s">
-        <v>378</v>
-      </c>
-      <c r="B6" s="56" t="s">
-        <v>279</v>
-      </c>
-      <c r="C6" s="42" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" ht="87" x14ac:dyDescent="0.35">
-      <c r="A7" s="42"/>
-      <c r="B7" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="C7" s="42" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A8" s="58" t="s">
-        <v>363</v>
-      </c>
-      <c r="B8" s="59"/>
-      <c r="C8" s="59"/>
-    </row>
-    <row r="9" spans="1:22" ht="58" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" ht="15" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="D16" s="61" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A17" s="60" t="s">
-        <v>365</v>
-      </c>
-      <c r="C17" s="2"/>
-    </row>
-    <row r="18" spans="1:21" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="B18" s="56" t="s">
-        <v>366</v>
-      </c>
-      <c r="C18" s="56" t="s">
-        <v>367</v>
-      </c>
-      <c r="D18" s="56" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A19" s="58" t="s">
-        <v>364</v>
-      </c>
-      <c r="B19" s="44" t="s">
-        <v>299</v>
-      </c>
-      <c r="C19" s="44" t="s">
-        <v>293</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" ht="275.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="42" t="s">
-        <v>297</v>
-      </c>
-      <c r="B20" s="42" t="s">
-        <v>295</v>
-      </c>
-      <c r="C20" s="42" t="s">
-        <v>296</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A21" s="42"/>
-      <c r="B21" s="42"/>
-      <c r="C21" s="42"/>
-    </row>
-    <row r="22" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="5"/>
-      <c r="C22" s="6"/>
-      <c r="G22" s="5"/>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="5"/>
-      <c r="S22" s="5"/>
-      <c r="T22" s="25"/>
-      <c r="U22" s="5"/>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A23" s="2"/>
-      <c r="B23" s="42"/>
-      <c r="C23" s="43" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A24" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="B24" s="42"/>
-      <c r="C24" s="42"/>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A25" s="2"/>
-      <c r="B25" s="31" t="s">
-        <v>284</v>
-      </c>
-      <c r="C25" s="31" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" ht="29" x14ac:dyDescent="0.35">
-      <c r="A26" s="46" t="s">
-        <v>304</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21" ht="29" x14ac:dyDescent="0.35">
-      <c r="A27" s="46" t="s">
-        <v>304</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" ht="29" x14ac:dyDescent="0.35">
-      <c r="A28" s="46" t="s">
-        <v>304</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="C28" s="42" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" ht="203" x14ac:dyDescent="0.35">
-      <c r="A29" s="46" t="s">
-        <v>303</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="C29" s="45" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" ht="203" x14ac:dyDescent="0.35">
-      <c r="A30" s="46" t="s">
-        <v>303</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="C30" s="45" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" ht="116" x14ac:dyDescent="0.35">
-      <c r="A31" s="46" t="s">
-        <v>303</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="C31" s="45" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A32" s="11" t="s">
-        <v>293</v>
-      </c>
-      <c r="C32" s="44" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" ht="232" x14ac:dyDescent="0.35">
-      <c r="B33" s="42" t="s">
-        <v>297</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>294</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D3" r:id="rId1" location="imports--exports" display="Ссылка" xr:uid="{5F2650EE-EC1A-4EB5-A54A-484006789CA4}"/>
-    <hyperlink ref="D4" r:id="rId2" display="Ссылка" xr:uid="{7D3863D0-674C-43DF-8581-E2D9E02F5CED}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08DE618A-9635-4194-B69D-D0533DA1C310}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A2:V45"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="36" style="1" customWidth="1"/>
-    <col min="2" max="2" width="62.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="81.08984375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="56.453125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.36328125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="43.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.08984375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="67.90625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="64.453125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="7.90625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="39.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.90625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="72.54296875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="43.90625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7.90625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="56.90625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="46.6328125" style="2" customWidth="1"/>
-    <col min="18" max="18" width="62.90625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="49.08984375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="67.6328125" style="2" customWidth="1"/>
-    <col min="22" max="22" width="68.453125" style="1" customWidth="1"/>
-    <col min="23" max="24" width="59.453125" style="1" customWidth="1"/>
-    <col min="25" max="25" width="59.54296875" style="1" customWidth="1"/>
-    <col min="26" max="26" width="99.453125" style="1" customWidth="1"/>
-    <col min="27" max="27" width="41.36328125" style="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.6328125" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
-      <c r="G2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="5"/>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A3" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="P3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="2"/>
-    </row>
-    <row r="4" spans="1:22" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="C4" s="37" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C10" s="32"/>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C11" s="32"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C12" s="32"/>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C13" s="32"/>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="C38" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B39" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B40" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B41" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B42" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B43" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B44" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B45" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>48</v>
+    <row r="2" spans="1:5" s="64" customFormat="1">
+      <c r="E2" s="65"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -10982,45 +14421,45 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28458EAD-FB50-44A9-A1C4-98CED7A280D0}">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:V38"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.54296875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="81.08984375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="56.453125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.36328125" style="7" customWidth="1"/>
-    <col min="6" max="6" width="43.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.08984375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="67.90625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="64.453125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="7.90625" style="7" customWidth="1"/>
-    <col min="11" max="11" width="39.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.90625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="72.54296875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="43.90625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7.90625" style="7" customWidth="1"/>
-    <col min="16" max="16" width="56.90625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="46.6328125" style="2" customWidth="1"/>
-    <col min="18" max="18" width="62.90625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="49.08984375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="8.6328125" style="8"/>
-    <col min="21" max="21" width="67.6328125" style="2" customWidth="1"/>
-    <col min="22" max="22" width="68.453125" style="1" customWidth="1"/>
-    <col min="23" max="24" width="59.453125" style="1" customWidth="1"/>
-    <col min="25" max="25" width="59.54296875" style="1" customWidth="1"/>
-    <col min="26" max="26" width="99.453125" style="1" customWidth="1"/>
-    <col min="27" max="27" width="41.36328125" style="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.6328125" style="1"/>
+    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="81.109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="43.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" style="7" customWidth="1"/>
+    <col min="11" max="11" width="39.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.5546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.88671875" style="7" customWidth="1"/>
+    <col min="16" max="16" width="56.88671875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.6640625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.109375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.6640625" style="8"/>
+    <col min="21" max="21" width="67.6640625" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.44140625" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.44140625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.5546875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.33203125" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="6"/>
@@ -11039,7 +14478,7 @@
       <c r="S2" s="5"/>
       <c r="U2" s="5"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -11053,7 +14492,7 @@
       <c r="U3" s="1"/>
       <c r="V3" s="2"/>
     </row>
-    <row r="4" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" ht="43.2">
       <c r="A4" s="50" t="s">
         <v>331</v>
       </c>
@@ -11061,7 +14500,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="87" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" ht="86.4">
       <c r="A5" s="1" t="s">
         <v>332</v>
       </c>
@@ -11075,7 +14514,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22">
       <c r="A6" s="1" t="s">
         <v>332</v>
       </c>
@@ -11089,7 +14528,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="7" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22" ht="43.2">
       <c r="A7" s="1" t="s">
         <v>353</v>
       </c>
@@ -11103,7 +14542,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22" ht="43.2">
       <c r="A8" s="1" t="s">
         <v>353</v>
       </c>
@@ -11117,7 +14556,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22">
       <c r="A9" s="50" t="s">
         <v>355</v>
       </c>
@@ -11125,7 +14564,7 @@
       <c r="C9" s="2"/>
       <c r="D9" s="51"/>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22">
       <c r="A10" s="1" t="s">
         <v>356</v>
       </c>
@@ -11137,12 +14576,12 @@
         <v>357</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22">
       <c r="A11" s="49" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:22" ht="116" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22" ht="115.2">
       <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
@@ -11154,7 +14593,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:22" ht="58" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" ht="57.6">
       <c r="A13" s="1" t="s">
         <v>59</v>
       </c>
@@ -11166,7 +14605,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:22" ht="29" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" ht="28.8">
       <c r="A14" s="1" t="s">
         <v>58</v>
       </c>
@@ -11180,7 +14619,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:22" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" ht="129.6">
       <c r="A15" s="1" t="s">
         <v>57</v>
       </c>
@@ -11194,7 +14633,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22">
       <c r="A16" s="50" t="s">
         <v>31</v>
       </c>
@@ -11202,12 +14641,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4">
       <c r="A17" s="11" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" ht="57.6">
       <c r="B18" s="29" t="s">
         <v>226</v>
       </c>
@@ -11218,12 +14657,12 @@
         <v>228</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4">
       <c r="A19" s="11" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" ht="129.6">
       <c r="B20" s="29" t="s">
         <v>230</v>
       </c>
@@ -11234,12 +14673,12 @@
         <v>231</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4">
       <c r="A21" s="11" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" ht="187.2">
       <c r="A22" s="1" t="s">
         <v>232</v>
       </c>
@@ -11251,7 +14690,7 @@
       </c>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" ht="116" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" ht="115.2">
       <c r="A23" s="1" t="s">
         <v>233</v>
       </c>
@@ -11262,7 +14701,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="145" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" ht="144">
       <c r="B24" s="2" t="s">
         <v>236</v>
       </c>
@@ -11270,7 +14709,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="290" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" ht="288">
       <c r="B25" s="2" t="s">
         <v>237</v>
       </c>
@@ -11278,7 +14717,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4">
       <c r="A26" s="50" t="s">
         <v>35</v>
       </c>
@@ -11286,12 +14725,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" ht="72">
       <c r="B27" s="47" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" ht="28.8">
       <c r="A28" s="28" t="s">
         <v>315</v>
       </c>
@@ -11299,7 +14738,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="116" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" ht="115.2">
       <c r="A29" s="1" t="s">
         <v>318</v>
       </c>
@@ -11310,7 +14749,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="319" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" ht="316.8">
       <c r="A30" s="1" t="s">
         <v>319</v>
       </c>
@@ -11324,7 +14763,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4">
       <c r="A31" s="50" t="s">
         <v>39</v>
       </c>
@@ -11332,7 +14771,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="261" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" ht="259.2">
       <c r="B32" s="48" t="s">
         <v>330</v>
       </c>
@@ -11340,7 +14779,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4">
       <c r="A33" s="50" t="s">
         <v>43</v>
       </c>
@@ -11348,7 +14787,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" ht="129.6">
       <c r="A34" s="1" t="s">
         <v>337</v>
       </c>
@@ -11356,7 +14795,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" ht="72">
       <c r="A35" s="1" t="s">
         <v>352</v>
       </c>
@@ -11364,7 +14803,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" ht="28.8">
       <c r="A36" s="1" t="s">
         <v>340</v>
       </c>
@@ -11372,7 +14811,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" ht="57.6">
       <c r="A37" s="1" t="s">
         <v>341</v>
       </c>
@@ -11381,7 +14820,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4">
       <c r="A38" s="1" t="s">
         <v>344</v>
       </c>
@@ -11393,45 +14832,45 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE361D92-5DE0-4FA8-8123-F169A0DA3581}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:V14"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.54296875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="81.08984375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="56.453125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.36328125" style="7" customWidth="1"/>
-    <col min="6" max="6" width="43.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.08984375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="67.90625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="64.453125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="7.90625" style="7" customWidth="1"/>
-    <col min="11" max="11" width="39.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.90625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="72.54296875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="43.90625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7.90625" style="7" customWidth="1"/>
-    <col min="16" max="16" width="56.90625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="46.6328125" style="2" customWidth="1"/>
-    <col min="18" max="18" width="62.90625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="49.08984375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="8.6328125" style="8"/>
-    <col min="21" max="21" width="67.6328125" style="2" customWidth="1"/>
-    <col min="22" max="22" width="68.453125" style="1" customWidth="1"/>
-    <col min="23" max="24" width="59.453125" style="1" customWidth="1"/>
-    <col min="25" max="25" width="59.54296875" style="1" customWidth="1"/>
-    <col min="26" max="26" width="99.453125" style="1" customWidth="1"/>
-    <col min="27" max="27" width="41.36328125" style="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.6328125" style="1"/>
+    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="81.109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="43.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" style="7" customWidth="1"/>
+    <col min="11" max="11" width="39.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.5546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.88671875" style="7" customWidth="1"/>
+    <col min="16" max="16" width="56.88671875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.6640625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.109375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.6640625" style="8"/>
+    <col min="21" max="21" width="67.6640625" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.44140625" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.44140625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.5546875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.33203125" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="6"/>
@@ -11450,7 +14889,7 @@
       <c r="S2" s="5"/>
       <c r="U2" s="5"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22">
       <c r="C3" s="11" t="s">
         <v>1</v>
       </c>
@@ -11461,7 +14900,7 @@
       <c r="U3" s="1"/>
       <c r="V3" s="2"/>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22">
       <c r="A4" s="10" t="s">
         <v>379</v>
       </c>
@@ -11470,7 +14909,7 @@
       <c r="U4" s="1"/>
       <c r="V4" s="2"/>
     </row>
-    <row r="5" spans="1:22" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" ht="129.6">
       <c r="A5" s="14" t="s">
         <v>103</v>
       </c>
@@ -11484,7 +14923,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22" ht="129.6">
       <c r="A6" s="14" t="s">
         <v>122</v>
       </c>
@@ -11496,7 +14935,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="7" spans="1:22" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22" ht="100.8">
       <c r="A7" s="14" t="s">
         <v>123</v>
       </c>
@@ -11510,7 +14949,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22" ht="129.6">
       <c r="A8" s="14"/>
       <c r="B8" s="36" t="s">
         <v>247</v>
@@ -11519,7 +14958,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22">
       <c r="A9" s="14"/>
       <c r="B9" s="30" t="s">
         <v>244</v>
@@ -11528,24 +14967,24 @@
         <v>245</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22">
       <c r="A10" s="10" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C11" s="62" t="s">
+    <row r="11" spans="1:22">
+      <c r="C11" s="61" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22">
       <c r="A12" s="10" t="s">
         <v>382</v>
       </c>
       <c r="B12" s="12"/>
       <c r="C12" s="9"/>
     </row>
-    <row r="13" spans="1:22" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" ht="129.6">
       <c r="A13" s="2" t="s">
         <v>85</v>
       </c>
@@ -11557,9 +14996,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="14" spans="1:22" ht="29" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" ht="28.8">
       <c r="B14" s="12"/>
-      <c r="C14" s="56" t="s">
+      <c r="C14" s="55" t="s">
         <v>383</v>
       </c>
     </row>
@@ -11569,44 +15008,44 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2A651A-02D2-4C6D-91FC-2CBD73190D44}">
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:V38"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
-    <col min="2" max="2" width="62.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="81.08984375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="56.453125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.36328125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="43.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.08984375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="67.90625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="64.453125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="7.90625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="39.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.90625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="72.54296875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="43.90625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7.90625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="56.90625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="46.6328125" style="2" customWidth="1"/>
-    <col min="18" max="18" width="62.90625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="49.08984375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="67.6328125" style="2" customWidth="1"/>
-    <col min="22" max="22" width="68.453125" style="1" customWidth="1"/>
-    <col min="23" max="24" width="59.453125" style="1" customWidth="1"/>
-    <col min="25" max="25" width="59.54296875" style="1" customWidth="1"/>
-    <col min="26" max="26" width="99.453125" style="1" customWidth="1"/>
-    <col min="27" max="27" width="41.36328125" style="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.6328125" style="1"/>
+    <col min="2" max="2" width="62.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="81.109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="43.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.5546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.88671875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="56.88671875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.6640625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.109375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="67.6640625" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.44140625" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.44140625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.5546875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.33203125" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22" s="3" customFormat="1">
       <c r="B2" s="5"/>
       <c r="C2" s="6"/>
       <c r="G2" s="5"/>
@@ -11617,7 +15056,7 @@
       <c r="T2" s="25"/>
       <c r="U2" s="5"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22">
       <c r="C3" s="11" t="s">
         <v>258</v>
       </c>
@@ -11625,17 +15064,17 @@
       <c r="U3" s="1"/>
       <c r="V3" s="2"/>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22">
       <c r="A4" s="31" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="116" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" ht="115.2">
       <c r="C5" s="40" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22">
       <c r="A6" s="10" t="s">
         <v>7</v>
       </c>
@@ -11643,7 +15082,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22">
       <c r="A7" s="23" t="s">
         <v>20</v>
       </c>
@@ -11657,7 +15096,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22" ht="57.6">
       <c r="A8" s="4" t="s">
         <v>17</v>
       </c>
@@ -11671,7 +15110,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="29" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22" ht="28.8">
       <c r="A9" s="4" t="s">
         <v>16</v>
       </c>
@@ -11685,7 +15124,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:22" ht="29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22" ht="28.8">
       <c r="A10" s="9" t="s">
         <v>9</v>
       </c>
@@ -11699,7 +15138,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:22" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22" ht="100.8">
       <c r="A11" s="4" t="s">
         <v>18</v>
       </c>
@@ -11713,7 +15152,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:22" ht="29" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22" ht="28.8">
       <c r="A12" s="9" t="s">
         <v>14</v>
       </c>
@@ -11727,7 +15166,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22">
       <c r="A13" s="14" t="s">
         <v>103</v>
       </c>
@@ -11739,7 +15178,7 @@
       </c>
       <c r="D13" s="14"/>
     </row>
-    <row r="14" spans="1:22" ht="29" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" ht="28.8">
       <c r="A14" s="14" t="s">
         <v>77</v>
       </c>
@@ -11753,7 +15192,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="15" spans="1:22" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" ht="100.8">
       <c r="A15" s="14" t="s">
         <v>105</v>
       </c>
@@ -11767,7 +15206,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="16" spans="1:22" ht="29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22" ht="28.8">
       <c r="A16" s="9" t="s">
         <v>11</v>
       </c>
@@ -11781,7 +15220,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" ht="28.8">
       <c r="A17" s="9" t="s">
         <v>12</v>
       </c>
@@ -11795,7 +15234,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4">
       <c r="A18" s="9" t="s">
         <v>10</v>
       </c>
@@ -11809,7 +15248,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" ht="43.2">
       <c r="A19" s="9" t="s">
         <v>13</v>
       </c>
@@ -11821,7 +15260,7 @@
       </c>
       <c r="D19" s="14"/>
     </row>
-    <row r="38" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="3:3">
       <c r="C38" s="24"/>
     </row>
   </sheetData>
@@ -11830,45 +15269,45 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1120C29B-A224-406A-9A85-6A1751B09B3B}">
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:V10"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.54296875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="81.08984375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="56.453125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.36328125" style="7" customWidth="1"/>
-    <col min="6" max="6" width="43.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.08984375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="67.90625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="64.453125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="7.90625" style="7" customWidth="1"/>
-    <col min="11" max="11" width="39.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.90625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="72.54296875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="43.90625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7.90625" style="7" customWidth="1"/>
-    <col min="16" max="16" width="56.90625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="46.6328125" style="2" customWidth="1"/>
-    <col min="18" max="18" width="62.90625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="49.08984375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="8.6328125" style="8"/>
-    <col min="21" max="21" width="67.6328125" style="2" customWidth="1"/>
-    <col min="22" max="22" width="68.453125" style="1" customWidth="1"/>
-    <col min="23" max="24" width="59.453125" style="1" customWidth="1"/>
-    <col min="25" max="25" width="59.54296875" style="1" customWidth="1"/>
-    <col min="26" max="26" width="99.453125" style="1" customWidth="1"/>
-    <col min="27" max="27" width="41.36328125" style="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.6328125" style="1"/>
+    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="81.109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="43.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" style="7" customWidth="1"/>
+    <col min="11" max="11" width="39.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.5546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.88671875" style="7" customWidth="1"/>
+    <col min="16" max="16" width="56.88671875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.6640625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.109375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.6640625" style="8"/>
+    <col min="21" max="21" width="67.6640625" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.44140625" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.44140625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.5546875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.33203125" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="6"/>
@@ -11887,7 +15326,7 @@
       <c r="S2" s="5"/>
       <c r="U2" s="5"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22">
       <c r="C3" s="11" t="s">
         <v>1</v>
       </c>
@@ -11898,14 +15337,14 @@
       <c r="U3" s="1"/>
       <c r="V3" s="2"/>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22">
       <c r="A4" s="10" t="s">
         <v>60</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
     </row>
-    <row r="5" spans="1:22" ht="58" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" ht="57.6">
       <c r="A5" s="1" t="s">
         <v>60</v>
       </c>
@@ -11919,7 +15358,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:22" s="7" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22" s="7" customFormat="1" ht="129.6">
       <c r="A6" s="2" t="s">
         <v>86</v>
       </c>
@@ -11948,7 +15387,7 @@
       <c r="U6" s="2"/>
       <c r="V6" s="1"/>
     </row>
-    <row r="7" spans="1:22" s="7" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22" s="7" customFormat="1" ht="72">
       <c r="A7" s="2"/>
       <c r="B7" s="13" t="s">
         <v>89</v>
@@ -11973,7 +15412,7 @@
       <c r="U7" s="2"/>
       <c r="V7" s="1"/>
     </row>
-    <row r="8" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22" s="7" customFormat="1">
       <c r="A8" s="31" t="s">
         <v>219</v>
       </c>
@@ -11998,7 +15437,7 @@
       <c r="U8" s="2"/>
       <c r="V8" s="1"/>
     </row>
-    <row r="9" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22" s="7" customFormat="1">
       <c r="A9" s="1" t="s">
         <v>103</v>
       </c>
@@ -12025,7 +15464,7 @@
       <c r="U9" s="2"/>
       <c r="V9" s="1"/>
     </row>
-    <row r="10" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22" s="7" customFormat="1">
       <c r="A10" s="1" t="s">
         <v>77</v>
       </c>
@@ -12056,45 +15495,45 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7BEB5B2-92F5-4415-BAF1-6F4428F63827}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:V58"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.54296875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="81.08984375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="56.453125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.36328125" style="7" customWidth="1"/>
-    <col min="6" max="6" width="43.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.08984375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="67.90625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="64.453125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="7.90625" style="7" customWidth="1"/>
-    <col min="11" max="11" width="39.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.90625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="72.54296875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="43.90625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7.90625" style="7" customWidth="1"/>
-    <col min="16" max="16" width="56.90625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="46.6328125" style="2" customWidth="1"/>
-    <col min="18" max="18" width="62.90625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="49.08984375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="8.6328125" style="8"/>
-    <col min="21" max="21" width="67.6328125" style="2" customWidth="1"/>
-    <col min="22" max="22" width="68.453125" style="1" customWidth="1"/>
-    <col min="23" max="24" width="59.453125" style="1" customWidth="1"/>
-    <col min="25" max="25" width="59.54296875" style="1" customWidth="1"/>
-    <col min="26" max="26" width="99.453125" style="1" customWidth="1"/>
-    <col min="27" max="27" width="41.36328125" style="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.6328125" style="1"/>
+    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="81.109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="43.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" style="7" customWidth="1"/>
+    <col min="11" max="11" width="39.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.5546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.88671875" style="7" customWidth="1"/>
+    <col min="16" max="16" width="56.88671875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.6640625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.109375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.6640625" style="8"/>
+    <col min="21" max="21" width="67.6640625" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.44140625" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.44140625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.5546875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.33203125" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="6"/>
@@ -12113,7 +15552,7 @@
       <c r="S2" s="5"/>
       <c r="U2" s="5"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22">
       <c r="C3" s="11" t="s">
         <v>1</v>
       </c>
@@ -12124,7 +15563,7 @@
       <c r="U3" s="1"/>
       <c r="V3" s="2"/>
     </row>
-    <row r="4" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" s="7" customFormat="1">
       <c r="A4" s="10" t="s">
         <v>400</v>
       </c>
@@ -12147,14 +15586,14 @@
       <c r="U4" s="2"/>
       <c r="V4" s="1"/>
     </row>
-    <row r="5" spans="1:22" s="7" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" s="7" customFormat="1" ht="86.4">
       <c r="A5" s="2" t="s">
         <v>406</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="C5" s="56" t="s">
+      <c r="C5" s="55" t="s">
         <v>386</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -12176,14 +15615,14 @@
       <c r="U5" s="2"/>
       <c r="V5" s="1"/>
     </row>
-    <row r="6" spans="1:22" s="7" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22" s="7" customFormat="1" ht="86.4">
       <c r="A6" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="B6" s="56" t="s">
+      <c r="B6" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="C6" s="56" t="s">
+      <c r="C6" s="55" t="s">
         <v>385</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -12205,14 +15644,14 @@
       <c r="U6" s="2"/>
       <c r="V6" s="1"/>
     </row>
-    <row r="7" spans="1:22" s="7" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22" s="7" customFormat="1" ht="86.4">
       <c r="A7" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="B7" s="56" t="s">
+      <c r="B7" s="55" t="s">
         <v>384</v>
       </c>
-      <c r="C7" s="63" t="s">
+      <c r="C7" s="62" t="s">
         <v>391</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -12234,7 +15673,7 @@
       <c r="U7" s="2"/>
       <c r="V7" s="1"/>
     </row>
-    <row r="8" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22" s="7" customFormat="1">
       <c r="A8" s="31" t="s">
         <v>219</v>
       </c>
@@ -12259,7 +15698,7 @@
       <c r="U8" s="2"/>
       <c r="V8" s="1"/>
     </row>
-    <row r="9" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22" s="7" customFormat="1">
       <c r="A9" s="1" t="s">
         <v>103</v>
       </c>
@@ -12286,7 +15725,7 @@
       <c r="U9" s="2"/>
       <c r="V9" s="1"/>
     </row>
-    <row r="10" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22" s="7" customFormat="1">
       <c r="A10" s="1" t="s">
         <v>77</v>
       </c>
@@ -12311,7 +15750,7 @@
       <c r="U10" s="2"/>
       <c r="V10" s="1"/>
     </row>
-    <row r="11" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22" s="7" customFormat="1">
       <c r="A11" s="10" t="s">
         <v>15</v>
       </c>
@@ -12336,14 +15775,14 @@
       <c r="U11" s="2"/>
       <c r="V11" s="1"/>
     </row>
-    <row r="12" spans="1:22" s="7" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22" s="7" customFormat="1" ht="115.2">
       <c r="A12" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="56" t="s">
+      <c r="B12" s="55" t="s">
         <v>401</v>
       </c>
-      <c r="C12" s="56" t="s">
+      <c r="C12" s="55" t="s">
         <v>402</v>
       </c>
       <c r="D12" s="33" t="s">
@@ -12365,14 +15804,14 @@
       <c r="U12" s="2"/>
       <c r="V12" s="1"/>
     </row>
-    <row r="13" spans="1:22" s="7" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" s="7" customFormat="1" ht="72">
       <c r="A13" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B13" s="56" t="s">
+      <c r="B13" s="55" t="s">
         <v>403</v>
       </c>
-      <c r="C13" s="56" t="s">
+      <c r="C13" s="55" t="s">
         <v>404</v>
       </c>
       <c r="D13" s="33" t="s">
@@ -12394,7 +15833,7 @@
       <c r="U13" s="2"/>
       <c r="V13" s="1"/>
     </row>
-    <row r="14" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" s="7" customFormat="1">
       <c r="A14" s="10" t="s">
         <v>71</v>
       </c>
@@ -12419,7 +15858,7 @@
       <c r="U14" s="2"/>
       <c r="V14" s="1"/>
     </row>
-    <row r="15" spans="1:22" s="7" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" s="7" customFormat="1" ht="100.8">
       <c r="A15" s="1"/>
       <c r="B15" s="13" t="s">
         <v>74</v>
@@ -12427,7 +15866,7 @@
       <c r="C15" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="D15" s="56" t="s">
+      <c r="D15" s="55" t="s">
         <v>392</v>
       </c>
       <c r="F15" s="1"/>
@@ -12446,7 +15885,7 @@
       <c r="U15" s="2"/>
       <c r="V15" s="1"/>
     </row>
-    <row r="16" spans="1:22" s="7" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22" s="7" customFormat="1" ht="72">
       <c r="A16" s="1" t="s">
         <v>79</v>
       </c>
@@ -12475,12 +15914,12 @@
       <c r="U16" s="2"/>
       <c r="V16" s="1"/>
     </row>
-    <row r="17" spans="1:22" s="7" customFormat="1" ht="174" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:22" s="7" customFormat="1" ht="172.8">
       <c r="A17" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B17" s="13"/>
-      <c r="C17" s="56" t="s">
+      <c r="C17" s="55" t="s">
         <v>387</v>
       </c>
       <c r="D17" s="2" t="s">
@@ -12502,7 +15941,7 @@
       <c r="U17" s="2"/>
       <c r="V17" s="1"/>
     </row>
-    <row r="18" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:22" s="7" customFormat="1">
       <c r="A18" s="10" t="s">
         <v>92</v>
       </c>
@@ -12525,14 +15964,14 @@
       <c r="U18" s="2"/>
       <c r="V18" s="1"/>
     </row>
-    <row r="19" spans="1:22" s="7" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" s="7" customFormat="1" ht="100.8">
       <c r="A19" s="1" t="s">
         <v>393</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="56" t="s">
+      <c r="C19" s="55" t="s">
         <v>388</v>
       </c>
       <c r="D19" s="2" t="s">
@@ -12554,14 +15993,14 @@
       <c r="U19" s="2"/>
       <c r="V19" s="1"/>
     </row>
-    <row r="20" spans="1:22" s="7" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:22" s="7" customFormat="1" ht="100.8">
       <c r="A20" s="1" t="s">
         <v>395</v>
       </c>
       <c r="B20" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C20" s="56" t="s">
+      <c r="C20" s="55" t="s">
         <v>389</v>
       </c>
       <c r="D20" s="2" t="s">
@@ -12583,14 +16022,14 @@
       <c r="U20" s="2"/>
       <c r="V20" s="1"/>
     </row>
-    <row r="21" spans="1:22" s="7" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:22" s="7" customFormat="1" ht="86.4">
       <c r="A21" s="1" t="s">
         <v>397</v>
       </c>
       <c r="B21" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="C21" s="56" t="s">
+      <c r="C21" s="55" t="s">
         <v>390</v>
       </c>
       <c r="D21" s="1"/>
@@ -12610,7 +16049,7 @@
       <c r="U21" s="2"/>
       <c r="V21" s="1"/>
     </row>
-    <row r="22" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:22" s="7" customFormat="1">
       <c r="A22" s="10" t="s">
         <v>155</v>
       </c>
@@ -12633,7 +16072,7 @@
       <c r="U22" s="2"/>
       <c r="V22" s="1"/>
     </row>
-    <row r="23" spans="1:22" s="7" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:22" s="7" customFormat="1" ht="57.6">
       <c r="A23" s="1"/>
       <c r="B23" s="2"/>
       <c r="C23" s="14" t="s">
@@ -12656,7 +16095,7 @@
       <c r="U23" s="2"/>
       <c r="V23" s="1"/>
     </row>
-    <row r="24" spans="1:22" s="7" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:22" s="7" customFormat="1" ht="100.8">
       <c r="A24" s="1" t="s">
         <v>103</v>
       </c>
@@ -12683,7 +16122,7 @@
       <c r="U24" s="2"/>
       <c r="V24" s="1"/>
     </row>
-    <row r="25" spans="1:22" s="7" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:22" s="7" customFormat="1" ht="86.4">
       <c r="A25" s="1" t="s">
         <v>77</v>
       </c>
@@ -12710,7 +16149,7 @@
       <c r="U25" s="2"/>
       <c r="V25" s="1"/>
     </row>
-    <row r="26" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:22" s="7" customFormat="1">
       <c r="A26" s="10" t="s">
         <v>167</v>
       </c>
@@ -12735,7 +16174,7 @@
       <c r="U26" s="2"/>
       <c r="V26" s="1"/>
     </row>
-    <row r="27" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:22" s="7" customFormat="1">
       <c r="A27" s="27" t="s">
         <v>163</v>
       </c>
@@ -12758,14 +16197,14 @@
       <c r="U27" s="2"/>
       <c r="V27" s="1"/>
     </row>
-    <row r="28" spans="1:22" s="7" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:22" s="7" customFormat="1" ht="86.4">
       <c r="A28" s="2" t="s">
         <v>84</v>
       </c>
       <c r="B28" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="C28" s="56" t="s">
+      <c r="C28" s="55" t="s">
         <v>386</v>
       </c>
       <c r="D28" s="1" t="s">
@@ -12787,7 +16226,7 @@
       <c r="U28" s="2"/>
       <c r="V28" s="1"/>
     </row>
-    <row r="29" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:22" s="7" customFormat="1">
       <c r="A29" s="28" t="s">
         <v>164</v>
       </c>
@@ -12810,7 +16249,7 @@
       <c r="U29" s="2"/>
       <c r="V29" s="1"/>
     </row>
-    <row r="30" spans="1:22" s="7" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:22" s="7" customFormat="1" ht="72">
       <c r="A30" s="2"/>
       <c r="B30" s="14"/>
       <c r="C30" s="26" t="s">
@@ -12835,7 +16274,7 @@
       <c r="U30" s="2"/>
       <c r="V30" s="1"/>
     </row>
-    <row r="31" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:22" s="7" customFormat="1">
       <c r="A31" s="10" t="s">
         <v>168</v>
       </c>
@@ -12860,7 +16299,7 @@
       <c r="U31" s="2"/>
       <c r="V31" s="1"/>
     </row>
-    <row r="32" spans="1:22" s="7" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:22" s="7" customFormat="1" ht="86.4">
       <c r="A32" s="2" t="s">
         <v>169</v>
       </c>
@@ -12887,7 +16326,7 @@
       <c r="U32" s="2"/>
       <c r="V32" s="1"/>
     </row>
-    <row r="33" spans="1:22" s="7" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:22" s="7" customFormat="1" ht="86.4">
       <c r="A33" s="2" t="s">
         <v>170</v>
       </c>
@@ -12914,7 +16353,7 @@
       <c r="U33" s="2"/>
       <c r="V33" s="1"/>
     </row>
-    <row r="34" spans="1:22" s="7" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:22" s="7" customFormat="1" ht="86.4">
       <c r="A34" s="2" t="s">
         <v>171</v>
       </c>
@@ -12943,7 +16382,7 @@
       <c r="U34" s="2"/>
       <c r="V34" s="1"/>
     </row>
-    <row r="35" spans="1:22" s="7" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:22" s="7" customFormat="1" ht="115.2">
       <c r="A35" s="2" t="s">
         <v>172</v>
       </c>
@@ -12972,7 +16411,7 @@
       <c r="U35" s="2"/>
       <c r="V35" s="1"/>
     </row>
-    <row r="36" spans="1:22" s="7" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:22" s="7" customFormat="1" ht="28.8">
       <c r="A36" s="2" t="s">
         <v>173</v>
       </c>
@@ -12999,7 +16438,7 @@
       <c r="U36" s="2"/>
       <c r="V36" s="1"/>
     </row>
-    <row r="37" spans="1:22" s="7" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:22" s="7" customFormat="1" ht="100.8">
       <c r="A37" s="2" t="s">
         <v>174</v>
       </c>
@@ -13026,7 +16465,7 @@
       <c r="U37" s="2"/>
       <c r="V37" s="1"/>
     </row>
-    <row r="38" spans="1:22" s="7" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:22" s="7" customFormat="1" ht="86.4">
       <c r="A38" s="1" t="s">
         <v>221</v>
       </c>
@@ -13053,7 +16492,7 @@
       <c r="U38" s="2"/>
       <c r="V38" s="1"/>
     </row>
-    <row r="39" spans="1:22" s="7" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:22" s="7" customFormat="1" ht="57.6">
       <c r="A39" s="1" t="s">
         <v>181</v>
       </c>
@@ -13080,7 +16519,7 @@
       <c r="U39" s="2"/>
       <c r="V39" s="1"/>
     </row>
-    <row r="40" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:22" s="7" customFormat="1">
       <c r="A40" s="10" t="s">
         <v>194</v>
       </c>
@@ -13105,7 +16544,7 @@
       <c r="U40" s="2"/>
       <c r="V40" s="1"/>
     </row>
-    <row r="41" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:22" s="7" customFormat="1">
       <c r="A41" s="2" t="s">
         <v>196</v>
       </c>
@@ -13128,7 +16567,7 @@
       <c r="U41" s="2"/>
       <c r="V41" s="1"/>
     </row>
-    <row r="42" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:22" s="7" customFormat="1">
       <c r="A42" s="2" t="s">
         <v>197</v>
       </c>
@@ -13151,7 +16590,7 @@
       <c r="U42" s="2"/>
       <c r="V42" s="1"/>
     </row>
-    <row r="43" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:22" s="7" customFormat="1">
       <c r="A43" s="2" t="s">
         <v>215</v>
       </c>
@@ -13176,7 +16615,7 @@
       <c r="U43" s="2"/>
       <c r="V43" s="1"/>
     </row>
-    <row r="44" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:22" s="7" customFormat="1">
       <c r="A44" s="2" t="s">
         <v>198</v>
       </c>
@@ -13199,7 +16638,7 @@
       <c r="U44" s="2"/>
       <c r="V44" s="1"/>
     </row>
-    <row r="45" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:22" s="7" customFormat="1">
       <c r="A45" s="2" t="s">
         <v>199</v>
       </c>
@@ -13222,7 +16661,7 @@
       <c r="U45" s="2"/>
       <c r="V45" s="1"/>
     </row>
-    <row r="46" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:22" s="7" customFormat="1">
       <c r="A46" s="2" t="s">
         <v>200</v>
       </c>
@@ -13245,7 +16684,7 @@
       <c r="U46" s="2"/>
       <c r="V46" s="1"/>
     </row>
-    <row r="47" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:22" s="7" customFormat="1">
       <c r="A47" s="2" t="s">
         <v>201</v>
       </c>
@@ -13268,7 +16707,7 @@
       <c r="U47" s="2"/>
       <c r="V47" s="1"/>
     </row>
-    <row r="48" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:22" s="7" customFormat="1">
       <c r="A48" s="2" t="s">
         <v>202</v>
       </c>
@@ -13291,7 +16730,7 @@
       <c r="U48" s="2"/>
       <c r="V48" s="1"/>
     </row>
-    <row r="49" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:22" s="7" customFormat="1">
       <c r="A49" s="2" t="s">
         <v>203</v>
       </c>
@@ -13314,7 +16753,7 @@
       <c r="U49" s="2"/>
       <c r="V49" s="1"/>
     </row>
-    <row r="50" spans="1:22" s="7" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:22" s="7" customFormat="1" ht="86.4">
       <c r="A50" s="29" t="s">
         <v>209</v>
       </c>
@@ -13339,7 +16778,7 @@
       <c r="U50" s="2"/>
       <c r="V50" s="1"/>
     </row>
-    <row r="51" spans="1:22" s="7" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:22" s="7" customFormat="1" ht="57.6">
       <c r="A51" s="29" t="s">
         <v>211</v>
       </c>
@@ -13368,7 +16807,7 @@
       <c r="U51" s="2"/>
       <c r="V51" s="1"/>
     </row>
-    <row r="52" spans="1:22" s="7" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:22" s="7" customFormat="1" ht="28.8">
       <c r="A52" s="1" t="s">
         <v>202</v>
       </c>
@@ -13393,7 +16832,7 @@
       <c r="U52" s="2"/>
       <c r="V52" s="1"/>
     </row>
-    <row r="53" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:22" s="7" customFormat="1">
       <c r="A53" s="1" t="s">
         <v>203</v>
       </c>
@@ -13416,7 +16855,7 @@
       <c r="U53" s="2"/>
       <c r="V53" s="1"/>
     </row>
-    <row r="54" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:22" s="7" customFormat="1">
       <c r="A54" s="1" t="s">
         <v>213</v>
       </c>
@@ -13439,7 +16878,7 @@
       <c r="U54" s="2"/>
       <c r="V54" s="1"/>
     </row>
-    <row r="55" spans="1:22" s="7" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:22" s="7" customFormat="1" ht="28.8">
       <c r="A55" s="1" t="s">
         <v>207</v>
       </c>
@@ -13466,7 +16905,7 @@
       <c r="U55" s="2"/>
       <c r="V55" s="1"/>
     </row>
-    <row r="56" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:22" s="7" customFormat="1">
       <c r="A56" s="1" t="s">
         <v>220</v>
       </c>
@@ -13493,7 +16932,7 @@
       <c r="U56" s="2"/>
       <c r="V56" s="1"/>
     </row>
-    <row r="57" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:22" s="7" customFormat="1">
       <c r="A57" s="10" t="s">
         <v>242</v>
       </c>
@@ -13516,7 +16955,7 @@
       <c r="U57" s="2"/>
       <c r="V57" s="1"/>
     </row>
-    <row r="58" spans="1:22" s="7" customFormat="1" ht="145" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:22" s="7" customFormat="1" ht="144">
       <c r="A58" s="1" t="s">
         <v>243</v>
       </c>
@@ -13547,45 +16986,45 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{377CB944-0109-4965-A1E5-5F7F873C41B0}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:V6"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.54296875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="81.08984375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="56.453125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.36328125" style="7" customWidth="1"/>
-    <col min="6" max="6" width="43.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.08984375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="67.90625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="64.453125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="7.90625" style="7" customWidth="1"/>
-    <col min="11" max="11" width="39.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.90625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="72.54296875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="43.90625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7.90625" style="7" customWidth="1"/>
-    <col min="16" max="16" width="56.90625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="46.6328125" style="2" customWidth="1"/>
-    <col min="18" max="18" width="62.90625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="49.08984375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="8.6328125" style="8"/>
-    <col min="21" max="21" width="67.6328125" style="2" customWidth="1"/>
-    <col min="22" max="22" width="68.453125" style="1" customWidth="1"/>
-    <col min="23" max="24" width="59.453125" style="1" customWidth="1"/>
-    <col min="25" max="25" width="59.54296875" style="1" customWidth="1"/>
-    <col min="26" max="26" width="99.453125" style="1" customWidth="1"/>
-    <col min="27" max="27" width="41.36328125" style="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.6328125" style="1"/>
+    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="81.109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="43.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" style="7" customWidth="1"/>
+    <col min="11" max="11" width="39.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.5546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.88671875" style="7" customWidth="1"/>
+    <col min="16" max="16" width="56.88671875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.6640625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.109375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.6640625" style="8"/>
+    <col min="21" max="21" width="67.6640625" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.44140625" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.44140625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.5546875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.33203125" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="6"/>
@@ -13604,7 +17043,7 @@
       <c r="S2" s="5"/>
       <c r="U2" s="5"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22">
       <c r="C3" s="11" t="s">
         <v>1</v>
       </c>
@@ -13615,8 +17054,8 @@
       <c r="U3" s="1"/>
       <c r="V3" s="2"/>
     </row>
-    <row r="4" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="64" t="s">
+    <row r="4" spans="1:22" s="7" customFormat="1">
+      <c r="A4" s="63" t="s">
         <v>95</v>
       </c>
       <c r="B4" s="13"/>
@@ -13640,7 +17079,7 @@
       <c r="U4" s="2"/>
       <c r="V4" s="1"/>
     </row>
-    <row r="5" spans="1:22" s="7" customFormat="1" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" s="7" customFormat="1" ht="187.2">
       <c r="A5" s="1"/>
       <c r="B5" s="14" t="s">
         <v>96</v>
@@ -13667,7 +17106,7 @@
       <c r="U5" s="2"/>
       <c r="V5" s="1"/>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22">
       <c r="A6" s="1" t="s">
         <v>398</v>
       </c>
@@ -13678,43 +17117,43 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30C41A25-38CA-486A-87ED-62C44A5DF611}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:V48"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
-    <col min="2" max="2" width="62.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="81.08984375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="56.453125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.36328125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="43.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.08984375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="67.90625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="64.453125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="7.90625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="39.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.90625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="72.54296875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="43.90625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7.90625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="56.90625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="46.6328125" style="2" customWidth="1"/>
-    <col min="18" max="18" width="62.90625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="49.08984375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="67.6328125" style="2" customWidth="1"/>
-    <col min="22" max="22" width="68.453125" style="1" customWidth="1"/>
-    <col min="23" max="24" width="59.453125" style="1" customWidth="1"/>
-    <col min="25" max="25" width="59.54296875" style="1" customWidth="1"/>
-    <col min="26" max="26" width="99.453125" style="1" customWidth="1"/>
-    <col min="27" max="27" width="41.36328125" style="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.6328125" style="1"/>
+    <col min="2" max="2" width="62.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="81.109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="43.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.5546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.88671875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="56.88671875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.6640625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.109375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="67.6640625" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.44140625" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.44140625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.5546875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.33203125" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22" s="3" customFormat="1">
       <c r="B2" s="5"/>
       <c r="C2" s="6"/>
       <c r="G2" s="5"/>
@@ -13725,7 +17164,7 @@
       <c r="T2" s="25"/>
       <c r="U2" s="5"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22">
       <c r="C3" s="11" t="s">
         <v>1</v>
       </c>
@@ -13736,7 +17175,7 @@
       <c r="U3" s="1"/>
       <c r="V3" s="2"/>
     </row>
-    <row r="4" spans="1:22" ht="58" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" ht="43.2">
       <c r="A4" s="31" t="s">
         <v>37</v>
       </c>
@@ -13750,7 +17189,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="261" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" ht="259.2">
       <c r="A5" s="48" t="s">
         <v>327</v>
       </c>
@@ -13764,10 +17203,10 @@
         <v>326</v>
       </c>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:4">
       <c r="C41" s="24"/>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:4">
       <c r="B47" s="2" t="s">
         <v>45</v>
       </c>
@@ -13775,7 +17214,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:4">
       <c r="B48" s="2" t="s">
         <v>47</v>
       </c>
@@ -13787,56 +17226,56 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C33:D47">
     <sortCondition ref="D33:D47"/>
   </sortState>
-  <phoneticPr fontId="25" type="noConversion"/>
+  <phoneticPr fontId="29" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{031AACE7-BBB7-40D6-880D-BFAE2A5485BC}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V14"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="36" style="16" customWidth="1"/>
-    <col min="2" max="2" width="50.54296875" style="17" customWidth="1"/>
-    <col min="3" max="3" width="100.453125" style="17" customWidth="1"/>
-    <col min="4" max="4" width="56.453125" style="16" customWidth="1"/>
-    <col min="5" max="5" width="6.1796875" style="15" customWidth="1"/>
-    <col min="6" max="6" width="43.1796875" style="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.08984375" style="17" customWidth="1"/>
-    <col min="8" max="8" width="67.90625" style="16" customWidth="1"/>
-    <col min="9" max="9" width="64.36328125" style="16" customWidth="1"/>
-    <col min="10" max="10" width="7.81640625" style="15" customWidth="1"/>
-    <col min="11" max="11" width="39.1796875" style="16" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.90625" style="16" customWidth="1"/>
-    <col min="13" max="13" width="72.6328125" style="16" customWidth="1"/>
-    <col min="14" max="14" width="43.90625" style="16" customWidth="1"/>
-    <col min="15" max="15" width="7.81640625" style="15" customWidth="1"/>
-    <col min="16" max="16" width="56.81640625" style="17" customWidth="1"/>
-    <col min="17" max="17" width="46.81640625" style="17" customWidth="1"/>
-    <col min="18" max="18" width="62.90625" style="17" customWidth="1"/>
-    <col min="19" max="19" width="49.1796875" style="16" customWidth="1"/>
-    <col min="20" max="20" width="8.81640625" style="18"/>
-    <col min="21" max="21" width="67.81640625" style="17" customWidth="1"/>
-    <col min="22" max="22" width="68.36328125" style="16" customWidth="1"/>
-    <col min="23" max="24" width="59.36328125" style="16" customWidth="1"/>
-    <col min="25" max="25" width="59.6328125" style="16" customWidth="1"/>
-    <col min="26" max="26" width="99.453125" style="16" customWidth="1"/>
-    <col min="27" max="27" width="41.1796875" style="16" customWidth="1"/>
-    <col min="28" max="16384" width="8.81640625" style="16"/>
+    <col min="2" max="2" width="50.5546875" style="17" customWidth="1"/>
+    <col min="3" max="3" width="100.44140625" style="17" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="16" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="15" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="17" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="16" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="16" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="15" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="16" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="16" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="16" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="16" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="15" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="17" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="17" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="17" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="16" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="18"/>
+    <col min="21" max="21" width="67.77734375" style="17" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="16" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="16" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="16" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="16" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="16" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A1" s="55"/>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22">
+      <c r="A1" s="91"/>
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+    </row>
+    <row r="2" spans="1:22">
       <c r="A2" s="19"/>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -13855,7 +17294,7 @@
       <c r="S2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22">
       <c r="C3" s="21" t="s">
         <v>102</v>
       </c>
@@ -13863,7 +17302,7 @@
       <c r="U3" s="16"/>
       <c r="V3" s="17"/>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22">
       <c r="A4" s="22" t="s">
         <v>107</v>
       </c>
@@ -13871,7 +17310,7 @@
       <c r="U4" s="16"/>
       <c r="V4" s="17"/>
     </row>
-    <row r="5" spans="1:22" ht="58" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" ht="57.6">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>115</v>
@@ -13881,7 +17320,7 @@
       </c>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:22" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22" ht="57.6">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>251</v>
@@ -13891,7 +17330,7 @@
       </c>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:22" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22" ht="129.6">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>116</v>
@@ -13903,7 +17342,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22">
       <c r="A8" s="22" t="s">
         <v>110</v>
       </c>
@@ -13911,7 +17350,7 @@
       <c r="C8" s="14"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22">
       <c r="A9" s="1" t="s">
         <v>112</v>
       </c>
@@ -13923,7 +17362,7 @@
       </c>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>250</v>
@@ -13933,7 +17372,7 @@
       </c>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:22" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22" ht="100.8">
       <c r="A11" s="1" t="s">
         <v>113</v>
       </c>
@@ -13945,7 +17384,7 @@
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:22" ht="116" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22" ht="115.2">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>119</v>
@@ -13955,7 +17394,7 @@
       </c>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:22" ht="87" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" ht="86.4">
       <c r="A13" s="1" t="s">
         <v>114</v>
       </c>
@@ -13967,7 +17406,7 @@
       </c>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:22" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" ht="216">
       <c r="A14" s="1" t="s">
         <v>93</v>
       </c>
@@ -13985,4 +17424,2739 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08DE618A-9635-4194-B69D-D0533DA1C310}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:V45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="36" style="1" customWidth="1"/>
+    <col min="2" max="2" width="62.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="81.109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="43.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.5546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.88671875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="56.88671875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.6640625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.109375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="67.6640625" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.44140625" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.44140625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.5546875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.33203125" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.6640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:22" s="3" customFormat="1">
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
+      <c r="G2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="25"/>
+      <c r="U2" s="5"/>
+    </row>
+    <row r="3" spans="1:22">
+      <c r="A3" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="2"/>
+    </row>
+    <row r="4" spans="1:22" ht="409.6">
+      <c r="A4" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C4" s="37" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+    </row>
+    <row r="8" spans="1:22">
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+    </row>
+    <row r="10" spans="1:22">
+      <c r="C10" s="32"/>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:22">
+      <c r="C11" s="32"/>
+    </row>
+    <row r="12" spans="1:22">
+      <c r="C12" s="32"/>
+    </row>
+    <row r="13" spans="1:22">
+      <c r="C13" s="32"/>
+    </row>
+    <row r="38" spans="2:4">
+      <c r="C38" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4">
+      <c r="B39" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4">
+      <c r="B40" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4">
+      <c r="B41" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4">
+      <c r="B42" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4">
+      <c r="B43" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4">
+      <c r="B44" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4">
+      <c r="B45" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66028E03-DC1C-4884-967A-52D62E8CDBFA}">
+  <sheetPr>
+    <tabColor rgb="FF7030A0"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:F47"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="39.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="44.77734375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="33.109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="59.21875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="37.88671875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="2"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="2" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="2" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="2" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="2" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6">
+      <c r="A2" s="75" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="75" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="75" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="76" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="76" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="75" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="75" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="75" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="77" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="76" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="64" customFormat="1"/>
+    <row r="14" spans="1:6">
+      <c r="A14" s="66" t="s">
+        <v>407</v>
+      </c>
+      <c r="B14" s="66" t="s">
+        <v>408</v>
+      </c>
+      <c r="C14" s="66" t="s">
+        <v>410</v>
+      </c>
+      <c r="D14" s="66" t="s">
+        <v>411</v>
+      </c>
+      <c r="E14" s="66" t="s">
+        <v>409</v>
+      </c>
+      <c r="F14" s="66" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="78" t="s">
+        <v>527</v>
+      </c>
+      <c r="C15" s="66"/>
+      <c r="D15" s="66"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="66"/>
+    </row>
+    <row r="16" spans="1:6" ht="172.8">
+      <c r="A16" s="68" t="s">
+        <v>413</v>
+      </c>
+      <c r="B16" s="67" t="s">
+        <v>414</v>
+      </c>
+      <c r="C16" s="67" t="s">
+        <v>527</v>
+      </c>
+      <c r="D16" s="70" t="s">
+        <v>502</v>
+      </c>
+      <c r="E16" s="67" t="s">
+        <v>501</v>
+      </c>
+      <c r="F16" s="69" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="28.8">
+      <c r="A17" s="68" t="s">
+        <v>417</v>
+      </c>
+      <c r="B17" s="67" t="s">
+        <v>418</v>
+      </c>
+      <c r="C17" s="67" t="s">
+        <v>528</v>
+      </c>
+      <c r="D17" s="74" t="s">
+        <v>420</v>
+      </c>
+      <c r="E17" s="67" t="s">
+        <v>419</v>
+      </c>
+      <c r="F17" s="69" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="115.2">
+      <c r="A18" s="68" t="s">
+        <v>422</v>
+      </c>
+      <c r="B18" s="67" t="s">
+        <v>423</v>
+      </c>
+      <c r="C18" s="67" t="s">
+        <v>527</v>
+      </c>
+      <c r="D18" s="70" t="s">
+        <v>503</v>
+      </c>
+      <c r="E18" s="67" t="s">
+        <v>424</v>
+      </c>
+      <c r="F18" s="67" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="28.8">
+      <c r="A19" s="68" t="s">
+        <v>425</v>
+      </c>
+      <c r="B19" s="67" t="s">
+        <v>426</v>
+      </c>
+      <c r="C19" s="67" t="s">
+        <v>527</v>
+      </c>
+      <c r="D19" s="68" t="s">
+        <v>425</v>
+      </c>
+      <c r="E19" s="67" t="s">
+        <v>427</v>
+      </c>
+      <c r="F19" s="67" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="28.8">
+      <c r="A20" s="68" t="s">
+        <v>428</v>
+      </c>
+      <c r="B20" s="67" t="s">
+        <v>429</v>
+      </c>
+      <c r="C20" s="67" t="s">
+        <v>527</v>
+      </c>
+      <c r="D20" s="68" t="s">
+        <v>430</v>
+      </c>
+      <c r="E20" s="67" t="s">
+        <v>415</v>
+      </c>
+      <c r="F20" s="67" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="78" t="s">
+        <v>536</v>
+      </c>
+      <c r="C21" s="67"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="67"/>
+    </row>
+    <row r="22" spans="1:6" ht="145.19999999999999">
+      <c r="A22" s="68" t="s">
+        <v>431</v>
+      </c>
+      <c r="B22" s="67" t="s">
+        <v>432</v>
+      </c>
+      <c r="C22" s="67" t="s">
+        <v>529</v>
+      </c>
+      <c r="D22" s="68" t="s">
+        <v>504</v>
+      </c>
+      <c r="E22" s="67" t="s">
+        <v>433</v>
+      </c>
+      <c r="F22" s="69" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="211.2">
+      <c r="A23" s="68" t="s">
+        <v>435</v>
+      </c>
+      <c r="B23" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="C23" s="67" t="s">
+        <v>530</v>
+      </c>
+      <c r="D23" s="68" t="s">
+        <v>505</v>
+      </c>
+      <c r="E23" s="67" t="s">
+        <v>437</v>
+      </c>
+      <c r="F23" s="69" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="198">
+      <c r="A24" s="68" t="s">
+        <v>443</v>
+      </c>
+      <c r="B24" s="67" t="s">
+        <v>444</v>
+      </c>
+      <c r="C24" s="68" t="s">
+        <v>520</v>
+      </c>
+      <c r="D24" s="71" t="s">
+        <v>507</v>
+      </c>
+      <c r="E24" s="67" t="s">
+        <v>445</v>
+      </c>
+      <c r="F24" s="70" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="57.6">
+      <c r="A25" s="68"/>
+      <c r="B25" s="67" t="s">
+        <v>488</v>
+      </c>
+      <c r="C25" s="68" t="s">
+        <v>519</v>
+      </c>
+      <c r="D25" s="68" t="s">
+        <v>518</v>
+      </c>
+      <c r="E25" s="67" t="s">
+        <v>489</v>
+      </c>
+      <c r="F25" s="69" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="78" t="s">
+        <v>509</v>
+      </c>
+      <c r="C26" s="68"/>
+      <c r="D26" s="71"/>
+      <c r="E26" s="67"/>
+      <c r="F26" s="70"/>
+    </row>
+    <row r="27" spans="1:6" ht="118.8">
+      <c r="A27" s="68" t="s">
+        <v>446</v>
+      </c>
+      <c r="B27" s="67" t="s">
+        <v>447</v>
+      </c>
+      <c r="C27" s="67" t="s">
+        <v>509</v>
+      </c>
+      <c r="D27" s="71" t="s">
+        <v>508</v>
+      </c>
+      <c r="E27" s="67" t="s">
+        <v>448</v>
+      </c>
+      <c r="F27" s="67" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="78" t="s">
+        <v>537</v>
+      </c>
+      <c r="C28" s="67"/>
+      <c r="D28" s="71"/>
+      <c r="E28" s="67"/>
+      <c r="F28" s="67"/>
+    </row>
+    <row r="29" spans="1:6" ht="72">
+      <c r="A29" s="68"/>
+      <c r="B29" s="67" t="s">
+        <v>439</v>
+      </c>
+      <c r="C29" s="72" t="s">
+        <v>514</v>
+      </c>
+      <c r="D29" s="68" t="s">
+        <v>441</v>
+      </c>
+      <c r="E29" s="67" t="s">
+        <v>440</v>
+      </c>
+      <c r="F29" s="69" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="118.8">
+      <c r="A30" s="68" t="s">
+        <v>449</v>
+      </c>
+      <c r="B30" s="67" t="s">
+        <v>450</v>
+      </c>
+      <c r="C30" s="67" t="s">
+        <v>531</v>
+      </c>
+      <c r="D30" s="71" t="s">
+        <v>511</v>
+      </c>
+      <c r="E30" s="67" t="s">
+        <v>451</v>
+      </c>
+      <c r="F30" s="69" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="78" t="s">
+        <v>533</v>
+      </c>
+      <c r="C31" s="67"/>
+      <c r="D31" s="71"/>
+      <c r="E31" s="67"/>
+      <c r="F31" s="69"/>
+    </row>
+    <row r="32" spans="1:6" ht="28.8">
+      <c r="A32" s="68" t="s">
+        <v>453</v>
+      </c>
+      <c r="B32" s="67" t="s">
+        <v>454</v>
+      </c>
+      <c r="C32" s="67" t="s">
+        <v>538</v>
+      </c>
+      <c r="D32" s="68" t="s">
+        <v>456</v>
+      </c>
+      <c r="E32" s="67" t="s">
+        <v>455</v>
+      </c>
+      <c r="F32" s="67" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="100.8">
+      <c r="A33" s="68" t="s">
+        <v>457</v>
+      </c>
+      <c r="B33" s="67" t="s">
+        <v>458</v>
+      </c>
+      <c r="C33" s="67" t="s">
+        <v>512</v>
+      </c>
+      <c r="D33" s="68" t="s">
+        <v>460</v>
+      </c>
+      <c r="E33" s="67" t="s">
+        <v>459</v>
+      </c>
+      <c r="F33" s="69" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="57.6">
+      <c r="A34" s="68" t="s">
+        <v>462</v>
+      </c>
+      <c r="B34" s="67" t="s">
+        <v>463</v>
+      </c>
+      <c r="C34" s="67" t="s">
+        <v>533</v>
+      </c>
+      <c r="D34" s="68" t="s">
+        <v>465</v>
+      </c>
+      <c r="E34" s="67" t="s">
+        <v>464</v>
+      </c>
+      <c r="F34" s="67" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="43.2">
+      <c r="A35" s="68" t="s">
+        <v>466</v>
+      </c>
+      <c r="B35" s="67" t="s">
+        <v>467</v>
+      </c>
+      <c r="C35" s="68" t="s">
+        <v>532</v>
+      </c>
+      <c r="D35" s="68" t="s">
+        <v>469</v>
+      </c>
+      <c r="E35" s="67" t="s">
+        <v>468</v>
+      </c>
+      <c r="F35" s="69" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="72">
+      <c r="A36" s="68" t="s">
+        <v>498</v>
+      </c>
+      <c r="B36" s="67" t="s">
+        <v>499</v>
+      </c>
+      <c r="C36" s="72" t="s">
+        <v>526</v>
+      </c>
+      <c r="D36" s="68" t="s">
+        <v>525</v>
+      </c>
+      <c r="E36" s="67" t="s">
+        <v>500</v>
+      </c>
+      <c r="F36" s="67" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="78" t="s">
+        <v>539</v>
+      </c>
+      <c r="C37" s="68"/>
+      <c r="D37" s="68"/>
+      <c r="E37" s="67"/>
+      <c r="F37" s="69"/>
+    </row>
+    <row r="38" spans="1:6" ht="115.2">
+      <c r="A38" s="68" t="s">
+        <v>471</v>
+      </c>
+      <c r="B38" s="67" t="s">
+        <v>472</v>
+      </c>
+      <c r="C38" s="67" t="s">
+        <v>513</v>
+      </c>
+      <c r="D38" s="67" t="s">
+        <v>415</v>
+      </c>
+      <c r="E38" s="67" t="s">
+        <v>473</v>
+      </c>
+      <c r="F38" s="69" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="57.6">
+      <c r="A39" s="68" t="s">
+        <v>475</v>
+      </c>
+      <c r="B39" s="67" t="s">
+        <v>476</v>
+      </c>
+      <c r="C39" s="72" t="s">
+        <v>514</v>
+      </c>
+      <c r="D39" s="71" t="s">
+        <v>510</v>
+      </c>
+      <c r="E39" s="67" t="s">
+        <v>477</v>
+      </c>
+      <c r="F39" s="69" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="86.4">
+      <c r="A40" s="68" t="s">
+        <v>479</v>
+      </c>
+      <c r="B40" s="67" t="s">
+        <v>480</v>
+      </c>
+      <c r="C40" s="72" t="s">
+        <v>514</v>
+      </c>
+      <c r="D40" s="68" t="s">
+        <v>516</v>
+      </c>
+      <c r="E40" s="68" t="s">
+        <v>481</v>
+      </c>
+      <c r="F40" s="67" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="57.6">
+      <c r="A41" s="68" t="s">
+        <v>482</v>
+      </c>
+      <c r="B41" s="67" t="s">
+        <v>483</v>
+      </c>
+      <c r="C41" s="72" t="s">
+        <v>514</v>
+      </c>
+      <c r="D41" s="68" t="s">
+        <v>515</v>
+      </c>
+      <c r="E41" s="67" t="s">
+        <v>484</v>
+      </c>
+      <c r="F41" s="67" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="57.6">
+      <c r="A42" s="68" t="s">
+        <v>485</v>
+      </c>
+      <c r="B42" s="67" t="s">
+        <v>486</v>
+      </c>
+      <c r="C42" s="72" t="s">
+        <v>514</v>
+      </c>
+      <c r="D42" s="68" t="s">
+        <v>517</v>
+      </c>
+      <c r="E42" s="67" t="s">
+        <v>487</v>
+      </c>
+      <c r="F42" s="67" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="78" t="s">
+        <v>522</v>
+      </c>
+      <c r="C43" s="68"/>
+      <c r="D43" s="68"/>
+      <c r="E43" s="67"/>
+      <c r="F43" s="67"/>
+    </row>
+    <row r="44" spans="1:6" ht="330">
+      <c r="A44" s="68" t="s">
+        <v>491</v>
+      </c>
+      <c r="B44" s="67" t="s">
+        <v>492</v>
+      </c>
+      <c r="C44" s="68" t="s">
+        <v>534</v>
+      </c>
+      <c r="D44" s="73" t="s">
+        <v>521</v>
+      </c>
+      <c r="E44" s="67" t="s">
+        <v>493</v>
+      </c>
+      <c r="F44" s="69" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="78" t="s">
+        <v>535</v>
+      </c>
+      <c r="C45" s="68"/>
+      <c r="D45" s="73"/>
+      <c r="E45" s="67"/>
+      <c r="F45" s="69"/>
+    </row>
+    <row r="46" spans="1:6" ht="66">
+      <c r="A46" s="68" t="s">
+        <v>495</v>
+      </c>
+      <c r="B46" s="67" t="s">
+        <v>496</v>
+      </c>
+      <c r="C46" s="68" t="s">
+        <v>524</v>
+      </c>
+      <c r="D46" s="68" t="s">
+        <v>523</v>
+      </c>
+      <c r="E46" s="67" t="s">
+        <v>415</v>
+      </c>
+      <c r="F46" s="69" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="36.6" customHeight="1"/>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F16" r:id="rId1" display="https://vuejs.org/guide/essentials/application" xr:uid="{B0A68C33-2796-41F4-BB42-598440D225B0}"/>
+    <hyperlink ref="F17" r:id="rId2" location="client-hydration" display="https://vuejs.org/guide/scaling-up/ssr - client-hydration" xr:uid="{DCB59A82-4A4A-49AF-AFC7-D93806C44E03}"/>
+    <hyperlink ref="F22" r:id="rId3" display="https://vuejs.org/guide/components/registration" xr:uid="{B883B29C-9611-46AA-A618-756F361674E8}"/>
+    <hyperlink ref="F23" r:id="rId4" display="https://vuejs.org/guide/reusability/custom-directives" xr:uid="{0C95DB69-14CE-4538-AE95-D47A7D77CC40}"/>
+    <hyperlink ref="F29" r:id="rId5" display="https://vuejs.org/guide/reusability/plugins" xr:uid="{B4C412B1-C93A-4915-9F98-B6301E3A0B5A}"/>
+    <hyperlink ref="F30" r:id="rId6" location="version" display="https://vuejs.org/api/general - version" xr:uid="{2DA6132D-8527-4F6D-AADF-3DFCEB070F0E}"/>
+    <hyperlink ref="F33" r:id="rId7" display="https://vuejs.org/error-reference/" xr:uid="{3DE77557-838F-411E-9FF3-2934D5D77C2C}"/>
+    <hyperlink ref="F35" r:id="rId8" display="https://vuejs.org/guide/best-practices/performance" xr:uid="{1138E947-FAEE-4314-AA64-6380BB8DC98C}"/>
+    <hyperlink ref="F38" r:id="rId9" location="compileroptions" display="https://vuejs.org/api/options-rendering - compileroptions" xr:uid="{EEB4D2DB-02D8-4978-8D14-924DAC5A2E02}"/>
+    <hyperlink ref="F39" r:id="rId10" display="https://vuejs.org/guide/extras/web-components" xr:uid="{C4A714F8-4CE1-425B-8D81-77F5E9DF8EA8}"/>
+    <hyperlink ref="F25" r:id="rId11" location="augmenting-global-properties" display="https://vuejs.org/guide/typescript/options-api - augmenting-global-properties" xr:uid="{64A25FCA-C4AC-4223-8841-E2685F78E4A0}"/>
+    <hyperlink ref="F44" r:id="rId12" location="options" display="https://vuejs.org/api/component-instance - options" xr:uid="{6D13655F-05DE-47C5-89E0-8D7ACCBB6C46}"/>
+    <hyperlink ref="F46" r:id="rId13" location="useid" display="https://vuejs.org/api/composition-api-helpers - useid" xr:uid="{B25F5883-F1B0-42A8-B00F-EBB6F5FDB15F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId14"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFD612E0-A553-42AC-8ADD-A8089131F6A7}">
+  <sheetPr>
+    <tabColor rgb="FF7030A0"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:F40"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="39.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="44.77734375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="33.109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="59.21875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="37.88671875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="2" customWidth="1"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="2" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="2" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="2" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="2" customWidth="1"/>
+    <col min="28" max="28" width="8.77734375" style="2" customWidth="1"/>
+    <col min="29" max="16384" width="8.77734375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6">
+      <c r="A2" s="79" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2" s="80" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="79" t="s">
+        <v>564</v>
+      </c>
+      <c r="B3" s="80" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="79" t="s">
+        <v>592</v>
+      </c>
+      <c r="B4" s="80" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="64" customFormat="1"/>
+    <row r="7" spans="1:6">
+      <c r="A7" s="66" t="s">
+        <v>407</v>
+      </c>
+      <c r="B7" s="66" t="s">
+        <v>408</v>
+      </c>
+      <c r="C7" s="66" t="s">
+        <v>410</v>
+      </c>
+      <c r="D7" s="66" t="s">
+        <v>411</v>
+      </c>
+      <c r="E7" s="66" t="s">
+        <v>409</v>
+      </c>
+      <c r="F7" s="66" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="81" customFormat="1">
+      <c r="A8" s="79" t="s">
+        <v>540</v>
+      </c>
+      <c r="B8" s="80"/>
+    </row>
+    <row r="9" spans="1:6" s="81" customFormat="1" ht="158.4">
+      <c r="A9" s="82" t="s">
+        <v>542</v>
+      </c>
+      <c r="B9" s="82" t="s">
+        <v>543</v>
+      </c>
+      <c r="C9" s="82" t="s">
+        <v>544</v>
+      </c>
+      <c r="D9" s="82" t="s">
+        <v>545</v>
+      </c>
+      <c r="E9" s="82" t="s">
+        <v>546</v>
+      </c>
+      <c r="F9" s="83" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="81" customFormat="1" ht="86.4">
+      <c r="A10" s="82" t="s">
+        <v>548</v>
+      </c>
+      <c r="B10" s="82" t="s">
+        <v>549</v>
+      </c>
+      <c r="C10" s="82" t="s">
+        <v>550</v>
+      </c>
+      <c r="D10" s="82" t="s">
+        <v>551</v>
+      </c>
+      <c r="E10" s="82" t="s">
+        <v>552</v>
+      </c>
+      <c r="F10" s="83" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="81" customFormat="1" ht="115.2">
+      <c r="A11" s="82" t="s">
+        <v>553</v>
+      </c>
+      <c r="B11" s="82" t="s">
+        <v>554</v>
+      </c>
+      <c r="C11" s="82" t="s">
+        <v>555</v>
+      </c>
+      <c r="D11" s="82" t="s">
+        <v>556</v>
+      </c>
+      <c r="E11" s="82" t="s">
+        <v>557</v>
+      </c>
+      <c r="F11" s="83" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="81" customFormat="1" ht="86.4">
+      <c r="A12" s="82" t="s">
+        <v>559</v>
+      </c>
+      <c r="B12" s="82" t="s">
+        <v>560</v>
+      </c>
+      <c r="C12" s="82" t="s">
+        <v>561</v>
+      </c>
+      <c r="D12" s="82" t="s">
+        <v>562</v>
+      </c>
+      <c r="E12" s="82" t="s">
+        <v>563</v>
+      </c>
+      <c r="F12" s="83" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="81" customFormat="1">
+      <c r="A13" s="79" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="81" customFormat="1" ht="86.4">
+      <c r="A14" s="82" t="s">
+        <v>565</v>
+      </c>
+      <c r="B14" s="82" t="s">
+        <v>566</v>
+      </c>
+      <c r="C14" s="82" t="s">
+        <v>564</v>
+      </c>
+      <c r="D14" s="82" t="s">
+        <v>567</v>
+      </c>
+      <c r="E14" s="82" t="s">
+        <v>568</v>
+      </c>
+      <c r="F14" s="83" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" s="81" customFormat="1" ht="72">
+      <c r="A15" s="82" t="s">
+        <v>569</v>
+      </c>
+      <c r="B15" s="82" t="s">
+        <v>570</v>
+      </c>
+      <c r="C15" s="82" t="s">
+        <v>571</v>
+      </c>
+      <c r="D15" s="82" t="s">
+        <v>572</v>
+      </c>
+      <c r="E15" s="82" t="s">
+        <v>573</v>
+      </c>
+      <c r="F15" s="83" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" s="81" customFormat="1" ht="57.6">
+      <c r="A16" s="82" t="s">
+        <v>575</v>
+      </c>
+      <c r="B16" s="82" t="s">
+        <v>576</v>
+      </c>
+      <c r="C16" s="82" t="s">
+        <v>577</v>
+      </c>
+      <c r="D16" s="82" t="s">
+        <v>578</v>
+      </c>
+      <c r="E16" s="82" t="s">
+        <v>579</v>
+      </c>
+      <c r="F16" s="83" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" s="81" customFormat="1" ht="43.2">
+      <c r="A17" s="82" t="s">
+        <v>581</v>
+      </c>
+      <c r="B17" s="82" t="s">
+        <v>582</v>
+      </c>
+      <c r="C17" s="82" t="s">
+        <v>583</v>
+      </c>
+      <c r="D17" s="82" t="s">
+        <v>584</v>
+      </c>
+      <c r="E17" s="82" t="s">
+        <v>585</v>
+      </c>
+      <c r="F17" s="83" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="81" customFormat="1" ht="86.4">
+      <c r="A18" s="82" t="s">
+        <v>587</v>
+      </c>
+      <c r="B18" s="82" t="s">
+        <v>588</v>
+      </c>
+      <c r="C18" s="82" t="s">
+        <v>589</v>
+      </c>
+      <c r="D18" s="82" t="s">
+        <v>590</v>
+      </c>
+      <c r="E18" s="82" t="s">
+        <v>591</v>
+      </c>
+      <c r="F18" s="83" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="81" customFormat="1">
+      <c r="A19" s="79" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" s="81" customFormat="1" ht="144">
+      <c r="A20" s="82" t="s">
+        <v>593</v>
+      </c>
+      <c r="B20" s="82" t="s">
+        <v>594</v>
+      </c>
+      <c r="C20" s="82" t="s">
+        <v>595</v>
+      </c>
+      <c r="D20" s="82" t="s">
+        <v>596</v>
+      </c>
+      <c r="E20" s="82" t="s">
+        <v>597</v>
+      </c>
+      <c r="F20" s="83" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" s="81" customFormat="1"/>
+    <row r="22" spans="1:6" s="81" customFormat="1"/>
+    <row r="23" spans="1:6" s="81" customFormat="1"/>
+    <row r="24" spans="1:6" s="81" customFormat="1"/>
+    <row r="25" spans="1:6" s="81" customFormat="1"/>
+    <row r="26" spans="1:6" s="81" customFormat="1"/>
+    <row r="27" spans="1:6" ht="57.6" customHeight="1"/>
+    <row r="28" spans="1:6" ht="43.2" customHeight="1"/>
+    <row r="29" spans="1:6" ht="72" customHeight="1"/>
+    <row r="31" spans="1:6" ht="115.2" customHeight="1"/>
+    <row r="32" spans="1:6" ht="57.6" customHeight="1"/>
+    <row r="33" ht="86.4" customHeight="1"/>
+    <row r="34" ht="57.6" customHeight="1"/>
+    <row r="35" ht="57.6" customHeight="1"/>
+    <row r="37" ht="330" customHeight="1"/>
+    <row r="39" ht="66" customHeight="1"/>
+    <row r="40" ht="36.6" customHeight="1"/>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F9" r:id="rId1" xr:uid="{0BC35BC1-A738-42F1-9F64-879FFEA9E3C5}"/>
+    <hyperlink ref="F10" r:id="rId2" xr:uid="{593523E3-A9C1-4546-B440-5B6B81E99A34}"/>
+    <hyperlink ref="F11" r:id="rId3" location="torefs" xr:uid="{C381662B-70B1-4BD0-8E64-4DC4ABCB1256}"/>
+    <hyperlink ref="F12" r:id="rId4" xr:uid="{FE8A6778-B8A4-4528-9084-CECA9B302D7D}"/>
+    <hyperlink ref="F14" r:id="rId5" xr:uid="{70739E9C-8EA0-47D7-88AF-EF73AD62676C}"/>
+    <hyperlink ref="F15" r:id="rId6" xr:uid="{30BE7754-8CE7-457D-BC9B-5FBCE4445A2C}"/>
+    <hyperlink ref="F16" r:id="rId7" xr:uid="{4FB7FFC4-AD0B-4B93-BE00-D014439426E0}"/>
+    <hyperlink ref="F17" r:id="rId8" xr:uid="{20E58446-133B-43AB-B41D-BF53FA621D61}"/>
+    <hyperlink ref="F18" r:id="rId9" xr:uid="{30C98C66-F3DA-4505-852C-9600AB78A563}"/>
+    <hyperlink ref="F20" r:id="rId10" xr:uid="{65E1B679-4FE0-4321-BD12-0AB5515BA93B}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{210DA791-C7ED-44BB-9246-34E9255D02EC}">
+  <sheetPr>
+    <tabColor rgb="FF7030A0"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:F12"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="39.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="44.77734375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="33.109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="59.21875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="37.88671875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="2" customWidth="1"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="2" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="2" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="2" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="2" customWidth="1"/>
+    <col min="28" max="28" width="8.77734375" style="2" customWidth="1"/>
+    <col min="29" max="16384" width="8.77734375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6">
+      <c r="A2" s="76" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="76" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="64" customFormat="1"/>
+    <row r="6" spans="1:6">
+      <c r="A6" s="66" t="s">
+        <v>407</v>
+      </c>
+      <c r="B6" s="66" t="s">
+        <v>408</v>
+      </c>
+      <c r="C6" s="66" t="s">
+        <v>410</v>
+      </c>
+      <c r="D6" s="66" t="s">
+        <v>411</v>
+      </c>
+      <c r="E6" s="66" t="s">
+        <v>409</v>
+      </c>
+      <c r="F6" s="66" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15" customHeight="1">
+      <c r="A7" s="76" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="41.4">
+      <c r="A8" s="84" t="s">
+        <v>601</v>
+      </c>
+      <c r="B8" s="85" t="s">
+        <v>602</v>
+      </c>
+      <c r="C8" s="85" t="s">
+        <v>603</v>
+      </c>
+      <c r="D8" s="86" t="s">
+        <v>604</v>
+      </c>
+      <c r="E8" s="85" t="s">
+        <v>605</v>
+      </c>
+      <c r="F8" s="87" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="179.4">
+      <c r="A9" s="84" t="s">
+        <v>606</v>
+      </c>
+      <c r="B9" s="85" t="s">
+        <v>607</v>
+      </c>
+      <c r="C9" s="85" t="s">
+        <v>608</v>
+      </c>
+      <c r="D9" s="86" t="s">
+        <v>609</v>
+      </c>
+      <c r="E9" s="85" t="s">
+        <v>610</v>
+      </c>
+      <c r="F9" s="87" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15" customHeight="1">
+      <c r="A10" s="76" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="220.8">
+      <c r="A11" s="84" t="s">
+        <v>612</v>
+      </c>
+      <c r="B11" s="85" t="s">
+        <v>613</v>
+      </c>
+      <c r="C11" s="85" t="s">
+        <v>614</v>
+      </c>
+      <c r="D11" s="86" t="s">
+        <v>615</v>
+      </c>
+      <c r="E11" s="85" t="s">
+        <v>616</v>
+      </c>
+      <c r="F11" s="87" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="220.8">
+      <c r="A12" s="84" t="s">
+        <v>618</v>
+      </c>
+      <c r="B12" s="85" t="s">
+        <v>619</v>
+      </c>
+      <c r="C12" s="85" t="s">
+        <v>620</v>
+      </c>
+      <c r="D12" s="86" t="s">
+        <v>621</v>
+      </c>
+      <c r="E12" s="85" t="s">
+        <v>622</v>
+      </c>
+      <c r="F12" s="87" t="s">
+        <v>623</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F9" r:id="rId1" location="nexttick" xr:uid="{D1032574-D520-44D9-AB9D-F8C848B0E4CB}"/>
+    <hyperlink ref="F11" r:id="rId2" xr:uid="{1A38CE5F-1921-4E29-BBE0-6091BDA8F7C0}"/>
+    <hyperlink ref="F12" r:id="rId3" xr:uid="{C8FC45D7-DA7C-41E5-9D4D-9A7023E4050D}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId4"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7742DC2D-8356-42AF-A171-521A8B3CCEEA}">
+  <sheetPr>
+    <tabColor rgb="FF7030A0"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:F17"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="39.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="44.77734375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="33.109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="59.21875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="37.88671875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="2" customWidth="1"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="2" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="2" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="2" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="2" customWidth="1"/>
+    <col min="28" max="28" width="8.77734375" style="2" customWidth="1"/>
+    <col min="29" max="16384" width="8.77734375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6">
+      <c r="A2" s="75"/>
+    </row>
+    <row r="4" spans="1:6" s="64" customFormat="1"/>
+    <row r="5" spans="1:6">
+      <c r="A5" s="66" t="s">
+        <v>407</v>
+      </c>
+      <c r="B5" s="66" t="s">
+        <v>408</v>
+      </c>
+      <c r="C5" s="66" t="s">
+        <v>410</v>
+      </c>
+      <c r="D5" s="66" t="s">
+        <v>411</v>
+      </c>
+      <c r="E5" s="66" t="s">
+        <v>409</v>
+      </c>
+      <c r="F5" s="66" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="72">
+      <c r="A6" s="82" t="s">
+        <v>624</v>
+      </c>
+      <c r="B6" s="82" t="s">
+        <v>625</v>
+      </c>
+      <c r="C6" s="82" t="s">
+        <v>626</v>
+      </c>
+      <c r="D6" s="82" t="s">
+        <v>627</v>
+      </c>
+      <c r="E6" s="82" t="s">
+        <v>628</v>
+      </c>
+      <c r="F6" s="83" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="86.4">
+      <c r="A7" s="82" t="s">
+        <v>630</v>
+      </c>
+      <c r="B7" s="82" t="s">
+        <v>631</v>
+      </c>
+      <c r="C7" s="82" t="s">
+        <v>626</v>
+      </c>
+      <c r="D7" s="82" t="s">
+        <v>632</v>
+      </c>
+      <c r="E7" s="82" t="s">
+        <v>633</v>
+      </c>
+      <c r="F7" s="83" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="72">
+      <c r="A8" s="82" t="s">
+        <v>634</v>
+      </c>
+      <c r="B8" s="82" t="s">
+        <v>635</v>
+      </c>
+      <c r="C8" s="82" t="s">
+        <v>636</v>
+      </c>
+      <c r="D8" s="82" t="s">
+        <v>637</v>
+      </c>
+      <c r="E8" s="82" t="s">
+        <v>638</v>
+      </c>
+      <c r="F8" s="83" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="86.4">
+      <c r="A9" s="82" t="s">
+        <v>639</v>
+      </c>
+      <c r="B9" s="82" t="s">
+        <v>640</v>
+      </c>
+      <c r="C9" s="82" t="s">
+        <v>636</v>
+      </c>
+      <c r="D9" s="82" t="s">
+        <v>641</v>
+      </c>
+      <c r="E9" s="82" t="s">
+        <v>642</v>
+      </c>
+      <c r="F9" s="83" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="72">
+      <c r="A10" s="82" t="s">
+        <v>643</v>
+      </c>
+      <c r="B10" s="82" t="s">
+        <v>644</v>
+      </c>
+      <c r="C10" s="82" t="s">
+        <v>645</v>
+      </c>
+      <c r="D10" s="82" t="s">
+        <v>646</v>
+      </c>
+      <c r="E10" s="82" t="s">
+        <v>647</v>
+      </c>
+      <c r="F10" s="83" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="72">
+      <c r="A11" s="82" t="s">
+        <v>648</v>
+      </c>
+      <c r="B11" s="82" t="s">
+        <v>649</v>
+      </c>
+      <c r="C11" s="82" t="s">
+        <v>645</v>
+      </c>
+      <c r="D11" s="82" t="s">
+        <v>650</v>
+      </c>
+      <c r="E11" s="82" t="s">
+        <v>651</v>
+      </c>
+      <c r="F11" s="83" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="86.4">
+      <c r="A12" s="82" t="s">
+        <v>652</v>
+      </c>
+      <c r="B12" s="82" t="s">
+        <v>653</v>
+      </c>
+      <c r="C12" s="82" t="s">
+        <v>654</v>
+      </c>
+      <c r="D12" s="82" t="s">
+        <v>655</v>
+      </c>
+      <c r="E12" s="82" t="s">
+        <v>656</v>
+      </c>
+      <c r="F12" s="83" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="72">
+      <c r="A13" s="82" t="s">
+        <v>658</v>
+      </c>
+      <c r="B13" s="82" t="s">
+        <v>659</v>
+      </c>
+      <c r="C13" s="82" t="s">
+        <v>660</v>
+      </c>
+      <c r="D13" s="82" t="s">
+        <v>661</v>
+      </c>
+      <c r="E13" s="82" t="s">
+        <v>662</v>
+      </c>
+      <c r="F13" s="83" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="72">
+      <c r="A14" s="82" t="s">
+        <v>664</v>
+      </c>
+      <c r="B14" s="82" t="s">
+        <v>665</v>
+      </c>
+      <c r="C14" s="82" t="s">
+        <v>660</v>
+      </c>
+      <c r="D14" s="82" t="s">
+        <v>666</v>
+      </c>
+      <c r="E14" s="82" t="s">
+        <v>667</v>
+      </c>
+      <c r="F14" s="83" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="72">
+      <c r="A15" s="82" t="s">
+        <v>668</v>
+      </c>
+      <c r="B15" s="82" t="s">
+        <v>669</v>
+      </c>
+      <c r="C15" s="82" t="s">
+        <v>670</v>
+      </c>
+      <c r="D15" s="82" t="s">
+        <v>671</v>
+      </c>
+      <c r="E15" s="82" t="s">
+        <v>672</v>
+      </c>
+      <c r="F15" s="83" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="72">
+      <c r="A16" s="82" t="s">
+        <v>674</v>
+      </c>
+      <c r="B16" s="82" t="s">
+        <v>675</v>
+      </c>
+      <c r="C16" s="82" t="s">
+        <v>670</v>
+      </c>
+      <c r="D16" s="82" t="s">
+        <v>676</v>
+      </c>
+      <c r="E16" s="82" t="s">
+        <v>672</v>
+      </c>
+      <c r="F16" s="83" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="129.6">
+      <c r="A17" s="82" t="s">
+        <v>677</v>
+      </c>
+      <c r="B17" s="82" t="s">
+        <v>678</v>
+      </c>
+      <c r="C17" s="82" t="s">
+        <v>679</v>
+      </c>
+      <c r="D17" s="82" t="s">
+        <v>680</v>
+      </c>
+      <c r="E17" s="82" t="s">
+        <v>681</v>
+      </c>
+      <c r="F17" s="83" t="s">
+        <v>682</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F6" r:id="rId1" xr:uid="{BCEDF5A9-AC9D-4B18-8FBC-704E1C4E35E0}"/>
+    <hyperlink ref="F7" r:id="rId2" xr:uid="{BF973FE4-46C9-45BD-A0D7-BDB80A784126}"/>
+    <hyperlink ref="F8" r:id="rId3" xr:uid="{276747C2-1EE8-4753-A0F4-4578E91151A9}"/>
+    <hyperlink ref="F9" r:id="rId4" xr:uid="{B5A71B51-F713-45BB-9829-67643F7D1D21}"/>
+    <hyperlink ref="F10" r:id="rId5" xr:uid="{8E4441EE-D698-4A6C-8D21-F92553B19E51}"/>
+    <hyperlink ref="F11" r:id="rId6" xr:uid="{07711047-0E0A-4356-AC98-13FCB68D4BE4}"/>
+    <hyperlink ref="F12" r:id="rId7" xr:uid="{18852E30-E696-4133-96A1-C252B084455B}"/>
+    <hyperlink ref="F13" r:id="rId8" xr:uid="{89843FA1-DC4B-4D5B-8552-9D3BA9234690}"/>
+    <hyperlink ref="F14" r:id="rId9" xr:uid="{3C0DDCF3-333B-4DEE-9CBB-B6585965FFB3}"/>
+    <hyperlink ref="F15" r:id="rId10" location="lifecycle-of-cached-instance" xr:uid="{26921D4F-4677-415E-B2D6-0776521C8D9F}"/>
+    <hyperlink ref="F16" r:id="rId11" location="lifecycle-of-cached-instance" xr:uid="{933483F2-6232-441A-B2FA-07FE98326D89}"/>
+    <hyperlink ref="F17" r:id="rId12" xr:uid="{F3874539-CD42-4120-94FA-AD48E696674F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId13"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0C2F5D0-3AD2-4E17-93C5-780C9492ED89}">
+  <sheetPr>
+    <tabColor rgb="FF7030A0"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:F40"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="39.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="44.77734375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="33.109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="59.21875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="37.88671875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="2" customWidth="1"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="2" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="2" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="2" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="2" customWidth="1"/>
+    <col min="28" max="28" width="8.77734375" style="2" customWidth="1"/>
+    <col min="29" max="16384" width="8.77734375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6">
+      <c r="A2" s="79" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="79" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="64" customFormat="1"/>
+    <row r="6" spans="1:6">
+      <c r="A6" s="66" t="s">
+        <v>407</v>
+      </c>
+      <c r="B6" s="66" t="s">
+        <v>408</v>
+      </c>
+      <c r="C6" s="66" t="s">
+        <v>410</v>
+      </c>
+      <c r="D6" s="66" t="s">
+        <v>411</v>
+      </c>
+      <c r="E6" s="66" t="s">
+        <v>409</v>
+      </c>
+      <c r="F6" s="66" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="81" customFormat="1" ht="15" customHeight="1">
+      <c r="A7" s="79" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="81" customFormat="1" ht="90" customHeight="1">
+      <c r="A8" s="82" t="s">
+        <v>684</v>
+      </c>
+      <c r="B8" s="82" t="s">
+        <v>685</v>
+      </c>
+      <c r="C8" s="82" t="s">
+        <v>686</v>
+      </c>
+      <c r="D8" s="82" t="s">
+        <v>687</v>
+      </c>
+      <c r="E8" s="82" t="s">
+        <v>688</v>
+      </c>
+      <c r="F8" s="83" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="81" customFormat="1" ht="105" customHeight="1">
+      <c r="A9" s="82" t="s">
+        <v>689</v>
+      </c>
+      <c r="B9" s="82" t="s">
+        <v>690</v>
+      </c>
+      <c r="C9" s="82" t="s">
+        <v>691</v>
+      </c>
+      <c r="D9" s="82" t="s">
+        <v>692</v>
+      </c>
+      <c r="E9" s="82" t="s">
+        <v>693</v>
+      </c>
+      <c r="F9" s="83" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="81" customFormat="1" ht="172.8">
+      <c r="A10" s="82" t="s">
+        <v>694</v>
+      </c>
+      <c r="B10" s="82" t="s">
+        <v>695</v>
+      </c>
+      <c r="C10" s="82" t="s">
+        <v>696</v>
+      </c>
+      <c r="D10" s="82" t="s">
+        <v>697</v>
+      </c>
+      <c r="E10" s="82" t="s">
+        <v>698</v>
+      </c>
+      <c r="F10" s="83" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="81" customFormat="1" ht="115.2">
+      <c r="A11" s="82"/>
+      <c r="B11" s="82"/>
+      <c r="C11" s="82" t="s">
+        <v>775</v>
+      </c>
+      <c r="D11" s="82" t="s">
+        <v>773</v>
+      </c>
+      <c r="E11" s="82" t="s">
+        <v>774</v>
+      </c>
+      <c r="F11" s="83"/>
+    </row>
+    <row r="12" spans="1:6" s="81" customFormat="1" ht="225" customHeight="1">
+      <c r="A12" s="82" t="s">
+        <v>700</v>
+      </c>
+      <c r="B12" s="82" t="s">
+        <v>701</v>
+      </c>
+      <c r="C12" s="82" t="s">
+        <v>702</v>
+      </c>
+      <c r="D12" s="82" t="s">
+        <v>703</v>
+      </c>
+      <c r="E12" s="82" t="s">
+        <v>704</v>
+      </c>
+      <c r="F12" s="83" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="81" customFormat="1" ht="150" customHeight="1">
+      <c r="A13" s="82" t="s">
+        <v>705</v>
+      </c>
+      <c r="B13" s="82" t="s">
+        <v>706</v>
+      </c>
+      <c r="C13" s="82" t="s">
+        <v>707</v>
+      </c>
+      <c r="D13" s="82" t="s">
+        <v>708</v>
+      </c>
+      <c r="E13" s="82" t="s">
+        <v>709</v>
+      </c>
+      <c r="F13" s="83" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="81" customFormat="1" ht="15" customHeight="1">
+      <c r="A14" s="79" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" s="81" customFormat="1" ht="75" customHeight="1">
+      <c r="A15" s="82" t="s">
+        <v>711</v>
+      </c>
+      <c r="B15" s="82" t="s">
+        <v>712</v>
+      </c>
+      <c r="C15" s="82" t="s">
+        <v>713</v>
+      </c>
+      <c r="D15" s="82" t="s">
+        <v>714</v>
+      </c>
+      <c r="E15" s="82" t="s">
+        <v>415</v>
+      </c>
+      <c r="F15" s="83" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" s="81" customFormat="1" ht="60" customHeight="1">
+      <c r="A16" s="82" t="s">
+        <v>715</v>
+      </c>
+      <c r="B16" s="82" t="s">
+        <v>716</v>
+      </c>
+      <c r="C16" s="82" t="s">
+        <v>717</v>
+      </c>
+      <c r="D16" s="82" t="s">
+        <v>718</v>
+      </c>
+      <c r="E16" s="82" t="s">
+        <v>719</v>
+      </c>
+      <c r="F16" s="83" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" s="81" customFormat="1" ht="60" customHeight="1">
+      <c r="A17" s="82" t="s">
+        <v>720</v>
+      </c>
+      <c r="B17" s="82" t="s">
+        <v>721</v>
+      </c>
+      <c r="C17" s="82" t="s">
+        <v>722</v>
+      </c>
+      <c r="D17" s="82" t="s">
+        <v>723</v>
+      </c>
+      <c r="E17" s="82" t="s">
+        <v>724</v>
+      </c>
+      <c r="F17" s="83" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="81" customFormat="1" ht="57.6" customHeight="1"/>
+    <row r="20" spans="1:6" ht="118.8" customHeight="1"/>
+    <row r="22" spans="1:6" ht="72" customHeight="1"/>
+    <row r="23" spans="1:6" ht="118.8" customHeight="1"/>
+    <row r="25" spans="1:6" ht="28.8" customHeight="1"/>
+    <row r="26" spans="1:6" ht="100.8" customHeight="1"/>
+    <row r="27" spans="1:6" ht="57.6" customHeight="1"/>
+    <row r="28" spans="1:6" ht="43.2" customHeight="1"/>
+    <row r="29" spans="1:6" ht="72" customHeight="1"/>
+    <row r="31" spans="1:6" ht="115.2" customHeight="1"/>
+    <row r="32" spans="1:6" ht="57.6" customHeight="1"/>
+    <row r="33" ht="86.4" customHeight="1"/>
+    <row r="34" ht="57.6" customHeight="1"/>
+    <row r="35" ht="57.6" customHeight="1"/>
+    <row r="37" ht="330" customHeight="1"/>
+    <row r="39" ht="66" customHeight="1"/>
+    <row r="40" ht="36.6" customHeight="1"/>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F10" r:id="rId1" location="toref" xr:uid="{EA6E4AA4-C1A4-4557-B58B-DAB66AEC9CF9}"/>
+    <hyperlink ref="F12" r:id="rId2" location="tovalue" xr:uid="{7EC0DF21-0B65-4959-B622-BF88CF629FDA}"/>
+    <hyperlink ref="F13" r:id="rId3" location="torefs" xr:uid="{289ED8AA-7B50-48FB-98B0-A40C31B3C325}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId4"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35186FB0-D6EE-48D6-AD0A-EC687D3766B2}">
+  <sheetPr>
+    <tabColor rgb="FF7030A0"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:F27"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="39.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="31.44140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="33.109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="59.21875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="55.33203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="2" customWidth="1"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="2" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="2" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="2" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="2" customWidth="1"/>
+    <col min="28" max="28" width="8.77734375" style="2" customWidth="1"/>
+    <col min="29" max="16384" width="8.77734375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6">
+      <c r="A2" s="79" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="79" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="75"/>
+    </row>
+    <row r="6" spans="1:6" s="64" customFormat="1"/>
+    <row r="7" spans="1:6">
+      <c r="A7" s="66" t="s">
+        <v>407</v>
+      </c>
+      <c r="B7" s="66" t="s">
+        <v>408</v>
+      </c>
+      <c r="C7" s="66" t="s">
+        <v>410</v>
+      </c>
+      <c r="D7" s="66" t="s">
+        <v>411</v>
+      </c>
+      <c r="E7" s="66" t="s">
+        <v>409</v>
+      </c>
+      <c r="F7" s="66" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="81" customFormat="1" ht="15" customHeight="1">
+      <c r="A8" s="79" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="81" customFormat="1" ht="100.8">
+      <c r="A9" s="82" t="s">
+        <v>727</v>
+      </c>
+      <c r="B9" s="82" t="s">
+        <v>728</v>
+      </c>
+      <c r="C9" s="82" t="s">
+        <v>729</v>
+      </c>
+      <c r="D9" s="82" t="s">
+        <v>730</v>
+      </c>
+      <c r="E9" s="82" t="s">
+        <v>731</v>
+      </c>
+      <c r="F9" s="83" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="81" customFormat="1" ht="43.2">
+      <c r="A10" s="82"/>
+      <c r="B10" s="82"/>
+      <c r="C10" s="82" t="s">
+        <v>776</v>
+      </c>
+      <c r="D10" s="82" t="s">
+        <v>779</v>
+      </c>
+      <c r="E10" s="82" t="s">
+        <v>777</v>
+      </c>
+      <c r="F10" s="83"/>
+    </row>
+    <row r="11" spans="1:6" s="81" customFormat="1" ht="180" customHeight="1">
+      <c r="A11" s="82" t="s">
+        <v>733</v>
+      </c>
+      <c r="B11" s="82" t="s">
+        <v>734</v>
+      </c>
+      <c r="C11" s="82" t="s">
+        <v>735</v>
+      </c>
+      <c r="D11" s="82" t="s">
+        <v>736</v>
+      </c>
+      <c r="E11" s="82" t="s">
+        <v>737</v>
+      </c>
+      <c r="F11" s="83" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="81" customFormat="1" ht="180" customHeight="1">
+      <c r="A12" s="82" t="s">
+        <v>739</v>
+      </c>
+      <c r="B12" s="82" t="s">
+        <v>740</v>
+      </c>
+      <c r="C12" s="82" t="s">
+        <v>741</v>
+      </c>
+      <c r="D12" s="82" t="s">
+        <v>742</v>
+      </c>
+      <c r="E12" s="82" t="s">
+        <v>743</v>
+      </c>
+      <c r="F12" s="83" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="81" customFormat="1" ht="57.6">
+      <c r="A13" s="82"/>
+      <c r="B13" s="82"/>
+      <c r="C13" s="82"/>
+      <c r="D13" s="82" t="s">
+        <v>778</v>
+      </c>
+      <c r="E13" s="82" t="s">
+        <v>784</v>
+      </c>
+      <c r="F13" s="83"/>
+    </row>
+    <row r="14" spans="1:6" s="81" customFormat="1" ht="165" customHeight="1">
+      <c r="A14" s="82" t="s">
+        <v>744</v>
+      </c>
+      <c r="B14" s="82" t="s">
+        <v>745</v>
+      </c>
+      <c r="C14" s="82" t="s">
+        <v>746</v>
+      </c>
+      <c r="D14" s="82" t="s">
+        <v>747</v>
+      </c>
+      <c r="E14" s="82" t="s">
+        <v>748</v>
+      </c>
+      <c r="F14" s="83" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" s="81" customFormat="1" ht="15" customHeight="1">
+      <c r="A15" s="79" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" s="81" customFormat="1" ht="210" customHeight="1">
+      <c r="A16" s="82" t="s">
+        <v>763</v>
+      </c>
+      <c r="B16" s="82" t="s">
+        <v>764</v>
+      </c>
+      <c r="C16" s="82" t="s">
+        <v>765</v>
+      </c>
+      <c r="D16" s="82" t="s">
+        <v>781</v>
+      </c>
+      <c r="E16" s="82" t="s">
+        <v>766</v>
+      </c>
+      <c r="F16" s="83" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="115.2">
+      <c r="A17" s="89" t="s">
+        <v>789</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="E17" s="89" t="s">
+        <v>792</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="86.4">
+      <c r="A18" s="89" t="s">
+        <v>788</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="E18" s="89" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="100.8">
+      <c r="A19" s="89" t="s">
+        <v>788</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="E19" s="89" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="86.4">
+      <c r="A20" s="89" t="s">
+        <v>797</v>
+      </c>
+      <c r="D20" s="90" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="43.2">
+      <c r="A21" s="89" t="s">
+        <v>797</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="D21" s="90" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="201.6">
+      <c r="A22" s="82" t="s">
+        <v>749</v>
+      </c>
+      <c r="B22" s="82" t="s">
+        <v>750</v>
+      </c>
+      <c r="C22" s="82" t="s">
+        <v>751</v>
+      </c>
+      <c r="D22" s="82" t="s">
+        <v>752</v>
+      </c>
+      <c r="E22" s="88" t="s">
+        <v>780</v>
+      </c>
+      <c r="F22" s="83" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="115.2">
+      <c r="A23" s="82" t="s">
+        <v>754</v>
+      </c>
+      <c r="B23" s="82" t="s">
+        <v>755</v>
+      </c>
+      <c r="C23" s="82" t="s">
+        <v>756</v>
+      </c>
+      <c r="D23" s="82" t="s">
+        <v>782</v>
+      </c>
+      <c r="E23" s="82" t="s">
+        <v>757</v>
+      </c>
+      <c r="F23" s="83" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="115.2">
+      <c r="A24" s="82" t="s">
+        <v>759</v>
+      </c>
+      <c r="B24" s="82" t="s">
+        <v>760</v>
+      </c>
+      <c r="C24" s="82" t="s">
+        <v>761</v>
+      </c>
+      <c r="D24" s="82" t="s">
+        <v>783</v>
+      </c>
+      <c r="E24" s="82" t="s">
+        <v>762</v>
+      </c>
+      <c r="F24" s="83" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="129.6">
+      <c r="A25" s="82" t="s">
+        <v>767</v>
+      </c>
+      <c r="B25" s="82" t="s">
+        <v>768</v>
+      </c>
+      <c r="C25" s="82" t="s">
+        <v>769</v>
+      </c>
+      <c r="D25" s="82" t="s">
+        <v>770</v>
+      </c>
+      <c r="E25" s="82" t="s">
+        <v>771</v>
+      </c>
+      <c r="F25" s="83" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="57.6">
+      <c r="C27" s="2" t="s">
+        <v>798</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F9" r:id="rId1" xr:uid="{145FF146-8E7D-4F24-BB13-C3C5F8373C2E}"/>
+    <hyperlink ref="F11" r:id="rId2" xr:uid="{53916E9C-B906-4991-B692-EB833D4426C1}"/>
+    <hyperlink ref="F12" r:id="rId3" xr:uid="{9C8CEED2-146E-481A-86AC-421438A99810}"/>
+    <hyperlink ref="F22" r:id="rId4" xr:uid="{1542023A-8EDF-4161-BCCC-948B440C3C17}"/>
+    <hyperlink ref="F23" r:id="rId5" location="callback-flush-timing" xr:uid="{EC6C0840-5242-4E5A-ADB6-A576D6F5C973}"/>
+    <hyperlink ref="F24" r:id="rId6" location="callback-flush-timing" xr:uid="{33235B97-EDDF-4148-A660-6DF3C203DA0B}"/>
+    <hyperlink ref="F16" r:id="rId7" xr:uid="{173F7953-2F52-4B2B-960B-62EED16C9711}"/>
+    <hyperlink ref="F25" r:id="rId8" location="onwatchercleanup" xr:uid="{9BB0DC7C-DD5C-450C-9546-280A55F627D2}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FA03920-7645-46F8-9F58-C9234F096C57}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:E3"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="36" style="2" customWidth="1"/>
+    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="71.21875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="65" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="2"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="2" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="2" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="2" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="2" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5" s="64" customFormat="1">
+      <c r="E2" s="65"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B7CAD42-95E0-4E20-A7EA-DF3B831CFF68}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:V33"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="46.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="62.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="81.109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="43.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.5546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.88671875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="56.88671875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.6640625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.109375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="67.6640625" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.44140625" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.44140625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.5546875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.33203125" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.6640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:22" s="3" customFormat="1">
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
+      <c r="G2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="25"/>
+      <c r="U2" s="5"/>
+    </row>
+    <row r="3" spans="1:22">
+      <c r="C3" s="43" t="s">
+        <v>278</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>309</v>
+      </c>
+      <c r="P3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="2"/>
+    </row>
+    <row r="4" spans="1:22">
+      <c r="B4" s="57" t="s">
+        <v>261</v>
+      </c>
+      <c r="C4" s="57" t="s">
+        <v>260</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>310</v>
+      </c>
+      <c r="P4" s="1"/>
+      <c r="U4" s="1"/>
+      <c r="V4" s="2"/>
+    </row>
+    <row r="5" spans="1:22">
+      <c r="A5" s="56" t="s">
+        <v>377</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+    </row>
+    <row r="6" spans="1:22" ht="115.2">
+      <c r="A6" s="55" t="s">
+        <v>378</v>
+      </c>
+      <c r="B6" s="55" t="s">
+        <v>279</v>
+      </c>
+      <c r="C6" s="42" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="72">
+      <c r="A7" s="42"/>
+      <c r="B7" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C7" s="42" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22">
+      <c r="A8" s="57" t="s">
+        <v>363</v>
+      </c>
+      <c r="B8" s="58"/>
+      <c r="C8" s="58"/>
+    </row>
+    <row r="9" spans="1:22" ht="57.6">
+      <c r="A9" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:22">
+      <c r="A10" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22">
+      <c r="A11" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22">
+      <c r="A12" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22">
+      <c r="A13" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22">
+      <c r="A14" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22">
+      <c r="A15" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22">
+      <c r="A16" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D16" s="60" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
+      <c r="A17" s="59" t="s">
+        <v>365</v>
+      </c>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18" spans="1:21" ht="72">
+      <c r="B18" s="55" t="s">
+        <v>366</v>
+      </c>
+      <c r="C18" s="55" t="s">
+        <v>367</v>
+      </c>
+      <c r="D18" s="55" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21">
+      <c r="A19" s="57" t="s">
+        <v>364</v>
+      </c>
+      <c r="B19" s="44" t="s">
+        <v>299</v>
+      </c>
+      <c r="C19" s="44" t="s">
+        <v>293</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" ht="273.60000000000002">
+      <c r="A20" s="42" t="s">
+        <v>297</v>
+      </c>
+      <c r="B20" s="42" t="s">
+        <v>295</v>
+      </c>
+      <c r="C20" s="42" t="s">
+        <v>296</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21">
+      <c r="A21" s="42"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="42"/>
+    </row>
+    <row r="22" spans="1:21" s="3" customFormat="1">
+      <c r="B22" s="5"/>
+      <c r="C22" s="6"/>
+      <c r="G22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="5"/>
+      <c r="S22" s="5"/>
+      <c r="T22" s="25"/>
+      <c r="U22" s="5"/>
+    </row>
+    <row r="23" spans="1:21">
+      <c r="A23" s="2"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="43" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21">
+      <c r="A24" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="B24" s="42"/>
+      <c r="C24" s="42"/>
+    </row>
+    <row r="25" spans="1:21">
+      <c r="A25" s="2"/>
+      <c r="B25" s="31" t="s">
+        <v>284</v>
+      </c>
+      <c r="C25" s="31" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" ht="28.8">
+      <c r="A26" s="46" t="s">
+        <v>304</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" ht="28.8">
+      <c r="A27" s="46" t="s">
+        <v>304</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" ht="28.8">
+      <c r="A28" s="46" t="s">
+        <v>304</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C28" s="42" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" ht="201.6">
+      <c r="A29" s="46" t="s">
+        <v>303</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C29" s="45" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" ht="201.6">
+      <c r="A30" s="46" t="s">
+        <v>303</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="C30" s="45" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" ht="115.2">
+      <c r="A31" s="46" t="s">
+        <v>303</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C31" s="45" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21">
+      <c r="A32" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="C32" s="44" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" ht="230.4">
+      <c r="B33" s="42" t="s">
+        <v>297</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D3" r:id="rId1" location="imports--exports" display="Ссылка" xr:uid="{5F2650EE-EC1A-4EB5-A54A-484006789CA4}"/>
+    <hyperlink ref="D4" r:id="rId2" display="Ссылка" xr:uid="{7D3863D0-674C-43DF-8581-E2D9E02F5CED}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
+</worksheet>
 </file>
--- a/4 четверть_9_JavaScript_Vue 3 Composition API.xlsx
+++ b/4 четверть_9_JavaScript_Vue 3 Composition API.xlsx
@@ -8,29 +8,31 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{634F1F54-9667-416E-9001-51A252EA15EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB23B21D-F556-437F-8C43-6742CA0E698B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4470" yWindow="-18225" windowWidth="23250" windowHeight="12450" firstSheet="11" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4470" yWindow="-18225" windowWidth="23250" windowHeight="12450" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Продолжить" sheetId="14" r:id="rId1"/>
     <sheet name="import require" sheetId="17" r:id="rId2"/>
     <sheet name="App" sheetId="25" r:id="rId3"/>
-    <sheet name="batch" sheetId="40" r:id="rId4"/>
-    <sheet name="ref" sheetId="31" r:id="rId5"/>
-    <sheet name="reactive" sheetId="38" r:id="rId6"/>
-    <sheet name="setup()" sheetId="27" r:id="rId7"/>
-    <sheet name="lifecycle" sheetId="29" r:id="rId8"/>
-    <sheet name="computed, readonly" sheetId="37" r:id="rId9"/>
-    <sheet name="watch" sheetId="36" r:id="rId10"/>
-    <sheet name="provide, inject" sheetId="33" r:id="rId11"/>
-    <sheet name="Vue Css" sheetId="39" r:id="rId12"/>
-    <sheet name="Reactivity Advanced" sheetId="32" r:id="rId13"/>
-    <sheet name="Composition Helpers" sheetId="34" r:id="rId14"/>
-    <sheet name="Built-in Components" sheetId="35" r:id="rId15"/>
-    <sheet name="Директивы" sheetId="16" r:id="rId16"/>
-    <sheet name="{{ }}" sheetId="21" r:id="rId17"/>
-    <sheet name="value, v-model, @" sheetId="22" r:id="rId18"/>
+    <sheet name="setup()" sheetId="27" r:id="rId4"/>
+    <sheet name="Templates" sheetId="42" r:id="rId5"/>
+    <sheet name="batch" sheetId="40" r:id="rId6"/>
+    <sheet name="ref selector" sheetId="41" r:id="rId7"/>
+    <sheet name="ref" sheetId="31" r:id="rId8"/>
+    <sheet name="reactive" sheetId="38" r:id="rId9"/>
+    <sheet name="lifecycle" sheetId="29" r:id="rId10"/>
+    <sheet name="computed, readonly" sheetId="37" r:id="rId11"/>
+    <sheet name="watch" sheetId="36" r:id="rId12"/>
+    <sheet name="provide, inject" sheetId="33" r:id="rId13"/>
+    <sheet name="Vue Css" sheetId="39" r:id="rId14"/>
+    <sheet name="Reactivity Advanced" sheetId="32" r:id="rId15"/>
+    <sheet name="Composition Helpers" sheetId="34" r:id="rId16"/>
+    <sheet name="Built-in Components" sheetId="35" r:id="rId17"/>
+    <sheet name="Директивы" sheetId="16" r:id="rId18"/>
+    <sheet name="{{ }}" sheetId="21" r:id="rId19"/>
+    <sheet name="value, v-model, @" sheetId="22" r:id="rId20"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -45,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="868">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="885">
   <si>
     <t>Vue</t>
   </si>
@@ -7927,9 +7929,6 @@
     <t>Точка входа Composition API в компоненте.</t>
   </si>
   <si>
-    <t>Точка входа Composition API</t>
-  </si>
-  <si>
     <t>import { ref } from 'vue'
 export default {
   setup() {
@@ -7954,9 +7953,6 @@
     <t>Первый аргумент setup — реактивные props компонента.</t>
   </si>
   <si>
-    <t>Доступ к props</t>
-  </si>
-  <si>
     <t>export default {
   props: { title: String },
   setup(props) {
@@ -7974,9 +7970,6 @@
     <t>Утилиты для деструктуризации props с сохранением reactivity.</t>
   </si>
   <si>
-    <t>Деструктуризация props</t>
-  </si>
-  <si>
     <t>import { toRefs, toRef } from 'vue'
 setup(props) {
   const { title } = toRefs(props)
@@ -7998,9 +7991,6 @@
     <t>Асинхронная форма setup с top-level await.</t>
   </si>
   <si>
-    <t>Асинхронный setup (Suspense)</t>
-  </si>
-  <si>
     <t>export default {
   async setup() {
     const data = await fetchData()
@@ -8058,9 +8048,6 @@
     <t>Слоты компонента.</t>
   </si>
   <si>
-    <t>Слоты</t>
-  </si>
-  <si>
     <t>setup(props, { slots }) {
   console.log(slots.default)
 }</t>
@@ -8078,9 +8065,6 @@
     <t>Функция для emit событий.</t>
   </si>
   <si>
-    <t>Emit событий</t>
-  </si>
-  <si>
     <t>setup(props, { emit }) {
   emit('submit', payload)
 }</t>
@@ -8096,9 +8080,6 @@
   </si>
   <si>
     <t>Явно ограничивает свойства, доступные родителю через template ref.</t>
-  </si>
-  <si>
-    <t>Expose для template refs</t>
   </si>
   <si>
     <t>setup(props, { expose }) {
@@ -8119,9 +8100,6 @@
   </si>
   <si>
     <t>setup может вернуть render function вместо объекта.</t>
-  </si>
-  <si>
-    <t>Render function из setup</t>
   </si>
   <si>
     <t>import { h, ref } from 'vue'
@@ -8145,9 +8123,6 @@
   </si>
   <si>
     <t>defineComponent()</t>
-  </si>
-  <si>
-    <t>Type helper для определения компонента Vue с выводом типов.</t>
   </si>
   <si>
     <t>Для TypeScript и определения компонентов</t>
@@ -8178,9 +8153,6 @@
   </si>
   <si>
     <t>Определяет асинхронный компонент с ленивой загрузкой при рендере.</t>
-  </si>
-  <si>
-    <t>Для ленивой загрузки компонентов</t>
   </si>
   <si>
     <t>import { defineAsyncComponent } from 'vue'
@@ -13477,67 +13449,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">watch() </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>{ flush: 'sync' } с безопасным</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>получением DOM элементов</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> = </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>watchPostEffect()</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <rPr>
         <b/>
         <sz val="11"/>
@@ -16387,17 +16298,928 @@
   <si>
     <t>&gt; Vue 3.4</t>
   </si>
+  <si>
+    <t>&lt;3.5</t>
+  </si>
+  <si>
+    <t>&gt;3.5</t>
+  </si>
+  <si>
+    <t>import { ref, onMounted } from 'vue'
+export default {
+  setup() {
+    const count = ref(0)
+    onMounted(() =&gt; {
+      console.log(count.value) // 0
+    })
+    return { count }
+  }
+}</t>
+  </si>
+  <si>
+    <t>Composotion + Options API</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;script setup&gt;
+import { ref, onMounted } from 'vue'
+const </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>input</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ref</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>null</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)
+onMounted(() =&gt; {
+  input.value.focus()
+})
+&lt;/script&gt;
+&lt;template&gt;
+  &lt;input ref="</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>input</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" /&gt;
+&lt;/template&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;script setup&gt;
+import { useTemplateRef, onMounted } from 'vue'
+const input = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>useTemplateRef</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'my-input'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)
+onMounted(() =&gt; {
+  input.value.focus()
+})
+&lt;/script&gt;
+&lt;template&gt;
+  &lt;input ref="</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>my-input</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" /&gt;
+&lt;/template&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>По умолчанию компоненты в &lt;script setup&gt; закрыты — их внутренние переменные, методы и реактивные данные недоступны из родительского компонента. defineExpose открывает доступ к выбранным элементам.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;script setup&gt;
+import { ref } from 'vue'
+const a = 1
+const b = ref(2)
+function someMethod() {
+  console.log('Hello from child!')
+  b.value++
+}
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">defineExpose({
+  a,
+  b,
+  someMethod
+})
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;/script&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>`https://vuejs.org/guide/essentials/template-refs.html#accessing-the-refs
+watchEffect(() =&gt; {
+  if (input.value) {
+    input.value.focus()
+  } else {
+    // not mounted yet, or the element was unmounted (e.g. by v-if)
+  }
+})</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Array
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>useTemplateRef('items') = ref([])</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Value</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+useTemplateRef('my-input') = ref(null)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;script setup&gt;
+import { ref, useTemplateRef, onMounted } from 'vue'
+const list = ref([
+  /* ... */
+])
+const itemRefs = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>useTemplateRef</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>('items')</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+onMounted(() =&gt; console.log(itemRefs.value))
+&lt;/script&gt;
+&lt;template&gt;
+  &lt;ul&gt;
+    &lt;li v-for="item in list" ref="items"&gt;
+      {{ item }}
+    &lt;/li&gt;
+  &lt;/ul&gt;
+&lt;/template&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;script setup&gt;
+import { ref, onMounted } from 'vue'
+const list = ref([
+  /* ... */
+])
+const itemRefs = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ref([])</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+onMounted(() =&gt; console.log(itemRefs.value))
+&lt;/script&gt;
+&lt;template&gt;
+  &lt;ul&gt;
+    &lt;li v-for="item in list" ref="itemRefs"&gt;
+      {{ item }}
+    &lt;/li&gt;
+  &lt;/ul&gt;
+&lt;/template&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;input </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:ref="(el) =&gt; { /* assign el to a property or ref */ }"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Assign in HTML</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, not in Vue component</t>
+    </r>
+  </si>
+  <si>
+    <t>Оптимальный способ!</t>
+  </si>
+  <si>
+    <t>Options API (классический подход)</t>
+  </si>
+  <si>
+    <t>Composition API с &lt;script setup&gt;</t>
+  </si>
+  <si>
+    <t>Composition API с setup()</t>
+  </si>
+  <si>
+    <t>&lt;script setup&gt;
+import { ref, computed, watch, onMounted } from 'vue'
+// ========== Пропсы ==========
+const props = defineProps({
+  initialCount: {
+    type: Number,
+    default: 0,
+    validator(value) {
+      return value &gt;= 0 &amp;&amp; value &lt;= 100
+    }
+  },
+  step: {
+    type: Number,
+    default: 1,
+    validator(value) {
+      return value &gt; 0
+    }
+  },
+  max: {
+    type: Number,
+    default: Infinity
+  },
+  min: {
+    type: Number,
+    default: -Infinity
+  }
+})
+// ========== Эмиты ==========
+const emit = defineEmits({
+  'update:count': (value) =&gt; {
+    return typeof value === 'number' &amp;&amp; !isNaN(value)
+  },
+  'change': (value, oldValue) =&gt; {
+    return typeof value === 'number' &amp;&amp; typeof oldValue === 'number'
+  },
+  'error': (message) =&gt; {
+    return typeof message === 'string'
+  },
+  'reset': null
+})
+// ========== Реактивные данные ==========
+const count = ref(props.initialCount)
+const message = ref('Привет!')
+const error = ref(null)
+// ========== Вычисляемые свойства ==========
+const doubledCount = computed(() =&gt; count.value * 2)
+// ========== Приватные методы ==========
+const setError = (text) =&gt; {
+  error.value = text
+  emit('error', text)
+}
+const emitChange = (oldValue) =&gt; {
+  emit('change', count.value, oldValue)
+}
+// ========== Публичные методы ==========
+const increment = () =&gt; {
+  if (count.value + props.step &lt;= props.max) {
+    const oldValue = count.value
+    count.value += props.step
+    error.value = null
+    emitChange(oldValue)
+    emit('update:count', count.value)
+  } else {
+    setError(`Нельзя превысить максимум (${props.max})`)
+  }
+}
+const decrement = () =&gt; {
+  if (count.value - props.step &gt;= props.min) {
+    const oldValue = count.value
+    count.value -= props.step
+    error.value = null
+    emitChange(oldValue)
+    emit('update:count', count.value)
+  } else {
+    setError(`Нельзя опуститься ниже минимума (${props.min})`)
+  }
+}
+const reset = () =&gt; {
+  const oldValue = count.value
+  count.value = props.initialCount
+  message.value = 'Сброшено!'
+  error.value = null
+  emit('reset')
+  emitChange(oldValue)
+  emit('update:count', count.value)
+}
+// ========== Хуки жизненного цикла ==========
+onMounted(() =&gt; {
+  console.log('Компонент смонтирован!', count.value)
+  emit('update:count', count.value)
+})
+// ========== Watch ==========
+watch(count, (newVal, oldVal) =&gt; {
+  console.log(`Счетчик изменился: ${oldVal} → ${newVal}`)
+})
+// ========== Expose (доступ из родителя) ==========
+defineExpose({
+  count,
+  message,
+  reset,
+  increment,
+  decrement
+})
+&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;template&gt;
+  &lt;div class="counter"&gt;
+    &lt;h1&gt;Composition API + &amp;lt;script setup&amp;gt;&lt;/h1&gt;
+    &lt;p&gt;Счетчик: {{ count }}&lt;/p&gt;
+    &lt;p&gt;Сообщение: {{ message }}&lt;/p&gt;
+    &lt;p&gt;Шаг: {{ props.step }}&lt;/p&gt;
+    &lt;input 
+      v-model="message" 
+      placeholder="Введите сообщение"
+    /&gt;
+    &lt;button @click="increment"&gt;+{{ props.step }}&lt;/button&gt;
+    &lt;button @click="decrement"&gt;-{{ props.step }}&lt;/button&gt;
+    &lt;button @click="reset"&gt;Сброс&lt;/button&gt;
+    &lt;p&gt;Двойное значение: {{ doubledCount }}&lt;/p&gt;
+    &lt;p v-if="error" class="error"&gt;{{ error }}&lt;/p&gt;
+  &lt;/div&gt;
+&lt;/template&gt;</t>
+  </si>
+  <si>
+    <t>&lt;style scoped&gt;
+.counter {
+  padding: 20px;
+  border: 2px solid #f1c40f;
+  border-radius: 8px;
+  margin: 10px;
+}
+.error {
+  color: red;
+  font-weight: bold;
+}
+&lt;/style&gt;</t>
+  </si>
+  <si>
+    <t>&lt;template&gt;
+  &lt;div class="counter"&gt;
+    &lt;h1&gt;Composition API + setup()&lt;/h1&gt;
+    &lt;p&gt;Счетчик: {{ count }}&lt;/p&gt;
+    &lt;p&gt;Сообщение: {{ message }}&lt;/p&gt;
+    &lt;p&gt;Шаг: {{ step }}&lt;/p&gt;
+    &lt;input 
+      v-model="message" 
+      placeholder="Введите сообщение"
+    /&gt;
+    &lt;button @click="increment"&gt;+{{ step }}&lt;/button&gt;
+    &lt;button @click="decrement"&gt;-{{ step }}&lt;/button&gt;
+    &lt;button @click="reset"&gt;Сброс&lt;/button&gt;
+    &lt;p&gt;Двойное значение: {{ doubledCount }}&lt;/p&gt;
+    &lt;p v-if="error" class="error"&gt;{{ error }}&lt;/p&gt;
+  &lt;/div&gt;
+&lt;/template&gt;</t>
+  </si>
+  <si>
+    <t>&lt;script&gt;
+import { ref, computed, watch, onMounted } from 'vue'
+export default {
+  // ========== Пропсы ==========
+  props: {
+    initialCount: {
+      type: Number,
+      default: 0,
+      validator(value) {
+        return value &gt;= 0 &amp;&amp; value &lt;= 100
+      }
+    },
+    step: {
+      type: Number,
+      default: 1,
+      validator(value) {
+        return value &gt; 0
+      }
+    },
+    max: {
+      type: Number,
+      default: Infinity
+    },
+    min: {
+      type: Number,
+      default: -Infinity
+    }
+  },
+  // ========== Эмиты ==========
+  emits: {
+    'update:count': (value) =&gt; {
+      return typeof value === 'number' &amp;&amp; !isNaN(value)
+    },
+    'change': (value, oldValue) =&gt; {
+      return typeof value === 'number' &amp;&amp; typeof oldValue === 'number'
+    },
+    'error': (message) =&gt; {
+      return typeof message === 'string'
+    },
+    'reset': null
+  },
+  // ========== Setup ==========
+  setup(props, { emit, expose }) {
+    // ===== Реактивные данные =====
+    const count = ref(props.initialCount)
+    const message = ref('Привет!')
+    const error = ref(null)
+    // ===== Вычисляемые свойства =====
+    const doubledCount = computed(() =&gt; count.value * 2)
+    // ===== Приватные методы =====
+    const setError = (text) =&gt; {
+      error.value = text
+      emit('error', text)
+    }
+    const emitChange = (oldValue) =&gt; {
+      emit('change', count.value, oldValue)
+    }
+    // ===== Публичные методы =====
+    const increment = () =&gt; {
+      if (count.value + props.step &lt;= props.max) {
+        const oldValue = count.value
+        count.value += props.step
+        error.value = null
+        emitChange(oldValue)
+        emit('update:count', count.value)
+      } else {
+        setError(`Нельзя превысить максимум (${props.max})`)
+      }
+    }
+    const decrement = () =&gt; {
+      if (count.value - props.step &gt;= props.min) {
+        const oldValue = count.value
+        count.value -= props.step
+        error.value = null
+        emitChange(oldValue)
+        emit('update:count', count.value)
+      } else {
+        setError(`Нельзя опуститься ниже минимума (${props.min})`)
+      }
+    }
+    const reset = () =&gt; {
+      const oldValue = count.value
+      count.value = props.initialCount
+      message.value = 'Сброшено!'
+      error.value = null
+      emit('reset')
+      emitChange(oldValue)
+      emit('update:count', count.value)
+    }
+    // ===== Хуки жизненного цикла =====
+    onMounted(() =&gt; {
+      console.log('Компонент смонтирован!', count.value)
+      emit('update:count', count.value)
+    })
+    // ===== Watch =====
+    watch(count, (newVal, oldVal) =&gt; {
+      console.log(`Счетчик изменился: ${oldVal} → ${newVal}`)
+    })
+    // ===== Expose (доступ из родителя) =====
+    expose({
+      count,
+      message,
+      reset,
+      increment,
+      decrement
+    })
+    // ===== Возвращаем для шаблона =====
+    return {
+      count,
+      message,
+      error,
+      step: props.step,
+      doubledCount,
+      increment,
+      decrement,
+      reset
+    }
+  }
+}
+&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;style scoped&gt;
+.counter {
+  padding: 20px;
+  border: 2px solid #e74c3c;
+  border-radius: 8px;
+  margin: 10px;
+}
+.error {
+  color: red;
+  font-weight: bold;
+}
+&lt;/style&gt;</t>
+  </si>
+  <si>
+    <t>&lt;template&gt;
+  &lt;div class="counter"&gt;
+    &lt;h1&gt;Options API&lt;/h1&gt;
+    &lt;p&gt;Счетчик: {{ count }}&lt;/p&gt;
+    &lt;p&gt;Сообщение: {{ message }}&lt;/p&gt;
+    &lt;p&gt;Шаг: {{ step }}&lt;/p&gt;
+    &lt;input 
+      v-model="message" 
+      placeholder="Введите сообщение"
+    /&gt;
+    &lt;button @click="increment"&gt;+{{ step }}&lt;/button&gt;
+    &lt;button @click="decrement"&gt;-{{ step }}&lt;/button&gt;
+    &lt;button @click="reset"&gt;Сброс&lt;/button&gt;
+    &lt;p&gt;Двойное значение: {{ doubledCount }}&lt;/p&gt;
+    &lt;!-- Отображаем ошибки --&gt;
+    &lt;p v-if="error" class="error"&gt;{{ error }}&lt;/p&gt;
+  &lt;/div&gt;
+&lt;/template&gt;</t>
+  </si>
+  <si>
+    <t>&lt;script&gt;
+export default {
+  // ========== Пропсы ==========
+  props: {
+    // Начальное значение счетчика
+    initialCount: {
+      type: Number,
+      default: 0,
+      validator(value) {
+        return value &gt;= 0 &amp;&amp; value &lt;= 100
+      }
+    },
+    // Шаг изменения
+    step: {
+      type: Number,
+      default: 1,
+      validator(value) {
+        return value &gt; 0
+      }
+    },
+    // Максимальное значение
+    max: {
+      type: Number,
+      default: Infinity
+    },
+    // Минимальное значение
+    min: {
+      type: Number,
+      default: -Infinity
+    }
+  },
+  // ========== Эмиты ==========
+  emits: {
+    // Валидация эмитов
+    'update:count': (value) =&gt; {
+      return typeof value === 'number' &amp;&amp; !isNaN(value)
+    },
+    'change': (value, oldValue) =&gt; {
+      return typeof value === 'number' &amp;&amp; typeof oldValue === 'number'
+    },
+    'error': (message) =&gt; {
+      return typeof message === 'string'
+    },
+    'reset': null // Без валидации
+  },
+  // ========== Данные ==========
+  data() {
+    return {
+      count: this.initialCount,
+      message: 'Привет!',
+      error: null
+    }
+  },
+  // ========== Вычисляемые свойства ==========
+  computed: {
+    doubledCount() {
+      return this.count * 2
+    }
+  },
+  // ========== Методы ==========
+  methods: {
+    increment() {
+      if (this.count + this.step &lt;= this.max) {
+        const oldValue = this.count
+        this.count += this.step
+        this.error = null
+        this.emitChange(oldValue)
+        this.$emit('update:count', this.count)
+      } else {
+        this.setError(`Нельзя превысить максимум (${this.max})`)
+      }
+    },
+    decrement() {
+      if (this.count - this.step &gt;= this.min) {
+        const oldValue = this.count
+        this.count -= this.step
+        this.error = null
+        this.emitChange(oldValue)
+        this.$emit('update:count', this.count)
+      } else {
+        this.setError(`Нельзя опуститься ниже минимума (${this.min})`)
+      }
+    },
+    reset() {
+      const oldValue = this.count
+      this.count = this.initialCount
+      this.message = 'Сброшено!'
+      this.error = null
+      this.$emit('reset')
+      this.emitChange(oldValue)
+      this.$emit('update:count', this.count)
+    },
+    emitChange(oldValue) {
+      this.$emit('change', this.count, oldValue)
+    },
+    setError(message) {
+      this.error = message
+      this.$emit('error', message)
+    }
+  },
+  // ========== Watch ==========
+  watch: {
+    count(newVal, oldVal) {
+      console.log(`Счетчик изменился: ${oldVal} → ${newVal}`)
+    }
+  },
+  // ========== Хуки жизненного цикла ==========
+  mounted() {
+    console.log('Компонент смонтирован!', this.count)
+    this.$emit('update:count', this.count)
+  }
+}
+&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;style scoped&gt;
+.counter {
+  padding: 20px;
+  border: 2px solid #42b883;
+  border-radius: 8px;
+  margin: 10px;
+}
+.error {
+  color: red;
+  font-weight: bold;
+}
+&lt;/style&gt;</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="54">
+  <fonts count="55">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -16825,7 +17647,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -16916,6 +17738,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -16928,13 +17756,13 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -16945,20 +17773,20 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -16967,38 +17795,41 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -17007,85 +17838,82 @@
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="27" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="42" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="48" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="49" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -17094,7 +17922,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -17103,25 +17931,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="4" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -17130,37 +17958,37 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="4" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -17169,72 +17997,90 @@
     <xf numFmtId="49" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="5" applyFill="1"/>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="5" applyFill="1"/>
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="8" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="30" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="31" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="30" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="30" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -17600,13 +18446,453 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C4:D11">
     <sortCondition ref="D4:D11"/>
   </sortState>
-  <phoneticPr fontId="22" type="noConversion"/>
+  <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7742DC2D-8356-42AF-A171-521A8B3CCEEA}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:F17"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="39.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="44.77734375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="33.109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="59.21875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="37.88671875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="2" customWidth="1"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="2" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="2" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="2" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="2" customWidth="1"/>
+    <col min="28" max="28" width="8.77734375" style="2" customWidth="1"/>
+    <col min="29" max="16384" width="8.77734375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6">
+      <c r="A2" s="50"/>
+    </row>
+    <row r="4" spans="1:6" s="40" customFormat="1"/>
+    <row r="5" spans="1:6">
+      <c r="A5" s="41" t="s">
+        <v>268</v>
+      </c>
+      <c r="B5" s="41" t="s">
+        <v>269</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>271</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>272</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>270</v>
+      </c>
+      <c r="F5" s="41" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="72">
+      <c r="A6" s="57" t="s">
+        <v>463</v>
+      </c>
+      <c r="B6" s="57" t="s">
+        <v>464</v>
+      </c>
+      <c r="C6" s="57" t="s">
+        <v>465</v>
+      </c>
+      <c r="D6" s="57" t="s">
+        <v>466</v>
+      </c>
+      <c r="E6" s="57" t="s">
+        <v>467</v>
+      </c>
+      <c r="F6" s="58" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="86.4">
+      <c r="A7" s="57" t="s">
+        <v>469</v>
+      </c>
+      <c r="B7" s="57" t="s">
+        <v>470</v>
+      </c>
+      <c r="C7" s="57" t="s">
+        <v>465</v>
+      </c>
+      <c r="D7" s="57" t="s">
+        <v>471</v>
+      </c>
+      <c r="E7" s="57" t="s">
+        <v>472</v>
+      </c>
+      <c r="F7" s="58" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="72">
+      <c r="A8" s="57" t="s">
+        <v>473</v>
+      </c>
+      <c r="B8" s="57" t="s">
+        <v>474</v>
+      </c>
+      <c r="C8" s="57" t="s">
+        <v>475</v>
+      </c>
+      <c r="D8" s="57" t="s">
+        <v>476</v>
+      </c>
+      <c r="E8" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="F8" s="58" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="86.4">
+      <c r="A9" s="57" t="s">
+        <v>478</v>
+      </c>
+      <c r="B9" s="57" t="s">
+        <v>479</v>
+      </c>
+      <c r="C9" s="57" t="s">
+        <v>475</v>
+      </c>
+      <c r="D9" s="57" t="s">
+        <v>480</v>
+      </c>
+      <c r="E9" s="57" t="s">
+        <v>481</v>
+      </c>
+      <c r="F9" s="58" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="72">
+      <c r="A10" s="57" t="s">
+        <v>482</v>
+      </c>
+      <c r="B10" s="57" t="s">
+        <v>483</v>
+      </c>
+      <c r="C10" s="57" t="s">
+        <v>484</v>
+      </c>
+      <c r="D10" s="57" t="s">
+        <v>485</v>
+      </c>
+      <c r="E10" s="57" t="s">
+        <v>486</v>
+      </c>
+      <c r="F10" s="58" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="72">
+      <c r="A11" s="57" t="s">
+        <v>487</v>
+      </c>
+      <c r="B11" s="57" t="s">
+        <v>488</v>
+      </c>
+      <c r="C11" s="57" t="s">
+        <v>484</v>
+      </c>
+      <c r="D11" s="57" t="s">
+        <v>489</v>
+      </c>
+      <c r="E11" s="57" t="s">
+        <v>490</v>
+      </c>
+      <c r="F11" s="58" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="86.4">
+      <c r="A12" s="57" t="s">
+        <v>491</v>
+      </c>
+      <c r="B12" s="57" t="s">
+        <v>492</v>
+      </c>
+      <c r="C12" s="57" t="s">
+        <v>493</v>
+      </c>
+      <c r="D12" s="57" t="s">
+        <v>494</v>
+      </c>
+      <c r="E12" s="57" t="s">
+        <v>495</v>
+      </c>
+      <c r="F12" s="58" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="72">
+      <c r="A13" s="57" t="s">
+        <v>497</v>
+      </c>
+      <c r="B13" s="57" t="s">
+        <v>498</v>
+      </c>
+      <c r="C13" s="57" t="s">
+        <v>499</v>
+      </c>
+      <c r="D13" s="57" t="s">
+        <v>500</v>
+      </c>
+      <c r="E13" s="57" t="s">
+        <v>501</v>
+      </c>
+      <c r="F13" s="58" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="72">
+      <c r="A14" s="57" t="s">
+        <v>503</v>
+      </c>
+      <c r="B14" s="57" t="s">
+        <v>504</v>
+      </c>
+      <c r="C14" s="57" t="s">
+        <v>499</v>
+      </c>
+      <c r="D14" s="57" t="s">
+        <v>505</v>
+      </c>
+      <c r="E14" s="57" t="s">
+        <v>506</v>
+      </c>
+      <c r="F14" s="58" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="72">
+      <c r="A15" s="57" t="s">
+        <v>507</v>
+      </c>
+      <c r="B15" s="57" t="s">
+        <v>508</v>
+      </c>
+      <c r="C15" s="57" t="s">
+        <v>509</v>
+      </c>
+      <c r="D15" s="57" t="s">
+        <v>510</v>
+      </c>
+      <c r="E15" s="57" t="s">
+        <v>511</v>
+      </c>
+      <c r="F15" s="58" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="72">
+      <c r="A16" s="57" t="s">
+        <v>513</v>
+      </c>
+      <c r="B16" s="57" t="s">
+        <v>514</v>
+      </c>
+      <c r="C16" s="57" t="s">
+        <v>509</v>
+      </c>
+      <c r="D16" s="57" t="s">
+        <v>515</v>
+      </c>
+      <c r="E16" s="57" t="s">
+        <v>511</v>
+      </c>
+      <c r="F16" s="58" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="129.6">
+      <c r="A17" s="57" t="s">
+        <v>516</v>
+      </c>
+      <c r="B17" s="57" t="s">
+        <v>517</v>
+      </c>
+      <c r="C17" s="57" t="s">
+        <v>518</v>
+      </c>
+      <c r="D17" s="57" t="s">
+        <v>519</v>
+      </c>
+      <c r="E17" s="57" t="s">
+        <v>520</v>
+      </c>
+      <c r="F17" s="58" t="s">
+        <v>521</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F6" r:id="rId1" xr:uid="{BCEDF5A9-AC9D-4B18-8FBC-704E1C4E35E0}"/>
+    <hyperlink ref="F7" r:id="rId2" xr:uid="{BF973FE4-46C9-45BD-A0D7-BDB80A784126}"/>
+    <hyperlink ref="F8" r:id="rId3" xr:uid="{276747C2-1EE8-4753-A0F4-4578E91151A9}"/>
+    <hyperlink ref="F9" r:id="rId4" xr:uid="{B5A71B51-F713-45BB-9829-67643F7D1D21}"/>
+    <hyperlink ref="F10" r:id="rId5" xr:uid="{8E4441EE-D698-4A6C-8D21-F92553B19E51}"/>
+    <hyperlink ref="F11" r:id="rId6" xr:uid="{07711047-0E0A-4356-AC98-13FCB68D4BE4}"/>
+    <hyperlink ref="F12" r:id="rId7" xr:uid="{18852E30-E696-4133-96A1-C252B084455B}"/>
+    <hyperlink ref="F13" r:id="rId8" xr:uid="{89843FA1-DC4B-4D5B-8552-9D3BA9234690}"/>
+    <hyperlink ref="F14" r:id="rId9" xr:uid="{3C0DDCF3-333B-4DEE-9CBB-B6585965FFB3}"/>
+    <hyperlink ref="F15" r:id="rId10" location="lifecycle-of-cached-instance" xr:uid="{26921D4F-4677-415E-B2D6-0776521C8D9F}"/>
+    <hyperlink ref="F16" r:id="rId11" location="lifecycle-of-cached-instance" xr:uid="{933483F2-6232-441A-B2FA-07FE98326D89}"/>
+    <hyperlink ref="F17" r:id="rId12" xr:uid="{F3874539-CD42-4120-94FA-AD48E696674F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId13"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A618EC0-3EC6-431F-A43F-335526068004}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:D11"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="39.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="59.21875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="55.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="43.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="55.109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="67.88671875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="64.33203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7.77734375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="39.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="48.88671875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="72.6640625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="43.88671875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="7.77734375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="56.77734375" style="2" customWidth="1"/>
+    <col min="15" max="15" width="46.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="62.88671875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="49.21875" style="2" customWidth="1"/>
+    <col min="18" max="18" width="8.77734375" style="2" customWidth="1"/>
+    <col min="19" max="19" width="67.77734375" style="2" customWidth="1"/>
+    <col min="20" max="20" width="68.33203125" style="2" customWidth="1"/>
+    <col min="21" max="22" width="59.33203125" style="2" customWidth="1"/>
+    <col min="23" max="23" width="59.6640625" style="2" customWidth="1"/>
+    <col min="24" max="24" width="99.44140625" style="2" customWidth="1"/>
+    <col min="25" max="25" width="41.21875" style="2" customWidth="1"/>
+    <col min="26" max="26" width="8.77734375" style="2" customWidth="1"/>
+    <col min="27" max="16384" width="8.77734375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:4">
+      <c r="A2" s="54" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="54" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="50" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="40" customFormat="1"/>
+    <row r="7" spans="1:4">
+      <c r="A7" s="41" t="s">
+        <v>268</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>272</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>270</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="56" customFormat="1">
+      <c r="A8" s="54" t="s">
+        <v>534</v>
+      </c>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="58"/>
+    </row>
+    <row r="9" spans="1:4" s="56" customFormat="1" ht="265.2" customHeight="1">
+      <c r="B9" s="57" t="s">
+        <v>753</v>
+      </c>
+      <c r="C9" s="75" t="s">
+        <v>754</v>
+      </c>
+      <c r="D9" s="58" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" s="56" customFormat="1">
+      <c r="A10" s="54" t="s">
+        <v>537</v>
+      </c>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="58"/>
+    </row>
+    <row r="11" spans="1:4" s="56" customFormat="1" ht="165" customHeight="1">
+      <c r="A11" s="56" t="s">
+        <v>552</v>
+      </c>
+      <c r="B11" s="57" t="s">
+        <v>738</v>
+      </c>
+      <c r="C11" s="57" t="s">
+        <v>742</v>
+      </c>
+      <c r="D11" s="58" t="s">
+        <v>276</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D9" r:id="rId1" xr:uid="{BCBCEA9E-F432-4A47-B60F-5B013B8D935F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{699DA14B-4B03-4F00-B701-816422181365}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
@@ -17646,65 +18932,65 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="54" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="54" t="s">
-        <v>780</v>
+        <v>770</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="54" t="s">
-        <v>776</v>
+        <v>766</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="54" t="s">
-        <v>785</v>
+        <v>775</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28.8">
       <c r="A6" s="54" t="s">
-        <v>794</v>
+        <v>783</v>
       </c>
       <c r="B6" s="93" t="s">
-        <v>796</v>
+        <v>785</v>
       </c>
       <c r="E6" s="97" t="s">
-        <v>828</v>
+        <v>817</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28.8">
       <c r="A7" s="54" t="s">
-        <v>798</v>
+        <v>787</v>
       </c>
       <c r="B7" s="93" t="s">
-        <v>795</v>
+        <v>784</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="43.2">
       <c r="A8" s="93" t="s">
-        <v>818</v>
+        <v>807</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="40" customFormat="1"/>
     <row r="13" spans="1:5" s="56" customFormat="1">
       <c r="A13" s="54" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="B13" s="57"/>
       <c r="C13" s="57" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="D13" s="57"/>
       <c r="E13" s="58" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="56" customFormat="1">
       <c r="A14" s="70" t="s">
-        <v>726</v>
+        <v>716</v>
       </c>
       <c r="B14" s="57"/>
       <c r="C14" s="57"/>
@@ -17713,21 +18999,21 @@
     </row>
     <row r="15" spans="1:5" s="56" customFormat="1" ht="100.8">
       <c r="B15" s="2" t="s">
-        <v>771</v>
+        <v>761</v>
       </c>
       <c r="C15" s="57" t="s">
-        <v>768</v>
+        <v>758</v>
       </c>
       <c r="D15" s="71" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="56" customFormat="1" ht="28.8">
       <c r="A16" s="89" t="s">
-        <v>727</v>
+        <v>717</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="57"/>
@@ -17736,32 +19022,32 @@
     </row>
     <row r="17" spans="1:5" s="56" customFormat="1" ht="129.6">
       <c r="B17" s="2" t="s">
-        <v>769</v>
+        <v>759</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>767</v>
+        <v>757</v>
       </c>
       <c r="D17" s="64" t="s">
-        <v>554</v>
+        <v>544</v>
       </c>
       <c r="E17" s="58"/>
     </row>
     <row r="18" spans="1:5" s="56" customFormat="1" ht="115.2">
       <c r="A18" s="57"/>
       <c r="B18" s="2" t="s">
-        <v>770</v>
+        <v>760</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>774</v>
+        <v>764</v>
       </c>
       <c r="D18" s="64" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
       <c r="E18" s="58"/>
     </row>
     <row r="19" spans="1:5" s="56" customFormat="1">
       <c r="A19" s="90" t="s">
-        <v>556</v>
+        <v>546</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -17770,104 +19056,104 @@
     </row>
     <row r="20" spans="1:5" ht="86.4">
       <c r="B20" s="2" t="s">
-        <v>772</v>
+        <v>762</v>
       </c>
       <c r="C20" s="65" t="s">
-        <v>765</v>
+        <v>755</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="20" t="s">
-        <v>766</v>
+        <v>756</v>
       </c>
       <c r="C21" s="65"/>
     </row>
     <row r="22" spans="1:5" ht="43.2">
       <c r="A22" s="64"/>
       <c r="B22" s="2" t="s">
-        <v>773</v>
+        <v>763</v>
       </c>
       <c r="C22" s="65" t="s">
-        <v>553</v>
+        <v>543</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="54" t="s">
-        <v>780</v>
+        <v>770</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>781</v>
+        <v>771</v>
       </c>
       <c r="C23" s="91" t="s">
-        <v>782</v>
+        <v>772</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="100.8">
       <c r="A24" s="64"/>
       <c r="C24" s="2" t="s">
-        <v>775</v>
+        <v>765</v>
       </c>
       <c r="D24" s="76" t="s">
-        <v>778</v>
+        <v>768</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>783</v>
+        <v>773</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="115.2">
       <c r="A25" s="64"/>
       <c r="B25" s="95" t="s">
-        <v>804</v>
+        <v>793</v>
       </c>
       <c r="C25" s="76" t="s">
-        <v>806</v>
+        <v>795</v>
       </c>
       <c r="D25" s="76" t="s">
-        <v>805</v>
+        <v>794</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="54" t="s">
-        <v>776</v>
+        <v>766</v>
       </c>
       <c r="C26" s="65"/>
     </row>
     <row r="27" spans="1:5" ht="100.8">
       <c r="A27" s="64"/>
       <c r="C27" s="65" t="s">
-        <v>779</v>
+        <v>769</v>
       </c>
       <c r="D27" s="76" t="s">
-        <v>777</v>
+        <v>767</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="54" t="s">
-        <v>785</v>
+        <v>775</v>
       </c>
       <c r="B28" s="92" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="C28" s="92" t="s">
-        <v>788</v>
+        <v>778</v>
       </c>
       <c r="D28" s="76"/>
     </row>
     <row r="29" spans="1:5" ht="216">
       <c r="A29" s="76"/>
       <c r="B29" s="2" t="s">
-        <v>786</v>
+        <v>776</v>
       </c>
       <c r="C29" s="76" t="s">
-        <v>789</v>
+        <v>779</v>
       </c>
       <c r="D29" s="76" t="s">
-        <v>784</v>
+        <v>774</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="28.8">
       <c r="A30" s="54" t="s">
-        <v>794</v>
+        <v>783</v>
       </c>
       <c r="C30" s="65"/>
       <c r="D30" s="76"/>
@@ -17876,25 +19162,25 @@
       <c r="A31" s="64"/>
       <c r="B31" s="64"/>
       <c r="C31" s="65" t="s">
-        <v>802</v>
+        <v>791</v>
       </c>
       <c r="D31" s="76" t="s">
-        <v>790</v>
+        <v>780</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="72">
       <c r="A32" s="64"/>
       <c r="B32" s="95" t="s">
-        <v>803</v>
+        <v>792</v>
       </c>
       <c r="C32" s="65" t="s">
-        <v>801</v>
+        <v>790</v>
       </c>
       <c r="D32" s="76"/>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="54" t="s">
-        <v>798</v>
+        <v>787</v>
       </c>
       <c r="C33" s="65"/>
       <c r="D33" s="76"/>
@@ -17902,65 +19188,65 @@
     <row r="34" spans="1:5" ht="172.8">
       <c r="A34" s="76"/>
       <c r="B34" s="94" t="s">
-        <v>797</v>
+        <v>786</v>
       </c>
       <c r="C34" s="65" t="s">
-        <v>793</v>
+        <v>782</v>
       </c>
       <c r="D34" s="76" t="s">
-        <v>792</v>
+        <v>781</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="72">
       <c r="B35" s="94" t="s">
-        <v>800</v>
+        <v>789</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>799</v>
+        <v>788</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="43.2">
       <c r="A36" s="54" t="s">
-        <v>807</v>
+        <v>796</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="100.8">
       <c r="A37" s="2" t="s">
-        <v>811</v>
+        <v>800</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>814</v>
+        <v>803</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>809</v>
+        <v>798</v>
       </c>
       <c r="D37" s="76" t="s">
-        <v>816</v>
+        <v>805</v>
       </c>
       <c r="E37" s="97" t="s">
-        <v>828</v>
+        <v>817</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="345.6">
       <c r="A38" s="2" t="s">
-        <v>812</v>
+        <v>801</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>813</v>
+        <v>802</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>810</v>
+        <v>799</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="57.6">
       <c r="A39" s="2" t="s">
-        <v>815</v>
+        <v>804</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>808</v>
+        <v>797</v>
       </c>
       <c r="D39" s="76" t="s">
-        <v>817</v>
+        <v>806</v>
       </c>
     </row>
   </sheetData>
@@ -17972,7 +19258,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5196872-622E-452B-BF08-E278EFE9C4AC}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
@@ -18013,12 +19299,12 @@
   <sheetData>
     <row r="2" spans="1:7">
       <c r="A2" s="54" t="s">
-        <v>602</v>
+        <v>592</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="54" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="40" customFormat="1"/>
@@ -18039,7 +19325,7 @@
         <v>270</v>
       </c>
       <c r="F6" t="s">
-        <v>557</v>
+        <v>547</v>
       </c>
       <c r="G6" t="s">
         <v>273</v>
@@ -18047,7 +19333,7 @@
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1">
       <c r="A7" s="54" t="s">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="B7" s="56"/>
       <c r="C7" s="56"/>
@@ -18058,53 +19344,53 @@
     </row>
     <row r="8" spans="1:7" ht="244.8">
       <c r="A8" s="57" t="s">
-        <v>603</v>
+        <v>593</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="C8" s="57" t="s">
-        <v>605</v>
+        <v>595</v>
       </c>
       <c r="D8" s="57" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="E8" s="57" t="s">
-        <v>607</v>
+        <v>597</v>
       </c>
       <c r="F8" s="57" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="G8" s="58" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="403.2">
       <c r="A9" s="57" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="C9" s="57" t="s">
-        <v>612</v>
+        <v>602</v>
       </c>
       <c r="D9" s="57" t="s">
-        <v>613</v>
+        <v>603</v>
       </c>
       <c r="E9" s="57" t="s">
-        <v>614</v>
+        <v>604</v>
       </c>
       <c r="F9" s="57" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="G9" s="58" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1">
       <c r="A10" s="54" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="B10" s="56"/>
       <c r="C10" s="56"/>
@@ -18115,25 +19401,25 @@
     </row>
     <row r="11" spans="1:7" ht="201.6">
       <c r="A11" s="57" t="s">
-        <v>617</v>
+        <v>607</v>
       </c>
       <c r="B11" s="57" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
       <c r="C11" s="57" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
       <c r="D11" s="57" t="s">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="E11" s="57" t="s">
-        <v>621</v>
+        <v>611</v>
       </c>
       <c r="F11" s="57" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="G11" s="58" t="s">
-        <v>623</v>
+        <v>613</v>
       </c>
     </row>
   </sheetData>
@@ -18147,7 +19433,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC84526A-FEB5-4E92-A2D1-9E62E1253250}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -18194,7 +19480,7 @@
       <c r="A2" s="99"/>
       <c r="B2" s="99"/>
       <c r="C2" s="96" t="s">
-        <v>842</v>
+        <v>831</v>
       </c>
       <c r="D2" s="99"/>
     </row>
@@ -18251,7 +19537,7 @@
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="87" t="s">
-        <v>753</v>
+        <v>743</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="4"/>
@@ -18264,7 +19550,7 @@
       <c r="A10" s="1"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>699</v>
+        <v>689</v>
       </c>
       <c r="D10" s="1"/>
       <c r="P10" s="81"/>
@@ -18275,7 +19561,7 @@
       <c r="A11" s="1"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="D11" s="1"/>
       <c r="P11" s="81"/>
@@ -18285,10 +19571,10 @@
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="96" t="s">
-        <v>842</v>
+        <v>831</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>698</v>
+        <v>688</v>
       </c>
       <c r="D12" s="1"/>
       <c r="P12" s="81"/>
@@ -18298,10 +19584,10 @@
     <row r="13" spans="1:22" ht="72">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
-        <v>701</v>
+        <v>691</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="D13" s="1"/>
       <c r="P13" s="81"/>
@@ -18350,7 +19636,7 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="87" t="s">
-        <v>756</v>
+        <v>746</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="76"/>
@@ -18358,7 +19644,7 @@
     </row>
     <row r="19" spans="1:4" ht="28.8">
       <c r="A19" s="88" t="s">
-        <v>754</v>
+        <v>744</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="81"/>
@@ -18367,26 +19653,26 @@
     <row r="20" spans="1:4" ht="57.6">
       <c r="A20" s="2"/>
       <c r="B20" s="2" t="s">
-        <v>758</v>
+        <v>748</v>
       </c>
       <c r="C20" s="76" t="s">
-        <v>760</v>
+        <v>750</v>
       </c>
       <c r="D20" s="2"/>
     </row>
     <row r="21" spans="1:4" ht="72">
       <c r="A21" s="2"/>
       <c r="B21" s="2" t="s">
-        <v>757</v>
+        <v>747</v>
       </c>
       <c r="C21" s="76" t="s">
-        <v>759</v>
+        <v>749</v>
       </c>
       <c r="D21" s="2"/>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="88" t="s">
-        <v>755</v>
+        <v>745</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="76"/>
@@ -18436,7 +19722,7 @@
       </c>
       <c r="D26" s="1"/>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" ht="86.4">
       <c r="A27" s="1" t="s">
         <v>72</v>
       </c>
@@ -18453,10 +19739,10 @@
         <v>58</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>761</v>
+        <v>751</v>
       </c>
       <c r="C28" s="82" t="s">
-        <v>762</v>
+        <v>752</v>
       </c>
       <c r="D28" s="82"/>
     </row>
@@ -18466,7 +19752,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A35D37AB-889F-4E36-AD27-D38FD2468E4E}">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
@@ -18507,22 +19793,22 @@
   <sheetData>
     <row r="2" spans="1:7">
       <c r="A2" s="66" t="s">
-        <v>558</v>
+        <v>548</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="54" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="54" t="s">
-        <v>570</v>
+        <v>560</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="54" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="40" customFormat="1"/>
@@ -18543,7 +19829,7 @@
         <v>270</v>
       </c>
       <c r="F9" t="s">
-        <v>557</v>
+        <v>547</v>
       </c>
       <c r="G9" t="s">
         <v>273</v>
@@ -18551,28 +19837,28 @@
     </row>
     <row r="10" spans="1:7" s="56" customFormat="1">
       <c r="A10" s="54" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="F10" s="57"/>
     </row>
     <row r="11" spans="1:7" s="56" customFormat="1" ht="374.4">
       <c r="A11" s="57" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
       <c r="B11" s="57" t="s">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="C11" s="57" t="s">
-        <v>566</v>
+        <v>556</v>
       </c>
       <c r="D11" s="57" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="E11" s="57" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="F11" s="57" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="G11" s="58" t="s">
         <v>276</v>
@@ -18580,28 +19866,28 @@
     </row>
     <row r="12" spans="1:7" s="56" customFormat="1">
       <c r="A12" s="54" t="s">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="F12" s="57"/>
     </row>
     <row r="13" spans="1:7" s="56" customFormat="1" ht="144">
       <c r="A13" s="57" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="B13" s="57" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="C13" s="57" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
       <c r="D13" s="57" t="s">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="E13" s="57" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="F13" s="57" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="G13" s="58" t="s">
         <v>276</v>
@@ -18609,22 +19895,22 @@
     </row>
     <row r="14" spans="1:7" ht="302.39999999999998">
       <c r="A14" s="57" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="B14" s="57" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="C14" s="57" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="D14" s="57" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="E14" s="57" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="F14" s="57" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="G14" s="58" t="s">
         <v>276</v>
@@ -18632,7 +19918,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="54" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="B15" s="56"/>
       <c r="C15" s="56"/>
@@ -18643,22 +19929,22 @@
     </row>
     <row r="16" spans="1:7" ht="230.4">
       <c r="A16" s="57" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="B16" s="57" t="s">
-        <v>585</v>
+        <v>575</v>
       </c>
       <c r="C16" s="57" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="D16" s="57" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="E16" s="57" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="F16" s="57" t="s">
-        <v>589</v>
+        <v>579</v>
       </c>
       <c r="G16" s="58" t="s">
         <v>276</v>
@@ -18666,22 +19952,22 @@
     </row>
     <row r="17" spans="1:7" ht="129.6">
       <c r="A17" s="57" t="s">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="B17" s="57" t="s">
-        <v>591</v>
+        <v>581</v>
       </c>
       <c r="C17" s="57" t="s">
-        <v>592</v>
+        <v>582</v>
       </c>
       <c r="D17" s="57" t="s">
-        <v>593</v>
+        <v>583</v>
       </c>
       <c r="E17" s="57" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="F17" s="57" t="s">
-        <v>595</v>
+        <v>585</v>
       </c>
       <c r="G17" s="58" t="s">
         <v>276</v>
@@ -18689,22 +19975,22 @@
     </row>
     <row r="18" spans="1:7" ht="158.4">
       <c r="A18" s="57" t="s">
-        <v>596</v>
+        <v>586</v>
       </c>
       <c r="B18" s="57" t="s">
-        <v>597</v>
+        <v>587</v>
       </c>
       <c r="C18" s="57" t="s">
-        <v>598</v>
+        <v>588</v>
       </c>
       <c r="D18" s="57" t="s">
-        <v>599</v>
+        <v>589</v>
       </c>
       <c r="E18" s="57" t="s">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="F18" s="57" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="G18" s="58" t="s">
         <v>276</v>
@@ -18748,7 +20034,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{648F1C38-3365-45E9-B4F4-D0AF4AA4A465}">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
@@ -18835,7 +20121,7 @@
         <v>270</v>
       </c>
       <c r="F14" t="s">
-        <v>557</v>
+        <v>547</v>
       </c>
       <c r="G14" t="s">
         <v>273</v>
@@ -18843,7 +20129,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="54" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="B15" s="56"/>
       <c r="C15" s="56"/>
@@ -18854,53 +20140,53 @@
     </row>
     <row r="16" spans="1:7" ht="201.6">
       <c r="A16" s="57" t="s">
-        <v>624</v>
+        <v>614</v>
       </c>
       <c r="B16" s="57" t="s">
-        <v>625</v>
+        <v>615</v>
       </c>
       <c r="C16" s="57" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D16" s="57" t="s">
-        <v>626</v>
+        <v>616</v>
       </c>
       <c r="E16" s="57" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="F16" s="57" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
       <c r="G16" s="67" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="201.6">
       <c r="A17" s="57" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="B17" s="57" t="s">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="C17" s="57" t="s">
-        <v>631</v>
+        <v>621</v>
       </c>
       <c r="D17" s="57" t="s">
-        <v>632</v>
+        <v>622</v>
       </c>
       <c r="E17" s="57" t="s">
-        <v>633</v>
+        <v>623</v>
       </c>
       <c r="F17" s="57" t="s">
-        <v>634</v>
+        <v>624</v>
       </c>
       <c r="G17" s="67" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="54" t="s">
-        <v>635</v>
+        <v>625</v>
       </c>
       <c r="B18" s="56"/>
       <c r="C18" s="56"/>
@@ -18911,22 +20197,22 @@
     </row>
     <row r="19" spans="1:7" ht="201.6">
       <c r="A19" s="57" t="s">
-        <v>636</v>
+        <v>626</v>
       </c>
       <c r="B19" s="57" t="s">
-        <v>637</v>
+        <v>627</v>
       </c>
       <c r="C19" s="57" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D19" s="57" t="s">
-        <v>639</v>
+        <v>629</v>
       </c>
       <c r="E19" s="57" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
       <c r="F19" s="57" t="s">
-        <v>641</v>
+        <v>631</v>
       </c>
       <c r="G19" s="67" t="s">
         <v>276</v>
@@ -18934,30 +20220,30 @@
     </row>
     <row r="20" spans="1:7" ht="201.6">
       <c r="A20" s="57" t="s">
-        <v>642</v>
+        <v>632</v>
       </c>
       <c r="B20" s="57" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="C20" s="57" t="s">
-        <v>644</v>
+        <v>634</v>
       </c>
       <c r="D20" s="57" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
       <c r="E20" s="57" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
       <c r="F20" s="57" t="s">
-        <v>647</v>
+        <v>637</v>
       </c>
       <c r="G20" s="67" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="54" t="s">
-        <v>649</v>
+        <v>639</v>
       </c>
       <c r="B21" s="56"/>
       <c r="C21" s="56"/>
@@ -18971,19 +20257,19 @@
         <v>358</v>
       </c>
       <c r="B22" s="57" t="s">
-        <v>650</v>
+        <v>640</v>
       </c>
       <c r="C22" s="57" t="s">
-        <v>651</v>
+        <v>641</v>
       </c>
       <c r="D22" s="57" t="s">
-        <v>652</v>
+        <v>642</v>
       </c>
       <c r="E22" s="57" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="F22" s="57" t="s">
-        <v>654</v>
+        <v>644</v>
       </c>
       <c r="G22" s="67" t="s">
         <v>276</v>
@@ -19002,7 +20288,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1CE5012-6BDF-4D83-9304-D3C1725959C1}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -19043,17 +20329,17 @@
   <sheetData>
     <row r="2" spans="1:8">
       <c r="A2" s="54" t="s">
-        <v>655</v>
+        <v>645</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="54" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="54" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -19078,7 +20364,7 @@
         <v>270</v>
       </c>
       <c r="G8" t="s">
-        <v>557</v>
+        <v>547</v>
       </c>
       <c r="H8" t="s">
         <v>273</v>
@@ -19086,33 +20372,33 @@
     </row>
     <row r="9" spans="1:8" s="56" customFormat="1">
       <c r="A9" s="54" t="s">
-        <v>655</v>
+        <v>645</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="56" customFormat="1" ht="409.6">
       <c r="A10" s="57" t="s">
-        <v>656</v>
+        <v>646</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>657</v>
+        <v>647</v>
       </c>
       <c r="C10" s="57" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
       <c r="D10" s="57" t="s">
-        <v>692</v>
+        <v>682</v>
       </c>
       <c r="E10" s="57" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="F10" s="57" t="s">
-        <v>691</v>
+        <v>681</v>
       </c>
       <c r="G10" s="57" t="s">
-        <v>659</v>
+        <v>649</v>
       </c>
       <c r="H10" s="58" t="s">
-        <v>660</v>
+        <v>650</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="56" customFormat="1" ht="129.6">
@@ -19120,10 +20406,10 @@
       <c r="B11" s="57"/>
       <c r="C11" s="57"/>
       <c r="D11" s="57" t="s">
-        <v>693</v>
+        <v>683</v>
       </c>
       <c r="E11" s="57" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="F11" s="57"/>
       <c r="G11" s="57"/>
@@ -19134,7 +20420,7 @@
       <c r="B12" s="57"/>
       <c r="C12" s="57"/>
       <c r="D12" s="68" t="s">
-        <v>696</v>
+        <v>686</v>
       </c>
       <c r="E12" s="57"/>
       <c r="F12" s="57"/>
@@ -19153,110 +20439,110 @@
     </row>
     <row r="14" spans="1:8" s="56" customFormat="1" ht="216">
       <c r="A14" s="57" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="B14" s="57" t="s">
-        <v>662</v>
+        <v>652</v>
       </c>
       <c r="C14" s="57" t="s">
-        <v>663</v>
+        <v>653</v>
       </c>
       <c r="D14" s="57" t="s">
-        <v>664</v>
+        <v>654</v>
       </c>
       <c r="E14" s="57"/>
       <c r="F14" s="57" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
       <c r="G14" s="57" t="s">
-        <v>666</v>
+        <v>656</v>
       </c>
       <c r="H14" s="58" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="56" customFormat="1">
       <c r="A15" s="54" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
       <c r="G15" s="57"/>
     </row>
     <row r="16" spans="1:8" s="56" customFormat="1" ht="244.8">
       <c r="A16" s="57" t="s">
-        <v>669</v>
+        <v>659</v>
       </c>
       <c r="B16" s="57" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="C16" s="57" t="s">
-        <v>671</v>
+        <v>661</v>
       </c>
       <c r="D16" s="57" t="s">
-        <v>672</v>
+        <v>662</v>
       </c>
       <c r="E16" s="57"/>
       <c r="F16" s="57" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="G16" s="57" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="H16" s="58" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="56" customFormat="1" ht="201.6">
       <c r="A17" s="57" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="B17" s="57" t="s">
-        <v>677</v>
+        <v>667</v>
       </c>
       <c r="C17" s="57" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="D17" s="57" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="E17" s="57"/>
       <c r="F17" s="57" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="G17" s="57" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="H17" s="58" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="56" customFormat="1">
       <c r="A18" s="54" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="G18" s="57"/>
     </row>
     <row r="19" spans="1:8" s="56" customFormat="1" ht="216">
       <c r="A19" s="57" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="B19" s="57" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="C19" s="57" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D19" s="57" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
       <c r="E19" s="57"/>
       <c r="F19" s="57" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="G19" s="57" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="H19" s="58" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
     </row>
   </sheetData>
@@ -19272,7 +20558,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2A651A-02D2-4C6D-91FC-2CBD73190D44}">
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
@@ -19533,7 +20819,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1120C29B-A224-406A-9A85-6A1751B09B3B}">
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
@@ -19759,1809 +21045,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7BEB5B2-92F5-4415-BAF1-6F4428F63827}">
-  <sheetPr codeName="Лист1">
-    <tabColor rgb="FF00B0F0"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A2:V80"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="36" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="81.109375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.33203125" style="7" customWidth="1"/>
-    <col min="6" max="6" width="43.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="64.44140625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="7.88671875" style="7" customWidth="1"/>
-    <col min="11" max="11" width="39.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="72.5546875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7.88671875" style="7" customWidth="1"/>
-    <col min="16" max="16" width="56.88671875" style="2" customWidth="1"/>
-    <col min="17" max="17" width="46.6640625" style="2" customWidth="1"/>
-    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
-    <col min="19" max="19" width="49.109375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="8.6640625" style="8"/>
-    <col min="21" max="21" width="67.6640625" style="2" customWidth="1"/>
-    <col min="22" max="22" width="68.44140625" style="1" customWidth="1"/>
-    <col min="23" max="24" width="59.44140625" style="1" customWidth="1"/>
-    <col min="25" max="25" width="59.5546875" style="1" customWidth="1"/>
-    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="41.33203125" style="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.6640625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:22">
-      <c r="A2" s="10" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22">
-      <c r="A3" s="23" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22">
-      <c r="A4" s="10" t="s">
-        <v>822</v>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="D4" s="96" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22">
-      <c r="A5" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="D5" s="96" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" ht="28.8">
-      <c r="A6" s="98" t="s">
-        <v>848</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="D6" s="96"/>
-    </row>
-    <row r="7" spans="1:22">
-      <c r="A7" s="10" t="s">
-        <v>864</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="D7" s="96"/>
-    </row>
-    <row r="8" spans="1:22">
-      <c r="A8" s="10" t="s">
-        <v>865</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="D8" s="96"/>
-    </row>
-    <row r="9" spans="1:22">
-      <c r="A9" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22">
-      <c r="A10" s="10" t="s">
-        <v>819</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>820</v>
-      </c>
-      <c r="D10" s="96" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22">
-      <c r="A11" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22">
-      <c r="A12" s="10" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22">
-      <c r="A13" s="2"/>
-    </row>
-    <row r="14" spans="1:22">
-      <c r="A14" s="3"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="5"/>
-      <c r="S14" s="5"/>
-      <c r="U14" s="5"/>
-    </row>
-    <row r="15" spans="1:22">
-      <c r="C15" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="P15" s="1"/>
-      <c r="U15" s="1"/>
-      <c r="V15" s="2"/>
-    </row>
-    <row r="16" spans="1:22">
-      <c r="A16" s="10" t="s">
-        <v>823</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="P16" s="1"/>
-      <c r="U16" s="1"/>
-      <c r="V16" s="2"/>
-    </row>
-    <row r="17" spans="1:22" ht="86.4">
-      <c r="A17" s="2"/>
-      <c r="B17" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="C17" s="76" t="s">
-        <v>821</v>
-      </c>
-      <c r="P17" s="1"/>
-      <c r="U17" s="1"/>
-      <c r="V17" s="2"/>
-    </row>
-    <row r="18" spans="1:22" s="7" customFormat="1">
-      <c r="A18" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="1"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="P18" s="2"/>
-      <c r="Q18" s="2"/>
-      <c r="R18" s="2"/>
-      <c r="S18" s="1"/>
-      <c r="T18" s="8"/>
-      <c r="U18" s="2"/>
-      <c r="V18" s="1"/>
-    </row>
-    <row r="19" spans="1:22" s="7" customFormat="1">
-      <c r="A19" s="1"/>
-      <c r="B19" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="D19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="1"/>
-      <c r="T19" s="8"/>
-      <c r="U19" s="2"/>
-      <c r="V19" s="1"/>
-    </row>
-    <row r="20" spans="1:22" s="7" customFormat="1">
-      <c r="A20" s="1"/>
-      <c r="B20" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="2"/>
-      <c r="R20" s="2"/>
-      <c r="S20" s="1"/>
-      <c r="T20" s="8"/>
-      <c r="U20" s="2"/>
-      <c r="V20" s="1"/>
-    </row>
-    <row r="21" spans="1:22" s="7" customFormat="1">
-      <c r="A21" s="10" t="s">
-        <v>822</v>
-      </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="1"/>
-      <c r="T21" s="8"/>
-      <c r="U21" s="2"/>
-      <c r="V21" s="1"/>
-    </row>
-    <row r="22" spans="1:22" s="7" customFormat="1" ht="144">
-      <c r="A22" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="B22" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="C22" s="76" t="s">
-        <v>826</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F22" s="1"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="P22" s="2"/>
-      <c r="Q22" s="2"/>
-      <c r="R22" s="2"/>
-      <c r="S22" s="1"/>
-      <c r="T22" s="8"/>
-      <c r="U22" s="2"/>
-      <c r="V22" s="1"/>
-    </row>
-    <row r="23" spans="1:22" s="7" customFormat="1" ht="100.8">
-      <c r="A23" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="B23" s="33" t="s">
-        <v>251</v>
-      </c>
-      <c r="C23" s="39" t="s">
-        <v>825</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F23" s="1"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="P23" s="2"/>
-      <c r="Q23" s="2"/>
-      <c r="R23" s="2"/>
-      <c r="S23" s="1"/>
-      <c r="T23" s="8"/>
-      <c r="U23" s="2"/>
-      <c r="V23" s="1"/>
-    </row>
-    <row r="24" spans="1:22" s="7" customFormat="1">
-      <c r="A24" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F24" s="1"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
-      <c r="R24" s="2"/>
-      <c r="S24" s="1"/>
-      <c r="T24" s="8"/>
-      <c r="U24" s="2"/>
-      <c r="V24" s="1"/>
-    </row>
-    <row r="25" spans="1:22" s="7" customFormat="1" ht="115.2">
-      <c r="A25" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B25" s="76" t="s">
-        <v>824</v>
-      </c>
-      <c r="C25" s="33" t="s">
-        <v>264</v>
-      </c>
-      <c r="D25" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="F25" s="1"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="P25" s="2"/>
-      <c r="Q25" s="2"/>
-      <c r="R25" s="2"/>
-      <c r="S25" s="1"/>
-      <c r="T25" s="8"/>
-      <c r="U25" s="2"/>
-      <c r="V25" s="1"/>
-    </row>
-    <row r="26" spans="1:22" s="7" customFormat="1" ht="72">
-      <c r="A26" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B26" s="33" t="s">
-        <v>265</v>
-      </c>
-      <c r="C26" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="D26" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="F26" s="1"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="P26" s="2"/>
-      <c r="Q26" s="2"/>
-      <c r="R26" s="2"/>
-      <c r="S26" s="1"/>
-      <c r="T26" s="8"/>
-      <c r="U26" s="2"/>
-      <c r="V26" s="1"/>
-    </row>
-    <row r="27" spans="1:22" s="7" customFormat="1">
-      <c r="A27" s="1" t="s">
-        <v>829</v>
-      </c>
-      <c r="B27" s="76" t="s">
-        <v>831</v>
-      </c>
-      <c r="C27" s="76" t="s">
-        <v>834</v>
-      </c>
-      <c r="D27" s="24"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="P27" s="2"/>
-      <c r="Q27" s="2"/>
-      <c r="R27" s="2"/>
-      <c r="S27" s="1"/>
-      <c r="T27" s="8"/>
-      <c r="U27" s="2"/>
-      <c r="V27" s="1"/>
-    </row>
-    <row r="28" spans="1:22" s="7" customFormat="1">
-      <c r="A28" s="1" t="s">
-        <v>830</v>
-      </c>
-      <c r="B28" s="76" t="s">
-        <v>832</v>
-      </c>
-      <c r="C28" s="76" t="s">
-        <v>833</v>
-      </c>
-      <c r="D28" s="24"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="P28" s="2"/>
-      <c r="Q28" s="2"/>
-      <c r="R28" s="2"/>
-      <c r="S28" s="1"/>
-      <c r="T28" s="8"/>
-      <c r="U28" s="2"/>
-      <c r="V28" s="1"/>
-    </row>
-    <row r="29" spans="1:22" s="7" customFormat="1">
-      <c r="A29" s="1" t="s">
-        <v>835</v>
-      </c>
-      <c r="B29" s="76" t="s">
-        <v>836</v>
-      </c>
-      <c r="C29" s="76" t="s">
-        <v>837</v>
-      </c>
-      <c r="D29" s="24"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="P29" s="2"/>
-      <c r="Q29" s="2"/>
-      <c r="R29" s="2"/>
-      <c r="S29" s="1"/>
-      <c r="T29" s="8"/>
-      <c r="U29" s="2"/>
-      <c r="V29" s="1"/>
-    </row>
-    <row r="30" spans="1:22" s="7" customFormat="1">
-      <c r="A30" s="98" t="s">
-        <v>838</v>
-      </c>
-      <c r="B30" s="76"/>
-      <c r="C30" s="76"/>
-      <c r="D30" s="24"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="P30" s="2"/>
-      <c r="Q30" s="2"/>
-      <c r="R30" s="2"/>
-      <c r="S30" s="1"/>
-      <c r="T30" s="8"/>
-      <c r="U30" s="2"/>
-      <c r="V30" s="1"/>
-    </row>
-    <row r="31" spans="1:22" s="7" customFormat="1" ht="172.8">
-      <c r="A31" s="101" t="s">
-        <v>847</v>
-      </c>
-      <c r="B31" s="76" t="s">
-        <v>841</v>
-      </c>
-      <c r="C31" s="76" t="s">
-        <v>839</v>
-      </c>
-      <c r="D31" s="76" t="s">
-        <v>840</v>
-      </c>
-      <c r="F31" s="1"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="P31" s="2"/>
-      <c r="Q31" s="2"/>
-      <c r="R31" s="2"/>
-      <c r="S31" s="1"/>
-      <c r="T31" s="8"/>
-      <c r="U31" s="2"/>
-      <c r="V31" s="1"/>
-    </row>
-    <row r="32" spans="1:22" s="7" customFormat="1">
-      <c r="A32" s="102" t="s">
-        <v>849</v>
-      </c>
-      <c r="B32" s="76"/>
-      <c r="C32" s="76" t="s">
-        <v>854</v>
-      </c>
-      <c r="D32" s="76"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="P32" s="2"/>
-      <c r="Q32" s="2"/>
-      <c r="R32" s="2"/>
-      <c r="S32" s="1"/>
-      <c r="T32" s="8"/>
-      <c r="U32" s="2"/>
-      <c r="V32" s="1"/>
-    </row>
-    <row r="33" spans="1:22" s="7" customFormat="1">
-      <c r="A33" s="102" t="s">
-        <v>850</v>
-      </c>
-      <c r="B33" s="76"/>
-      <c r="C33" s="76" t="s">
-        <v>853</v>
-      </c>
-      <c r="D33" s="76"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="P33" s="2"/>
-      <c r="Q33" s="2"/>
-      <c r="R33" s="2"/>
-      <c r="S33" s="1"/>
-      <c r="T33" s="8"/>
-      <c r="U33" s="2"/>
-      <c r="V33" s="1"/>
-    </row>
-    <row r="34" spans="1:22" s="7" customFormat="1" ht="158.4">
-      <c r="A34" s="102" t="s">
-        <v>851</v>
-      </c>
-      <c r="B34" s="102" t="s">
-        <v>855</v>
-      </c>
-      <c r="C34" s="76" t="s">
-        <v>852</v>
-      </c>
-      <c r="D34" s="76"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="P34" s="2"/>
-      <c r="Q34" s="2"/>
-      <c r="R34" s="2"/>
-      <c r="S34" s="1"/>
-      <c r="T34" s="8"/>
-      <c r="U34" s="2"/>
-      <c r="V34" s="1"/>
-    </row>
-    <row r="35" spans="1:22" s="7" customFormat="1" ht="158.4">
-      <c r="A35" s="100" t="s">
-        <v>843</v>
-      </c>
-      <c r="B35" s="76" t="s">
-        <v>845</v>
-      </c>
-      <c r="C35" s="76" t="s">
-        <v>846</v>
-      </c>
-      <c r="D35" s="76"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="P35" s="2"/>
-      <c r="Q35" s="2"/>
-      <c r="R35" s="2"/>
-      <c r="S35" s="1"/>
-      <c r="T35" s="8"/>
-      <c r="U35" s="2"/>
-      <c r="V35" s="1"/>
-    </row>
-    <row r="36" spans="1:22" s="7" customFormat="1">
-      <c r="A36" s="10" t="s">
-        <v>863</v>
-      </c>
-      <c r="B36" s="76"/>
-      <c r="C36" s="76"/>
-      <c r="D36" s="76"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
-      <c r="P36" s="2"/>
-      <c r="Q36" s="2"/>
-      <c r="R36" s="2"/>
-      <c r="S36" s="1"/>
-      <c r="T36" s="8"/>
-      <c r="U36" s="2"/>
-      <c r="V36" s="1"/>
-    </row>
-    <row r="37" spans="1:22" s="7" customFormat="1" ht="244.8">
-      <c r="A37" s="76" t="s">
-        <v>858</v>
-      </c>
-      <c r="B37" s="76" t="s">
-        <v>857</v>
-      </c>
-      <c r="C37" s="76" t="s">
-        <v>856</v>
-      </c>
-      <c r="D37" s="76"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="P37" s="2"/>
-      <c r="Q37" s="2"/>
-      <c r="R37" s="2"/>
-      <c r="S37" s="1"/>
-      <c r="T37" s="8"/>
-      <c r="U37" s="2"/>
-      <c r="V37" s="1"/>
-    </row>
-    <row r="38" spans="1:22" s="7" customFormat="1">
-      <c r="A38" s="10" t="s">
-        <v>859</v>
-      </c>
-      <c r="B38" s="76"/>
-      <c r="C38" s="76" t="s">
-        <v>867</v>
-      </c>
-      <c r="D38" s="76" t="s">
-        <v>866</v>
-      </c>
-      <c r="F38" s="1"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-      <c r="P38" s="2"/>
-      <c r="Q38" s="2"/>
-      <c r="R38" s="2"/>
-      <c r="S38" s="1"/>
-      <c r="T38" s="8"/>
-      <c r="U38" s="2"/>
-      <c r="V38" s="1"/>
-    </row>
-    <row r="39" spans="1:22" s="7" customFormat="1" ht="302.39999999999998">
-      <c r="A39" s="100"/>
-      <c r="B39" s="76" t="s">
-        <v>860</v>
-      </c>
-      <c r="C39" s="76" t="s">
-        <v>861</v>
-      </c>
-      <c r="D39" s="76" t="s">
-        <v>862</v>
-      </c>
-      <c r="F39" s="1"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
-      <c r="P39" s="2"/>
-      <c r="Q39" s="2"/>
-      <c r="R39" s="2"/>
-      <c r="S39" s="1"/>
-      <c r="T39" s="8"/>
-      <c r="U39" s="2"/>
-      <c r="V39" s="1"/>
-    </row>
-    <row r="40" spans="1:22" s="7" customFormat="1">
-      <c r="A40" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="12"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F40" s="1"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
-      <c r="P40" s="2"/>
-      <c r="Q40" s="2"/>
-      <c r="R40" s="2"/>
-      <c r="S40" s="1"/>
-      <c r="T40" s="8"/>
-      <c r="U40" s="2"/>
-      <c r="V40" s="1"/>
-    </row>
-    <row r="41" spans="1:22" s="7" customFormat="1" ht="100.8">
-      <c r="A41" s="1"/>
-      <c r="B41" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C41" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D41" s="33" t="s">
-        <v>257</v>
-      </c>
-      <c r="F41" s="1"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="P41" s="2"/>
-      <c r="Q41" s="2"/>
-      <c r="R41" s="2"/>
-      <c r="S41" s="1"/>
-      <c r="T41" s="8"/>
-      <c r="U41" s="2"/>
-      <c r="V41" s="1"/>
-    </row>
-    <row r="42" spans="1:22" s="7" customFormat="1" ht="72">
-      <c r="A42" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B42" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="C42" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F42" s="1"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
-      <c r="P42" s="2"/>
-      <c r="Q42" s="2"/>
-      <c r="R42" s="2"/>
-      <c r="S42" s="1"/>
-      <c r="T42" s="8"/>
-      <c r="U42" s="2"/>
-      <c r="V42" s="1"/>
-    </row>
-    <row r="43" spans="1:22" s="7" customFormat="1" ht="172.8">
-      <c r="A43" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B43" s="13"/>
-      <c r="C43" s="33" t="s">
-        <v>253</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F43" s="1"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-      <c r="P43" s="2"/>
-      <c r="Q43" s="2"/>
-      <c r="R43" s="2"/>
-      <c r="S43" s="1"/>
-      <c r="T43" s="8"/>
-      <c r="U43" s="2"/>
-      <c r="V43" s="1"/>
-    </row>
-    <row r="44" spans="1:22" s="7" customFormat="1">
-      <c r="A44" s="10" t="s">
-        <v>819</v>
-      </c>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="F44" s="1"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="P44" s="2"/>
-      <c r="Q44" s="2"/>
-      <c r="R44" s="2"/>
-      <c r="S44" s="1"/>
-      <c r="T44" s="8"/>
-      <c r="U44" s="2"/>
-      <c r="V44" s="1"/>
-    </row>
-    <row r="45" spans="1:22" s="7" customFormat="1">
-      <c r="A45" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="B45" s="12"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="1"/>
-      <c r="N45" s="1"/>
-      <c r="P45" s="2"/>
-      <c r="Q45" s="2"/>
-      <c r="R45" s="2"/>
-      <c r="S45" s="1"/>
-      <c r="T45" s="8"/>
-      <c r="U45" s="2"/>
-      <c r="V45" s="1"/>
-    </row>
-    <row r="46" spans="1:22" s="7" customFormat="1" ht="86.4">
-      <c r="A46" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B46" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="C46" s="33" t="s">
-        <v>252</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F46" s="1"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
-      <c r="N46" s="1"/>
-      <c r="P46" s="2"/>
-      <c r="Q46" s="2"/>
-      <c r="R46" s="2"/>
-      <c r="S46" s="1"/>
-      <c r="T46" s="8"/>
-      <c r="U46" s="2"/>
-      <c r="V46" s="1"/>
-    </row>
-    <row r="47" spans="1:22" s="7" customFormat="1">
-      <c r="A47" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-      <c r="M47" s="1"/>
-      <c r="N47" s="1"/>
-      <c r="P47" s="2"/>
-      <c r="Q47" s="2"/>
-      <c r="R47" s="2"/>
-      <c r="S47" s="1"/>
-      <c r="T47" s="8"/>
-      <c r="U47" s="2"/>
-      <c r="V47" s="1"/>
-    </row>
-    <row r="48" spans="1:22" s="7" customFormat="1" ht="72">
-      <c r="A48" s="2"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F48" s="1"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
-      <c r="N48" s="1"/>
-      <c r="P48" s="2"/>
-      <c r="Q48" s="2"/>
-      <c r="R48" s="2"/>
-      <c r="S48" s="1"/>
-      <c r="T48" s="8"/>
-      <c r="U48" s="2"/>
-      <c r="V48" s="1"/>
-    </row>
-    <row r="49" spans="1:22" s="7" customFormat="1">
-      <c r="A49" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F49" s="1"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="K49" s="1"/>
-      <c r="L49" s="1"/>
-      <c r="M49" s="1"/>
-      <c r="N49" s="1"/>
-      <c r="P49" s="2"/>
-      <c r="Q49" s="2"/>
-      <c r="R49" s="2"/>
-      <c r="S49" s="1"/>
-      <c r="T49" s="8"/>
-      <c r="U49" s="2"/>
-      <c r="V49" s="1"/>
-    </row>
-    <row r="50" spans="1:22" s="7" customFormat="1" ht="86.4">
-      <c r="A50" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C50" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="D50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="1"/>
-      <c r="M50" s="1"/>
-      <c r="N50" s="1"/>
-      <c r="P50" s="2"/>
-      <c r="Q50" s="2"/>
-      <c r="R50" s="2"/>
-      <c r="S50" s="1"/>
-      <c r="T50" s="8"/>
-      <c r="U50" s="2"/>
-      <c r="V50" s="1"/>
-    </row>
-    <row r="51" spans="1:22" s="7" customFormat="1" ht="86.4">
-      <c r="A51" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C51" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="D51" s="2"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="K51" s="1"/>
-      <c r="L51" s="1"/>
-      <c r="M51" s="1"/>
-      <c r="N51" s="1"/>
-      <c r="P51" s="2"/>
-      <c r="Q51" s="2"/>
-      <c r="R51" s="2"/>
-      <c r="S51" s="1"/>
-      <c r="T51" s="8"/>
-      <c r="U51" s="2"/>
-      <c r="V51" s="1"/>
-    </row>
-    <row r="52" spans="1:22" s="7" customFormat="1" ht="86.4">
-      <c r="A52" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B52" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="C52" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F52" s="1"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
-      <c r="M52" s="1"/>
-      <c r="N52" s="1"/>
-      <c r="P52" s="2"/>
-      <c r="Q52" s="2"/>
-      <c r="R52" s="2"/>
-      <c r="S52" s="1"/>
-      <c r="T52" s="8"/>
-      <c r="U52" s="2"/>
-      <c r="V52" s="1"/>
-    </row>
-    <row r="53" spans="1:22" s="7" customFormat="1" ht="115.2">
-      <c r="A53" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C53" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F53" s="1"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
-      <c r="K53" s="1"/>
-      <c r="L53" s="1"/>
-      <c r="M53" s="1"/>
-      <c r="N53" s="1"/>
-      <c r="P53" s="2"/>
-      <c r="Q53" s="2"/>
-      <c r="R53" s="2"/>
-      <c r="S53" s="1"/>
-      <c r="T53" s="8"/>
-      <c r="U53" s="2"/>
-      <c r="V53" s="1"/>
-    </row>
-    <row r="54" spans="1:22" s="7" customFormat="1" ht="28.8">
-      <c r="A54" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C54" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="D54" s="1"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="1"/>
-      <c r="M54" s="1"/>
-      <c r="N54" s="1"/>
-      <c r="P54" s="2"/>
-      <c r="Q54" s="2"/>
-      <c r="R54" s="2"/>
-      <c r="S54" s="1"/>
-      <c r="T54" s="8"/>
-      <c r="U54" s="2"/>
-      <c r="V54" s="1"/>
-    </row>
-    <row r="55" spans="1:22" s="7" customFormat="1" ht="100.8">
-      <c r="A55" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C55" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="D55" s="96" t="s">
-        <v>827</v>
-      </c>
-      <c r="F55" s="1"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
-      <c r="K55" s="1"/>
-      <c r="L55" s="1"/>
-      <c r="M55" s="1"/>
-      <c r="N55" s="1"/>
-      <c r="P55" s="2"/>
-      <c r="Q55" s="2"/>
-      <c r="R55" s="2"/>
-      <c r="S55" s="1"/>
-      <c r="T55" s="8"/>
-      <c r="U55" s="2"/>
-      <c r="V55" s="1"/>
-    </row>
-    <row r="56" spans="1:22" s="7" customFormat="1" ht="86.4">
-      <c r="A56" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C56" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="D56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="2"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
-      <c r="K56" s="1"/>
-      <c r="L56" s="1"/>
-      <c r="M56" s="1"/>
-      <c r="N56" s="1"/>
-      <c r="P56" s="2"/>
-      <c r="Q56" s="2"/>
-      <c r="R56" s="2"/>
-      <c r="S56" s="1"/>
-      <c r="T56" s="8"/>
-      <c r="U56" s="2"/>
-      <c r="V56" s="1"/>
-    </row>
-    <row r="57" spans="1:22" s="7" customFormat="1" ht="57.6">
-      <c r="A57" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C57" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="D57" s="1"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="K57" s="1"/>
-      <c r="L57" s="1"/>
-      <c r="M57" s="1"/>
-      <c r="N57" s="1"/>
-      <c r="P57" s="2"/>
-      <c r="Q57" s="2"/>
-      <c r="R57" s="2"/>
-      <c r="S57" s="1"/>
-      <c r="T57" s="8"/>
-      <c r="U57" s="2"/>
-      <c r="V57" s="1"/>
-    </row>
-    <row r="58" spans="1:22" s="7" customFormat="1">
-      <c r="A58" s="10" t="s">
-        <v>820</v>
-      </c>
-      <c r="B58" s="12"/>
-      <c r="C58" s="13"/>
-      <c r="D58" s="2"/>
-      <c r="F58" s="1"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="K58" s="1"/>
-      <c r="L58" s="1"/>
-      <c r="M58" s="1"/>
-      <c r="N58" s="1"/>
-      <c r="P58" s="2"/>
-      <c r="Q58" s="2"/>
-      <c r="R58" s="2"/>
-      <c r="S58" s="1"/>
-      <c r="T58" s="8"/>
-      <c r="U58" s="2"/>
-      <c r="V58" s="1"/>
-    </row>
-    <row r="59" spans="1:22" s="7" customFormat="1" ht="100.8">
-      <c r="A59" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="B59" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="C59" s="33" t="s">
-        <v>254</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="F59" s="1"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
-      <c r="K59" s="1"/>
-      <c r="L59" s="1"/>
-      <c r="M59" s="1"/>
-      <c r="N59" s="1"/>
-      <c r="P59" s="2"/>
-      <c r="Q59" s="2"/>
-      <c r="R59" s="2"/>
-      <c r="S59" s="1"/>
-      <c r="T59" s="8"/>
-      <c r="U59" s="2"/>
-      <c r="V59" s="1"/>
-    </row>
-    <row r="60" spans="1:22" s="7" customFormat="1" ht="100.8">
-      <c r="A60" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B60" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C60" s="33" t="s">
-        <v>255</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="F60" s="1"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="1"/>
-      <c r="K60" s="1"/>
-      <c r="L60" s="1"/>
-      <c r="M60" s="1"/>
-      <c r="N60" s="1"/>
-      <c r="P60" s="2"/>
-      <c r="Q60" s="2"/>
-      <c r="R60" s="2"/>
-      <c r="S60" s="1"/>
-      <c r="T60" s="8"/>
-      <c r="U60" s="2"/>
-      <c r="V60" s="1"/>
-    </row>
-    <row r="61" spans="1:22" s="7" customFormat="1" ht="86.4">
-      <c r="A61" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="B61" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="C61" s="33" t="s">
-        <v>256</v>
-      </c>
-      <c r="D61" s="1"/>
-      <c r="F61" s="1"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-      <c r="K61" s="1"/>
-      <c r="L61" s="1"/>
-      <c r="M61" s="1"/>
-      <c r="N61" s="1"/>
-      <c r="P61" s="2"/>
-      <c r="Q61" s="2"/>
-      <c r="R61" s="2"/>
-      <c r="S61" s="1"/>
-      <c r="T61" s="8"/>
-      <c r="U61" s="2"/>
-      <c r="V61" s="1"/>
-    </row>
-    <row r="62" spans="1:22" s="7" customFormat="1">
-      <c r="A62" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="B62" s="2"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="F62" s="1"/>
-      <c r="G62" s="2"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="K62" s="1"/>
-      <c r="L62" s="1"/>
-      <c r="M62" s="1"/>
-      <c r="N62" s="1"/>
-      <c r="P62" s="2"/>
-      <c r="Q62" s="2"/>
-      <c r="R62" s="2"/>
-      <c r="S62" s="1"/>
-      <c r="T62" s="8"/>
-      <c r="U62" s="2"/>
-      <c r="V62" s="1"/>
-    </row>
-    <row r="63" spans="1:22" s="7" customFormat="1">
-      <c r="A63" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B63" s="2"/>
-      <c r="C63" s="9"/>
-      <c r="D63" s="2"/>
-      <c r="F63" s="1"/>
-      <c r="G63" s="2"/>
-      <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
-      <c r="K63" s="1"/>
-      <c r="L63" s="1"/>
-      <c r="M63" s="1"/>
-      <c r="N63" s="1"/>
-      <c r="P63" s="2"/>
-      <c r="Q63" s="2"/>
-      <c r="R63" s="2"/>
-      <c r="S63" s="1"/>
-      <c r="T63" s="8"/>
-      <c r="U63" s="2"/>
-      <c r="V63" s="1"/>
-    </row>
-    <row r="64" spans="1:22" s="7" customFormat="1">
-      <c r="A64" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B64" s="2"/>
-      <c r="C64" s="9"/>
-      <c r="D64" s="1"/>
-      <c r="F64" s="1"/>
-      <c r="G64" s="2"/>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
-      <c r="K64" s="1"/>
-      <c r="L64" s="1"/>
-      <c r="M64" s="1"/>
-      <c r="N64" s="1"/>
-      <c r="P64" s="2"/>
-      <c r="Q64" s="2"/>
-      <c r="R64" s="2"/>
-      <c r="S64" s="1"/>
-      <c r="T64" s="8"/>
-      <c r="U64" s="2"/>
-      <c r="V64" s="1"/>
-    </row>
-    <row r="65" spans="1:22" s="7" customFormat="1">
-      <c r="A65" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C65" s="9"/>
-      <c r="D65" s="1"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-      <c r="K65" s="1"/>
-      <c r="L65" s="1"/>
-      <c r="M65" s="1"/>
-      <c r="N65" s="1"/>
-      <c r="P65" s="2"/>
-      <c r="Q65" s="2"/>
-      <c r="R65" s="2"/>
-      <c r="S65" s="1"/>
-      <c r="T65" s="8"/>
-      <c r="U65" s="2"/>
-      <c r="V65" s="1"/>
-    </row>
-    <row r="66" spans="1:22" s="7" customFormat="1">
-      <c r="A66" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B66" s="2"/>
-      <c r="C66" s="9"/>
-      <c r="D66" s="1"/>
-      <c r="F66" s="1"/>
-      <c r="G66" s="2"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
-      <c r="K66" s="1"/>
-      <c r="L66" s="1"/>
-      <c r="M66" s="1"/>
-      <c r="N66" s="1"/>
-      <c r="P66" s="2"/>
-      <c r="Q66" s="2"/>
-      <c r="R66" s="2"/>
-      <c r="S66" s="1"/>
-      <c r="T66" s="8"/>
-      <c r="U66" s="2"/>
-      <c r="V66" s="1"/>
-    </row>
-    <row r="67" spans="1:22" s="7" customFormat="1">
-      <c r="A67" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B67" s="2"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="1"/>
-      <c r="F67" s="1"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
-      <c r="K67" s="1"/>
-      <c r="L67" s="1"/>
-      <c r="M67" s="1"/>
-      <c r="N67" s="1"/>
-      <c r="P67" s="2"/>
-      <c r="Q67" s="2"/>
-      <c r="R67" s="2"/>
-      <c r="S67" s="1"/>
-      <c r="T67" s="8"/>
-      <c r="U67" s="2"/>
-      <c r="V67" s="1"/>
-    </row>
-    <row r="68" spans="1:22" s="7" customFormat="1">
-      <c r="A68" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B68" s="2"/>
-      <c r="C68" s="9"/>
-      <c r="D68" s="1"/>
-      <c r="F68" s="1"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-      <c r="K68" s="1"/>
-      <c r="L68" s="1"/>
-      <c r="M68" s="1"/>
-      <c r="N68" s="1"/>
-      <c r="P68" s="2"/>
-      <c r="Q68" s="2"/>
-      <c r="R68" s="2"/>
-      <c r="S68" s="1"/>
-      <c r="T68" s="8"/>
-      <c r="U68" s="2"/>
-      <c r="V68" s="1"/>
-    </row>
-    <row r="69" spans="1:22" s="7" customFormat="1">
-      <c r="A69" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B69" s="2"/>
-      <c r="C69" s="9"/>
-      <c r="D69" s="1"/>
-      <c r="F69" s="1"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="K69" s="1"/>
-      <c r="L69" s="1"/>
-      <c r="M69" s="1"/>
-      <c r="N69" s="1"/>
-      <c r="P69" s="2"/>
-      <c r="Q69" s="2"/>
-      <c r="R69" s="2"/>
-      <c r="S69" s="1"/>
-      <c r="T69" s="8"/>
-      <c r="U69" s="2"/>
-      <c r="V69" s="1"/>
-    </row>
-    <row r="70" spans="1:22" s="7" customFormat="1">
-      <c r="A70" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="B70" s="2"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="1"/>
-      <c r="F70" s="1"/>
-      <c r="G70" s="2"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="K70" s="1"/>
-      <c r="L70" s="1"/>
-      <c r="M70" s="1"/>
-      <c r="N70" s="1"/>
-      <c r="P70" s="2"/>
-      <c r="Q70" s="2"/>
-      <c r="R70" s="2"/>
-      <c r="S70" s="1"/>
-      <c r="T70" s="8"/>
-      <c r="U70" s="2"/>
-      <c r="V70" s="1"/>
-    </row>
-    <row r="71" spans="1:22" s="7" customFormat="1">
-      <c r="A71" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B71" s="2"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="1"/>
-      <c r="F71" s="1"/>
-      <c r="G71" s="2"/>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
-      <c r="K71" s="1"/>
-      <c r="L71" s="1"/>
-      <c r="M71" s="1"/>
-      <c r="N71" s="1"/>
-      <c r="P71" s="2"/>
-      <c r="Q71" s="2"/>
-      <c r="R71" s="2"/>
-      <c r="S71" s="1"/>
-      <c r="T71" s="8"/>
-      <c r="U71" s="2"/>
-      <c r="V71" s="1"/>
-    </row>
-    <row r="72" spans="1:22" s="7" customFormat="1" ht="86.4">
-      <c r="A72" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="B72" s="21"/>
-      <c r="C72" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="D72" s="1"/>
-      <c r="F72" s="1"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="1"/>
-      <c r="I72" s="1"/>
-      <c r="K72" s="1"/>
-      <c r="L72" s="1"/>
-      <c r="M72" s="1"/>
-      <c r="N72" s="1"/>
-      <c r="P72" s="2"/>
-      <c r="Q72" s="2"/>
-      <c r="R72" s="2"/>
-      <c r="S72" s="1"/>
-      <c r="T72" s="8"/>
-      <c r="U72" s="2"/>
-      <c r="V72" s="1"/>
-    </row>
-    <row r="73" spans="1:22" s="7" customFormat="1" ht="57.6">
-      <c r="A73" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="B73" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="C73" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="D73" s="21" t="s">
-        <v>162</v>
-      </c>
-      <c r="F73" s="1"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
-      <c r="K73" s="1"/>
-      <c r="L73" s="1"/>
-      <c r="M73" s="1"/>
-      <c r="N73" s="1"/>
-      <c r="P73" s="2"/>
-      <c r="Q73" s="2"/>
-      <c r="R73" s="2"/>
-      <c r="S73" s="1"/>
-      <c r="T73" s="8"/>
-      <c r="U73" s="2"/>
-      <c r="V73" s="1"/>
-    </row>
-    <row r="74" spans="1:22" s="7" customFormat="1" ht="28.8">
-      <c r="A74" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B74" s="21" t="s">
-        <v>166</v>
-      </c>
-      <c r="C74" s="4"/>
-      <c r="D74" s="1"/>
-      <c r="F74" s="1"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
-      <c r="K74" s="1"/>
-      <c r="L74" s="1"/>
-      <c r="M74" s="1"/>
-      <c r="N74" s="1"/>
-      <c r="P74" s="2"/>
-      <c r="Q74" s="2"/>
-      <c r="R74" s="2"/>
-      <c r="S74" s="1"/>
-      <c r="T74" s="8"/>
-      <c r="U74" s="2"/>
-      <c r="V74" s="1"/>
-    </row>
-    <row r="75" spans="1:22" s="7" customFormat="1">
-      <c r="A75" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B75" s="2"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="1"/>
-      <c r="F75" s="1"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="1"/>
-      <c r="I75" s="1"/>
-      <c r="K75" s="1"/>
-      <c r="L75" s="1"/>
-      <c r="M75" s="1"/>
-      <c r="N75" s="1"/>
-      <c r="P75" s="2"/>
-      <c r="Q75" s="2"/>
-      <c r="R75" s="2"/>
-      <c r="S75" s="1"/>
-      <c r="T75" s="8"/>
-      <c r="U75" s="2"/>
-      <c r="V75" s="1"/>
-    </row>
-    <row r="76" spans="1:22" s="7" customFormat="1">
-      <c r="A76" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B76" s="2"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="1"/>
-      <c r="F76" s="1"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="1"/>
-      <c r="I76" s="1"/>
-      <c r="K76" s="1"/>
-      <c r="L76" s="1"/>
-      <c r="M76" s="1"/>
-      <c r="N76" s="1"/>
-      <c r="P76" s="2"/>
-      <c r="Q76" s="2"/>
-      <c r="R76" s="2"/>
-      <c r="S76" s="1"/>
-      <c r="T76" s="8"/>
-      <c r="U76" s="2"/>
-      <c r="V76" s="1"/>
-    </row>
-    <row r="77" spans="1:22" s="7" customFormat="1" ht="28.8">
-      <c r="A77" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B77" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="C77" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="D77" s="1"/>
-      <c r="F77" s="1"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
-      <c r="K77" s="1"/>
-      <c r="L77" s="1"/>
-      <c r="M77" s="1"/>
-      <c r="N77" s="1"/>
-      <c r="P77" s="2"/>
-      <c r="Q77" s="2"/>
-      <c r="R77" s="2"/>
-      <c r="S77" s="1"/>
-      <c r="T77" s="8"/>
-      <c r="U77" s="2"/>
-      <c r="V77" s="1"/>
-    </row>
-    <row r="78" spans="1:22" s="7" customFormat="1">
-      <c r="A78" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C78" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="D78" s="1"/>
-      <c r="F78" s="1"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="1"/>
-      <c r="I78" s="1"/>
-      <c r="K78" s="1"/>
-      <c r="L78" s="1"/>
-      <c r="M78" s="1"/>
-      <c r="N78" s="1"/>
-      <c r="P78" s="2"/>
-      <c r="Q78" s="2"/>
-      <c r="R78" s="2"/>
-      <c r="S78" s="1"/>
-      <c r="T78" s="8"/>
-      <c r="U78" s="2"/>
-      <c r="V78" s="1"/>
-    </row>
-    <row r="79" spans="1:22" s="7" customFormat="1">
-      <c r="A79" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="B79" s="2"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="1"/>
-      <c r="F79" s="1"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="1"/>
-      <c r="I79" s="1"/>
-      <c r="K79" s="1"/>
-      <c r="L79" s="1"/>
-      <c r="M79" s="1"/>
-      <c r="N79" s="1"/>
-      <c r="P79" s="2"/>
-      <c r="Q79" s="2"/>
-      <c r="R79" s="2"/>
-      <c r="S79" s="1"/>
-      <c r="T79" s="8"/>
-      <c r="U79" s="2"/>
-      <c r="V79" s="1"/>
-    </row>
-    <row r="80" spans="1:22" s="7" customFormat="1" ht="144">
-      <c r="A80" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="B80" s="2"/>
-      <c r="C80" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="D80" s="1"/>
-      <c r="F80" s="1"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="1"/>
-      <c r="I80" s="1"/>
-      <c r="K80" s="1"/>
-      <c r="L80" s="1"/>
-      <c r="M80" s="1"/>
-      <c r="N80" s="1"/>
-      <c r="P80" s="2"/>
-      <c r="Q80" s="2"/>
-      <c r="R80" s="2"/>
-      <c r="S80" s="1"/>
-      <c r="T80" s="8"/>
-      <c r="U80" s="2"/>
-      <c r="V80" s="1"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B7CAD42-95E0-4E20-A7EA-DF3B831CFF68}">
   <sheetPr>
@@ -21936,6 +21419,1809 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7BEB5B2-92F5-4415-BAF1-6F4428F63827}">
+  <sheetPr codeName="Лист1">
+    <tabColor rgb="FF00B0F0"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:V80"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="36" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="81.109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="43.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" style="7" customWidth="1"/>
+    <col min="11" max="11" width="39.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.5546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.88671875" style="7" customWidth="1"/>
+    <col min="16" max="16" width="56.88671875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.6640625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.109375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.6640625" style="8"/>
+    <col min="21" max="21" width="67.6640625" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.44140625" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.44140625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.5546875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.33203125" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.6640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:22">
+      <c r="A2" s="10" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22">
+      <c r="A3" s="23" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22">
+      <c r="A4" s="10" t="s">
+        <v>811</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="D4" s="96" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
+      <c r="A5" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="D5" s="96" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="28.8">
+      <c r="A6" s="98" t="s">
+        <v>837</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="D6" s="96"/>
+    </row>
+    <row r="7" spans="1:22">
+      <c r="A7" s="10" t="s">
+        <v>853</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="D7" s="96"/>
+    </row>
+    <row r="8" spans="1:22">
+      <c r="A8" s="10" t="s">
+        <v>854</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="D8" s="96"/>
+    </row>
+    <row r="9" spans="1:22">
+      <c r="A9" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
+      <c r="A10" s="10" t="s">
+        <v>808</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>809</v>
+      </c>
+      <c r="D10" s="96" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22">
+      <c r="A11" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22">
+      <c r="A12" s="10" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22">
+      <c r="A13" s="2"/>
+    </row>
+    <row r="14" spans="1:22">
+      <c r="A14" s="3"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
+      <c r="S14" s="5"/>
+      <c r="U14" s="5"/>
+    </row>
+    <row r="15" spans="1:22">
+      <c r="C15" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P15" s="1"/>
+      <c r="U15" s="1"/>
+      <c r="V15" s="2"/>
+    </row>
+    <row r="16" spans="1:22">
+      <c r="A16" s="10" t="s">
+        <v>812</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="P16" s="1"/>
+      <c r="U16" s="1"/>
+      <c r="V16" s="2"/>
+    </row>
+    <row r="17" spans="1:22" ht="86.4">
+      <c r="A17" s="2"/>
+      <c r="B17" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C17" s="76" t="s">
+        <v>810</v>
+      </c>
+      <c r="P17" s="1"/>
+      <c r="U17" s="1"/>
+      <c r="V17" s="2"/>
+    </row>
+    <row r="18" spans="1:22" s="7" customFormat="1">
+      <c r="A18" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" s="1"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="8"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="1"/>
+    </row>
+    <row r="19" spans="1:22" s="7" customFormat="1">
+      <c r="A19" s="1"/>
+      <c r="B19" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="D19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="8"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="1"/>
+    </row>
+    <row r="20" spans="1:22" s="7" customFormat="1">
+      <c r="A20" s="1"/>
+      <c r="B20" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="8"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="1"/>
+    </row>
+    <row r="21" spans="1:22" s="7" customFormat="1">
+      <c r="A21" s="10" t="s">
+        <v>811</v>
+      </c>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="8"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="1"/>
+    </row>
+    <row r="22" spans="1:22" s="7" customFormat="1" ht="144">
+      <c r="A22" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B22" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="76" t="s">
+        <v>815</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="1"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="8"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="1"/>
+    </row>
+    <row r="23" spans="1:22" s="7" customFormat="1" ht="100.8">
+      <c r="A23" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B23" s="33" t="s">
+        <v>251</v>
+      </c>
+      <c r="C23" s="39" t="s">
+        <v>814</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" s="1"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="1"/>
+      <c r="T23" s="8"/>
+      <c r="U23" s="2"/>
+      <c r="V23" s="1"/>
+    </row>
+    <row r="24" spans="1:22" s="7" customFormat="1">
+      <c r="A24" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F24" s="1"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="8"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="1"/>
+    </row>
+    <row r="25" spans="1:22" s="7" customFormat="1" ht="115.2">
+      <c r="A25" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="76" t="s">
+        <v>813</v>
+      </c>
+      <c r="C25" s="33" t="s">
+        <v>264</v>
+      </c>
+      <c r="D25" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="F25" s="1"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="8"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="1"/>
+    </row>
+    <row r="26" spans="1:22" s="7" customFormat="1" ht="72">
+      <c r="A26" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="33" t="s">
+        <v>265</v>
+      </c>
+      <c r="C26" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F26" s="1"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="8"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="1"/>
+    </row>
+    <row r="27" spans="1:22" s="7" customFormat="1">
+      <c r="A27" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="B27" s="76" t="s">
+        <v>820</v>
+      </c>
+      <c r="C27" s="76" t="s">
+        <v>823</v>
+      </c>
+      <c r="D27" s="24"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="1"/>
+      <c r="T27" s="8"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="1"/>
+    </row>
+    <row r="28" spans="1:22" s="7" customFormat="1">
+      <c r="A28" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="B28" s="76" t="s">
+        <v>821</v>
+      </c>
+      <c r="C28" s="76" t="s">
+        <v>822</v>
+      </c>
+      <c r="D28" s="24"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="8"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="1"/>
+    </row>
+    <row r="29" spans="1:22" s="7" customFormat="1">
+      <c r="A29" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="B29" s="76" t="s">
+        <v>825</v>
+      </c>
+      <c r="C29" s="76" t="s">
+        <v>826</v>
+      </c>
+      <c r="D29" s="24"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="1"/>
+      <c r="T29" s="8"/>
+      <c r="U29" s="2"/>
+      <c r="V29" s="1"/>
+    </row>
+    <row r="30" spans="1:22" s="7" customFormat="1">
+      <c r="A30" s="98" t="s">
+        <v>827</v>
+      </c>
+      <c r="B30" s="76"/>
+      <c r="C30" s="76"/>
+      <c r="D30" s="24"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="1"/>
+      <c r="T30" s="8"/>
+      <c r="U30" s="2"/>
+      <c r="V30" s="1"/>
+    </row>
+    <row r="31" spans="1:22" s="7" customFormat="1" ht="172.8">
+      <c r="A31" s="101" t="s">
+        <v>836</v>
+      </c>
+      <c r="B31" s="76" t="s">
+        <v>830</v>
+      </c>
+      <c r="C31" s="76" t="s">
+        <v>828</v>
+      </c>
+      <c r="D31" s="76" t="s">
+        <v>829</v>
+      </c>
+      <c r="F31" s="1"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="8"/>
+      <c r="U31" s="2"/>
+      <c r="V31" s="1"/>
+    </row>
+    <row r="32" spans="1:22" s="7" customFormat="1">
+      <c r="A32" s="102" t="s">
+        <v>838</v>
+      </c>
+      <c r="B32" s="76"/>
+      <c r="C32" s="76" t="s">
+        <v>843</v>
+      </c>
+      <c r="D32" s="76"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="8"/>
+      <c r="U32" s="2"/>
+      <c r="V32" s="1"/>
+    </row>
+    <row r="33" spans="1:22" s="7" customFormat="1">
+      <c r="A33" s="102" t="s">
+        <v>839</v>
+      </c>
+      <c r="B33" s="76"/>
+      <c r="C33" s="76" t="s">
+        <v>842</v>
+      </c>
+      <c r="D33" s="76"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="8"/>
+      <c r="U33" s="2"/>
+      <c r="V33" s="1"/>
+    </row>
+    <row r="34" spans="1:22" s="7" customFormat="1" ht="158.4">
+      <c r="A34" s="102" t="s">
+        <v>840</v>
+      </c>
+      <c r="B34" s="102" t="s">
+        <v>844</v>
+      </c>
+      <c r="C34" s="76" t="s">
+        <v>841</v>
+      </c>
+      <c r="D34" s="76"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="8"/>
+      <c r="U34" s="2"/>
+      <c r="V34" s="1"/>
+    </row>
+    <row r="35" spans="1:22" s="7" customFormat="1" ht="158.4">
+      <c r="A35" s="100" t="s">
+        <v>832</v>
+      </c>
+      <c r="B35" s="76" t="s">
+        <v>834</v>
+      </c>
+      <c r="C35" s="104" t="s">
+        <v>835</v>
+      </c>
+      <c r="D35" s="76"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="1"/>
+      <c r="T35" s="8"/>
+      <c r="U35" s="2"/>
+      <c r="V35" s="1"/>
+    </row>
+    <row r="36" spans="1:22" s="7" customFormat="1">
+      <c r="A36" s="10" t="s">
+        <v>852</v>
+      </c>
+      <c r="B36" s="76"/>
+      <c r="C36" s="76"/>
+      <c r="D36" s="76"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="1"/>
+      <c r="T36" s="8"/>
+      <c r="U36" s="2"/>
+      <c r="V36" s="1"/>
+    </row>
+    <row r="37" spans="1:22" s="7" customFormat="1" ht="244.8">
+      <c r="A37" s="76" t="s">
+        <v>847</v>
+      </c>
+      <c r="B37" s="76" t="s">
+        <v>846</v>
+      </c>
+      <c r="C37" s="76" t="s">
+        <v>845</v>
+      </c>
+      <c r="D37" s="76"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="2"/>
+      <c r="S37" s="1"/>
+      <c r="T37" s="8"/>
+      <c r="U37" s="2"/>
+      <c r="V37" s="1"/>
+    </row>
+    <row r="38" spans="1:22" s="7" customFormat="1">
+      <c r="A38" s="10" t="s">
+        <v>848</v>
+      </c>
+      <c r="B38" s="76"/>
+      <c r="C38" s="76" t="s">
+        <v>856</v>
+      </c>
+      <c r="D38" s="76" t="s">
+        <v>855</v>
+      </c>
+      <c r="F38" s="1"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="2"/>
+      <c r="S38" s="1"/>
+      <c r="T38" s="8"/>
+      <c r="U38" s="2"/>
+      <c r="V38" s="1"/>
+    </row>
+    <row r="39" spans="1:22" s="7" customFormat="1" ht="302.39999999999998">
+      <c r="A39" s="100"/>
+      <c r="B39" s="76" t="s">
+        <v>849</v>
+      </c>
+      <c r="C39" s="76" t="s">
+        <v>850</v>
+      </c>
+      <c r="D39" s="76" t="s">
+        <v>851</v>
+      </c>
+      <c r="F39" s="1"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="2"/>
+      <c r="R39" s="2"/>
+      <c r="S39" s="1"/>
+      <c r="T39" s="8"/>
+      <c r="U39" s="2"/>
+      <c r="V39" s="1"/>
+    </row>
+    <row r="40" spans="1:22" s="7" customFormat="1">
+      <c r="A40" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="12"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F40" s="1"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2"/>
+      <c r="R40" s="2"/>
+      <c r="S40" s="1"/>
+      <c r="T40" s="8"/>
+      <c r="U40" s="2"/>
+      <c r="V40" s="1"/>
+    </row>
+    <row r="41" spans="1:22" s="7" customFormat="1" ht="100.8">
+      <c r="A41" s="1"/>
+      <c r="B41" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D41" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="F41" s="1"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="P41" s="2"/>
+      <c r="Q41" s="2"/>
+      <c r="R41" s="2"/>
+      <c r="S41" s="1"/>
+      <c r="T41" s="8"/>
+      <c r="U41" s="2"/>
+      <c r="V41" s="1"/>
+    </row>
+    <row r="42" spans="1:22" s="7" customFormat="1" ht="72">
+      <c r="A42" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F42" s="1"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="P42" s="2"/>
+      <c r="Q42" s="2"/>
+      <c r="R42" s="2"/>
+      <c r="S42" s="1"/>
+      <c r="T42" s="8"/>
+      <c r="U42" s="2"/>
+      <c r="V42" s="1"/>
+    </row>
+    <row r="43" spans="1:22" s="7" customFormat="1" ht="172.8">
+      <c r="A43" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" s="13"/>
+      <c r="C43" s="33" t="s">
+        <v>253</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F43" s="1"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+      <c r="P43" s="2"/>
+      <c r="Q43" s="2"/>
+      <c r="R43" s="2"/>
+      <c r="S43" s="1"/>
+      <c r="T43" s="8"/>
+      <c r="U43" s="2"/>
+      <c r="V43" s="1"/>
+    </row>
+    <row r="44" spans="1:22" s="7" customFormat="1">
+      <c r="A44" s="10" t="s">
+        <v>808</v>
+      </c>
+      <c r="B44" s="14"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="F44" s="1"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="P44" s="2"/>
+      <c r="Q44" s="2"/>
+      <c r="R44" s="2"/>
+      <c r="S44" s="1"/>
+      <c r="T44" s="8"/>
+      <c r="U44" s="2"/>
+      <c r="V44" s="1"/>
+    </row>
+    <row r="45" spans="1:22" s="7" customFormat="1">
+      <c r="A45" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="B45" s="12"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="P45" s="2"/>
+      <c r="Q45" s="2"/>
+      <c r="R45" s="2"/>
+      <c r="S45" s="1"/>
+      <c r="T45" s="8"/>
+      <c r="U45" s="2"/>
+      <c r="V45" s="1"/>
+    </row>
+    <row r="46" spans="1:22" s="7" customFormat="1" ht="86.4">
+      <c r="A46" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C46" s="33" t="s">
+        <v>252</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F46" s="1"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+      <c r="P46" s="2"/>
+      <c r="Q46" s="2"/>
+      <c r="R46" s="2"/>
+      <c r="S46" s="1"/>
+      <c r="T46" s="8"/>
+      <c r="U46" s="2"/>
+      <c r="V46" s="1"/>
+    </row>
+    <row r="47" spans="1:22" s="7" customFormat="1">
+      <c r="A47" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="B47" s="14"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+      <c r="P47" s="2"/>
+      <c r="Q47" s="2"/>
+      <c r="R47" s="2"/>
+      <c r="S47" s="1"/>
+      <c r="T47" s="8"/>
+      <c r="U47" s="2"/>
+      <c r="V47" s="1"/>
+    </row>
+    <row r="48" spans="1:22" s="7" customFormat="1" ht="72">
+      <c r="A48" s="2"/>
+      <c r="B48" s="14"/>
+      <c r="C48" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F48" s="1"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
+      <c r="P48" s="2"/>
+      <c r="Q48" s="2"/>
+      <c r="R48" s="2"/>
+      <c r="S48" s="1"/>
+      <c r="T48" s="8"/>
+      <c r="U48" s="2"/>
+      <c r="V48" s="1"/>
+    </row>
+    <row r="49" spans="1:22" s="7" customFormat="1">
+      <c r="A49" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B49" s="14"/>
+      <c r="C49" s="14"/>
+      <c r="D49" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F49" s="1"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1"/>
+      <c r="P49" s="2"/>
+      <c r="Q49" s="2"/>
+      <c r="R49" s="2"/>
+      <c r="S49" s="1"/>
+      <c r="T49" s="8"/>
+      <c r="U49" s="2"/>
+      <c r="V49" s="1"/>
+    </row>
+    <row r="50" spans="1:22" s="7" customFormat="1" ht="86.4">
+      <c r="A50" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C50" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="D50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
+      <c r="P50" s="2"/>
+      <c r="Q50" s="2"/>
+      <c r="R50" s="2"/>
+      <c r="S50" s="1"/>
+      <c r="T50" s="8"/>
+      <c r="U50" s="2"/>
+      <c r="V50" s="1"/>
+    </row>
+    <row r="51" spans="1:22" s="7" customFormat="1" ht="86.4">
+      <c r="A51" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C51" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="D51" s="2"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="P51" s="2"/>
+      <c r="Q51" s="2"/>
+      <c r="R51" s="2"/>
+      <c r="S51" s="1"/>
+      <c r="T51" s="8"/>
+      <c r="U51" s="2"/>
+      <c r="V51" s="1"/>
+    </row>
+    <row r="52" spans="1:22" s="7" customFormat="1" ht="86.4">
+      <c r="A52" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B52" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="C52" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F52" s="1"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
+      <c r="M52" s="1"/>
+      <c r="N52" s="1"/>
+      <c r="P52" s="2"/>
+      <c r="Q52" s="2"/>
+      <c r="R52" s="2"/>
+      <c r="S52" s="1"/>
+      <c r="T52" s="8"/>
+      <c r="U52" s="2"/>
+      <c r="V52" s="1"/>
+    </row>
+    <row r="53" spans="1:22" s="7" customFormat="1" ht="115.2">
+      <c r="A53" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C53" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F53" s="1"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
+      <c r="M53" s="1"/>
+      <c r="N53" s="1"/>
+      <c r="P53" s="2"/>
+      <c r="Q53" s="2"/>
+      <c r="R53" s="2"/>
+      <c r="S53" s="1"/>
+      <c r="T53" s="8"/>
+      <c r="U53" s="2"/>
+      <c r="V53" s="1"/>
+    </row>
+    <row r="54" spans="1:22" s="7" customFormat="1" ht="28.8">
+      <c r="A54" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C54" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="D54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
+      <c r="M54" s="1"/>
+      <c r="N54" s="1"/>
+      <c r="P54" s="2"/>
+      <c r="Q54" s="2"/>
+      <c r="R54" s="2"/>
+      <c r="S54" s="1"/>
+      <c r="T54" s="8"/>
+      <c r="U54" s="2"/>
+      <c r="V54" s="1"/>
+    </row>
+    <row r="55" spans="1:22" s="7" customFormat="1" ht="100.8">
+      <c r="A55" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C55" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="D55" s="96" t="s">
+        <v>816</v>
+      </c>
+      <c r="F55" s="1"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
+      <c r="M55" s="1"/>
+      <c r="N55" s="1"/>
+      <c r="P55" s="2"/>
+      <c r="Q55" s="2"/>
+      <c r="R55" s="2"/>
+      <c r="S55" s="1"/>
+      <c r="T55" s="8"/>
+      <c r="U55" s="2"/>
+      <c r="V55" s="1"/>
+    </row>
+    <row r="56" spans="1:22" s="7" customFormat="1" ht="86.4">
+      <c r="A56" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C56" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="D56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="K56" s="1"/>
+      <c r="L56" s="1"/>
+      <c r="M56" s="1"/>
+      <c r="N56" s="1"/>
+      <c r="P56" s="2"/>
+      <c r="Q56" s="2"/>
+      <c r="R56" s="2"/>
+      <c r="S56" s="1"/>
+      <c r="T56" s="8"/>
+      <c r="U56" s="2"/>
+      <c r="V56" s="1"/>
+    </row>
+    <row r="57" spans="1:22" s="7" customFormat="1" ht="57.6">
+      <c r="A57" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C57" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="D57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
+      <c r="M57" s="1"/>
+      <c r="N57" s="1"/>
+      <c r="P57" s="2"/>
+      <c r="Q57" s="2"/>
+      <c r="R57" s="2"/>
+      <c r="S57" s="1"/>
+      <c r="T57" s="8"/>
+      <c r="U57" s="2"/>
+      <c r="V57" s="1"/>
+    </row>
+    <row r="58" spans="1:22" s="7" customFormat="1">
+      <c r="A58" s="10" t="s">
+        <v>809</v>
+      </c>
+      <c r="B58" s="12"/>
+      <c r="C58" s="13"/>
+      <c r="D58" s="2"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
+      <c r="M58" s="1"/>
+      <c r="N58" s="1"/>
+      <c r="P58" s="2"/>
+      <c r="Q58" s="2"/>
+      <c r="R58" s="2"/>
+      <c r="S58" s="1"/>
+      <c r="T58" s="8"/>
+      <c r="U58" s="2"/>
+      <c r="V58" s="1"/>
+    </row>
+    <row r="59" spans="1:22" s="7" customFormat="1" ht="100.8">
+      <c r="A59" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B59" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C59" s="33" t="s">
+        <v>254</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F59" s="1"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="K59" s="1"/>
+      <c r="L59" s="1"/>
+      <c r="M59" s="1"/>
+      <c r="N59" s="1"/>
+      <c r="P59" s="2"/>
+      <c r="Q59" s="2"/>
+      <c r="R59" s="2"/>
+      <c r="S59" s="1"/>
+      <c r="T59" s="8"/>
+      <c r="U59" s="2"/>
+      <c r="V59" s="1"/>
+    </row>
+    <row r="60" spans="1:22" s="7" customFormat="1" ht="100.8">
+      <c r="A60" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B60" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C60" s="33" t="s">
+        <v>255</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="F60" s="1"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+      <c r="K60" s="1"/>
+      <c r="L60" s="1"/>
+      <c r="M60" s="1"/>
+      <c r="N60" s="1"/>
+      <c r="P60" s="2"/>
+      <c r="Q60" s="2"/>
+      <c r="R60" s="2"/>
+      <c r="S60" s="1"/>
+      <c r="T60" s="8"/>
+      <c r="U60" s="2"/>
+      <c r="V60" s="1"/>
+    </row>
+    <row r="61" spans="1:22" s="7" customFormat="1" ht="86.4">
+      <c r="A61" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B61" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C61" s="33" t="s">
+        <v>256</v>
+      </c>
+      <c r="D61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
+      <c r="M61" s="1"/>
+      <c r="N61" s="1"/>
+      <c r="P61" s="2"/>
+      <c r="Q61" s="2"/>
+      <c r="R61" s="2"/>
+      <c r="S61" s="1"/>
+      <c r="T61" s="8"/>
+      <c r="U61" s="2"/>
+      <c r="V61" s="1"/>
+    </row>
+    <row r="62" spans="1:22" s="7" customFormat="1">
+      <c r="A62" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="B62" s="2"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F62" s="1"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="K62" s="1"/>
+      <c r="L62" s="1"/>
+      <c r="M62" s="1"/>
+      <c r="N62" s="1"/>
+      <c r="P62" s="2"/>
+      <c r="Q62" s="2"/>
+      <c r="R62" s="2"/>
+      <c r="S62" s="1"/>
+      <c r="T62" s="8"/>
+      <c r="U62" s="2"/>
+      <c r="V62" s="1"/>
+    </row>
+    <row r="63" spans="1:22" s="7" customFormat="1">
+      <c r="A63" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B63" s="2"/>
+      <c r="C63" s="9"/>
+      <c r="D63" s="2"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1"/>
+      <c r="M63" s="1"/>
+      <c r="N63" s="1"/>
+      <c r="P63" s="2"/>
+      <c r="Q63" s="2"/>
+      <c r="R63" s="2"/>
+      <c r="S63" s="1"/>
+      <c r="T63" s="8"/>
+      <c r="U63" s="2"/>
+      <c r="V63" s="1"/>
+    </row>
+    <row r="64" spans="1:22" s="7" customFormat="1">
+      <c r="A64" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B64" s="2"/>
+      <c r="C64" s="9"/>
+      <c r="D64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="K64" s="1"/>
+      <c r="L64" s="1"/>
+      <c r="M64" s="1"/>
+      <c r="N64" s="1"/>
+      <c r="P64" s="2"/>
+      <c r="Q64" s="2"/>
+      <c r="R64" s="2"/>
+      <c r="S64" s="1"/>
+      <c r="T64" s="8"/>
+      <c r="U64" s="2"/>
+      <c r="V64" s="1"/>
+    </row>
+    <row r="65" spans="1:22" s="7" customFormat="1">
+      <c r="A65" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C65" s="9"/>
+      <c r="D65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="K65" s="1"/>
+      <c r="L65" s="1"/>
+      <c r="M65" s="1"/>
+      <c r="N65" s="1"/>
+      <c r="P65" s="2"/>
+      <c r="Q65" s="2"/>
+      <c r="R65" s="2"/>
+      <c r="S65" s="1"/>
+      <c r="T65" s="8"/>
+      <c r="U65" s="2"/>
+      <c r="V65" s="1"/>
+    </row>
+    <row r="66" spans="1:22" s="7" customFormat="1">
+      <c r="A66" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B66" s="2"/>
+      <c r="C66" s="9"/>
+      <c r="D66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="K66" s="1"/>
+      <c r="L66" s="1"/>
+      <c r="M66" s="1"/>
+      <c r="N66" s="1"/>
+      <c r="P66" s="2"/>
+      <c r="Q66" s="2"/>
+      <c r="R66" s="2"/>
+      <c r="S66" s="1"/>
+      <c r="T66" s="8"/>
+      <c r="U66" s="2"/>
+      <c r="V66" s="1"/>
+    </row>
+    <row r="67" spans="1:22" s="7" customFormat="1">
+      <c r="A67" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B67" s="2"/>
+      <c r="C67" s="9"/>
+      <c r="D67" s="1"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="K67" s="1"/>
+      <c r="L67" s="1"/>
+      <c r="M67" s="1"/>
+      <c r="N67" s="1"/>
+      <c r="P67" s="2"/>
+      <c r="Q67" s="2"/>
+      <c r="R67" s="2"/>
+      <c r="S67" s="1"/>
+      <c r="T67" s="8"/>
+      <c r="U67" s="2"/>
+      <c r="V67" s="1"/>
+    </row>
+    <row r="68" spans="1:22" s="7" customFormat="1">
+      <c r="A68" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B68" s="2"/>
+      <c r="C68" s="9"/>
+      <c r="D68" s="1"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="K68" s="1"/>
+      <c r="L68" s="1"/>
+      <c r="M68" s="1"/>
+      <c r="N68" s="1"/>
+      <c r="P68" s="2"/>
+      <c r="Q68" s="2"/>
+      <c r="R68" s="2"/>
+      <c r="S68" s="1"/>
+      <c r="T68" s="8"/>
+      <c r="U68" s="2"/>
+      <c r="V68" s="1"/>
+    </row>
+    <row r="69" spans="1:22" s="7" customFormat="1">
+      <c r="A69" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B69" s="2"/>
+      <c r="C69" s="9"/>
+      <c r="D69" s="1"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1"/>
+      <c r="M69" s="1"/>
+      <c r="N69" s="1"/>
+      <c r="P69" s="2"/>
+      <c r="Q69" s="2"/>
+      <c r="R69" s="2"/>
+      <c r="S69" s="1"/>
+      <c r="T69" s="8"/>
+      <c r="U69" s="2"/>
+      <c r="V69" s="1"/>
+    </row>
+    <row r="70" spans="1:22" s="7" customFormat="1">
+      <c r="A70" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B70" s="2"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="K70" s="1"/>
+      <c r="L70" s="1"/>
+      <c r="M70" s="1"/>
+      <c r="N70" s="1"/>
+      <c r="P70" s="2"/>
+      <c r="Q70" s="2"/>
+      <c r="R70" s="2"/>
+      <c r="S70" s="1"/>
+      <c r="T70" s="8"/>
+      <c r="U70" s="2"/>
+      <c r="V70" s="1"/>
+    </row>
+    <row r="71" spans="1:22" s="7" customFormat="1">
+      <c r="A71" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B71" s="2"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="1"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+      <c r="K71" s="1"/>
+      <c r="L71" s="1"/>
+      <c r="M71" s="1"/>
+      <c r="N71" s="1"/>
+      <c r="P71" s="2"/>
+      <c r="Q71" s="2"/>
+      <c r="R71" s="2"/>
+      <c r="S71" s="1"/>
+      <c r="T71" s="8"/>
+      <c r="U71" s="2"/>
+      <c r="V71" s="1"/>
+    </row>
+    <row r="72" spans="1:22" s="7" customFormat="1" ht="86.4">
+      <c r="A72" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="B72" s="21"/>
+      <c r="C72" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="D72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="K72" s="1"/>
+      <c r="L72" s="1"/>
+      <c r="M72" s="1"/>
+      <c r="N72" s="1"/>
+      <c r="P72" s="2"/>
+      <c r="Q72" s="2"/>
+      <c r="R72" s="2"/>
+      <c r="S72" s="1"/>
+      <c r="T72" s="8"/>
+      <c r="U72" s="2"/>
+      <c r="V72" s="1"/>
+    </row>
+    <row r="73" spans="1:22" s="7" customFormat="1" ht="57.6">
+      <c r="A73" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="B73" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="C73" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="D73" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="F73" s="1"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="K73" s="1"/>
+      <c r="L73" s="1"/>
+      <c r="M73" s="1"/>
+      <c r="N73" s="1"/>
+      <c r="P73" s="2"/>
+      <c r="Q73" s="2"/>
+      <c r="R73" s="2"/>
+      <c r="S73" s="1"/>
+      <c r="T73" s="8"/>
+      <c r="U73" s="2"/>
+      <c r="V73" s="1"/>
+    </row>
+    <row r="74" spans="1:22" s="7" customFormat="1" ht="28.8">
+      <c r="A74" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B74" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="C74" s="4"/>
+      <c r="D74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="K74" s="1"/>
+      <c r="L74" s="1"/>
+      <c r="M74" s="1"/>
+      <c r="N74" s="1"/>
+      <c r="P74" s="2"/>
+      <c r="Q74" s="2"/>
+      <c r="R74" s="2"/>
+      <c r="S74" s="1"/>
+      <c r="T74" s="8"/>
+      <c r="U74" s="2"/>
+      <c r="V74" s="1"/>
+    </row>
+    <row r="75" spans="1:22" s="7" customFormat="1">
+      <c r="A75" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B75" s="2"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="K75" s="1"/>
+      <c r="L75" s="1"/>
+      <c r="M75" s="1"/>
+      <c r="N75" s="1"/>
+      <c r="P75" s="2"/>
+      <c r="Q75" s="2"/>
+      <c r="R75" s="2"/>
+      <c r="S75" s="1"/>
+      <c r="T75" s="8"/>
+      <c r="U75" s="2"/>
+      <c r="V75" s="1"/>
+    </row>
+    <row r="76" spans="1:22" s="7" customFormat="1">
+      <c r="A76" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B76" s="2"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="K76" s="1"/>
+      <c r="L76" s="1"/>
+      <c r="M76" s="1"/>
+      <c r="N76" s="1"/>
+      <c r="P76" s="2"/>
+      <c r="Q76" s="2"/>
+      <c r="R76" s="2"/>
+      <c r="S76" s="1"/>
+      <c r="T76" s="8"/>
+      <c r="U76" s="2"/>
+      <c r="V76" s="1"/>
+    </row>
+    <row r="77" spans="1:22" s="7" customFormat="1" ht="28.8">
+      <c r="A77" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B77" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="C77" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="D77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="K77" s="1"/>
+      <c r="L77" s="1"/>
+      <c r="M77" s="1"/>
+      <c r="N77" s="1"/>
+      <c r="P77" s="2"/>
+      <c r="Q77" s="2"/>
+      <c r="R77" s="2"/>
+      <c r="S77" s="1"/>
+      <c r="T77" s="8"/>
+      <c r="U77" s="2"/>
+      <c r="V77" s="1"/>
+    </row>
+    <row r="78" spans="1:22" s="7" customFormat="1">
+      <c r="A78" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C78" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="D78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="K78" s="1"/>
+      <c r="L78" s="1"/>
+      <c r="M78" s="1"/>
+      <c r="N78" s="1"/>
+      <c r="P78" s="2"/>
+      <c r="Q78" s="2"/>
+      <c r="R78" s="2"/>
+      <c r="S78" s="1"/>
+      <c r="T78" s="8"/>
+      <c r="U78" s="2"/>
+      <c r="V78" s="1"/>
+    </row>
+    <row r="79" spans="1:22" s="7" customFormat="1">
+      <c r="A79" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="B79" s="2"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="1"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+      <c r="K79" s="1"/>
+      <c r="L79" s="1"/>
+      <c r="M79" s="1"/>
+      <c r="N79" s="1"/>
+      <c r="P79" s="2"/>
+      <c r="Q79" s="2"/>
+      <c r="R79" s="2"/>
+      <c r="S79" s="1"/>
+      <c r="T79" s="8"/>
+      <c r="U79" s="2"/>
+      <c r="V79" s="1"/>
+    </row>
+    <row r="80" spans="1:22" s="7" customFormat="1" ht="144">
+      <c r="A80" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B80" s="2"/>
+      <c r="C80" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="D80" s="1"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="2"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="K80" s="1"/>
+      <c r="L80" s="1"/>
+      <c r="M80" s="1"/>
+      <c r="N80" s="1"/>
+      <c r="P80" s="2"/>
+      <c r="Q80" s="2"/>
+      <c r="R80" s="2"/>
+      <c r="S80" s="1"/>
+      <c r="T80" s="8"/>
+      <c r="U80" s="2"/>
+      <c r="V80" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66028E03-DC1C-4884-967A-52D62E8CDBFA}">
   <sheetPr>
@@ -22616,12 +23902,608 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFD612E0-A553-42AC-8ADD-A8089131F6A7}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:F44"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="39.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="44.77734375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="59.21875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="37.88671875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="43.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="55.109375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="67.88671875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="64.33203125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="7.77734375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="39.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="48.88671875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="72.6640625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="43.88671875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="7.77734375" style="2" customWidth="1"/>
+    <col min="15" max="15" width="56.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="46.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="62.88671875" style="2" customWidth="1"/>
+    <col min="18" max="18" width="49.21875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="8.77734375" style="2" customWidth="1"/>
+    <col min="20" max="20" width="67.77734375" style="2" customWidth="1"/>
+    <col min="21" max="21" width="68.33203125" style="2" customWidth="1"/>
+    <col min="22" max="23" width="59.33203125" style="2" customWidth="1"/>
+    <col min="24" max="24" width="59.6640625" style="2" customWidth="1"/>
+    <col min="25" max="25" width="99.44140625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="41.21875" style="2" customWidth="1"/>
+    <col min="27" max="27" width="8.77734375" style="2" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6">
+      <c r="A2" s="54" t="s">
+        <v>452</v>
+      </c>
+      <c r="B2" s="55" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="54" t="s">
+        <v>401</v>
+      </c>
+      <c r="B3" s="55" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="54" t="s">
+        <v>421</v>
+      </c>
+      <c r="B4" s="55" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="54" t="s">
+        <v>446</v>
+      </c>
+      <c r="B5" s="55" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="40" customFormat="1"/>
+    <row r="8" spans="1:6">
+      <c r="A8" s="41" t="s">
+        <v>268</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>269</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>272</v>
+      </c>
+      <c r="D8" s="41" t="s">
+        <v>270</v>
+      </c>
+      <c r="E8" s="41" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="51" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="220.8">
+      <c r="A10" s="59" t="s">
+        <v>453</v>
+      </c>
+      <c r="B10" s="60" t="s">
+        <v>454</v>
+      </c>
+      <c r="C10" s="61" t="s">
+        <v>455</v>
+      </c>
+      <c r="D10" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="E10" s="62" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="220.8">
+      <c r="A11" s="59" t="s">
+        <v>458</v>
+      </c>
+      <c r="B11" s="60" t="s">
+        <v>459</v>
+      </c>
+      <c r="C11" s="61" t="s">
+        <v>460</v>
+      </c>
+      <c r="D11" s="60" t="s">
+        <v>461</v>
+      </c>
+      <c r="E11" s="62" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="56" customFormat="1">
+      <c r="A12" s="54" t="s">
+        <v>401</v>
+      </c>
+      <c r="B12" s="55"/>
+      <c r="F12" s="103" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="56" customFormat="1" ht="187.2">
+      <c r="A13" s="57" t="s">
+        <v>403</v>
+      </c>
+      <c r="B13" s="57" t="s">
+        <v>404</v>
+      </c>
+      <c r="C13" s="57" t="s">
+        <v>859</v>
+      </c>
+      <c r="D13" s="57" t="s">
+        <v>406</v>
+      </c>
+      <c r="E13" s="58" t="s">
+        <v>407</v>
+      </c>
+      <c r="F13" s="57" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="56" customFormat="1" ht="86.4">
+      <c r="A14" s="57" t="s">
+        <v>408</v>
+      </c>
+      <c r="B14" s="57" t="s">
+        <v>409</v>
+      </c>
+      <c r="C14" s="57" t="s">
+        <v>410</v>
+      </c>
+      <c r="D14" s="57" t="s">
+        <v>411</v>
+      </c>
+      <c r="E14" s="58" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" s="56" customFormat="1" ht="115.2">
+      <c r="A15" s="57" t="s">
+        <v>412</v>
+      </c>
+      <c r="B15" s="57" t="s">
+        <v>413</v>
+      </c>
+      <c r="C15" s="57" t="s">
+        <v>414</v>
+      </c>
+      <c r="D15" s="57" t="s">
+        <v>415</v>
+      </c>
+      <c r="E15" s="58" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" s="56" customFormat="1" ht="86.4">
+      <c r="A16" s="57" t="s">
+        <v>417</v>
+      </c>
+      <c r="B16" s="57" t="s">
+        <v>418</v>
+      </c>
+      <c r="C16" s="57" t="s">
+        <v>419</v>
+      </c>
+      <c r="D16" s="57" t="s">
+        <v>420</v>
+      </c>
+      <c r="E16" s="58" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="56" customFormat="1">
+      <c r="A17" s="54" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="56" customFormat="1" ht="86.4">
+      <c r="A18" s="57" t="s">
+        <v>422</v>
+      </c>
+      <c r="B18" s="57" t="s">
+        <v>423</v>
+      </c>
+      <c r="C18" s="57" t="s">
+        <v>424</v>
+      </c>
+      <c r="D18" s="57" t="s">
+        <v>425</v>
+      </c>
+      <c r="E18" s="58" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="56" customFormat="1" ht="72">
+      <c r="A19" s="57" t="s">
+        <v>426</v>
+      </c>
+      <c r="B19" s="57" t="s">
+        <v>427</v>
+      </c>
+      <c r="C19" s="57" t="s">
+        <v>429</v>
+      </c>
+      <c r="D19" s="57" t="s">
+        <v>430</v>
+      </c>
+      <c r="E19" s="58" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" s="56" customFormat="1" ht="57.6">
+      <c r="A20" s="57" t="s">
+        <v>432</v>
+      </c>
+      <c r="B20" s="57" t="s">
+        <v>433</v>
+      </c>
+      <c r="C20" s="57" t="s">
+        <v>434</v>
+      </c>
+      <c r="D20" s="57" t="s">
+        <v>435</v>
+      </c>
+      <c r="E20" s="58" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="56" customFormat="1" ht="43.2">
+      <c r="A21" s="57" t="s">
+        <v>437</v>
+      </c>
+      <c r="B21" s="57" t="s">
+        <v>438</v>
+      </c>
+      <c r="C21" s="57" t="s">
+        <v>439</v>
+      </c>
+      <c r="D21" s="57" t="s">
+        <v>440</v>
+      </c>
+      <c r="E21" s="58" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" s="56" customFormat="1" ht="86.4">
+      <c r="A22" s="57" t="s">
+        <v>442</v>
+      </c>
+      <c r="B22" s="57" t="s">
+        <v>443</v>
+      </c>
+      <c r="C22" s="57" t="s">
+        <v>444</v>
+      </c>
+      <c r="D22" s="57" t="s">
+        <v>445</v>
+      </c>
+      <c r="E22" s="58" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" s="56" customFormat="1">
+      <c r="A23" s="54" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" s="56" customFormat="1" ht="144">
+      <c r="A24" s="57" t="s">
+        <v>447</v>
+      </c>
+      <c r="B24" s="57" t="s">
+        <v>448</v>
+      </c>
+      <c r="C24" s="57" t="s">
+        <v>449</v>
+      </c>
+      <c r="D24" s="57" t="s">
+        <v>450</v>
+      </c>
+      <c r="E24" s="58" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" s="56" customFormat="1"/>
+    <row r="26" spans="1:5" s="56" customFormat="1"/>
+    <row r="27" spans="1:5" s="56" customFormat="1"/>
+    <row r="28" spans="1:5" s="56" customFormat="1"/>
+    <row r="29" spans="1:5" s="56" customFormat="1"/>
+    <row r="30" spans="1:5" s="56" customFormat="1"/>
+    <row r="31" spans="1:5" ht="57.6" customHeight="1"/>
+    <row r="32" spans="1:5" ht="43.2" customHeight="1"/>
+    <row r="33" ht="72" customHeight="1"/>
+    <row r="35" ht="115.2" customHeight="1"/>
+    <row r="36" ht="57.6" customHeight="1"/>
+    <row r="37" ht="86.4" customHeight="1"/>
+    <row r="38" ht="57.6" customHeight="1"/>
+    <row r="39" ht="57.6" customHeight="1"/>
+    <row r="41" ht="330" customHeight="1"/>
+    <row r="43" ht="66" customHeight="1"/>
+    <row r="44" ht="36.6" customHeight="1"/>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E13" r:id="rId1" xr:uid="{0BC35BC1-A738-42F1-9F64-879FFEA9E3C5}"/>
+    <hyperlink ref="E14" r:id="rId2" xr:uid="{593523E3-A9C1-4546-B440-5B6B81E99A34}"/>
+    <hyperlink ref="E15" r:id="rId3" location="torefs" xr:uid="{C381662B-70B1-4BD0-8E64-4DC4ABCB1256}"/>
+    <hyperlink ref="E16" r:id="rId4" xr:uid="{FE8A6778-B8A4-4528-9084-CECA9B302D7D}"/>
+    <hyperlink ref="E18" r:id="rId5" xr:uid="{70739E9C-8EA0-47D7-88AF-EF73AD62676C}"/>
+    <hyperlink ref="E19" r:id="rId6" xr:uid="{30BE7754-8CE7-457D-BC9B-5FBCE4445A2C}"/>
+    <hyperlink ref="E20" r:id="rId7" xr:uid="{4FB7FFC4-AD0B-4B93-BE00-D014439426E0}"/>
+    <hyperlink ref="E21" r:id="rId8" xr:uid="{20E58446-133B-43AB-B41D-BF53FA621D61}"/>
+    <hyperlink ref="E22" r:id="rId9" xr:uid="{30C98C66-F3DA-4505-852C-9600AB78A563}"/>
+    <hyperlink ref="E24" r:id="rId10" xr:uid="{65E1B679-4FE0-4321-BD12-0AB5515BA93B}"/>
+    <hyperlink ref="E10" r:id="rId11" xr:uid="{1A38CE5F-1921-4E29-BBE0-6091BDA8F7C0}"/>
+    <hyperlink ref="E11" r:id="rId12" xr:uid="{C8FC45D7-DA7C-41E5-9D4D-9A7023E4050D}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BCD0E6E-DD2E-4D2F-A721-3BEA42FDB1B7}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:E30"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="39.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="42.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="85.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="43.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="107" customWidth="1"/>
+    <col min="6" max="6" width="67.88671875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="64.33203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7.77734375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="39.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="48.88671875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="72.6640625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="43.88671875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="7.77734375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="56.77734375" style="2" customWidth="1"/>
+    <col min="15" max="15" width="46.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="62.88671875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="49.21875" style="2" customWidth="1"/>
+    <col min="18" max="18" width="8.77734375" style="2" customWidth="1"/>
+    <col min="19" max="19" width="67.77734375" style="2" customWidth="1"/>
+    <col min="20" max="20" width="68.33203125" style="2" customWidth="1"/>
+    <col min="21" max="22" width="59.33203125" style="2" customWidth="1"/>
+    <col min="23" max="23" width="59.6640625" style="2" customWidth="1"/>
+    <col min="24" max="24" width="99.44140625" style="2" customWidth="1"/>
+    <col min="25" max="25" width="41.21875" style="2" customWidth="1"/>
+    <col min="26" max="26" width="8.77734375" style="2" customWidth="1"/>
+    <col min="27" max="16384" width="8.77734375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5">
+      <c r="A2" s="54"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="54"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="54"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="54"/>
+    </row>
+    <row r="7" spans="1:5" s="40" customFormat="1">
+      <c r="E7" s="107"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="57"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="108"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="54" t="s">
+        <v>873</v>
+      </c>
+      <c r="E9" s="108"/>
+    </row>
+    <row r="10" spans="1:5" ht="409.6">
+      <c r="A10" s="57"/>
+      <c r="B10" s="57" t="s">
+        <v>882</v>
+      </c>
+      <c r="C10" s="57" t="s">
+        <v>883</v>
+      </c>
+      <c r="D10" s="57" t="s">
+        <v>884</v>
+      </c>
+      <c r="E10" s="108"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="54" t="s">
+        <v>874</v>
+      </c>
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="108"/>
+    </row>
+    <row r="12" spans="1:5" s="56" customFormat="1" ht="409.6">
+      <c r="A12" s="57"/>
+      <c r="B12" s="57" t="s">
+        <v>877</v>
+      </c>
+      <c r="C12" s="57" t="s">
+        <v>876</v>
+      </c>
+      <c r="D12" s="57" t="s">
+        <v>878</v>
+      </c>
+      <c r="E12" s="108"/>
+    </row>
+    <row r="13" spans="1:5" s="56" customFormat="1">
+      <c r="A13" s="54" t="s">
+        <v>875</v>
+      </c>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="108"/>
+    </row>
+    <row r="14" spans="1:5" s="56" customFormat="1" ht="409.6">
+      <c r="A14" s="57"/>
+      <c r="B14" s="57" t="s">
+        <v>879</v>
+      </c>
+      <c r="C14" s="57" t="s">
+        <v>880</v>
+      </c>
+      <c r="D14" s="57" t="s">
+        <v>881</v>
+      </c>
+      <c r="E14" s="108"/>
+    </row>
+    <row r="15" spans="1:5" s="56" customFormat="1">
+      <c r="A15" s="57"/>
+      <c r="B15" s="57"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="108"/>
+    </row>
+    <row r="16" spans="1:5" s="56" customFormat="1">
+      <c r="A16" s="57"/>
+      <c r="B16" s="57"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="57"/>
+      <c r="E16" s="108"/>
+    </row>
+    <row r="17" spans="1:5" s="56" customFormat="1">
+      <c r="A17" s="57"/>
+      <c r="B17" s="57"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="108"/>
+    </row>
+    <row r="18" spans="1:5" s="56" customFormat="1">
+      <c r="A18" s="57"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="108"/>
+    </row>
+    <row r="19" spans="1:5" s="56" customFormat="1">
+      <c r="A19" s="57"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="108"/>
+    </row>
+    <row r="20" spans="1:5" s="56" customFormat="1">
+      <c r="A20" s="57"/>
+      <c r="B20" s="57"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="108"/>
+    </row>
+    <row r="21" spans="1:5" s="56" customFormat="1">
+      <c r="A21" s="57"/>
+      <c r="B21" s="57"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="108"/>
+    </row>
+    <row r="22" spans="1:5" s="56" customFormat="1">
+      <c r="A22" s="57"/>
+      <c r="B22" s="57"/>
+      <c r="C22" s="57"/>
+      <c r="D22" s="57"/>
+      <c r="E22" s="108"/>
+    </row>
+    <row r="23" spans="1:5" s="56" customFormat="1">
+      <c r="A23" s="57"/>
+      <c r="B23" s="57"/>
+      <c r="C23" s="57"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="108"/>
+    </row>
+    <row r="24" spans="1:5" s="56" customFormat="1">
+      <c r="A24" s="57"/>
+      <c r="B24" s="57"/>
+      <c r="C24" s="57"/>
+      <c r="D24" s="57"/>
+      <c r="E24" s="108"/>
+    </row>
+    <row r="25" spans="1:5" s="56" customFormat="1">
+      <c r="A25" s="57"/>
+      <c r="B25" s="57"/>
+      <c r="C25" s="57"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="108"/>
+    </row>
+    <row r="26" spans="1:5" s="56" customFormat="1">
+      <c r="A26" s="57"/>
+      <c r="B26" s="57"/>
+      <c r="C26" s="57"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="108"/>
+    </row>
+    <row r="27" spans="1:5" s="56" customFormat="1">
+      <c r="A27" s="57"/>
+      <c r="B27" s="57"/>
+      <c r="C27" s="57"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="108"/>
+    </row>
+    <row r="28" spans="1:5" s="56" customFormat="1">
+      <c r="A28" s="57"/>
+      <c r="B28" s="57"/>
+      <c r="C28" s="57"/>
+      <c r="D28" s="57"/>
+      <c r="E28" s="108"/>
+    </row>
+    <row r="29" spans="1:5" s="56" customFormat="1">
+      <c r="A29" s="57"/>
+      <c r="B29" s="57"/>
+      <c r="C29" s="57"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="108"/>
+    </row>
+    <row r="30" spans="1:5" s="56" customFormat="1">
+      <c r="A30" s="57"/>
+      <c r="B30" s="57"/>
+      <c r="C30" s="57"/>
+      <c r="D30" s="57"/>
+      <c r="E30" s="108"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F21ADC02-F754-4C6C-B18D-281EDEC7371E}">
   <sheetPr>
     <tabColor rgb="FFC00000"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:E11"/>
+  <dimension ref="A2:E13"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="39.33203125" style="2" customWidth="1"/>
@@ -22654,7 +24536,7 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="54" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -22674,7 +24556,7 @@
     </row>
     <row r="9" spans="1:5" s="56" customFormat="1">
       <c r="A9" s="54" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="B9" s="57"/>
       <c r="C9" s="57"/>
@@ -22683,17 +24565,42 @@
     <row r="10" spans="1:5" s="56" customFormat="1" ht="115.2">
       <c r="A10" s="57"/>
       <c r="B10" s="57" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="C10" s="69" t="s">
-        <v>722</v>
+        <v>712</v>
       </c>
       <c r="E10" s="79"/>
     </row>
-    <row r="11" spans="1:5" ht="43.2">
+    <row r="11" spans="1:5">
       <c r="A11" s="54" t="s">
-        <v>791</v>
-      </c>
+        <v>787</v>
+      </c>
+      <c r="C11" s="65"/>
+      <c r="D11" s="76"/>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:5" ht="187.2">
+      <c r="A12" s="76"/>
+      <c r="B12" s="94" t="s">
+        <v>786</v>
+      </c>
+      <c r="C12" s="65" t="s">
+        <v>782</v>
+      </c>
+      <c r="D12" s="76" t="s">
+        <v>781</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5" ht="72">
+      <c r="B13" s="94" t="s">
+        <v>789</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="E13" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -22701,7 +24608,125 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98729587-661C-4647-8A0E-68347CF7376F}">
+  <sheetPr>
+    <tabColor rgb="FF7030A0"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:E14"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="39.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="59.21875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="55.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="53" style="2" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" style="78" customWidth="1"/>
+    <col min="6" max="6" width="67.88671875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="64.33203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7.77734375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="39.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="48.88671875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="72.6640625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="43.88671875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="7.77734375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="56.77734375" style="2" customWidth="1"/>
+    <col min="15" max="15" width="46.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="62.88671875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="49.21875" style="2" customWidth="1"/>
+    <col min="18" max="18" width="8.77734375" style="2" customWidth="1"/>
+    <col min="19" max="19" width="67.77734375" style="2" customWidth="1"/>
+    <col min="20" max="20" width="68.33203125" style="2" customWidth="1"/>
+    <col min="21" max="22" width="59.33203125" style="2" customWidth="1"/>
+    <col min="23" max="23" width="59.6640625" style="2" customWidth="1"/>
+    <col min="24" max="24" width="99.44140625" style="2" customWidth="1"/>
+    <col min="25" max="25" width="41.21875" style="2" customWidth="1"/>
+    <col min="26" max="26" width="8.77734375" style="2" customWidth="1"/>
+    <col min="27" max="16384" width="8.77734375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5">
+      <c r="A2" s="87"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="54"/>
+      <c r="C3" s="96"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="54"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="54"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="54"/>
+    </row>
+    <row r="8" spans="1:5" s="40" customFormat="1">
+      <c r="E8" s="78"/>
+    </row>
+    <row r="10" spans="1:5" s="56" customFormat="1">
+      <c r="A10" s="54" t="s">
+        <v>531</v>
+      </c>
+      <c r="B10" s="106" t="s">
+        <v>857</v>
+      </c>
+      <c r="C10" s="105" t="s">
+        <v>858</v>
+      </c>
+      <c r="E10" s="78"/>
+    </row>
+    <row r="11" spans="1:5" ht="187.2">
+      <c r="A11" s="22" t="s">
+        <v>867</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="273.60000000000002">
+      <c r="A12" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="22" t="s">
+        <v>871</v>
+      </c>
+      <c r="B13" s="101" t="s">
+        <v>872</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="244.8">
+      <c r="B14" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35186FB0-D6EE-48D6-AD0A-EC687D3766B2}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -22740,30 +24765,30 @@
   <sheetData>
     <row r="2" spans="1:22">
       <c r="A2" s="87" t="s">
-        <v>753</v>
+        <v>743</v>
       </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="54" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="C3" s="96" t="s">
-        <v>842</v>
+        <v>831</v>
       </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="54" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="54" t="s">
-        <v>743</v>
+        <v>733</v>
       </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="54" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
     </row>
     <row r="8" spans="1:22" s="40" customFormat="1">
@@ -22785,7 +24810,7 @@
     </row>
     <row r="10" spans="1:22" s="81" customFormat="1">
       <c r="A10" s="87" t="s">
-        <v>753</v>
+        <v>743</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="4"/>
@@ -22803,7 +24828,7 @@
       <c r="A11" s="1"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>699</v>
+        <v>689</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="80"/>
@@ -22819,7 +24844,7 @@
       <c r="A12" s="1"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="80"/>
@@ -22833,11 +24858,11 @@
     </row>
     <row r="13" spans="1:22" s="81" customFormat="1">
       <c r="A13" s="96" t="s">
-        <v>842</v>
+        <v>831</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>698</v>
+        <v>688</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="80"/>
@@ -22851,13 +24876,13 @@
     </row>
     <row r="14" spans="1:22" s="81" customFormat="1" ht="72">
       <c r="A14" s="96" t="s">
-        <v>842</v>
+        <v>831</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>701</v>
+        <v>691</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="80"/>
@@ -22871,33 +24896,33 @@
     </row>
     <row r="15" spans="1:22" s="56" customFormat="1">
       <c r="A15" s="54" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="B15" s="73" t="s">
-        <v>718</v>
+        <v>708</v>
       </c>
       <c r="E15" s="79"/>
     </row>
     <row r="16" spans="1:22" s="56" customFormat="1" ht="100.8">
       <c r="A16" s="57"/>
       <c r="B16" s="57" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="C16" s="57" t="s">
-        <v>730</v>
+        <v>720</v>
       </c>
       <c r="D16" s="58" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="E16" s="79"/>
     </row>
     <row r="17" spans="1:5" s="56" customFormat="1" ht="43.2">
       <c r="A17" s="57"/>
       <c r="B17" s="57" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="C17" s="69" t="s">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="79"/>
@@ -22905,62 +24930,62 @@
     <row r="18" spans="1:5" s="56" customFormat="1">
       <c r="A18" s="57"/>
       <c r="B18" s="54" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="C18" s="54" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="79"/>
     </row>
     <row r="19" spans="1:5" s="56" customFormat="1" ht="172.8">
       <c r="B19" s="57" t="s">
-        <v>706</v>
+        <v>696</v>
       </c>
       <c r="C19" s="57" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="D19" s="58"/>
       <c r="E19" s="79"/>
     </row>
     <row r="20" spans="1:5" s="56" customFormat="1">
       <c r="B20" s="72" t="s">
-        <v>715</v>
+        <v>705</v>
       </c>
       <c r="C20" s="57"/>
       <c r="D20" s="54" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="E20" s="79"/>
     </row>
     <row r="21" spans="1:5" s="56" customFormat="1" ht="273.60000000000002">
       <c r="A21" s="57"/>
       <c r="B21" s="57" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="C21" s="69" t="s">
-        <v>720</v>
+        <v>710</v>
       </c>
       <c r="D21" s="69" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="E21" s="79"/>
     </row>
     <row r="22" spans="1:5" s="56" customFormat="1" ht="86.4">
       <c r="B22" s="57" t="s">
-        <v>719</v>
+        <v>709</v>
       </c>
       <c r="C22" s="69" t="s">
-        <v>724</v>
+        <v>714</v>
       </c>
       <c r="D22" s="57" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="E22" s="79"/>
     </row>
     <row r="23" spans="1:5" s="56" customFormat="1">
       <c r="A23" s="54" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
       <c r="B23" s="57"/>
       <c r="C23" s="69"/>
@@ -22968,29 +24993,29 @@
     </row>
     <row r="24" spans="1:5" s="56" customFormat="1" ht="100.8">
       <c r="A24" s="56" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
       <c r="B24" s="57" t="s">
-        <v>728</v>
+        <v>718</v>
       </c>
       <c r="C24" s="69"/>
       <c r="E24" s="79"/>
     </row>
     <row r="25" spans="1:5" s="56" customFormat="1" ht="201.6">
       <c r="A25" s="56" t="s">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="B25" s="57" t="s">
-        <v>729</v>
+        <v>719</v>
       </c>
       <c r="C25" s="77" t="s">
-        <v>734</v>
+        <v>724</v>
       </c>
       <c r="E25" s="79"/>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="54" t="s">
-        <v>743</v>
+        <v>733</v>
       </c>
       <c r="B26" s="56"/>
       <c r="C26" s="56"/>
@@ -22999,13 +25024,13 @@
     </row>
     <row r="27" spans="1:5" ht="86.4">
       <c r="A27" s="57" t="s">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="B27" s="57" t="s">
-        <v>740</v>
+        <v>730</v>
       </c>
       <c r="C27" s="57" t="s">
-        <v>735</v>
+        <v>725</v>
       </c>
       <c r="D27" s="58" t="s">
         <v>276</v>
@@ -23013,41 +25038,41 @@
     </row>
     <row r="28" spans="1:5" ht="172.8">
       <c r="A28" s="57" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="B28" s="57" t="s">
-        <v>738</v>
+        <v>728</v>
       </c>
       <c r="C28" s="57" t="s">
-        <v>736</v>
+        <v>726</v>
       </c>
       <c r="D28" s="58" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="216">
       <c r="A29" s="57" t="s">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="B29" s="57" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
       <c r="C29" s="75" t="s">
-        <v>742</v>
+        <v>732</v>
       </c>
       <c r="D29" s="58" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="100.8">
       <c r="A30" s="57" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
       <c r="B30" s="57" t="s">
-        <v>739</v>
+        <v>729</v>
       </c>
       <c r="C30" s="75" t="s">
-        <v>741</v>
+        <v>731</v>
       </c>
       <c r="D30" s="58" t="s">
         <v>276</v>
@@ -23064,7 +25089,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA21C6CE-E28C-44A8-8026-35145C4B3BB3}">
   <sheetPr>
     <tabColor rgb="FFC00000"/>
@@ -23103,12 +25128,12 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="54" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="54" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="40" customFormat="1"/>
@@ -23128,49 +25153,49 @@
     </row>
     <row r="11" spans="1:5" s="56" customFormat="1">
       <c r="A11" s="54" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="B11" s="74" t="s">
-        <v>717</v>
+        <v>707</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="56" customFormat="1" ht="144">
       <c r="A12" s="57" t="s">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="B12" s="57" t="s">
-        <v>711</v>
+        <v>701</v>
       </c>
       <c r="C12" s="57" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="56" customFormat="1" ht="86.4">
       <c r="A13" s="57"/>
       <c r="B13" s="57" t="s">
-        <v>723</v>
+        <v>713</v>
       </c>
       <c r="C13" s="69" t="s">
-        <v>725</v>
+        <v>715</v>
       </c>
       <c r="D13" s="58"/>
     </row>
     <row r="14" spans="1:5" s="56" customFormat="1" ht="57.6">
       <c r="A14" s="57"/>
       <c r="B14" s="57" t="s">
-        <v>716</v>
+        <v>706</v>
       </c>
       <c r="C14" s="57" t="s">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="D14" s="58"/>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="54" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="B15" s="56"/>
       <c r="C15" s="56"/>
@@ -23179,22 +25204,22 @@
     </row>
     <row r="16" spans="1:5" ht="144">
       <c r="A16" s="57" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="B16" s="57" t="s">
-        <v>733</v>
+        <v>723</v>
       </c>
       <c r="C16" s="76" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
       <c r="D16" s="57"/>
       <c r="E16" s="58" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="54" t="s">
-        <v>744</v>
+        <v>734</v>
       </c>
       <c r="B17" s="56"/>
       <c r="C17" s="56"/>
@@ -23202,13 +25227,13 @@
     </row>
     <row r="18" spans="1:4" ht="100.8">
       <c r="A18" s="57" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="B18" s="57" t="s">
-        <v>751</v>
+        <v>741</v>
       </c>
       <c r="C18" s="57" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
       <c r="D18" s="58" t="s">
         <v>276</v>
@@ -23216,13 +25241,13 @@
     </row>
     <row r="19" spans="1:4" ht="57.6">
       <c r="A19" s="57" t="s">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="B19" s="57" t="s">
-        <v>749</v>
+        <v>739</v>
       </c>
       <c r="C19" s="57" t="s">
-        <v>746</v>
+        <v>736</v>
       </c>
       <c r="D19" s="58" t="s">
         <v>276</v>
@@ -23230,13 +25255,13 @@
     </row>
     <row r="20" spans="1:4" ht="57.6">
       <c r="A20" s="57" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="B20" s="57" t="s">
-        <v>750</v>
+        <v>740</v>
       </c>
       <c r="C20" s="57" t="s">
-        <v>747</v>
+        <v>737</v>
       </c>
       <c r="D20" s="58" t="s">
         <v>276</v>
@@ -23250,834 +25275,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFD612E0-A553-42AC-8ADD-A8089131F6A7}">
-  <sheetPr>
-    <tabColor rgb="FFFFC000"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A2:F44"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="39.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="44.77734375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="33.109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="59.21875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="37.88671875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="64.33203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="7.77734375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="39.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.88671875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="72.6640625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="43.88671875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="7.77734375" style="2" customWidth="1"/>
-    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
-    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
-    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
-    <col min="19" max="19" width="49.21875" style="2" customWidth="1"/>
-    <col min="20" max="20" width="8.77734375" style="2" customWidth="1"/>
-    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
-    <col min="22" max="22" width="68.33203125" style="2" customWidth="1"/>
-    <col min="23" max="24" width="59.33203125" style="2" customWidth="1"/>
-    <col min="25" max="25" width="59.6640625" style="2" customWidth="1"/>
-    <col min="26" max="26" width="99.44140625" style="2" customWidth="1"/>
-    <col min="27" max="27" width="41.21875" style="2" customWidth="1"/>
-    <col min="28" max="28" width="8.77734375" style="2" customWidth="1"/>
-    <col min="29" max="16384" width="8.77734375" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:6">
-      <c r="A2" s="54" t="s">
-        <v>460</v>
-      </c>
-      <c r="B2" s="55" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="54" t="s">
-        <v>401</v>
-      </c>
-      <c r="B3" s="55" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="54" t="s">
-        <v>425</v>
-      </c>
-      <c r="B4" s="55" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="54" t="s">
-        <v>453</v>
-      </c>
-      <c r="B5" s="55" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="40" customFormat="1"/>
-    <row r="8" spans="1:6">
-      <c r="A8" s="41" t="s">
-        <v>268</v>
-      </c>
-      <c r="B8" s="41" t="s">
-        <v>269</v>
-      </c>
-      <c r="C8" s="41" t="s">
-        <v>271</v>
-      </c>
-      <c r="D8" s="41" t="s">
-        <v>272</v>
-      </c>
-      <c r="E8" s="41" t="s">
-        <v>270</v>
-      </c>
-      <c r="F8" s="41" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="51" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="220.8">
-      <c r="A10" s="59" t="s">
-        <v>461</v>
-      </c>
-      <c r="B10" s="60" t="s">
-        <v>462</v>
-      </c>
-      <c r="C10" s="60" t="s">
-        <v>463</v>
-      </c>
-      <c r="D10" s="61" t="s">
-        <v>464</v>
-      </c>
-      <c r="E10" s="60" t="s">
-        <v>465</v>
-      </c>
-      <c r="F10" s="62" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="220.8">
-      <c r="A11" s="59" t="s">
-        <v>467</v>
-      </c>
-      <c r="B11" s="60" t="s">
-        <v>468</v>
-      </c>
-      <c r="C11" s="60" t="s">
-        <v>469</v>
-      </c>
-      <c r="D11" s="61" t="s">
-        <v>470</v>
-      </c>
-      <c r="E11" s="60" t="s">
-        <v>471</v>
-      </c>
-      <c r="F11" s="62" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" s="56" customFormat="1">
-      <c r="A12" s="54" t="s">
-        <v>401</v>
-      </c>
-      <c r="B12" s="55"/>
-    </row>
-    <row r="13" spans="1:6" s="56" customFormat="1" ht="158.4">
-      <c r="A13" s="57" t="s">
-        <v>403</v>
-      </c>
-      <c r="B13" s="57" t="s">
-        <v>404</v>
-      </c>
-      <c r="C13" s="57" t="s">
-        <v>405</v>
-      </c>
-      <c r="D13" s="57" t="s">
-        <v>406</v>
-      </c>
-      <c r="E13" s="57" t="s">
-        <v>407</v>
-      </c>
-      <c r="F13" s="58" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" s="56" customFormat="1" ht="86.4">
-      <c r="A14" s="57" t="s">
-        <v>409</v>
-      </c>
-      <c r="B14" s="57" t="s">
-        <v>410</v>
-      </c>
-      <c r="C14" s="57" t="s">
-        <v>411</v>
-      </c>
-      <c r="D14" s="57" t="s">
-        <v>412</v>
-      </c>
-      <c r="E14" s="57" t="s">
-        <v>413</v>
-      </c>
-      <c r="F14" s="58" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" s="56" customFormat="1" ht="115.2">
-      <c r="A15" s="57" t="s">
-        <v>414</v>
-      </c>
-      <c r="B15" s="57" t="s">
-        <v>415</v>
-      </c>
-      <c r="C15" s="57" t="s">
-        <v>416</v>
-      </c>
-      <c r="D15" s="57" t="s">
-        <v>417</v>
-      </c>
-      <c r="E15" s="57" t="s">
-        <v>418</v>
-      </c>
-      <c r="F15" s="58" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" s="56" customFormat="1" ht="86.4">
-      <c r="A16" s="57" t="s">
-        <v>420</v>
-      </c>
-      <c r="B16" s="57" t="s">
-        <v>421</v>
-      </c>
-      <c r="C16" s="57" t="s">
-        <v>422</v>
-      </c>
-      <c r="D16" s="57" t="s">
-        <v>423</v>
-      </c>
-      <c r="E16" s="57" t="s">
-        <v>424</v>
-      </c>
-      <c r="F16" s="58" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" s="56" customFormat="1">
-      <c r="A17" s="54" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" s="56" customFormat="1" ht="86.4">
-      <c r="A18" s="57" t="s">
-        <v>426</v>
-      </c>
-      <c r="B18" s="57" t="s">
-        <v>427</v>
-      </c>
-      <c r="C18" s="57" t="s">
-        <v>425</v>
-      </c>
-      <c r="D18" s="57" t="s">
-        <v>428</v>
-      </c>
-      <c r="E18" s="57" t="s">
-        <v>429</v>
-      </c>
-      <c r="F18" s="58" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" s="56" customFormat="1" ht="72">
-      <c r="A19" s="57" t="s">
-        <v>430</v>
-      </c>
-      <c r="B19" s="57" t="s">
-        <v>431</v>
-      </c>
-      <c r="C19" s="57" t="s">
-        <v>432</v>
-      </c>
-      <c r="D19" s="57" t="s">
-        <v>433</v>
-      </c>
-      <c r="E19" s="57" t="s">
-        <v>434</v>
-      </c>
-      <c r="F19" s="58" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" s="56" customFormat="1" ht="57.6">
-      <c r="A20" s="57" t="s">
-        <v>436</v>
-      </c>
-      <c r="B20" s="57" t="s">
-        <v>437</v>
-      </c>
-      <c r="C20" s="57" t="s">
-        <v>438</v>
-      </c>
-      <c r="D20" s="57" t="s">
-        <v>439</v>
-      </c>
-      <c r="E20" s="57" t="s">
-        <v>440</v>
-      </c>
-      <c r="F20" s="58" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" s="56" customFormat="1" ht="43.2">
-      <c r="A21" s="57" t="s">
-        <v>442</v>
-      </c>
-      <c r="B21" s="57" t="s">
-        <v>443</v>
-      </c>
-      <c r="C21" s="57" t="s">
-        <v>444</v>
-      </c>
-      <c r="D21" s="57" t="s">
-        <v>445</v>
-      </c>
-      <c r="E21" s="57" t="s">
-        <v>446</v>
-      </c>
-      <c r="F21" s="58" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" s="56" customFormat="1" ht="86.4">
-      <c r="A22" s="57" t="s">
-        <v>448</v>
-      </c>
-      <c r="B22" s="57" t="s">
-        <v>449</v>
-      </c>
-      <c r="C22" s="57" t="s">
-        <v>450</v>
-      </c>
-      <c r="D22" s="57" t="s">
-        <v>451</v>
-      </c>
-      <c r="E22" s="57" t="s">
-        <v>452</v>
-      </c>
-      <c r="F22" s="58" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" s="56" customFormat="1">
-      <c r="A23" s="54" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" s="56" customFormat="1" ht="144">
-      <c r="A24" s="57" t="s">
-        <v>454</v>
-      </c>
-      <c r="B24" s="57" t="s">
-        <v>455</v>
-      </c>
-      <c r="C24" s="57" t="s">
-        <v>456</v>
-      </c>
-      <c r="D24" s="57" t="s">
-        <v>457</v>
-      </c>
-      <c r="E24" s="57" t="s">
-        <v>458</v>
-      </c>
-      <c r="F24" s="58" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" s="56" customFormat="1"/>
-    <row r="26" spans="1:6" s="56" customFormat="1"/>
-    <row r="27" spans="1:6" s="56" customFormat="1"/>
-    <row r="28" spans="1:6" s="56" customFormat="1"/>
-    <row r="29" spans="1:6" s="56" customFormat="1"/>
-    <row r="30" spans="1:6" s="56" customFormat="1"/>
-    <row r="31" spans="1:6" ht="57.6" customHeight="1"/>
-    <row r="32" spans="1:6" ht="43.2" customHeight="1"/>
-    <row r="33" ht="72" customHeight="1"/>
-    <row r="35" ht="115.2" customHeight="1"/>
-    <row r="36" ht="57.6" customHeight="1"/>
-    <row r="37" ht="86.4" customHeight="1"/>
-    <row r="38" ht="57.6" customHeight="1"/>
-    <row r="39" ht="57.6" customHeight="1"/>
-    <row r="41" ht="330" customHeight="1"/>
-    <row r="43" ht="66" customHeight="1"/>
-    <row r="44" ht="36.6" customHeight="1"/>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="F13" r:id="rId1" xr:uid="{0BC35BC1-A738-42F1-9F64-879FFEA9E3C5}"/>
-    <hyperlink ref="F14" r:id="rId2" xr:uid="{593523E3-A9C1-4546-B440-5B6B81E99A34}"/>
-    <hyperlink ref="F15" r:id="rId3" location="torefs" xr:uid="{C381662B-70B1-4BD0-8E64-4DC4ABCB1256}"/>
-    <hyperlink ref="F16" r:id="rId4" xr:uid="{FE8A6778-B8A4-4528-9084-CECA9B302D7D}"/>
-    <hyperlink ref="F18" r:id="rId5" xr:uid="{70739E9C-8EA0-47D7-88AF-EF73AD62676C}"/>
-    <hyperlink ref="F19" r:id="rId6" xr:uid="{30BE7754-8CE7-457D-BC9B-5FBCE4445A2C}"/>
-    <hyperlink ref="F20" r:id="rId7" xr:uid="{4FB7FFC4-AD0B-4B93-BE00-D014439426E0}"/>
-    <hyperlink ref="F21" r:id="rId8" xr:uid="{20E58446-133B-43AB-B41D-BF53FA621D61}"/>
-    <hyperlink ref="F22" r:id="rId9" xr:uid="{30C98C66-F3DA-4505-852C-9600AB78A563}"/>
-    <hyperlink ref="F24" r:id="rId10" xr:uid="{65E1B679-4FE0-4321-BD12-0AB5515BA93B}"/>
-    <hyperlink ref="F10" r:id="rId11" xr:uid="{1A38CE5F-1921-4E29-BBE0-6091BDA8F7C0}"/>
-    <hyperlink ref="F11" r:id="rId12" xr:uid="{C8FC45D7-DA7C-41E5-9D4D-9A7023E4050D}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7742DC2D-8356-42AF-A171-521A8B3CCEEA}">
-  <sheetPr>
-    <tabColor rgb="FFFFC000"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A2:F17"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="39.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="44.77734375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="33.109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="59.21875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="37.88671875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="64.33203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="7.77734375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="39.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.88671875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="72.6640625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="43.88671875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="7.77734375" style="2" customWidth="1"/>
-    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
-    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
-    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
-    <col min="19" max="19" width="49.21875" style="2" customWidth="1"/>
-    <col min="20" max="20" width="8.77734375" style="2" customWidth="1"/>
-    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
-    <col min="22" max="22" width="68.33203125" style="2" customWidth="1"/>
-    <col min="23" max="24" width="59.33203125" style="2" customWidth="1"/>
-    <col min="25" max="25" width="59.6640625" style="2" customWidth="1"/>
-    <col min="26" max="26" width="99.44140625" style="2" customWidth="1"/>
-    <col min="27" max="27" width="41.21875" style="2" customWidth="1"/>
-    <col min="28" max="28" width="8.77734375" style="2" customWidth="1"/>
-    <col min="29" max="16384" width="8.77734375" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:6">
-      <c r="A2" s="50"/>
-    </row>
-    <row r="4" spans="1:6" s="40" customFormat="1"/>
-    <row r="5" spans="1:6">
-      <c r="A5" s="41" t="s">
-        <v>268</v>
-      </c>
-      <c r="B5" s="41" t="s">
-        <v>269</v>
-      </c>
-      <c r="C5" s="41" t="s">
-        <v>271</v>
-      </c>
-      <c r="D5" s="41" t="s">
-        <v>272</v>
-      </c>
-      <c r="E5" s="41" t="s">
-        <v>270</v>
-      </c>
-      <c r="F5" s="41" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="72">
-      <c r="A6" s="57" t="s">
-        <v>473</v>
-      </c>
-      <c r="B6" s="57" t="s">
-        <v>474</v>
-      </c>
-      <c r="C6" s="57" t="s">
-        <v>475</v>
-      </c>
-      <c r="D6" s="57" t="s">
-        <v>476</v>
-      </c>
-      <c r="E6" s="57" t="s">
-        <v>477</v>
-      </c>
-      <c r="F6" s="58" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="86.4">
-      <c r="A7" s="57" t="s">
-        <v>479</v>
-      </c>
-      <c r="B7" s="57" t="s">
-        <v>480</v>
-      </c>
-      <c r="C7" s="57" t="s">
-        <v>475</v>
-      </c>
-      <c r="D7" s="57" t="s">
-        <v>481</v>
-      </c>
-      <c r="E7" s="57" t="s">
-        <v>482</v>
-      </c>
-      <c r="F7" s="58" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="72">
-      <c r="A8" s="57" t="s">
-        <v>483</v>
-      </c>
-      <c r="B8" s="57" t="s">
-        <v>484</v>
-      </c>
-      <c r="C8" s="57" t="s">
-        <v>485</v>
-      </c>
-      <c r="D8" s="57" t="s">
-        <v>486</v>
-      </c>
-      <c r="E8" s="57" t="s">
-        <v>487</v>
-      </c>
-      <c r="F8" s="58" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="86.4">
-      <c r="A9" s="57" t="s">
-        <v>488</v>
-      </c>
-      <c r="B9" s="57" t="s">
-        <v>489</v>
-      </c>
-      <c r="C9" s="57" t="s">
-        <v>485</v>
-      </c>
-      <c r="D9" s="57" t="s">
-        <v>490</v>
-      </c>
-      <c r="E9" s="57" t="s">
-        <v>491</v>
-      </c>
-      <c r="F9" s="58" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="72">
-      <c r="A10" s="57" t="s">
-        <v>492</v>
-      </c>
-      <c r="B10" s="57" t="s">
-        <v>493</v>
-      </c>
-      <c r="C10" s="57" t="s">
-        <v>494</v>
-      </c>
-      <c r="D10" s="57" t="s">
-        <v>495</v>
-      </c>
-      <c r="E10" s="57" t="s">
-        <v>496</v>
-      </c>
-      <c r="F10" s="58" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="72">
-      <c r="A11" s="57" t="s">
-        <v>497</v>
-      </c>
-      <c r="B11" s="57" t="s">
-        <v>498</v>
-      </c>
-      <c r="C11" s="57" t="s">
-        <v>494</v>
-      </c>
-      <c r="D11" s="57" t="s">
-        <v>499</v>
-      </c>
-      <c r="E11" s="57" t="s">
-        <v>500</v>
-      </c>
-      <c r="F11" s="58" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="86.4">
-      <c r="A12" s="57" t="s">
-        <v>501</v>
-      </c>
-      <c r="B12" s="57" t="s">
-        <v>502</v>
-      </c>
-      <c r="C12" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="D12" s="57" t="s">
-        <v>504</v>
-      </c>
-      <c r="E12" s="57" t="s">
-        <v>505</v>
-      </c>
-      <c r="F12" s="58" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="72">
-      <c r="A13" s="57" t="s">
-        <v>507</v>
-      </c>
-      <c r="B13" s="57" t="s">
-        <v>508</v>
-      </c>
-      <c r="C13" s="57" t="s">
-        <v>509</v>
-      </c>
-      <c r="D13" s="57" t="s">
-        <v>510</v>
-      </c>
-      <c r="E13" s="57" t="s">
-        <v>511</v>
-      </c>
-      <c r="F13" s="58" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="72">
-      <c r="A14" s="57" t="s">
-        <v>513</v>
-      </c>
-      <c r="B14" s="57" t="s">
-        <v>514</v>
-      </c>
-      <c r="C14" s="57" t="s">
-        <v>509</v>
-      </c>
-      <c r="D14" s="57" t="s">
-        <v>515</v>
-      </c>
-      <c r="E14" s="57" t="s">
-        <v>516</v>
-      </c>
-      <c r="F14" s="58" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="72">
-      <c r="A15" s="57" t="s">
-        <v>517</v>
-      </c>
-      <c r="B15" s="57" t="s">
-        <v>518</v>
-      </c>
-      <c r="C15" s="57" t="s">
-        <v>519</v>
-      </c>
-      <c r="D15" s="57" t="s">
-        <v>520</v>
-      </c>
-      <c r="E15" s="57" t="s">
-        <v>521</v>
-      </c>
-      <c r="F15" s="58" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="72">
-      <c r="A16" s="57" t="s">
-        <v>523</v>
-      </c>
-      <c r="B16" s="57" t="s">
-        <v>524</v>
-      </c>
-      <c r="C16" s="57" t="s">
-        <v>519</v>
-      </c>
-      <c r="D16" s="57" t="s">
-        <v>525</v>
-      </c>
-      <c r="E16" s="57" t="s">
-        <v>521</v>
-      </c>
-      <c r="F16" s="58" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="129.6">
-      <c r="A17" s="57" t="s">
-        <v>526</v>
-      </c>
-      <c r="B17" s="57" t="s">
-        <v>527</v>
-      </c>
-      <c r="C17" s="57" t="s">
-        <v>528</v>
-      </c>
-      <c r="D17" s="57" t="s">
-        <v>529</v>
-      </c>
-      <c r="E17" s="57" t="s">
-        <v>530</v>
-      </c>
-      <c r="F17" s="58" t="s">
-        <v>531</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="F6" r:id="rId1" xr:uid="{BCEDF5A9-AC9D-4B18-8FBC-704E1C4E35E0}"/>
-    <hyperlink ref="F7" r:id="rId2" xr:uid="{BF973FE4-46C9-45BD-A0D7-BDB80A784126}"/>
-    <hyperlink ref="F8" r:id="rId3" xr:uid="{276747C2-1EE8-4753-A0F4-4578E91151A9}"/>
-    <hyperlink ref="F9" r:id="rId4" xr:uid="{B5A71B51-F713-45BB-9829-67643F7D1D21}"/>
-    <hyperlink ref="F10" r:id="rId5" xr:uid="{8E4441EE-D698-4A6C-8D21-F92553B19E51}"/>
-    <hyperlink ref="F11" r:id="rId6" xr:uid="{07711047-0E0A-4356-AC98-13FCB68D4BE4}"/>
-    <hyperlink ref="F12" r:id="rId7" xr:uid="{18852E30-E696-4133-96A1-C252B084455B}"/>
-    <hyperlink ref="F13" r:id="rId8" xr:uid="{89843FA1-DC4B-4D5B-8552-9D3BA9234690}"/>
-    <hyperlink ref="F14" r:id="rId9" xr:uid="{3C0DDCF3-333B-4DEE-9CBB-B6585965FFB3}"/>
-    <hyperlink ref="F15" r:id="rId10" location="lifecycle-of-cached-instance" xr:uid="{26921D4F-4677-415E-B2D6-0776521C8D9F}"/>
-    <hyperlink ref="F16" r:id="rId11" location="lifecycle-of-cached-instance" xr:uid="{933483F2-6232-441A-B2FA-07FE98326D89}"/>
-    <hyperlink ref="F17" r:id="rId12" xr:uid="{F3874539-CD42-4120-94FA-AD48E696674F}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId13"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A618EC0-3EC6-431F-A43F-335526068004}">
-  <sheetPr>
-    <tabColor rgb="FFFFC000"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A2:D11"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="39.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="59.21875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="55.33203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="43.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="55.109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="67.88671875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="64.33203125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="7.77734375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="39.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="48.88671875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="72.6640625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="43.88671875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="7.77734375" style="2" customWidth="1"/>
-    <col min="14" max="14" width="56.77734375" style="2" customWidth="1"/>
-    <col min="15" max="15" width="46.77734375" style="2" customWidth="1"/>
-    <col min="16" max="16" width="62.88671875" style="2" customWidth="1"/>
-    <col min="17" max="17" width="49.21875" style="2" customWidth="1"/>
-    <col min="18" max="18" width="8.77734375" style="2" customWidth="1"/>
-    <col min="19" max="19" width="67.77734375" style="2" customWidth="1"/>
-    <col min="20" max="20" width="68.33203125" style="2" customWidth="1"/>
-    <col min="21" max="22" width="59.33203125" style="2" customWidth="1"/>
-    <col min="23" max="23" width="59.6640625" style="2" customWidth="1"/>
-    <col min="24" max="24" width="99.44140625" style="2" customWidth="1"/>
-    <col min="25" max="25" width="41.21875" style="2" customWidth="1"/>
-    <col min="26" max="26" width="8.77734375" style="2" customWidth="1"/>
-    <col min="27" max="16384" width="8.77734375" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:4">
-      <c r="A2" s="54" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="54" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="50" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" s="40" customFormat="1"/>
-    <row r="7" spans="1:4">
-      <c r="A7" s="41" t="s">
-        <v>268</v>
-      </c>
-      <c r="B7" s="41" t="s">
-        <v>272</v>
-      </c>
-      <c r="C7" s="41" t="s">
-        <v>270</v>
-      </c>
-      <c r="D7" s="41" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" s="56" customFormat="1">
-      <c r="A8" s="54" t="s">
-        <v>544</v>
-      </c>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="58"/>
-    </row>
-    <row r="9" spans="1:4" s="56" customFormat="1" ht="265.2" customHeight="1">
-      <c r="B9" s="57" t="s">
-        <v>763</v>
-      </c>
-      <c r="C9" s="75" t="s">
-        <v>764</v>
-      </c>
-      <c r="D9" s="58" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" s="56" customFormat="1">
-      <c r="A10" s="54" t="s">
-        <v>547</v>
-      </c>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="58"/>
-    </row>
-    <row r="11" spans="1:4" s="56" customFormat="1" ht="165" customHeight="1">
-      <c r="A11" s="56" t="s">
-        <v>562</v>
-      </c>
-      <c r="B11" s="57" t="s">
-        <v>748</v>
-      </c>
-      <c r="C11" s="57" t="s">
-        <v>752</v>
-      </c>
-      <c r="D11" s="58" t="s">
-        <v>276</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D9" r:id="rId1" xr:uid="{BCBCEA9E-F432-4A47-B60F-5B013B8D935F}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
-</worksheet>
 </file>
--- a/4 четверть_9_JavaScript_Vue 3 Composition API.xlsx
+++ b/4 четверть_9_JavaScript_Vue 3 Composition API.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAAA9B39-91B9-4B50-B82D-3948241688CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74AD8AB5-C62E-4E7D-BDE8-CD502E7568E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="17" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1368" yWindow="1104" windowWidth="23016" windowHeight="11136" firstSheet="7" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Литература" sheetId="14" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2024" uniqueCount="1644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2027" uniqueCount="1647">
   <si>
     <t>Vue</t>
   </si>
@@ -14447,117 +14447,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>default: () =&gt; ({ text: '' })	Каждый экземпляр получает свой уникальный объект → изоляция</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">&lt;!-- Parent.vue --&gt;
-&lt;template&gt;
-  &lt;UserForm 
-    </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>v-model:name</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>="userName"
-    v-model:email="userEmail"
-    v-model:age="userAge"
-  /&gt;
-&lt;/template&gt;
-&lt;script setup&gt;
-import { ref } from 'vue'
-import UserForm from './UserForm.vue'
-const userName = ref('Иван')
-const userEmail = ref('ivan@mail.com')
-const userAge = ref(25)
-&lt;/script&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">&lt;!-- UserForm.vue --&gt;
-&lt;script setup&gt;
-// Каждый v-model превращается в отдельный реактивный ref
-const name = </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>defineModel('name',</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> { default: '' })
-const email = defineModel('email', { default: '' })
-const age = defineModel('age', { default: 0 })
-&lt;/script&gt;
-&lt;template&gt;
-  &lt;div&gt;
-    &lt;input v-model="name" placeholder="Имя" /&gt;
-    &lt;input v-model="email" placeholder="Email" /&gt;
-    &lt;input v-model="age" type="number" placeholder="Возраст" /&gt;
-  &lt;/div&gt;
-&lt;/template&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Использование </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>нескольких v-model</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> на одном компоненте</t>
     </r>
   </si>
   <si>
@@ -39812,17 +39701,425 @@
       <t>// реактивно, то есть toRefs() нужен при деструктуризации</t>
     </r>
   </si>
+  <si>
+    <r>
+      <t>&lt;!-- Parent.vue --&gt;
+&lt;template&gt;
+  &lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>UserForm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>v-model:name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>="userName"
+    v-model:email="userEmail"
+    v-model:age="userAge"
+  /&gt;
+&lt;/template&gt;
+&lt;script setup&gt;
+import { ref } from 'vue'
+import UserForm from './UserForm.vue'
+const userName = ref('Иван')
+const userEmail = ref('ivan@mail.com')
+const userAge = ref(25)
+&lt;/script&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;!-- UserForm.vue --&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+&lt;script setup&gt;
+// Каждый v-model превращается в отдельный реактивный ref
+const name = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>defineModel('name',</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> { default: '' })
+const email = defineModel('email', { default: '' })
+const age = defineModel('age', { default: 0 })
+&lt;/script&gt;
+&lt;template&gt;
+  &lt;div&gt;
+    &lt;input v-model="name" placeholder="Имя" /&gt;
+    &lt;input v-model="email" placeholder="Email" /&gt;
+    &lt;input v-model="age" type="number" placeholder="Возраст" /&gt;
+  &lt;/div&gt;
+&lt;/template&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;hwc-panel
+    :title="$t('connection.connections')"
+    :caption="$t('connection.connectionNote')"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    v-model:search="connection.search"
+    v-model:edit="connection.edit"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    @add-item="addConnection"
+    icon="link"
+    searcheble
+    addable
+    expand&gt;
+    &lt;template v-slot:list&gt;
+      &lt;connection-list
+        v-model:connection="connection.selected"
+        :search="connection.search" /&gt;
+      &lt;tableselect
+        v-model:opened="tableSelectShow"
+        @select-table="createConnection" /&gt;
+    &lt;/template&gt;
+  &lt;/hwc-panel&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    props: {
+        </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>search</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: {
+            type: String,
+            default: () =&gt; '',
+        },
+        </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>edit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: {
+          type: Boolean,
+          default: () =&gt; false,
+        },
+    },
+   emits: [
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">        'update:search',
+        'update:edit',
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">         ...
+    ],</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Вариант 2 -</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> без defineModel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>v-model:search</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">="connection.search"
+эквивалентно:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:search</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">="connection.search"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@update:search</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">="connection.search = $event"
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Вариант 1 -</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>с defineModel</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="78">
+  <fonts count="79">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -40573,13 +40870,13 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="198">
+  <cellXfs count="199">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -40590,20 +40887,20 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="32" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="33" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -40612,122 +40909,122 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="25" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="38" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="53" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="37" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="52" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="60" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="59" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="60" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -40742,46 +41039,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="4" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="4" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -40790,77 +41087,77 @@
     <xf numFmtId="49" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="6" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="6" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="5" applyFill="1"/>
-    <xf numFmtId="49" fontId="14" fillId="7" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="5" applyFill="1"/>
+    <xf numFmtId="49" fontId="15" fillId="7" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="7" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="7" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="8" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="8" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="16" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="41" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="42" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="40" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -40869,97 +41166,97 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="16" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="16" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="16" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="16" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="42" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="43" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="42" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="43" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="42" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="43" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="38" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="8" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="8" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -40977,22 +41274,22 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -41004,71 +41301,71 @@
     <xf numFmtId="49" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="38" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="41" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="42" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="68" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="69" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -41077,77 +41374,80 @@
     <xf numFmtId="49" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="3" applyFill="1"/>
+    <xf numFmtId="49" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="72" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="43" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="43" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="43" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="3" applyFill="1"/>
-    <xf numFmtId="49" fontId="70" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="73" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="42" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="42" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="42" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -41156,10 +41456,10 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -41784,18 +42084,18 @@
     </row>
     <row r="4" spans="2:22">
       <c r="B4" s="2" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="C4" s="100" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
     </row>
     <row r="5" spans="2:22">
       <c r="B5" s="2" t="s">
-        <v>1409</v>
+        <v>1406</v>
       </c>
       <c r="C5" s="183" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
     </row>
     <row r="6" spans="2:22">
@@ -41803,23 +42103,23 @@
     </row>
     <row r="7" spans="2:22">
       <c r="B7" s="2" t="s">
-        <v>1408</v>
+        <v>1405</v>
       </c>
       <c r="C7" s="183" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="8" spans="2:22">
       <c r="B8" s="110" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="C8" s="189" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="9" spans="2:22">
       <c r="C9" s="110" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="11" spans="2:22">
@@ -41840,30 +42140,30 @@
     </row>
     <row r="19" spans="2:4">
       <c r="C19" s="187" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>1557</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="20" spans="2:4">
       <c r="B20" s="2" t="s">
-        <v>1560</v>
+        <v>1557</v>
       </c>
       <c r="C20" s="189" t="s">
-        <v>1558</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="21" spans="2:4" ht="115.2">
       <c r="C21" s="188" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C4:D11">
     <sortCondition ref="D4:D11"/>
   </sortState>
-  <phoneticPr fontId="33" type="noConversion"/>
+  <phoneticPr fontId="34" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -41919,7 +42219,7 @@
         <v>478</v>
       </c>
       <c r="B4" s="114" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -41946,7 +42246,7 @@
         <v>486</v>
       </c>
       <c r="B11" s="66" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="F11" s="71"/>
     </row>
@@ -41987,14 +42287,14 @@
         <v>478</v>
       </c>
       <c r="B15" s="112" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C15" s="69"/>
       <c r="D15" s="23" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="216">
@@ -42002,16 +42302,16 @@
         <v>478</v>
       </c>
       <c r="B16" s="113" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C16" s="113" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -42099,7 +42399,7 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="53" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="C2" s="87" t="s">
         <v>172</v>
@@ -42107,12 +42407,12 @@
     </row>
     <row r="3" spans="1:5">
       <c r="B3" s="153" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="B4" s="55" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -42122,17 +42422,17 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="53" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="23" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="23" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="39" customFormat="1">
@@ -42140,7 +42440,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="53" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="B12" s="55"/>
       <c r="C12" s="55"/>
@@ -42151,22 +42451,22 @@
         <v>482</v>
       </c>
       <c r="B13" s="88" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="C13" s="55" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D13" s="55"/>
     </row>
     <row r="14" spans="1:5" ht="158.4">
       <c r="A14" s="55" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="B14" s="150" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="C14" s="153" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="D14" s="55" t="s">
         <v>398</v>
@@ -42177,16 +42477,16 @@
         <v>484</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="C15" s="103" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="D15" s="55"/>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="23" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="B16" s="154" t="s">
         <v>172</v>
@@ -42194,148 +42494,148 @@
     </row>
     <row r="17" spans="1:4" ht="72">
       <c r="B17" s="155" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="72">
       <c r="A18" s="2" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="B18" s="38"/>
       <c r="C18" s="2" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="23" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="345.6">
       <c r="A20" s="55"/>
       <c r="C20" s="2" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="23" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="86.4">
       <c r="C22" s="2" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="43.2">
       <c r="A23" s="2" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="57.6">
       <c r="A25" s="2" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="57.6">
       <c r="A26" s="2" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="57.6">
       <c r="A27" s="2" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="86.4">
       <c r="A28" s="2" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="72">
       <c r="A29" s="2" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>751</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="100.8">
       <c r="A30" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>752</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="D30" s="100" t="s">
         <v>753</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>755</v>
-      </c>
-      <c r="D30" s="100" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="23" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="129.6">
       <c r="C32" s="2" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="86.4">
       <c r="A33" s="2" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="86.4">
       <c r="A34" s="2" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
     </row>
   </sheetData>
@@ -42383,7 +42683,7 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="23" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -42404,28 +42704,28 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="23" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="201.6">
       <c r="C11" s="2" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="23" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="288">
       <c r="B13" s="100" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
     </row>
   </sheetData>
@@ -42440,7 +42740,7 @@
     <tabColor rgb="FF0070C0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:V80"/>
+  <dimension ref="A2:V81"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
@@ -42509,14 +42809,14 @@
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="10" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="B7" s="4"/>
       <c r="D7" s="87"/>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="10" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="B8" s="4"/>
       <c r="D8" s="87"/>
@@ -42950,10 +43250,10 @@
         <v>668</v>
       </c>
       <c r="B31" s="111" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="C31" s="111" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="D31" s="68" t="s">
         <v>662</v>
@@ -42976,7 +43276,7 @@
     </row>
     <row r="32" spans="1:22" s="7" customFormat="1">
       <c r="A32" s="93" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="B32" s="68"/>
       <c r="C32" s="68" t="s">
@@ -43080,7 +43380,7 @@
     </row>
     <row r="36" spans="1:22" s="7" customFormat="1">
       <c r="A36" s="10" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B36" s="68"/>
       <c r="C36" s="68"/>
@@ -43102,14 +43402,14 @@
       <c r="V36" s="1"/>
     </row>
     <row r="37" spans="1:22" s="7" customFormat="1" ht="244.8">
-      <c r="A37" s="68" t="s">
-        <v>678</v>
-      </c>
-      <c r="B37" s="68" t="s">
-        <v>677</v>
-      </c>
-      <c r="C37" s="68" t="s">
-        <v>676</v>
+      <c r="A37" s="22" t="s">
+        <v>1646</v>
+      </c>
+      <c r="B37" s="198" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C37" s="198" t="s">
+        <v>1641</v>
       </c>
       <c r="D37" s="68"/>
       <c r="F37" s="1"/>
@@ -43128,17 +43428,17 @@
       <c r="U37" s="2"/>
       <c r="V37" s="1"/>
     </row>
-    <row r="38" spans="1:22" s="7" customFormat="1">
-      <c r="A38" s="10" t="s">
-        <v>679</v>
-      </c>
-      <c r="B38" s="68"/>
-      <c r="C38" s="68" t="s">
-        <v>687</v>
-      </c>
-      <c r="D38" s="68" t="s">
-        <v>686</v>
-      </c>
+    <row r="38" spans="1:22" s="7" customFormat="1" ht="273.60000000000002">
+      <c r="A38" s="198" t="s">
+        <v>1645</v>
+      </c>
+      <c r="B38" s="198" t="s">
+        <v>1644</v>
+      </c>
+      <c r="C38" s="198" t="s">
+        <v>1643</v>
+      </c>
+      <c r="D38" s="68"/>
       <c r="F38" s="1"/>
       <c r="G38" s="2"/>
       <c r="H38" s="1"/>
@@ -43155,16 +43455,16 @@
       <c r="U38" s="2"/>
       <c r="V38" s="1"/>
     </row>
-    <row r="39" spans="1:22" s="7" customFormat="1" ht="302.39999999999998">
-      <c r="A39" s="91"/>
-      <c r="B39" s="68" t="s">
-        <v>680</v>
-      </c>
+    <row r="39" spans="1:22" s="7" customFormat="1">
+      <c r="A39" s="10" t="s">
+        <v>676</v>
+      </c>
+      <c r="B39" s="68"/>
       <c r="C39" s="68" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="D39" s="68" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="2"/>
@@ -43182,14 +43482,16 @@
       <c r="U39" s="2"/>
       <c r="V39" s="1"/>
     </row>
-    <row r="40" spans="1:22" s="7" customFormat="1">
-      <c r="A40" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B40" s="12"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="1" t="s">
-        <v>38</v>
+    <row r="40" spans="1:22" s="7" customFormat="1" ht="302.39999999999998">
+      <c r="A40" s="91"/>
+      <c r="B40" s="68" t="s">
+        <v>677</v>
+      </c>
+      <c r="C40" s="68" t="s">
+        <v>678</v>
+      </c>
+      <c r="D40" s="68" t="s">
+        <v>679</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="2"/>
@@ -43207,16 +43509,14 @@
       <c r="U40" s="2"/>
       <c r="V40" s="1"/>
     </row>
-    <row r="41" spans="1:22" s="7" customFormat="1" ht="100.8">
-      <c r="A41" s="1"/>
-      <c r="B41" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C41" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D41" s="32" t="s">
-        <v>255</v>
+    <row r="41" spans="1:22" s="7" customFormat="1">
+      <c r="A41" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B41" s="12"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="2"/>
@@ -43234,18 +43534,16 @@
       <c r="U41" s="2"/>
       <c r="V41" s="1"/>
     </row>
-    <row r="42" spans="1:22" s="7" customFormat="1" ht="72">
-      <c r="A42" s="1" t="s">
-        <v>45</v>
-      </c>
+    <row r="42" spans="1:22" s="7" customFormat="1" ht="100.8">
+      <c r="A42" s="1"/>
       <c r="B42" s="13" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
+      </c>
+      <c r="D42" s="32" t="s">
+        <v>255</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="2"/>
@@ -43263,16 +43561,18 @@
       <c r="U42" s="2"/>
       <c r="V42" s="1"/>
     </row>
-    <row r="43" spans="1:22" s="7" customFormat="1" ht="172.8">
+    <row r="43" spans="1:22" s="7" customFormat="1" ht="72">
       <c r="A43" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="13"/>
-      <c r="C43" s="32" t="s">
-        <v>251</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="2"/>
@@ -43290,14 +43590,16 @@
       <c r="U43" s="2"/>
       <c r="V43" s="1"/>
     </row>
-    <row r="44" spans="1:22" s="7" customFormat="1">
-      <c r="A44" s="10" t="s">
-        <v>642</v>
-      </c>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14" t="s">
-        <v>106</v>
+    <row r="44" spans="1:22" s="7" customFormat="1" ht="172.8">
+      <c r="A44" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B44" s="13"/>
+      <c r="C44" s="32" t="s">
+        <v>251</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="2"/>
@@ -43316,12 +43618,14 @@
       <c r="V44" s="1"/>
     </row>
     <row r="45" spans="1:22" s="7" customFormat="1">
-      <c r="A45" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="B45" s="12"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="1"/>
+      <c r="A45" s="10" t="s">
+        <v>642</v>
+      </c>
+      <c r="B45" s="14"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="14" t="s">
+        <v>106</v>
+      </c>
       <c r="F45" s="1"/>
       <c r="G45" s="2"/>
       <c r="H45" s="1"/>
@@ -43338,19 +43642,13 @@
       <c r="U45" s="2"/>
       <c r="V45" s="1"/>
     </row>
-    <row r="46" spans="1:22" s="7" customFormat="1" ht="86.4">
-      <c r="A46" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B46" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="C46" s="32" t="s">
-        <v>250</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>33</v>
-      </c>
+    <row r="46" spans="1:22" s="7" customFormat="1">
+      <c r="A46" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B46" s="12"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="1"/>
       <c r="F46" s="1"/>
       <c r="G46" s="2"/>
       <c r="H46" s="1"/>
@@ -43367,13 +43665,19 @@
       <c r="U46" s="2"/>
       <c r="V46" s="1"/>
     </row>
-    <row r="47" spans="1:22" s="7" customFormat="1">
-      <c r="A47" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="1"/>
+    <row r="47" spans="1:22" s="7" customFormat="1" ht="86.4">
+      <c r="A47" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C47" s="32" t="s">
+        <v>250</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="F47" s="1"/>
       <c r="G47" s="2"/>
       <c r="H47" s="1"/>
@@ -43390,15 +43694,13 @@
       <c r="U47" s="2"/>
       <c r="V47" s="1"/>
     </row>
-    <row r="48" spans="1:22" s="7" customFormat="1" ht="72">
-      <c r="A48" s="2"/>
+    <row r="48" spans="1:22" s="7" customFormat="1">
+      <c r="A48" s="20" t="s">
+        <v>108</v>
+      </c>
       <c r="B48" s="14"/>
-      <c r="C48" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>110</v>
-      </c>
+      <c r="C48" s="14"/>
+      <c r="D48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="2"/>
       <c r="H48" s="1"/>
@@ -43415,14 +43717,14 @@
       <c r="U48" s="2"/>
       <c r="V48" s="1"/>
     </row>
-    <row r="49" spans="1:22" s="7" customFormat="1">
-      <c r="A49" s="10" t="s">
-        <v>111</v>
-      </c>
+    <row r="49" spans="1:22" s="7" customFormat="1" ht="72">
+      <c r="A49" s="2"/>
       <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="1" t="s">
-        <v>23</v>
+      <c r="C49" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="F49" s="1"/>
       <c r="G49" s="2"/>
@@ -43440,17 +43742,15 @@
       <c r="U49" s="2"/>
       <c r="V49" s="1"/>
     </row>
-    <row r="50" spans="1:22" s="7" customFormat="1" ht="86.4">
-      <c r="A50" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C50" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="D50" s="1"/>
+    <row r="50" spans="1:22" s="7" customFormat="1">
+      <c r="A50" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="B50" s="14"/>
+      <c r="C50" s="14"/>
+      <c r="D50" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="F50" s="1"/>
       <c r="G50" s="2"/>
       <c r="H50" s="1"/>
@@ -43469,15 +43769,15 @@
     </row>
     <row r="51" spans="1:22" s="7" customFormat="1" ht="86.4">
       <c r="A51" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="D51" s="2"/>
+        <v>119</v>
+      </c>
+      <c r="D51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="2"/>
       <c r="H51" s="1"/>
@@ -43496,17 +43796,15 @@
     </row>
     <row r="52" spans="1:22" s="7" customFormat="1" ht="86.4">
       <c r="A52" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B52" s="18" t="s">
-        <v>129</v>
+        <v>113</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>121</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="D52" s="2"/>
       <c r="F52" s="1"/>
       <c r="G52" s="2"/>
       <c r="H52" s="1"/>
@@ -43523,18 +43821,18 @@
       <c r="U52" s="2"/>
       <c r="V52" s="1"/>
     </row>
-    <row r="53" spans="1:22" s="7" customFormat="1" ht="115.2">
+    <row r="53" spans="1:22" s="7" customFormat="1" ht="86.4">
       <c r="A53" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>130</v>
+        <v>114</v>
+      </c>
+      <c r="B53" s="18" t="s">
+        <v>129</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F53" s="1"/>
       <c r="G53" s="2"/>
@@ -43552,17 +43850,19 @@
       <c r="U53" s="2"/>
       <c r="V53" s="1"/>
     </row>
-    <row r="54" spans="1:22" s="7" customFormat="1" ht="28.8">
+    <row r="54" spans="1:22" s="7" customFormat="1" ht="115.2">
       <c r="A54" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="D54" s="1"/>
+        <v>132</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>131</v>
+      </c>
       <c r="F54" s="1"/>
       <c r="G54" s="2"/>
       <c r="H54" s="1"/>
@@ -43579,19 +43879,17 @@
       <c r="U54" s="2"/>
       <c r="V54" s="1"/>
     </row>
-    <row r="55" spans="1:22" s="7" customFormat="1" ht="100.8">
+    <row r="55" spans="1:22" s="7" customFormat="1" ht="28.8">
       <c r="A55" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C55" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="D55" s="87" t="s">
-        <v>650</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="D55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="2"/>
       <c r="H55" s="1"/>
@@ -43608,17 +43906,19 @@
       <c r="U55" s="2"/>
       <c r="V55" s="1"/>
     </row>
-    <row r="56" spans="1:22" s="7" customFormat="1" ht="86.4">
-      <c r="A56" s="1" t="s">
-        <v>164</v>
+    <row r="56" spans="1:22" s="7" customFormat="1" ht="100.8">
+      <c r="A56" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C56" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="D56" s="1"/>
+        <v>136</v>
+      </c>
+      <c r="C56" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="D56" s="87" t="s">
+        <v>650</v>
+      </c>
       <c r="F56" s="1"/>
       <c r="G56" s="2"/>
       <c r="H56" s="1"/>
@@ -43635,15 +43935,15 @@
       <c r="U56" s="2"/>
       <c r="V56" s="1"/>
     </row>
-    <row r="57" spans="1:22" s="7" customFormat="1" ht="57.6">
+    <row r="57" spans="1:22" s="7" customFormat="1" ht="86.4">
       <c r="A57" s="1" t="s">
-        <v>124</v>
+        <v>164</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C57" s="18" t="s">
-        <v>125</v>
+        <v>122</v>
+      </c>
+      <c r="C57" s="21" t="s">
+        <v>123</v>
       </c>
       <c r="D57" s="1"/>
       <c r="F57" s="1"/>
@@ -43662,13 +43962,17 @@
       <c r="U57" s="2"/>
       <c r="V57" s="1"/>
     </row>
-    <row r="58" spans="1:22" s="7" customFormat="1">
-      <c r="A58" s="10" t="s">
-        <v>643</v>
-      </c>
-      <c r="B58" s="12"/>
-      <c r="C58" s="13"/>
-      <c r="D58" s="2"/>
+    <row r="58" spans="1:22" s="7" customFormat="1" ht="57.6">
+      <c r="A58" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C58" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="D58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="2"/>
       <c r="H58" s="1"/>
@@ -43685,19 +43989,13 @@
       <c r="U58" s="2"/>
       <c r="V58" s="1"/>
     </row>
-    <row r="59" spans="1:22" s="7" customFormat="1" ht="100.8">
-      <c r="A59" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="B59" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="C59" s="32" t="s">
-        <v>252</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>257</v>
-      </c>
+    <row r="59" spans="1:22" s="7" customFormat="1">
+      <c r="A59" s="10" t="s">
+        <v>643</v>
+      </c>
+      <c r="B59" s="12"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="2"/>
       <c r="F59" s="1"/>
       <c r="G59" s="2"/>
       <c r="H59" s="1"/>
@@ -43716,16 +44014,16 @@
     </row>
     <row r="60" spans="1:22" s="7" customFormat="1" ht="100.8">
       <c r="A60" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C60" s="32" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F60" s="1"/>
       <c r="G60" s="2"/>
@@ -43743,17 +44041,19 @@
       <c r="U60" s="2"/>
       <c r="V60" s="1"/>
     </row>
-    <row r="61" spans="1:22" s="7" customFormat="1" ht="86.4">
+    <row r="61" spans="1:22" s="7" customFormat="1" ht="100.8">
       <c r="A61" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C61" s="32" t="s">
-        <v>254</v>
-      </c>
-      <c r="D61" s="1"/>
+        <v>253</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>259</v>
+      </c>
       <c r="F61" s="1"/>
       <c r="G61" s="2"/>
       <c r="H61" s="1"/>
@@ -43770,15 +44070,17 @@
       <c r="U61" s="2"/>
       <c r="V61" s="1"/>
     </row>
-    <row r="62" spans="1:22" s="7" customFormat="1">
-      <c r="A62" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="B62" s="2"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="1" t="s">
-        <v>138</v>
-      </c>
+    <row r="62" spans="1:22" s="7" customFormat="1" ht="86.4">
+      <c r="A62" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B62" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C62" s="32" t="s">
+        <v>254</v>
+      </c>
+      <c r="D62" s="1"/>
       <c r="F62" s="1"/>
       <c r="G62" s="2"/>
       <c r="H62" s="1"/>
@@ -43796,12 +44098,14 @@
       <c r="V62" s="1"/>
     </row>
     <row r="63" spans="1:22" s="7" customFormat="1">
-      <c r="A63" s="2" t="s">
-        <v>139</v>
+      <c r="A63" s="10" t="s">
+        <v>137</v>
       </c>
       <c r="B63" s="2"/>
-      <c r="C63" s="9"/>
-      <c r="D63" s="2"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="F63" s="1"/>
       <c r="G63" s="2"/>
       <c r="H63" s="1"/>
@@ -43820,11 +44124,11 @@
     </row>
     <row r="64" spans="1:22" s="7" customFormat="1">
       <c r="A64" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" s="9"/>
-      <c r="D64" s="1"/>
+      <c r="D64" s="2"/>
       <c r="F64" s="1"/>
       <c r="G64" s="2"/>
       <c r="H64" s="1"/>
@@ -43843,11 +44147,9 @@
     </row>
     <row r="65" spans="1:22" s="7" customFormat="1">
       <c r="A65" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>157</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="B65" s="2"/>
       <c r="C65" s="9"/>
       <c r="D65" s="1"/>
       <c r="F65" s="1"/>
@@ -43868,9 +44170,11 @@
     </row>
     <row r="66" spans="1:22" s="7" customFormat="1">
       <c r="A66" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B66" s="2"/>
+        <v>158</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>157</v>
+      </c>
       <c r="C66" s="9"/>
       <c r="D66" s="1"/>
       <c r="F66" s="1"/>
@@ -43891,7 +44195,7 @@
     </row>
     <row r="67" spans="1:22" s="7" customFormat="1">
       <c r="A67" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" s="9"/>
@@ -43914,7 +44218,7 @@
     </row>
     <row r="68" spans="1:22" s="7" customFormat="1">
       <c r="A68" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" s="9"/>
@@ -43937,7 +44241,7 @@
     </row>
     <row r="69" spans="1:22" s="7" customFormat="1">
       <c r="A69" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="9"/>
@@ -43960,10 +44264,10 @@
     </row>
     <row r="70" spans="1:22" s="7" customFormat="1">
       <c r="A70" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B70" s="2"/>
-      <c r="C70" s="4"/>
+      <c r="C70" s="9"/>
       <c r="D70" s="1"/>
       <c r="F70" s="1"/>
       <c r="G70" s="2"/>
@@ -43983,7 +44287,7 @@
     </row>
     <row r="71" spans="1:22" s="7" customFormat="1">
       <c r="A71" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" s="4"/>
@@ -44004,14 +44308,12 @@
       <c r="U71" s="2"/>
       <c r="V71" s="1"/>
     </row>
-    <row r="72" spans="1:22" s="7" customFormat="1" ht="86.4">
-      <c r="A72" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="B72" s="21"/>
-      <c r="C72" s="21" t="s">
-        <v>153</v>
-      </c>
+    <row r="72" spans="1:22" s="7" customFormat="1">
+      <c r="A72" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B72" s="2"/>
+      <c r="C72" s="4"/>
       <c r="D72" s="1"/>
       <c r="F72" s="1"/>
       <c r="G72" s="2"/>
@@ -44029,19 +44331,15 @@
       <c r="U72" s="2"/>
       <c r="V72" s="1"/>
     </row>
-    <row r="73" spans="1:22" s="7" customFormat="1" ht="57.6">
+    <row r="73" spans="1:22" s="7" customFormat="1" ht="86.4">
       <c r="A73" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="B73" s="21" t="s">
-        <v>160</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="B73" s="21"/>
       <c r="C73" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="D73" s="21" t="s">
-        <v>161</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="D73" s="1"/>
       <c r="F73" s="1"/>
       <c r="G73" s="2"/>
       <c r="H73" s="1"/>
@@ -44058,15 +44356,19 @@
       <c r="U73" s="2"/>
       <c r="V73" s="1"/>
     </row>
-    <row r="74" spans="1:22" s="7" customFormat="1" ht="28.8">
-      <c r="A74" s="1" t="s">
-        <v>145</v>
+    <row r="74" spans="1:22" s="7" customFormat="1" ht="57.6">
+      <c r="A74" s="21" t="s">
+        <v>154</v>
       </c>
       <c r="B74" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="C74" s="4"/>
-      <c r="D74" s="1"/>
+        <v>160</v>
+      </c>
+      <c r="C74" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="D74" s="21" t="s">
+        <v>161</v>
+      </c>
       <c r="F74" s="1"/>
       <c r="G74" s="2"/>
       <c r="H74" s="1"/>
@@ -44083,11 +44385,13 @@
       <c r="U74" s="2"/>
       <c r="V74" s="1"/>
     </row>
-    <row r="75" spans="1:22" s="7" customFormat="1">
+    <row r="75" spans="1:22" s="7" customFormat="1" ht="28.8">
       <c r="A75" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B75" s="2"/>
+        <v>145</v>
+      </c>
+      <c r="B75" s="21" t="s">
+        <v>165</v>
+      </c>
       <c r="C75" s="4"/>
       <c r="D75" s="1"/>
       <c r="F75" s="1"/>
@@ -44108,7 +44412,7 @@
     </row>
     <row r="76" spans="1:22" s="7" customFormat="1">
       <c r="A76" s="1" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" s="4"/>
@@ -44129,16 +44433,12 @@
       <c r="U76" s="2"/>
       <c r="V76" s="1"/>
     </row>
-    <row r="77" spans="1:22" s="7" customFormat="1" ht="28.8">
+    <row r="77" spans="1:22" s="7" customFormat="1">
       <c r="A77" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B77" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="C77" s="21" t="s">
-        <v>151</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="B77" s="2"/>
+      <c r="C77" s="4"/>
       <c r="D77" s="1"/>
       <c r="F77" s="1"/>
       <c r="G77" s="2"/>
@@ -44156,15 +44456,15 @@
       <c r="U77" s="2"/>
       <c r="V77" s="1"/>
     </row>
-    <row r="78" spans="1:22" s="7" customFormat="1">
+    <row r="78" spans="1:22" s="7" customFormat="1" ht="28.8">
       <c r="A78" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C78" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
+      </c>
+      <c r="B78" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="C78" s="21" t="s">
+        <v>151</v>
       </c>
       <c r="D78" s="1"/>
       <c r="F78" s="1"/>
@@ -44184,11 +44484,15 @@
       <c r="V78" s="1"/>
     </row>
     <row r="79" spans="1:22" s="7" customFormat="1">
-      <c r="A79" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="B79" s="2"/>
-      <c r="C79" s="4"/>
+      <c r="A79" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C79" s="22" t="s">
+        <v>149</v>
+      </c>
       <c r="D79" s="1"/>
       <c r="F79" s="1"/>
       <c r="G79" s="2"/>
@@ -44206,14 +44510,12 @@
       <c r="U79" s="2"/>
       <c r="V79" s="1"/>
     </row>
-    <row r="80" spans="1:22" s="7" customFormat="1" ht="144">
-      <c r="A80" s="1" t="s">
-        <v>172</v>
+    <row r="80" spans="1:22" s="7" customFormat="1">
+      <c r="A80" s="10" t="s">
+        <v>171</v>
       </c>
       <c r="B80" s="2"/>
-      <c r="C80" s="25" t="s">
-        <v>170</v>
-      </c>
+      <c r="C80" s="4"/>
       <c r="D80" s="1"/>
       <c r="F80" s="1"/>
       <c r="G80" s="2"/>
@@ -44230,6 +44532,31 @@
       <c r="T80" s="8"/>
       <c r="U80" s="2"/>
       <c r="V80" s="1"/>
+    </row>
+    <row r="81" spans="1:22" s="7" customFormat="1" ht="144">
+      <c r="A81" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B81" s="2"/>
+      <c r="C81" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="D81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+      <c r="K81" s="1"/>
+      <c r="L81" s="1"/>
+      <c r="M81" s="1"/>
+      <c r="N81" s="1"/>
+      <c r="P81" s="2"/>
+      <c r="Q81" s="2"/>
+      <c r="R81" s="2"/>
+      <c r="S81" s="1"/>
+      <c r="T81" s="8"/>
+      <c r="U81" s="2"/>
+      <c r="V81" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -44504,17 +44831,17 @@
         <v>181</v>
       </c>
       <c r="C2" s="92" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="3" spans="1:21">
       <c r="A3" s="20" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
     </row>
     <row r="4" spans="1:21">
       <c r="A4" s="20" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="5" spans="1:21">
@@ -44524,7 +44851,7 @@
     </row>
     <row r="6" spans="1:21">
       <c r="A6" s="10" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="8" spans="1:21" s="3" customFormat="1">
@@ -44551,140 +44878,140 @@
         <v>181</v>
       </c>
       <c r="B11" s="152" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="C11" s="115" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="D11" s="115" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="273.60000000000002">
       <c r="B12" s="2" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="D12" s="140" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="13" spans="1:21">
       <c r="A13" s="23" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="C13" s="140"/>
     </row>
     <row r="14" spans="1:21">
       <c r="A14" s="140" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="C14" s="140" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="15" spans="1:21">
       <c r="A15" s="140" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="C15" s="140" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="16" spans="1:21">
       <c r="A16" s="140" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="C16" s="140" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="17" spans="1:20">
       <c r="A17" s="140" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="C17" s="140" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="18" spans="1:20">
       <c r="A18" s="140" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="C18" s="140" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="19" spans="1:20">
       <c r="A19" s="140" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="C19" s="140" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="20" spans="1:20">
       <c r="A20" s="140" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="C20" s="140" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="21" spans="1:20">
       <c r="A21" s="23" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
     </row>
     <row r="22" spans="1:20" ht="28.8">
       <c r="A22" s="142" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="B22" s="145" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="C22" s="142" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="D22" s="142"/>
     </row>
     <row r="23" spans="1:20" ht="86.4">
       <c r="A23" s="142" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="B23" s="145" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="C23" s="142" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D23" s="142" t="s">
         <v>1038</v>
-      </c>
-      <c r="D23" s="142" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="24" spans="1:20" ht="115.2">
@@ -44692,106 +45019,106 @@
         <v>645</v>
       </c>
       <c r="B24" s="141" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="C24" s="146" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="D24" s="141" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="28.8">
       <c r="A25" s="141" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="B25" s="147" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="C25" s="146" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="D25" s="141" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="26" spans="1:20">
       <c r="A26" s="141" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B26" s="141" t="s">
         <v>1019</v>
       </c>
-      <c r="B26" s="141" t="s">
-        <v>1022</v>
-      </c>
       <c r="C26" s="146" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="D26" s="141" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="27" spans="1:20">
       <c r="A27" s="141" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B27" s="141" t="s">
         <v>1023</v>
       </c>
-      <c r="B27" s="141" t="s">
-        <v>1026</v>
-      </c>
       <c r="C27" s="146" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="D27" s="141" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="28" spans="1:20" ht="187.2">
       <c r="A28" s="141" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="B28" s="147" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C28" s="146" t="s">
         <v>1043</v>
       </c>
-      <c r="C28" s="146" t="s">
-        <v>1046</v>
-      </c>
       <c r="D28" s="141" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="29" spans="1:20" ht="28.8">
       <c r="A29" s="141" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="B29" s="147" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="C29" s="146" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="D29" s="141" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="30" spans="1:20" ht="28.8">
       <c r="A30" s="143" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B30" s="145" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C30" s="144" t="s">
         <v>1034</v>
-      </c>
-      <c r="B30" s="145" t="s">
-        <v>1043</v>
-      </c>
-      <c r="C30" s="144" t="s">
-        <v>1037</v>
       </c>
       <c r="D30" s="144"/>
     </row>
     <row r="31" spans="1:20" ht="28.8">
       <c r="A31" s="143" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="B31" s="145" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="C31" s="144" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="D31" s="144"/>
     </row>
@@ -44813,7 +45140,7 @@
     <row r="33" spans="1:20" s="148" customFormat="1" ht="57.6">
       <c r="B33" s="133"/>
       <c r="C33" s="149" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="D33" s="150"/>
       <c r="E33" s="3"/>
@@ -44827,10 +45154,10 @@
     <row r="34" spans="1:20" s="148" customFormat="1" ht="186.6" customHeight="1">
       <c r="B34" s="133"/>
       <c r="C34" s="149" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="D34" s="149" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="133"/>
@@ -44842,7 +45169,7 @@
     </row>
     <row r="35" spans="1:20">
       <c r="A35" s="10" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>2</v>
@@ -44937,7 +45264,7 @@
         <v>355</v>
       </c>
       <c r="B42" s="55" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="C42" s="55" t="s">
         <v>528</v>
@@ -45090,25 +45417,25 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="138" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="B2" s="88" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="53" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="53" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="53" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="39" customFormat="1">
@@ -45116,80 +45443,80 @@
     </row>
     <row r="9" spans="1:5" ht="28.8">
       <c r="A9" s="53" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="B9" s="114" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="144">
       <c r="C10" s="111" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="20" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="115.2">
       <c r="C12" s="2" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="30" customHeight="1">
       <c r="A13" s="138" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="B13" s="114" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="20" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="28.8">
       <c r="B15" s="2" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="20" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="115.2">
       <c r="B17" s="2" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="20" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="57.6">
       <c r="B19" s="2" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="28.8">
       <c r="A20" s="20" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="B20" s="114" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="C20" s="114" t="s">
         <v>62</v>
@@ -45200,106 +45527,106 @@
     </row>
     <row r="21" spans="1:4" ht="43.2">
       <c r="B21" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>984</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>987</v>
-      </c>
       <c r="D21" s="2" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="20" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="20" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="115.2">
       <c r="B25" s="111" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="139" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="B26" s="111" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="216">
       <c r="B27" s="111" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="53" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="72">
       <c r="B29" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>966</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="187.2">
       <c r="B30" s="2" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="20" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="86.4">
       <c r="A32" s="2" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="B32" s="140" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="43.2">
       <c r="A33" s="2" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="B33" s="140" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="331.2">
       <c r="A34" s="2" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="B34" s="111" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
     </row>
   </sheetData>
@@ -45678,7 +46005,7 @@
         <v>487</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -45841,16 +46168,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="53" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" ht="86.4">
       <c r="C15" s="88" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="D15" s="111" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="F15" s="2"/>
     </row>
@@ -45859,7 +46186,7 @@
         <v>651</v>
       </c>
       <c r="D16" s="111" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="F16" s="2"/>
     </row>
@@ -46004,19 +46331,19 @@
         <v>629</v>
       </c>
       <c r="D29" s="111" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="374.4">
       <c r="A30" s="58"/>
       <c r="C30" s="111" t="s">
+        <v>952</v>
+      </c>
+      <c r="D30" s="111" t="s">
         <v>955</v>
       </c>
-      <c r="D30" s="111" t="s">
-        <v>958</v>
-      </c>
       <c r="E30" s="111" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -46579,30 +46906,30 @@
   <sheetData>
     <row r="2" spans="1:6">
       <c r="A2" s="23" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="57.6">
       <c r="A3" s="53" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="57.6">
       <c r="A4" s="53" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="72">
       <c r="A5" s="53" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="53" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="39" customFormat="1">
@@ -46610,91 +46937,91 @@
     </row>
     <row r="9" spans="1:6" s="133" customFormat="1">
       <c r="A9" s="23" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="133" customFormat="1">
       <c r="A10" s="134" t="s">
+        <v>894</v>
+      </c>
+      <c r="C10" s="133" t="s">
         <v>897</v>
-      </c>
-      <c r="C10" s="133" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="11" spans="1:6" s="133" customFormat="1" ht="86.4">
       <c r="A11" s="133" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="B11" s="135" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="C11" s="133" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="133" customFormat="1" ht="57.6">
       <c r="A12" s="133" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="C12" s="133" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="57.6">
       <c r="A13" s="53" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="C13" s="114" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="D13" s="114" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="E13" s="130"/>
       <c r="F13" s="56"/>
     </row>
     <row r="14" spans="1:6" ht="144">
       <c r="B14" s="111" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>870</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>873</v>
       </c>
       <c r="E14" s="130"/>
       <c r="F14" s="56"/>
     </row>
     <row r="15" spans="1:6" ht="231" customHeight="1">
       <c r="A15" s="22" t="s">
+        <v>888</v>
+      </c>
+      <c r="B15" s="111" t="s">
+        <v>890</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>891</v>
-      </c>
-      <c r="B15" s="111" t="s">
-        <v>893</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>894</v>
       </c>
       <c r="E15" s="130"/>
       <c r="F15" s="56"/>
     </row>
     <row r="16" spans="1:6" ht="86.4">
       <c r="A16" s="2" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="B16" s="111" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="E16" s="130"/>
       <c r="F16" s="56"/>
     </row>
     <row r="17" spans="1:6" ht="172.8">
       <c r="A17" s="55" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="B17" s="55"/>
       <c r="C17" s="55" t="s">
@@ -46706,13 +47033,13 @@
     </row>
     <row r="18" spans="1:6" ht="216">
       <c r="A18" s="55" t="s">
+        <v>883</v>
+      </c>
+      <c r="B18" s="113" t="s">
         <v>886</v>
       </c>
-      <c r="B18" s="113" t="s">
-        <v>889</v>
-      </c>
       <c r="C18" s="132" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="D18" s="55"/>
       <c r="E18" s="130"/>
@@ -46721,10 +47048,10 @@
     <row r="19" spans="1:6" ht="144">
       <c r="A19" s="55"/>
       <c r="B19" s="113" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="C19" s="132" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="D19" s="55"/>
       <c r="E19" s="130"/>
@@ -46732,14 +47059,14 @@
     </row>
     <row r="20" spans="1:6" ht="57.6">
       <c r="A20" s="53" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="B20" s="55"/>
       <c r="C20" s="114" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="D20" s="114" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="E20" s="130"/>
       <c r="F20" s="56"/>
@@ -46747,24 +47074,24 @@
     <row r="21" spans="1:6" ht="244.8">
       <c r="A21" s="55"/>
       <c r="B21" s="113" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="C21" s="55" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="D21" s="55" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="E21" s="130"/>
       <c r="F21" s="56"/>
     </row>
     <row r="22" spans="1:6" ht="72">
       <c r="A22" s="131" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="B22" s="55"/>
       <c r="C22" s="113" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="D22" s="55"/>
       <c r="E22" s="130"/>
@@ -46788,7 +47115,7 @@
         <v>524</v>
       </c>
       <c r="C24" s="55" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="D24" s="55" t="s">
         <v>525</v>
@@ -46907,7 +47234,7 @@
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="104" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="73"/>
@@ -47161,22 +47488,22 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="53" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="23" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="23" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="23" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="39" customFormat="1">
@@ -47184,7 +47511,7 @@
     </row>
     <row r="8" spans="1:5" s="54" customFormat="1">
       <c r="A8" s="53" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="B8" s="55"/>
       <c r="C8" s="55"/>
@@ -47194,37 +47521,37 @@
       <c r="A9" s="55"/>
       <c r="B9" s="55"/>
       <c r="C9" s="184" t="s">
-        <v>1411</v>
+        <v>1408</v>
       </c>
       <c r="E9" s="71"/>
     </row>
     <row r="10" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A10" s="55" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B10" s="55" t="s">
         <v>1412</v>
       </c>
-      <c r="B10" s="55" t="s">
-        <v>1415</v>
-      </c>
       <c r="C10" s="184" t="s">
-        <v>1416</v>
+        <v>1413</v>
       </c>
       <c r="E10" s="71"/>
     </row>
     <row r="11" spans="1:5" s="54" customFormat="1" ht="43.2">
       <c r="A11" s="55" t="s">
-        <v>1413</v>
+        <v>1410</v>
       </c>
       <c r="B11" s="55" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C11" s="55" t="s">
         <v>1414</v>
-      </c>
-      <c r="C11" s="55" t="s">
-        <v>1417</v>
       </c>
       <c r="E11" s="71"/>
     </row>
     <row r="12" spans="1:5" s="54" customFormat="1">
       <c r="A12" s="53" t="s">
-        <v>1420</v>
+        <v>1417</v>
       </c>
       <c r="B12" s="55"/>
       <c r="C12" s="55"/>
@@ -47235,13 +47562,13 @@
         <v>62</v>
       </c>
       <c r="B13" s="55" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="C13" s="54" t="s">
-        <v>1418</v>
+        <v>1415</v>
       </c>
       <c r="D13" s="54" t="s">
-        <v>1419</v>
+        <v>1416</v>
       </c>
       <c r="E13" s="71"/>
     </row>
@@ -47250,18 +47577,18 @@
         <v>43</v>
       </c>
       <c r="B14" s="55" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="43.2">
       <c r="A15" s="2" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="244.8">
@@ -47269,109 +47596,109 @@
         <v>270</v>
       </c>
       <c r="B16" s="111" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="23" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="230.4">
       <c r="C18" s="2" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28.8">
       <c r="A19" s="23" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="B19" s="183" t="s">
-        <v>1410</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="20" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="100.8">
       <c r="B21" s="2" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="20" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="86.4">
       <c r="B23" s="2" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="20" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="100.8">
       <c r="B25" s="2" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="20" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="100.8">
       <c r="B27" s="2" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="28.8">
       <c r="A28" s="20" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="345.6">
       <c r="C29" s="2" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="28.8">
       <c r="A30" s="23" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="43.2">
       <c r="C31" s="111" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
     </row>
   </sheetData>
@@ -47421,32 +47748,32 @@
   <sheetData>
     <row r="2" spans="1:6">
       <c r="A2" s="23" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="23" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="B4" s="20" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="B5" s="20" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="B6" s="20" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="B7" s="20" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="39" customFormat="1">
@@ -47455,7 +47782,7 @@
     <row r="10" spans="1:6" s="133" customFormat="1"/>
     <row r="11" spans="1:6">
       <c r="A11" s="23" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="D11" s="40"/>
       <c r="E11" s="156"/>
@@ -47463,7 +47790,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="20" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="D12" s="40"/>
       <c r="E12" s="156"/>
@@ -47471,10 +47798,10 @@
     </row>
     <row r="13" spans="1:6" ht="72">
       <c r="B13" s="176" t="s">
-        <v>1402</v>
+        <v>1399</v>
       </c>
       <c r="C13" s="169" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="D13" s="40"/>
       <c r="E13" s="156"/>
@@ -47482,7 +47809,7 @@
     </row>
     <row r="14" spans="1:6" ht="72">
       <c r="C14" s="169" t="s">
-        <v>1401</v>
+        <v>1398</v>
       </c>
       <c r="D14" s="40"/>
       <c r="E14" s="156"/>
@@ -47490,13 +47817,13 @@
     </row>
     <row r="15" spans="1:6" ht="28.8">
       <c r="A15" s="2" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="C15" s="93" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="D15" s="40"/>
       <c r="E15" s="156"/>
@@ -47504,13 +47831,13 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="C16" s="93" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="D16" s="40"/>
       <c r="E16" s="156"/>
@@ -47518,10 +47845,10 @@
     </row>
     <row r="17" spans="1:6" ht="100.8">
       <c r="B17" s="169" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="C17" s="93" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="D17" s="40"/>
       <c r="E17" s="156"/>
@@ -47529,7 +47856,7 @@
     </row>
     <row r="18" spans="1:6" ht="100.8">
       <c r="C18" s="93" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="D18" s="40"/>
       <c r="E18" s="156"/>
@@ -47537,13 +47864,13 @@
     </row>
     <row r="19" spans="1:6" ht="28.8">
       <c r="A19" s="2" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="B19" s="140" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="C19" s="93" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="D19" s="40"/>
       <c r="E19" s="156"/>
@@ -47551,13 +47878,13 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="C20" s="93" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="D20" s="40"/>
       <c r="E20" s="156"/>
@@ -47565,83 +47892,83 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="23" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="B22" s="2" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="72">
       <c r="B23" s="140" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="B24" s="2" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="172.8">
       <c r="C25" s="2" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="20" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="288">
       <c r="C27" s="2" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="20" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="B28" s="114" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="331.2">
       <c r="B29" s="2" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="C29" s="140" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="20" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="158.4">
       <c r="B31" s="2" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="20" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="33" spans="3:3" ht="187.2">
       <c r="C33" s="2" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="33" type="noConversion"/>
+  <phoneticPr fontId="34" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -47688,50 +48015,50 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="23" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="23" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="23" t="s">
-        <v>1310</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="23" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="175" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="175" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="175" t="s">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="D8" s="178" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="197" t="s">
-        <v>1365</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="175" t="s">
-        <v>1607</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="39" customFormat="1">
@@ -47739,14 +48066,14 @@
     </row>
     <row r="13" spans="1:5" s="133" customFormat="1">
       <c r="C13" s="168" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
       <c r="D13" s="172"/>
       <c r="E13" s="70"/>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="23" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="B14" s="169"/>
     </row>
@@ -47756,7 +48083,7 @@
         <v>62</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -47764,7 +48091,7 @@
         <v>43</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -47772,25 +48099,25 @@
         <v>64</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="B18" s="2" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="201.6">
       <c r="C19" s="2" t="s">
-        <v>1383</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="175" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
       <c r="B20" s="23" t="s">
         <v>62</v>
@@ -47800,80 +48127,80 @@
     </row>
     <row r="21" spans="1:4" ht="72">
       <c r="A21" s="2" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>1292</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>1298</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>1295</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="72">
       <c r="A22" s="2" t="s">
-        <v>1293</v>
+        <v>1290</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1299</v>
+        <v>1296</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="72">
       <c r="A23" s="2" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>1299</v>
+        <v>1296</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="168" t="s">
-        <v>1306</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="28.8">
       <c r="B25" s="2" t="s">
-        <v>1300</v>
+        <v>1297</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="57.6">
       <c r="B26" s="2" t="s">
-        <v>1303</v>
+        <v>1300</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="115.2">
       <c r="A27" s="2" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1305</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="72">
       <c r="A28" s="2" t="s">
-        <v>1293</v>
+        <v>1290</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="168" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>43</v>
@@ -47881,63 +48208,63 @@
     </row>
     <row r="30" spans="1:4" ht="201.6">
       <c r="C30" s="2" t="s">
-        <v>1308</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="23" t="s">
-        <v>1310</v>
+        <v>1307</v>
       </c>
       <c r="B31" s="23"/>
       <c r="C31" s="23"/>
       <c r="D31" s="23" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="43.2">
       <c r="A32" s="2" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
       <c r="B32" s="169" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="D32" s="170"/>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="176" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="C34" s="2" t="s">
-        <v>1314</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="23" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="302.39999999999998">
       <c r="A36" s="2" t="s">
-        <v>1317</v>
+        <v>1314</v>
       </c>
       <c r="B36" s="189" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>1379</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="28.8">
       <c r="A37" s="177" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
       <c r="B37" s="169" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
       <c r="C37" s="169"/>
     </row>
@@ -47945,212 +48272,212 @@
       <c r="A38" s="169"/>
       <c r="B38" s="169"/>
       <c r="C38" s="2" t="s">
-        <v>1385</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="176" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="115.2">
       <c r="C40" s="2" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="176" t="s">
-        <v>1332</v>
+        <v>1329</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="100.8">
       <c r="C42" s="169" t="s">
-        <v>1330</v>
+        <v>1327</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>1328</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="115.2">
       <c r="A43" s="2" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>1361</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="115.2">
       <c r="A44" s="2" t="s">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1321</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="144">
       <c r="A45" s="2" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>1360</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="57.6">
       <c r="A46" s="2" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>1325</v>
+        <v>1322</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="28.8">
       <c r="A47" s="177" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
       <c r="B47" s="169" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="187.2">
       <c r="A48" s="2" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="B48" s="169" t="s">
-        <v>1355</v>
+        <v>1352</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>1384</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="86.4">
       <c r="A49" s="2" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B49" s="169" t="s">
+        <v>1333</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>1338</v>
       </c>
-      <c r="B49" s="169" t="s">
+      <c r="D49" s="2" t="s">
         <v>1336</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>1341</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>1339</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="176" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="72">
       <c r="C51" s="2" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="176" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="187.2">
       <c r="C53" s="2" t="s">
-        <v>1359</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="45" customHeight="1">
       <c r="A54" s="177" t="s">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="B54" s="169" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="144">
       <c r="A55" s="2" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>1356</v>
+        <v>1353</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="72">
       <c r="A56" s="2" t="s">
-        <v>1344</v>
+        <v>1341</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>1346</v>
+        <v>1343</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>1345</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="129.6">
       <c r="A57" s="2" t="s">
-        <v>1348</v>
+        <v>1345</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>1347</v>
+        <v>1344</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>1349</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="244.8">
       <c r="B58" s="169" t="s">
-        <v>1350</v>
+        <v>1347</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>1364</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="176" t="s">
-        <v>1357</v>
+        <v>1354</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="C60" s="2" t="s">
-        <v>1367</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="176" t="s">
-        <v>1358</v>
+        <v>1355</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="172.8">
@@ -48158,7 +48485,7 @@
         <v>62</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>1363</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="144">
@@ -48166,48 +48493,48 @@
         <v>43</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>1362</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="28.8">
       <c r="A64" s="177" t="s">
-        <v>1365</v>
+        <v>1362</v>
       </c>
       <c r="B64" s="169" t="s">
-        <v>1366</v>
+        <v>1363</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="216">
       <c r="A65" s="2" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1369</v>
+        <v>1366</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>1368</v>
+        <v>1365</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>1370</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="244.8">
       <c r="A66" s="2" t="s">
-        <v>1348</v>
+        <v>1345</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>1375</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="176" t="s">
-        <v>1372</v>
+        <v>1369</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="172.8">
@@ -48215,7 +48542,7 @@
         <v>62</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>1374</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="144">
@@ -48223,92 +48550,92 @@
         <v>43</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>1373</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="23" t="s">
-        <v>1376</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="172.8">
       <c r="A71" s="2" t="s">
-        <v>1380</v>
+        <v>1377</v>
       </c>
       <c r="B71" s="169" t="s">
-        <v>1381</v>
+        <v>1378</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>1378</v>
+        <v>1375</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>1377</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="244.8">
       <c r="B72" s="2" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>1382</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="23" t="s">
-        <v>1386</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="100.8">
       <c r="A74" s="2" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="115.2">
       <c r="A75" s="2" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="244.8">
       <c r="A76" s="2" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>1642</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="43.2">
       <c r="A77" s="2" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="86.4">
       <c r="C78" s="2" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="175" t="s">
-        <v>1607</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="216">
       <c r="B80" s="2" t="s">
-        <v>1643</v>
+        <v>1640</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
     </row>
   </sheetData>
@@ -48358,7 +48685,7 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="23" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -48379,7 +48706,7 @@
     <row r="8" spans="1:5">
       <c r="A8" s="175"/>
       <c r="D8" s="178" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -48393,14 +48720,14 @@
     </row>
     <row r="13" spans="1:5" s="133" customFormat="1">
       <c r="C13" s="168" t="s">
-        <v>1309</v>
+        <v>1306</v>
       </c>
       <c r="D13" s="172"/>
       <c r="E13" s="70"/>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="23" t="s">
-        <v>1309</v>
+        <v>1306</v>
       </c>
     </row>
   </sheetData>
@@ -48450,30 +48777,30 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="23" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="B3" s="168" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="C3" s="92" t="s">
-        <v>1602</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="23" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="23" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="B6" s="23" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="39" customFormat="1">
@@ -48481,153 +48808,153 @@
     </row>
     <row r="12" spans="1:5" s="133" customFormat="1">
       <c r="C12" s="168" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="D12" s="172"/>
       <c r="E12" s="70"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="23" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="B13" s="169"/>
     </row>
     <row r="14" spans="1:5" ht="72">
       <c r="B14" s="169" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="C14" s="193"/>
     </row>
     <row r="15" spans="1:5" ht="302.39999999999998">
       <c r="A15" s="169" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="23" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="230.4">
       <c r="A17" s="2" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
       <c r="B17" s="183" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="201.6">
       <c r="A18" s="2" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
       <c r="B18" s="189" t="s">
-        <v>1608</v>
+        <v>1605</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="100.8">
       <c r="A19" s="2" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="23" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="273.60000000000002">
       <c r="A21" s="2" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
       <c r="B21" s="189" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1609</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="158.4">
       <c r="A22" s="2" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1434</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="100.8">
       <c r="A23" s="2" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>1432</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>1435</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="23" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="C24" s="114" t="s">
-        <v>1386</v>
+        <v>1383</v>
       </c>
       <c r="D24" s="114" t="s">
-        <v>1436</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="187.2">
       <c r="C25" s="2" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="115.2">
       <c r="B26" s="2" t="s">
-        <v>1615</v>
+        <v>1612</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1616</v>
+        <v>1613</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>1614</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="23" t="s">
-        <v>1617</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="115.2">
       <c r="B28" s="189" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="57.6">
       <c r="D29" s="110" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
     </row>
   </sheetData>
@@ -48657,84 +48984,84 @@
   <sheetData>
     <row r="2" spans="1:3">
       <c r="A2" s="177" t="s">
-        <v>1477</v>
+        <v>1474</v>
       </c>
       <c r="B2" s="177" t="s">
-        <v>1478</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>1446</v>
+        <v>1443</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="B5" s="190" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="28.8">
       <c r="A6" s="2" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
       <c r="B6" s="190" t="s">
-        <v>1597</v>
+        <v>1594</v>
       </c>
       <c r="C6" s="92" t="s">
-        <v>1602</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
       <c r="B7" s="190" t="s">
-        <v>1598</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
       <c r="B8" s="190" t="s">
-        <v>1599</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
       <c r="B9" s="190" t="s">
-        <v>1600</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>1453</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="21" spans="1:29" s="39" customFormat="1">
@@ -48742,69 +49069,69 @@
     </row>
     <row r="22" spans="1:29" s="133" customFormat="1">
       <c r="C22" s="168" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="D22" s="172"/>
       <c r="E22" s="70"/>
     </row>
     <row r="23" spans="1:29">
       <c r="A23" s="177" t="s">
-        <v>1477</v>
+        <v>1474</v>
       </c>
       <c r="B23" s="150"/>
       <c r="C23" s="150"/>
     </row>
     <row r="24" spans="1:29" ht="43.2">
       <c r="A24" s="114" t="s">
-        <v>1436</v>
+        <v>1433</v>
       </c>
       <c r="B24" s="186" t="s">
-        <v>1476</v>
+        <v>1473</v>
       </c>
       <c r="C24" s="189" t="s">
-        <v>1622</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="25" spans="1:29">
       <c r="A25" s="2" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>1466</v>
+        <v>1463</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="26" spans="1:29">
       <c r="A26" s="2" t="s">
-        <v>1446</v>
+        <v>1443</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>1467</v>
+        <v>1464</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>1456</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="27" spans="1:29" s="70" customFormat="1">
       <c r="A27" s="2" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>1468</v>
+        <v>1465</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>1457</v>
+        <v>1454</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -48833,16 +49160,16 @@
     </row>
     <row r="28" spans="1:29" s="70" customFormat="1">
       <c r="A28" s="2" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1469</v>
+        <v>1466</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>1458</v>
+        <v>1455</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -48871,16 +49198,16 @@
     </row>
     <row r="29" spans="1:29" s="70" customFormat="1">
       <c r="A29" s="2" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1470</v>
+        <v>1467</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>1442</v>
+        <v>1439</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>1459</v>
+        <v>1456</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -48909,16 +49236,16 @@
     </row>
     <row r="30" spans="1:29" s="70" customFormat="1">
       <c r="A30" s="2" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1471</v>
+        <v>1468</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1443</v>
+        <v>1440</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>1460</v>
+        <v>1457</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
@@ -48947,16 +49274,16 @@
     </row>
     <row r="31" spans="1:29" s="70" customFormat="1">
       <c r="A31" s="2" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1472</v>
+        <v>1469</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>1444</v>
+        <v>1441</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>1461</v>
+        <v>1458</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
@@ -48985,16 +49312,16 @@
     </row>
     <row r="32" spans="1:29" s="70" customFormat="1" ht="72">
       <c r="A32" s="2" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1473</v>
+        <v>1470</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>1465</v>
+        <v>1462</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>1462</v>
+        <v>1459</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -49023,16 +49350,16 @@
     </row>
     <row r="33" spans="1:29" s="70" customFormat="1">
       <c r="A33" s="2" t="s">
-        <v>1453</v>
+        <v>1450</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>1474</v>
+        <v>1471</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>1463</v>
+        <v>1460</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
@@ -49061,16 +49388,16 @@
     </row>
     <row r="34" spans="1:29" s="70" customFormat="1">
       <c r="A34" s="2" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1475</v>
+        <v>1472</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1445</v>
+        <v>1442</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>1464</v>
+        <v>1461</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -49099,7 +49426,7 @@
     </row>
     <row r="35" spans="1:29" s="70" customFormat="1">
       <c r="A35" s="177" t="s">
-        <v>1478</v>
+        <v>1475</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -49131,10 +49458,10 @@
     </row>
     <row r="36" spans="1:29" s="70" customFormat="1" ht="43.2">
       <c r="A36" s="114" t="s">
-        <v>1436</v>
+        <v>1433</v>
       </c>
       <c r="B36" s="186" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -49165,7 +49492,7 @@
     </row>
     <row r="37" spans="1:29" s="70" customFormat="1">
       <c r="A37" s="23" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -49197,14 +49524,14 @@
     </row>
     <row r="38" spans="1:29" s="70" customFormat="1" ht="28.8">
       <c r="A38" s="186" t="s">
-        <v>1529</v>
+        <v>1526</v>
       </c>
       <c r="B38" s="186" t="s">
-        <v>1530</v>
+        <v>1527</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2" t="s">
-        <v>1531</v>
+        <v>1528</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
@@ -49233,7 +49560,7 @@
     </row>
     <row r="39" spans="1:29" s="70" customFormat="1">
       <c r="A39" s="23" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -49265,16 +49592,16 @@
     </row>
     <row r="40" spans="1:29" s="70" customFormat="1">
       <c r="A40" s="2" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
@@ -49303,16 +49630,16 @@
     </row>
     <row r="41" spans="1:29" s="70" customFormat="1">
       <c r="A41" s="2" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>1485</v>
+        <v>1482</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>1536</v>
+        <v>1533</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -49341,16 +49668,16 @@
     </row>
     <row r="42" spans="1:29" s="70" customFormat="1">
       <c r="A42" s="2" t="s">
-        <v>1486</v>
+        <v>1483</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>1487</v>
+        <v>1484</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>1538</v>
+        <v>1535</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -49379,16 +49706,16 @@
     </row>
     <row r="43" spans="1:29" s="70" customFormat="1">
       <c r="A43" s="2" t="s">
-        <v>1488</v>
+        <v>1485</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>1489</v>
+        <v>1486</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>1539</v>
+        <v>1536</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>1490</v>
+        <v>1487</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
@@ -49417,16 +49744,16 @@
     </row>
     <row r="44" spans="1:29" s="70" customFormat="1">
       <c r="A44" s="2" t="s">
-        <v>1491</v>
+        <v>1488</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>1492</v>
+        <v>1489</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1540</v>
+        <v>1537</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>1493</v>
+        <v>1490</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
@@ -49455,16 +49782,16 @@
     </row>
     <row r="45" spans="1:29" s="70" customFormat="1">
       <c r="A45" s="2" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>1541</v>
+        <v>1538</v>
       </c>
       <c r="D45" s="183" t="s">
-        <v>1542</v>
+        <v>1539</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
@@ -49493,7 +49820,7 @@
     </row>
     <row r="46" spans="1:29" s="70" customFormat="1">
       <c r="A46" s="190" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="B46" s="183"/>
       <c r="C46" s="2"/>
@@ -49525,10 +49852,10 @@
     </row>
     <row r="47" spans="1:29" s="70" customFormat="1">
       <c r="A47" s="114" t="s">
-        <v>1494</v>
+        <v>1491</v>
       </c>
       <c r="B47" s="114" t="s">
-        <v>1495</v>
+        <v>1492</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -49560,10 +49887,10 @@
     <row r="48" spans="1:29" s="70" customFormat="1">
       <c r="A48" s="133"/>
       <c r="B48" s="190" t="s">
-        <v>1562</v>
+        <v>1559</v>
       </c>
       <c r="C48" s="23" t="s">
-        <v>1563</v>
+        <v>1560</v>
       </c>
       <c r="D48" s="2"/>
       <c r="F48" s="2"/>
@@ -49593,16 +49920,16 @@
     </row>
     <row r="49" spans="1:29" s="70" customFormat="1" ht="43.2">
       <c r="A49" s="183" t="s">
-        <v>1549</v>
+        <v>1546</v>
       </c>
       <c r="B49" s="189" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>1587</v>
+        <v>1584</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -49631,7 +49958,7 @@
     </row>
     <row r="50" spans="1:29" s="70" customFormat="1">
       <c r="A50" s="191" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="B50" s="183"/>
       <c r="C50" s="2"/>
@@ -49663,13 +49990,13 @@
     </row>
     <row r="51" spans="1:29" s="70" customFormat="1">
       <c r="A51" s="2" t="s">
-        <v>1577</v>
+        <v>1574</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>1570</v>
+        <v>1567</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="D51" s="2"/>
       <c r="F51" s="2"/>
@@ -49699,16 +50026,16 @@
     </row>
     <row r="52" spans="1:29" s="70" customFormat="1" ht="28.8">
       <c r="A52" s="2" t="s">
-        <v>1569</v>
+        <v>1566</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>1584</v>
+        <v>1581</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="D52" s="189" t="s">
-        <v>1586</v>
+        <v>1583</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
@@ -49738,13 +50065,13 @@
     <row r="53" spans="1:29" s="70" customFormat="1" ht="57.6">
       <c r="A53" s="2"/>
       <c r="B53" s="189" t="s">
-        <v>1555</v>
+        <v>1552</v>
       </c>
       <c r="C53" s="183" t="s">
-        <v>1556</v>
+        <v>1553</v>
       </c>
       <c r="D53" s="189" t="s">
-        <v>1586</v>
+        <v>1583</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
@@ -49774,13 +50101,13 @@
     <row r="54" spans="1:29" s="70" customFormat="1" ht="72">
       <c r="A54" s="2"/>
       <c r="B54" s="59" t="s">
-        <v>1554</v>
+        <v>1551</v>
       </c>
       <c r="C54" s="59" t="s">
-        <v>1553</v>
+        <v>1550</v>
       </c>
       <c r="D54" s="189" t="s">
-        <v>1586</v>
+        <v>1583</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
@@ -49810,13 +50137,13 @@
     <row r="55" spans="1:29" s="70" customFormat="1" ht="86.4">
       <c r="A55" s="2"/>
       <c r="B55" s="59" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="C55" s="59" t="s">
-        <v>1551</v>
+        <v>1548</v>
       </c>
       <c r="D55" s="189" t="s">
-        <v>1586</v>
+        <v>1583</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
@@ -49845,13 +50172,13 @@
     </row>
     <row r="56" spans="1:29" s="70" customFormat="1">
       <c r="A56" s="2" t="s">
-        <v>1571</v>
+        <v>1568</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>1571</v>
+        <v>1568</v>
       </c>
       <c r="C56" s="22" t="s">
-        <v>1568</v>
+        <v>1565</v>
       </c>
       <c r="D56" s="189"/>
       <c r="F56" s="2"/>
@@ -49881,7 +50208,7 @@
     </row>
     <row r="57" spans="1:29" s="70" customFormat="1">
       <c r="A57" s="191" t="s">
-        <v>1561</v>
+        <v>1558</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" s="22"/>
@@ -49913,13 +50240,13 @@
     </row>
     <row r="58" spans="1:29" s="70" customFormat="1">
       <c r="A58" s="2" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="C58" s="22" t="s">
-        <v>1572</v>
+        <v>1569</v>
       </c>
       <c r="D58" s="2"/>
       <c r="F58" s="2"/>
@@ -49949,13 +50276,13 @@
     </row>
     <row r="59" spans="1:29" s="70" customFormat="1">
       <c r="A59" s="2" t="s">
-        <v>1578</v>
+        <v>1575</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1578</v>
+        <v>1575</v>
       </c>
       <c r="C59" s="22" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="D59" s="189"/>
       <c r="F59" s="2"/>
@@ -49985,16 +50312,16 @@
     </row>
     <row r="60" spans="1:29" s="70" customFormat="1">
       <c r="A60" s="2" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="C60" s="22" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="D60" s="189" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
@@ -50024,10 +50351,10 @@
     <row r="61" spans="1:29" s="70" customFormat="1" ht="57.6">
       <c r="A61" s="2"/>
       <c r="B61" s="189" t="s">
-        <v>1555</v>
+        <v>1552</v>
       </c>
       <c r="C61" s="183" t="s">
-        <v>1556</v>
+        <v>1553</v>
       </c>
       <c r="D61" s="189"/>
       <c r="F61" s="2"/>
@@ -50087,13 +50414,13 @@
     </row>
     <row r="63" spans="1:29" s="70" customFormat="1">
       <c r="A63" s="2" t="s">
-        <v>1573</v>
+        <v>1570</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>1573</v>
+        <v>1570</v>
       </c>
       <c r="C63" s="22" t="s">
-        <v>1568</v>
+        <v>1565</v>
       </c>
       <c r="D63" s="189"/>
       <c r="F63" s="2"/>
@@ -50124,13 +50451,13 @@
     <row r="64" spans="1:29" s="70" customFormat="1" ht="86.4">
       <c r="A64" s="2"/>
       <c r="B64" s="2" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="C64" s="22" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="D64" s="189" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
@@ -50159,10 +50486,10 @@
     </row>
     <row r="65" spans="1:29" s="70" customFormat="1">
       <c r="A65" s="114" t="s">
-        <v>1496</v>
+        <v>1493</v>
       </c>
       <c r="B65" s="114" t="s">
-        <v>1497</v>
+        <v>1494</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
@@ -50194,10 +50521,10 @@
     <row r="66" spans="1:29" s="70" customFormat="1">
       <c r="A66" s="192"/>
       <c r="B66" s="190" t="s">
-        <v>1562</v>
+        <v>1559</v>
       </c>
       <c r="C66" s="23" t="s">
-        <v>1563</v>
+        <v>1560</v>
       </c>
       <c r="D66" s="2"/>
       <c r="F66" s="2"/>
@@ -50227,16 +50554,16 @@
     </row>
     <row r="67" spans="1:29" s="70" customFormat="1" ht="57.6">
       <c r="A67" s="183" t="s">
-        <v>1550</v>
+        <v>1547</v>
       </c>
       <c r="B67" s="189" t="s">
-        <v>1547</v>
+        <v>1544</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>1548</v>
+        <v>1545</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>1588</v>
+        <v>1585</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
@@ -50265,14 +50592,14 @@
     </row>
     <row r="68" spans="1:29" s="70" customFormat="1">
       <c r="A68" s="114" t="s">
-        <v>1498</v>
+        <v>1495</v>
       </c>
       <c r="B68" s="114" t="s">
-        <v>1499</v>
+        <v>1496</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="2" t="s">
-        <v>1500</v>
+        <v>1497</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
@@ -50302,10 +50629,10 @@
     <row r="69" spans="1:29" s="70" customFormat="1" ht="172.8">
       <c r="A69" s="2"/>
       <c r="B69" s="189" t="s">
-        <v>1621</v>
+        <v>1618</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>1620</v>
+        <v>1617</v>
       </c>
       <c r="D69" s="2"/>
       <c r="F69" s="2"/>
@@ -50335,16 +50662,16 @@
     </row>
     <row r="70" spans="1:29" s="70" customFormat="1">
       <c r="A70" s="114" t="s">
-        <v>1501</v>
+        <v>1498</v>
       </c>
       <c r="B70" s="114" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>1532</v>
+        <v>1529</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
@@ -50373,16 +50700,16 @@
     </row>
     <row r="71" spans="1:29" s="70" customFormat="1">
       <c r="A71" s="114" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="B71" s="114" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>1533</v>
+        <v>1530</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
@@ -50411,7 +50738,7 @@
     </row>
     <row r="72" spans="1:29" s="70" customFormat="1" ht="28.8">
       <c r="A72" s="190" t="s">
-        <v>1597</v>
+        <v>1594</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -50443,14 +50770,14 @@
     </row>
     <row r="73" spans="1:29" s="70" customFormat="1">
       <c r="A73" s="114" t="s">
-        <v>1507</v>
+        <v>1504</v>
       </c>
       <c r="B73" s="114" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" s="2" t="s">
-        <v>1594</v>
+        <v>1591</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
@@ -50479,13 +50806,13 @@
     </row>
     <row r="74" spans="1:29" s="70" customFormat="1" ht="115.2">
       <c r="A74" s="189" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B74" s="189" t="s">
+        <v>1590</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>1592</v>
-      </c>
-      <c r="B74" s="189" t="s">
-        <v>1593</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>1595</v>
       </c>
       <c r="D74" s="2"/>
       <c r="F74" s="2"/>
@@ -50515,7 +50842,7 @@
     </row>
     <row r="75" spans="1:29" s="70" customFormat="1">
       <c r="A75" s="190" t="s">
-        <v>1602</v>
+        <v>1599</v>
       </c>
       <c r="B75" s="189"/>
       <c r="C75" s="2"/>
@@ -50547,124 +50874,124 @@
     </row>
     <row r="76" spans="1:29" ht="216">
       <c r="B76" s="59" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="C76" s="189" t="s">
+        <v>1598</v>
+      </c>
+      <c r="D76" s="189" t="s">
         <v>1601</v>
-      </c>
-      <c r="D76" s="189" t="s">
-        <v>1604</v>
       </c>
     </row>
     <row r="77" spans="1:29">
       <c r="A77" s="186" t="s">
-        <v>1509</v>
+        <v>1506</v>
       </c>
       <c r="B77" s="186" t="s">
-        <v>1510</v>
+        <v>1507</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>1596</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="78" spans="1:29">
       <c r="A78" s="190" t="s">
-        <v>1598</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="79" spans="1:29">
       <c r="A79" s="186" t="s">
-        <v>1511</v>
+        <v>1508</v>
       </c>
       <c r="B79" s="186" t="s">
-        <v>1512</v>
+        <v>1509</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>1513</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="80" spans="1:29">
       <c r="A80" s="190" t="s">
-        <v>1599</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="186" t="s">
-        <v>1514</v>
+        <v>1511</v>
       </c>
       <c r="B81" s="186" t="s">
-        <v>1515</v>
+        <v>1512</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>1516</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="185" t="s">
-        <v>1505</v>
+        <v>1502</v>
       </c>
       <c r="B82" s="186" t="s">
-        <v>1506</v>
+        <v>1503</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>1591</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="216">
       <c r="B83" s="2" t="s">
-        <v>1590</v>
+        <v>1587</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>1589</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="190" t="s">
-        <v>1600</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="186" t="s">
-        <v>1517</v>
+        <v>1514</v>
       </c>
       <c r="B85" s="186" t="s">
-        <v>1518</v>
+        <v>1515</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>1519</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="186" t="s">
-        <v>1520</v>
+        <v>1517</v>
       </c>
       <c r="B86" s="186" t="s">
-        <v>1521</v>
+        <v>1518</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>1522</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="186" t="s">
-        <v>1523</v>
+        <v>1520</v>
       </c>
       <c r="B87" s="186" t="s">
-        <v>1524</v>
+        <v>1521</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>1525</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="186" t="s">
-        <v>1526</v>
+        <v>1523</v>
       </c>
       <c r="B88" s="186" t="s">
-        <v>1527</v>
+        <v>1524</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>1528</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -50719,71 +51046,71 @@
         <v>530</v>
       </c>
       <c r="B2" s="159" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="B3" s="62" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="D3" s="110" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="B4" s="62" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="B5" s="62" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="B6" s="62" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="B7" s="62" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="62" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="B9" s="62" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="B10" s="62" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="B11" s="62" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="B12" s="62" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="B13" s="62" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -50793,17 +51120,17 @@
     </row>
     <row r="15" spans="1:4">
       <c r="B15" s="62" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="B16" s="62" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="B17" s="62" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="39" customFormat="1">
@@ -50830,7 +51157,7 @@
     </row>
     <row r="23" spans="1:5" s="54" customFormat="1">
       <c r="A23" s="62" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C23" s="55"/>
       <c r="D23" s="55"/>
@@ -50838,19 +51165,19 @@
     </row>
     <row r="24" spans="1:5" s="54" customFormat="1" ht="129.6">
       <c r="B24" s="158" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="C24" s="55" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="D24" s="158" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="E24" s="71"/>
     </row>
     <row r="25" spans="1:5" s="54" customFormat="1" ht="86.4">
       <c r="B25" s="158" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
       <c r="C25" s="55"/>
       <c r="D25" s="158"/>
@@ -50858,7 +51185,7 @@
     </row>
     <row r="26" spans="1:5" s="54" customFormat="1">
       <c r="A26" s="62" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="B26" s="55"/>
       <c r="E26" s="71"/>
@@ -50866,16 +51193,16 @@
     <row r="27" spans="1:5" s="54" customFormat="1" ht="57.6">
       <c r="A27" s="55"/>
       <c r="B27" s="165" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="C27" s="69" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
       <c r="E27" s="71"/>
     </row>
     <row r="28" spans="1:5" s="54" customFormat="1">
       <c r="A28" s="62" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="B28" s="55"/>
       <c r="C28" s="55"/>
@@ -50886,317 +51213,317 @@
       <c r="A29" s="55"/>
       <c r="B29" s="55"/>
       <c r="C29" s="153" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="D29" s="55"/>
       <c r="E29" s="71"/>
     </row>
     <row r="30" spans="1:5" s="54" customFormat="1">
       <c r="A30" s="166" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="B30" s="166" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
       <c r="C30" s="166" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="D30" s="55"/>
       <c r="E30" s="71"/>
     </row>
     <row r="31" spans="1:5" s="54" customFormat="1">
       <c r="A31" s="166" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="B31" s="166" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="C31" s="166" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="D31" s="55"/>
       <c r="E31" s="71"/>
     </row>
     <row r="32" spans="1:5" s="54" customFormat="1" ht="129.6">
       <c r="A32" s="159" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="B32" s="140" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
       <c r="C32" s="55" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="D32" s="55"/>
       <c r="E32" s="71"/>
     </row>
     <row r="33" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A33" s="62" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="C33" s="55"/>
       <c r="D33" s="55" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
       <c r="E33" s="71"/>
     </row>
     <row r="34" spans="1:5" s="54" customFormat="1" ht="43.2">
       <c r="A34" s="55" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="C34" s="137" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="D34" s="55"/>
       <c r="E34" s="71"/>
     </row>
     <row r="35" spans="1:5" s="54" customFormat="1" ht="72">
       <c r="A35" s="55" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="C35" s="137" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="D35" s="55"/>
       <c r="E35" s="71"/>
     </row>
     <row r="36" spans="1:5" s="54" customFormat="1" ht="57.6">
       <c r="A36" s="55" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="C36" s="137" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="D36" s="55"/>
       <c r="E36" s="71"/>
     </row>
     <row r="37" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A37" s="55" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="C37" s="137" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="D37" s="55"/>
       <c r="E37" s="71"/>
     </row>
     <row r="38" spans="1:5" s="54" customFormat="1" ht="72">
       <c r="A38" s="55" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="C38" s="137" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="D38" s="55"/>
       <c r="E38" s="71"/>
     </row>
     <row r="39" spans="1:5" s="54" customFormat="1" ht="57.6">
       <c r="A39" s="55" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="C39" s="137" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="D39" s="55"/>
       <c r="E39" s="71"/>
     </row>
     <row r="40" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A40" s="62" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="C40" s="55"/>
       <c r="D40" s="55" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
       <c r="E40" s="71"/>
     </row>
     <row r="41" spans="1:5" s="54" customFormat="1" ht="129.6">
       <c r="A41" s="55"/>
       <c r="B41" s="54" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="C41" s="153" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="D41" s="55" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="E41" s="71"/>
     </row>
     <row r="42" spans="1:5" s="54" customFormat="1" ht="244.8">
       <c r="A42" s="55"/>
       <c r="B42" s="54" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="C42" s="55" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="D42" s="55" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="E42" s="71"/>
     </row>
     <row r="43" spans="1:5" s="54" customFormat="1" ht="244.8">
       <c r="A43" s="55"/>
       <c r="B43" s="54" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
       <c r="C43" s="153" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="D43" s="55" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="E43" s="71"/>
     </row>
     <row r="44" spans="1:5" s="54" customFormat="1" ht="43.2">
       <c r="A44" s="62" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="D44" s="54" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="E44" s="71"/>
     </row>
     <row r="45" spans="1:5" s="54" customFormat="1" ht="144">
       <c r="B45" s="158" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="C45" s="54" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="E45" s="71"/>
     </row>
     <row r="46" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A46" s="62" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="B46" s="55"/>
       <c r="C46" s="55"/>
       <c r="D46" s="55" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="E46" s="71"/>
     </row>
     <row r="47" spans="1:5" s="54" customFormat="1" ht="302.39999999999998">
       <c r="A47" s="55"/>
       <c r="B47" s="153" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="C47" s="55" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="E47" s="71"/>
     </row>
     <row r="48" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A48" s="62" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="B48" s="55"/>
       <c r="C48" s="55"/>
       <c r="D48" s="55" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="E48" s="71"/>
     </row>
     <row r="49" spans="1:5" s="54" customFormat="1" ht="43.2">
       <c r="A49" s="55"/>
       <c r="B49" s="153" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="C49" s="55" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="D49" s="55"/>
       <c r="E49" s="71"/>
     </row>
     <row r="50" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A50" s="62" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="C50" s="55"/>
       <c r="D50" s="55" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="E50" s="71"/>
     </row>
     <row r="51" spans="1:5" s="54" customFormat="1" ht="100.8">
       <c r="A51" s="160" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
       <c r="B51" s="153" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="C51" s="55" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="D51" s="55"/>
       <c r="E51" s="71"/>
     </row>
     <row r="52" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A52" s="62" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
       <c r="B52" s="55"/>
       <c r="C52" s="55"/>
       <c r="D52" s="55" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="E52" s="71"/>
     </row>
     <row r="53" spans="1:5" s="54" customFormat="1" ht="144">
       <c r="A53" s="161" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="B53" s="163" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="C53" s="163" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
       <c r="D53" s="55"/>
       <c r="E53" s="71"/>
     </row>
     <row r="54" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A54" s="62" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="B54" s="55"/>
       <c r="C54" s="55"/>
       <c r="D54" s="55" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="E54" s="71"/>
     </row>
     <row r="55" spans="1:5" s="54" customFormat="1" ht="43.2">
       <c r="A55" s="55"/>
       <c r="B55" s="55" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="C55" s="55" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="D55" s="55"/>
       <c r="E55" s="71"/>
     </row>
     <row r="56" spans="1:5" s="54" customFormat="1" ht="43.2">
       <c r="A56" s="62" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
       <c r="B56" s="55"/>
       <c r="C56" s="55"/>
       <c r="D56" s="55" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="E56" s="71"/>
     </row>
     <row r="57" spans="1:5" s="54" customFormat="1" ht="172.8">
       <c r="A57" s="55"/>
       <c r="B57" s="55" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
       <c r="C57" s="55" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="D57" s="55"/>
       <c r="E57" s="71"/>
@@ -51208,17 +51535,17 @@
       <c r="B58" s="53"/>
       <c r="C58" s="53"/>
       <c r="D58" s="53" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
       <c r="E58" s="71"/>
     </row>
     <row r="59" spans="1:5" s="54" customFormat="1" ht="43.2">
       <c r="A59" s="55"/>
       <c r="B59" s="163" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
       <c r="C59" s="55" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="D59" s="55"/>
       <c r="E59" s="71"/>
@@ -51226,17 +51553,17 @@
     <row r="60" spans="1:5" s="54" customFormat="1" ht="100.8">
       <c r="A60" s="55"/>
       <c r="B60" s="165" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
       <c r="C60" s="55" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
       <c r="D60" s="55"/>
       <c r="E60" s="71"/>
     </row>
     <row r="61" spans="1:5" s="54" customFormat="1">
       <c r="A61" s="164" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="B61" s="55"/>
       <c r="C61" s="55"/>
@@ -51247,7 +51574,7 @@
       <c r="A62" s="55"/>
       <c r="B62" s="55"/>
       <c r="C62" s="55" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
       <c r="D62" s="55"/>
       <c r="E62" s="71"/>
@@ -51256,7 +51583,7 @@
       <c r="A63" s="55"/>
       <c r="B63" s="55"/>
       <c r="C63" s="55" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
       <c r="D63" s="55"/>
       <c r="E63" s="71"/>
@@ -51265,7 +51592,7 @@
       <c r="A64" s="55"/>
       <c r="B64" s="55"/>
       <c r="C64" s="55" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="D64" s="55"/>
       <c r="E64" s="71"/>
@@ -51278,10 +51605,10 @@
     </row>
     <row r="66" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A66" s="62" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="B66" s="55" t="s">
-        <v>1183</v>
+        <v>1180</v>
       </c>
       <c r="C66" s="55"/>
       <c r="D66" s="55"/>
@@ -51291,19 +51618,19 @@
       <c r="A67" s="55"/>
       <c r="B67" s="55"/>
       <c r="C67" s="55" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="D67" s="55" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="E67" s="71"/>
     </row>
     <row r="68" spans="1:5" s="54" customFormat="1">
       <c r="A68" s="62" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
       <c r="B68" s="55" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="E68" s="71"/>
     </row>
@@ -51312,29 +51639,29 @@
       <c r="B69" s="55"/>
       <c r="C69" s="55"/>
       <c r="D69" s="165" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
       <c r="E69" s="71"/>
     </row>
     <row r="70" spans="1:5" s="54" customFormat="1" ht="16.2" customHeight="1">
       <c r="A70" s="62" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B70" s="54" t="s">
         <v>1178</v>
       </c>
-      <c r="B70" s="54" t="s">
-        <v>1181</v>
-      </c>
       <c r="C70" s="164" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="E70" s="71"/>
     </row>
     <row r="71" spans="1:5" s="54" customFormat="1" ht="216">
       <c r="A71" s="55"/>
       <c r="B71" s="55" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="C71" s="54" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="E71" s="71"/>
     </row>
@@ -51386,12 +51713,12 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="23" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="23" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -51401,22 +51728,22 @@
     </row>
     <row r="5" spans="1:5">
       <c r="C5" s="142" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="C6" s="142" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="B7" s="168" t="s">
-        <v>1208</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="B8" s="168" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="39" customFormat="1">
@@ -51424,58 +51751,58 @@
     </row>
     <row r="12" spans="1:5" s="133" customFormat="1">
       <c r="C12" s="168" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="23" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="D13" s="170" t="s">
-        <v>1207</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="100.8">
       <c r="B14" s="169" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="216.6" customHeight="1">
       <c r="B15" s="2" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="23" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
       <c r="D16" s="170" t="s">
-        <v>1207</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="86.4">
       <c r="B17" s="169" t="s">
-        <v>1203</v>
+        <v>1200</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="129.6">
       <c r="B18" s="2" t="s">
-        <v>1206</v>
+        <v>1203</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28.8">
@@ -51483,71 +51810,71 @@
         <v>468</v>
       </c>
       <c r="B19" s="169" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
       <c r="D19" s="170" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="142" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="115.2">
       <c r="B21" s="2" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="142" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="100.8">
       <c r="B23" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>1218</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>1221</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1">
       <c r="A24" s="168" t="s">
-        <v>1208</v>
+        <v>1205</v>
       </c>
       <c r="D24" s="170" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="201.6">
       <c r="A25" s="2" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="B25" s="169" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="168" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="D26" s="170" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="43.2">
       <c r="B27" s="169" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
     </row>
   </sheetData>
@@ -51613,7 +51940,7 @@
     </row>
     <row r="3" spans="1:22">
       <c r="C3" s="11" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="P3" s="1"/>
       <c r="U3" s="1"/>
@@ -51621,10 +51948,10 @@
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="P4" s="1"/>
       <c r="U4" s="1"/>
@@ -51632,119 +51959,119 @@
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="C5" s="99" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="C6" s="99" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
     </row>
     <row r="7" spans="1:22" ht="100.8">
       <c r="A7" s="1" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="C7" s="99" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="C8" s="99" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="28.8">
       <c r="A9" s="1" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="C9" s="194" t="s">
-        <v>1625</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="C10" s="99" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="10" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="C13" s="1"/>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="C14" s="195" t="s">
-        <v>1626</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1" t="s">
-        <v>1638</v>
+        <v>1635</v>
       </c>
       <c r="C15" s="195" t="s">
-        <v>1637</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="10" t="s">
-        <v>1640</v>
+        <v>1637</v>
       </c>
       <c r="C16" s="1"/>
     </row>
     <row r="17" spans="1:3" ht="28.8">
       <c r="A17" s="1" t="s">
-        <v>1641</v>
+        <v>1638</v>
       </c>
       <c r="C17" s="196" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="C18" s="195" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="57.6">
       <c r="A19" s="10" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
       <c r="C19" s="195" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="10" t="s">
-        <v>1309</v>
+        <v>1306</v>
       </c>
       <c r="C20" s="195" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -51801,20 +52128,20 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="23" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="B3" s="168" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="B4" s="168" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="39" customFormat="1">
@@ -51822,112 +52149,112 @@
     </row>
     <row r="7" spans="1:5" s="133" customFormat="1">
       <c r="C7" s="168" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="D7" s="171" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="E7" s="70"/>
     </row>
     <row r="8" spans="1:5" ht="28.8">
       <c r="A8" s="23" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="B8" s="169" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="43.2">
       <c r="C9" s="169" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="158.4">
       <c r="B10" s="169" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>1225</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>1228</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="158.4">
       <c r="B11" s="169" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="168" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="72">
       <c r="B13" s="2" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="28.8">
       <c r="A14" s="168" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="B14" s="114" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="100.8">
       <c r="C15" s="169" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="86.4">
       <c r="A16" s="2" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="216">
       <c r="A17" s="2" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="C17" s="169" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="216">
       <c r="B18" s="2" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="C18" s="169" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="168" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="D19" s="170" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="86.4">
       <c r="B20" s="2" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
     </row>
   </sheetData>
@@ -51981,12 +52308,12 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="23" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="B3" s="168" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -51997,10 +52324,10 @@
     </row>
     <row r="7" spans="1:5" s="133" customFormat="1">
       <c r="C7" s="168" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="D7" s="172" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="E7" s="70"/>
     </row>
@@ -52011,108 +52338,108 @@
     </row>
     <row r="9" spans="1:5" ht="129.6">
       <c r="B9" s="169" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="168" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="57.6">
       <c r="B11" s="2" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28.8">
       <c r="B12" s="2" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="86.4">
       <c r="B13" s="2" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>1258</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>1261</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="168" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="C15" s="2" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="30">
       <c r="A16" s="2" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C16" s="173" t="s">
         <v>1265</v>
-      </c>
-      <c r="C16" s="173" t="s">
-        <v>1268</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30">
       <c r="A17" s="2" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C17" s="174" t="s">
         <v>1266</v>
-      </c>
-      <c r="C17" s="174" t="s">
-        <v>1269</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="30">
       <c r="A18" s="2" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C18" s="174" t="s">
         <v>1267</v>
-      </c>
-      <c r="C18" s="174" t="s">
-        <v>1270</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="316.8">
       <c r="B19" s="2" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="168" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="144">
       <c r="B21" s="169" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="172.8">
       <c r="B22" s="169" t="s">
-        <v>1276</v>
+        <v>1273</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
     </row>
   </sheetData>
@@ -52168,25 +52495,25 @@
     <row r="3" spans="1:5">
       <c r="A3" s="131"/>
       <c r="B3" s="107" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="131"/>
       <c r="B4" s="107" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="131"/>
       <c r="B5" s="107" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="131"/>
       <c r="B6" s="107" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -52227,7 +52554,7 @@
         <v>502</v>
       </c>
       <c r="B13" s="55" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="C13" s="55" t="s">
         <v>503</v>
@@ -52237,7 +52564,7 @@
     </row>
     <row r="14" spans="1:5" s="54" customFormat="1">
       <c r="A14" s="62" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="B14" s="55"/>
       <c r="C14" s="55"/>
@@ -52247,10 +52574,10 @@
     <row r="15" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A15" s="55"/>
       <c r="B15" s="55" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="C15" s="137" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="D15" s="55"/>
       <c r="E15" s="71"/>
@@ -52258,10 +52585,10 @@
     <row r="16" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A16" s="55"/>
       <c r="B16" s="55" t="s">
+        <v>938</v>
+      </c>
+      <c r="C16" s="137" t="s">
         <v>941</v>
-      </c>
-      <c r="C16" s="137" t="s">
-        <v>944</v>
       </c>
       <c r="D16" s="55"/>
       <c r="E16" s="71"/>
@@ -52269,10 +52596,10 @@
     <row r="17" spans="1:5" s="54" customFormat="1" ht="57.6">
       <c r="A17" s="55"/>
       <c r="B17" s="55" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="C17" s="137" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="D17" s="55"/>
       <c r="E17" s="71"/>
@@ -52280,17 +52607,17 @@
     <row r="18" spans="1:5" s="54" customFormat="1" ht="43.2">
       <c r="A18" s="55"/>
       <c r="B18" s="55" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="C18" s="137" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="D18" s="55"/>
       <c r="E18" s="71"/>
     </row>
     <row r="19" spans="1:5" s="54" customFormat="1">
       <c r="A19" s="62" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="B19" s="55"/>
       <c r="C19" s="55"/>
@@ -52300,10 +52627,10 @@
     <row r="20" spans="1:5" s="54" customFormat="1" ht="43.2">
       <c r="A20" s="55"/>
       <c r="B20" s="55" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="C20" s="137" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="D20" s="55"/>
       <c r="E20" s="71"/>
@@ -52311,10 +52638,10 @@
     <row r="21" spans="1:5" s="54" customFormat="1" ht="57.6">
       <c r="A21" s="55"/>
       <c r="B21" s="55" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="C21" s="137" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="D21" s="55"/>
       <c r="E21" s="71"/>
@@ -52322,10 +52649,10 @@
     <row r="22" spans="1:5" s="54" customFormat="1" ht="43.2">
       <c r="A22" s="55"/>
       <c r="B22" s="55" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="C22" s="137" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="D22" s="55"/>
       <c r="E22" s="71"/>
@@ -52335,7 +52662,7 @@
         <v>504</v>
       </c>
       <c r="B23" s="96" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="E23" s="71"/>
     </row>
@@ -52591,7 +52918,7 @@
         <v>399</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -52601,17 +52928,17 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="62" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="62" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="62" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="39" customFormat="1">
@@ -52623,7 +52950,7 @@
       </c>
       <c r="B9" s="54"/>
       <c r="C9" s="53" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="D9" s="55"/>
       <c r="E9" s="98"/>
@@ -52639,7 +52966,7 @@
         <v>402</v>
       </c>
       <c r="D10" s="55" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="E10" s="98"/>
     </row>
@@ -52701,7 +53028,7 @@
       </c>
       <c r="B15" s="54"/>
       <c r="C15" s="53" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="D15" s="55"/>
       <c r="E15" s="98"/>
@@ -52721,26 +53048,26 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="53" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="E17" s="98"/>
     </row>
     <row r="18" spans="1:5" ht="409.6">
       <c r="A18" s="55"/>
       <c r="B18" s="55" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="C18" s="55" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="D18" s="55" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="E18" s="98"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="53" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="B19" s="55"/>
       <c r="C19" s="55"/>
@@ -52750,19 +53077,19 @@
     <row r="20" spans="1:5" s="54" customFormat="1" ht="409.6">
       <c r="A20" s="55"/>
       <c r="B20" s="55" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="C20" s="55" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="D20" s="55" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="E20" s="98"/>
     </row>
     <row r="21" spans="1:5" s="54" customFormat="1">
       <c r="A21" s="53" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B21" s="55"/>
       <c r="C21" s="55"/>
@@ -52772,13 +53099,13 @@
     <row r="22" spans="1:5" s="54" customFormat="1" ht="409.6">
       <c r="A22" s="55"/>
       <c r="B22" s="55" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="C22" s="55" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="D22" s="55" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="E22" s="98"/>
     </row>
@@ -52971,7 +53298,7 @@
     </row>
     <row r="4" spans="1:22" ht="57.6">
       <c r="C4" s="128" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="P4" s="73"/>
       <c r="U4" s="73"/>
@@ -52979,7 +53306,7 @@
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="104" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="P5" s="73"/>
       <c r="U5" s="73"/>
@@ -52987,7 +53314,7 @@
     </row>
     <row r="6" spans="1:22" ht="43.2">
       <c r="C6" s="105" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="P6" s="73"/>
       <c r="U6" s="73"/>
@@ -52995,10 +53322,10 @@
     </row>
     <row r="7" spans="1:22" ht="43.2">
       <c r="B7" s="105" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="C7" s="105" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="P7" s="73"/>
       <c r="U7" s="73"/>
@@ -53006,10 +53333,10 @@
     </row>
     <row r="8" spans="1:22" ht="28.8">
       <c r="B8" s="105" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="C8" s="105" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="P8" s="73"/>
       <c r="U8" s="73"/>
@@ -53017,13 +53344,13 @@
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="106" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="B9" s="115" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="C9" s="115" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="P9" s="73"/>
       <c r="U9" s="73"/>
@@ -53031,10 +53358,10 @@
     </row>
     <row r="10" spans="1:22" ht="86.4">
       <c r="B10" s="116" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="C10" s="116" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="P10" s="73"/>
       <c r="U10" s="73"/>
@@ -53042,7 +53369,7 @@
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="104" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="73"/>
@@ -53079,35 +53406,35 @@
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="129" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
     </row>
     <row r="15" spans="1:22" ht="28.8">
       <c r="C15" s="105" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="104" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="72">
       <c r="C17" s="105" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="104" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="B18" s="107" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="86.4">
       <c r="B19" s="105" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
     </row>
   </sheetData>
@@ -53162,7 +53489,7 @@
     </row>
     <row r="2" spans="1:22">
       <c r="A2" s="108" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="B2" s="90"/>
       <c r="C2" s="90"/>
@@ -53170,7 +53497,7 @@
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="108" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="B3" s="90"/>
       <c r="C3" s="90"/>
@@ -53178,7 +53505,7 @@
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="108" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="B4" s="90"/>
       <c r="C4" s="90"/>
@@ -53186,7 +53513,7 @@
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="108" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="B5" s="90"/>
       <c r="C5" s="90"/>
@@ -53194,7 +53521,7 @@
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="117" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="B6" s="90"/>
       <c r="C6" s="90"/>
@@ -53202,7 +53529,7 @@
     </row>
     <row r="7" spans="1:22" ht="28.8">
       <c r="A7" s="117" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="B7" s="90"/>
       <c r="C7" s="90"/>
@@ -53212,7 +53539,7 @@
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="117" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="B8" s="90"/>
       <c r="C8" s="90"/>
@@ -53220,7 +53547,7 @@
     </row>
     <row r="9" spans="1:22" ht="28.8">
       <c r="A9" s="117" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="B9" s="90"/>
       <c r="C9" s="90"/>
@@ -53265,7 +53592,7 @@
     <row r="14" spans="1:22">
       <c r="A14" s="74"/>
       <c r="C14" s="109" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="P14" s="73"/>
       <c r="U14" s="73"/>
@@ -53273,10 +53600,10 @@
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="108" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="B15" s="120" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="P15" s="73"/>
       <c r="U15" s="73"/>
@@ -53284,7 +53611,7 @@
     </row>
     <row r="16" spans="1:22" ht="104.4" customHeight="1">
       <c r="A16" s="116" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="P16" s="73"/>
       <c r="U16" s="73"/>
@@ -53293,10 +53620,10 @@
     <row r="17" spans="1:22" ht="43.2">
       <c r="A17" s="74"/>
       <c r="B17" s="116" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="C17" s="105" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="P17" s="73"/>
       <c r="U17" s="73"/>
@@ -53305,10 +53632,10 @@
     <row r="18" spans="1:22" ht="43.2">
       <c r="A18" s="74"/>
       <c r="B18" s="116" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="C18" s="105" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="P18" s="73"/>
       <c r="U18" s="73"/>
@@ -53317,10 +53644,10 @@
     <row r="19" spans="1:22" ht="57.6">
       <c r="A19" s="74"/>
       <c r="B19" s="116" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="C19" s="105" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="P19" s="73"/>
       <c r="U19" s="73"/>
@@ -53328,10 +53655,10 @@
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="108" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="B20" s="120" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="P20" s="73"/>
       <c r="U20" s="73"/>
@@ -53340,10 +53667,10 @@
     <row r="21" spans="1:22" ht="72">
       <c r="A21" s="74"/>
       <c r="B21" s="116" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="C21" s="116" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="D21" s="2"/>
       <c r="P21" s="73"/>
@@ -53352,10 +53679,10 @@
     </row>
     <row r="22" spans="1:22">
       <c r="A22" s="124" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="B22" s="118" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -53366,13 +53693,13 @@
     <row r="23" spans="1:22">
       <c r="A23" s="179"/>
       <c r="B23" s="180" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C23" s="181" t="s">
+        <v>1402</v>
+      </c>
+      <c r="D23" s="182" t="s">
         <v>1403</v>
-      </c>
-      <c r="C23" s="181" t="s">
-        <v>1405</v>
-      </c>
-      <c r="D23" s="182" t="s">
-        <v>1406</v>
       </c>
       <c r="P23" s="73"/>
       <c r="U23" s="73"/>
@@ -53380,16 +53707,16 @@
     </row>
     <row r="24" spans="1:22" ht="201.6">
       <c r="A24" s="116" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="B24" s="116" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="C24" s="116" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="D24" s="116" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="P24" s="73"/>
       <c r="U24" s="73"/>
@@ -53398,29 +53725,29 @@
     <row r="25" spans="1:22" ht="158.4">
       <c r="A25" s="74"/>
       <c r="B25" s="116" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="C25" s="116" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="28.8">
       <c r="A26" s="124" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="B26" s="120" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="C26" s="118" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
     </row>
     <row r="27" spans="1:22" ht="273.60000000000002">
       <c r="B27" s="116" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="C27" s="116" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="57.6">
@@ -53431,164 +53758,164 @@
         <v>527</v>
       </c>
       <c r="C28" s="55" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
     </row>
     <row r="29" spans="1:22">
       <c r="A29" s="117" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="B29" s="120" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C29" s="118" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="D29" s="122" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
     </row>
     <row r="30" spans="1:22" ht="72">
       <c r="A30" s="74"/>
       <c r="B30" s="123" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="C30" s="116" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="D30" s="116" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
     </row>
     <row r="31" spans="1:22" ht="28.8">
       <c r="A31" s="117" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="B31" s="120" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="C31" s="126" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="D31" s="125" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
     </row>
     <row r="32" spans="1:22" ht="86.4">
       <c r="A32" s="116" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="B32" s="116" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="C32" s="116" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="43.2">
       <c r="A33" s="121"/>
       <c r="B33" s="123" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="C33" s="116" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="D33" s="116" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="57.6">
       <c r="A34" s="74"/>
       <c r="B34" s="116" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="C34" s="116" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="117" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="B35" s="120" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C35" s="119" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="D35" s="125" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="187.2">
       <c r="A36" s="116" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="B36" s="123" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="C36" s="116" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="D36" s="116" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="57.6">
       <c r="A37" s="74"/>
       <c r="B37" s="116" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="C37" s="116" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="116" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="C38" s="126" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="D38" s="126" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="115.2">
       <c r="A39" s="74"/>
       <c r="B39" s="116" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="C39" s="116" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="D39" s="116" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="28.8">
       <c r="A40" s="117" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="B40" s="126" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="C40" s="126" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="D40" s="126" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="273.60000000000002">
       <c r="B41" s="116" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="C41" s="116" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="D41" s="116" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
     </row>
   </sheetData>
@@ -53661,7 +53988,7 @@
         <v>367</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -54004,7 +54331,7 @@
         <v>316</v>
       </c>
       <c r="B33" s="162" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="C33" s="41" t="s">
         <v>370</v>
@@ -54332,65 +54659,65 @@
     </row>
     <row r="11" spans="1:5" s="54" customFormat="1" ht="57.6">
       <c r="C11" s="101" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="E11" s="70"/>
     </row>
     <row r="12" spans="1:5" s="54" customFormat="1" ht="244.8">
       <c r="A12" s="102" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="E12" s="70"/>
     </row>
     <row r="13" spans="1:5" s="54" customFormat="1">
       <c r="B13" s="96" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="C13" s="95" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="E13" s="70"/>
     </row>
     <row r="14" spans="1:5" ht="187.2">
       <c r="A14" s="22" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>691</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="273.60000000000002">
       <c r="A15" s="100" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="409.6">
       <c r="A16" s="22" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B16" s="100" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="C16" s="100" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
     </row>
   </sheetData>
@@ -54456,10 +54783,10 @@
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="53" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="C5" s="92" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -54685,7 +55012,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="53" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="B26" s="54"/>
       <c r="C26" s="54"/>
@@ -54694,10 +55021,10 @@
     </row>
     <row r="27" spans="1:5" ht="100.8">
       <c r="A27" s="55" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="B27" s="113" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C27" s="55" t="s">
         <v>569</v>
@@ -54706,10 +55033,10 @@
     </row>
     <row r="28" spans="1:5" ht="302.39999999999998">
       <c r="A28" s="55" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="B28" s="113" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="C28" s="55" t="s">
         <v>570</v>
@@ -54718,37 +55045,37 @@
     </row>
     <row r="29" spans="1:5" ht="172.8">
       <c r="A29" s="55" t="s">
+        <v>806</v>
+      </c>
+      <c r="B29" s="113" t="s">
+        <v>813</v>
+      </c>
+      <c r="C29" s="113" t="s">
         <v>809</v>
-      </c>
-      <c r="B29" s="113" t="s">
-        <v>816</v>
-      </c>
-      <c r="C29" s="113" t="s">
-        <v>812</v>
       </c>
       <c r="D29" s="56"/>
     </row>
     <row r="30" spans="1:5" ht="86.4">
       <c r="A30" s="55" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="B30" s="55" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="C30" s="69" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="D30" s="56"/>
     </row>
     <row r="31" spans="1:5" ht="216">
       <c r="A31" s="55" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="B31" s="69" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="C31" s="113" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
     </row>
   </sheetData>

--- a/4 четверть_9_JavaScript_Vue 3 Composition API.xlsx
+++ b/4 четверть_9_JavaScript_Vue 3 Composition API.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74AD8AB5-C62E-4E7D-BDE8-CD502E7568E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7868CAFD-B021-4FF4-9C96-324BBD495140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1368" yWindow="1104" windowWidth="23016" windowHeight="11136" firstSheet="7" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="17" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Литература" sheetId="14" r:id="rId1"/>
@@ -40106,12 +40106,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="79">
+  <fonts count="80">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -40870,11 +40878,11 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="199">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -40887,20 +40895,20 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="34" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -40909,122 +40917,122 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="54" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="38" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="53" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="60" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="61" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -41039,46 +41047,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="4" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="4" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -41087,77 +41095,77 @@
     <xf numFmtId="49" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="6" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="6" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="5" applyFill="1"/>
-    <xf numFmtId="49" fontId="15" fillId="7" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="5" applyFill="1"/>
+    <xf numFmtId="49" fontId="16" fillId="7" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="7" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="7" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="8" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="8" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="18" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="42" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="43" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="42" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="41" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="42" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -41166,97 +41174,97 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="16" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="16" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="42" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="36" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="16" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="16" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="36" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="43" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="44" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="43" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="44" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="43" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="44" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="35" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="36" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="35" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="36" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="35" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="36" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="38" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="8" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="8" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -41274,22 +41282,22 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -41301,71 +41309,71 @@
     <xf numFmtId="49" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="35" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="36" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="35" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="36" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="42" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="43" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="69" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="70" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -41374,77 +41382,80 @@
     <xf numFmtId="49" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="3" applyFill="1"/>
+    <xf numFmtId="49" fontId="72" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="73" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="42" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="36" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="44" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="44" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="44" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="3" applyFill="1"/>
-    <xf numFmtId="49" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="72" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="43" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="43" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="43" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -41453,13 +41464,10 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -42163,7 +42171,7 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C4:D11">
     <sortCondition ref="D4:D11"/>
   </sortState>
-  <phoneticPr fontId="34" type="noConversion"/>
+  <phoneticPr fontId="35" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -47968,7 +47976,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="34" type="noConversion"/>
+  <phoneticPr fontId="35" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>

--- a/4 четверть_9_JavaScript_Vue 3 Composition API.xlsx
+++ b/4 четверть_9_JavaScript_Vue 3 Composition API.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7868CAFD-B021-4FF4-9C96-324BBD495140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89559D82-B49E-437D-928E-F1BA612CFE60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="17" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Литература" sheetId="14" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2027" uniqueCount="1647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2036" uniqueCount="1653">
   <si>
     <t>Vue</t>
   </si>
@@ -40101,17 +40101,43 @@
       <t>с defineModel</t>
     </r>
   </si>
+  <si>
+    <t>`https://handsontable.com/</t>
+  </si>
+  <si>
+    <t>HTML Excel</t>
+  </si>
+  <si>
+    <t>Библиотеки</t>
+  </si>
+  <si>
+    <t>`https://docs.univer.ai/guides/sheets/getting-started/integrations/vue</t>
+  </si>
+  <si>
+    <t>Element UI</t>
+  </si>
+  <si>
+    <t>Библиотека компонентов</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="80">
+  <fonts count="81">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -40878,13 +40904,13 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="199">
+  <cellXfs count="201">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -40895,20 +40921,20 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -40917,122 +40943,122 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="27" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="53" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="55" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="54" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="61" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="62" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="63" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -41047,46 +41073,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="4" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="4" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -41095,77 +41121,77 @@
     <xf numFmtId="49" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="6" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="6" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="5" applyFill="1"/>
-    <xf numFmtId="49" fontId="16" fillId="7" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="5" applyFill="1"/>
+    <xf numFmtId="49" fontId="17" fillId="7" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="7" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="7" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="8" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="8" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="18" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="43" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="44" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="42" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="43" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="42" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="43" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -41174,97 +41200,97 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="16" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="16" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="43" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="16" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="16" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="42" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="36" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="36" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="36" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="8" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="8" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -41282,22 +41308,22 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -41309,71 +41335,71 @@
     <xf numFmtId="49" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="36" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="40" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="36" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="43" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="44" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="70" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="71" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -41382,77 +41408,80 @@
     <xf numFmtId="49" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="3" applyFill="1"/>
+    <xf numFmtId="49" fontId="73" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="43" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="45" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="45" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="45" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="3" applyFill="1"/>
-    <xf numFmtId="49" fontId="72" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="73" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="42" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="44" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="44" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="44" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -41461,13 +41490,16 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -42037,7 +42069,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:V21"/>
+  <dimension ref="A2:V34"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
@@ -42068,7 +42100,7 @@
     <col min="28" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:22" s="3" customFormat="1">
+    <row r="2" spans="1:22" s="3" customFormat="1">
       <c r="B2" s="5"/>
       <c r="C2" s="6"/>
       <c r="G2" s="5"/>
@@ -42079,7 +42111,7 @@
       <c r="T2" s="17"/>
       <c r="U2" s="5"/>
     </row>
-    <row r="3" spans="2:22">
+    <row r="3" spans="1:22">
       <c r="C3" s="11" t="s">
         <v>0</v>
       </c>
@@ -42090,7 +42122,7 @@
       <c r="U3" s="1"/>
       <c r="V3" s="2"/>
     </row>
-    <row r="4" spans="2:22">
+    <row r="4" spans="1:22">
       <c r="B4" s="2" t="s">
         <v>717</v>
       </c>
@@ -42098,7 +42130,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="5" spans="2:22">
+    <row r="5" spans="1:22">
       <c r="B5" s="2" t="s">
         <v>1406</v>
       </c>
@@ -42106,72 +42138,132 @@
         <v>793</v>
       </c>
     </row>
-    <row r="6" spans="2:22">
-      <c r="C6" s="183"/>
-    </row>
-    <row r="7" spans="2:22">
-      <c r="B7" s="2" t="s">
+    <row r="6" spans="1:22">
+      <c r="B6" s="2" t="s">
         <v>1405</v>
       </c>
-      <c r="C7" s="183" t="s">
+      <c r="C6" s="183" t="s">
         <v>1404</v>
       </c>
     </row>
-    <row r="8" spans="2:22">
-      <c r="B8" s="110" t="s">
+    <row r="8" spans="1:22">
+      <c r="C8" s="183"/>
+    </row>
+    <row r="9" spans="1:22">
+      <c r="C9" s="183"/>
+    </row>
+    <row r="10" spans="1:22">
+      <c r="C10" s="183"/>
+    </row>
+    <row r="11" spans="1:22">
+      <c r="A11" s="1" t="s">
+        <v>1649</v>
+      </c>
+      <c r="C11" s="183"/>
+    </row>
+    <row r="12" spans="1:22">
+      <c r="B12" s="2" t="s">
+        <v>1648</v>
+      </c>
+      <c r="C12" s="199" t="s">
+        <v>1647</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22">
+      <c r="B13" s="2" t="s">
+        <v>1648</v>
+      </c>
+      <c r="C13" s="200" t="s">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22">
+      <c r="B14" s="2" t="s">
+        <v>1652</v>
+      </c>
+      <c r="C14" s="200" t="s">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22">
+      <c r="B15" s="2" t="s">
+        <v>1652</v>
+      </c>
+      <c r="C15" s="200" t="s">
+        <v>1627</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22">
+      <c r="C16" s="199"/>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="C17" s="199"/>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="C18" s="199"/>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="C19" s="199"/>
+    </row>
+    <row r="20" spans="2:4">
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+    </row>
+    <row r="21" spans="2:4">
+      <c r="B21" s="110" t="s">
         <v>791</v>
       </c>
-      <c r="C8" s="189" t="s">
+      <c r="C21" s="189" t="s">
         <v>1161</v>
       </c>
     </row>
-    <row r="9" spans="2:22">
-      <c r="C9" s="110" t="s">
+    <row r="22" spans="2:4">
+      <c r="C22" s="110" t="s">
         <v>1139</v>
       </c>
     </row>
-    <row r="11" spans="2:22">
-      <c r="B11" s="2" t="s">
+    <row r="24" spans="2:4">
+      <c r="B24" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:22">
-      <c r="B12" s="2" t="s">
+    <row r="25" spans="2:4">
+      <c r="B25" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="2:4">
-      <c r="C19" s="187" t="s">
+    <row r="32" spans="2:4">
+      <c r="C32" s="187" t="s">
         <v>791</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D32" s="1" t="s">
         <v>1554</v>
       </c>
     </row>
-    <row r="20" spans="2:4">
-      <c r="B20" s="2" t="s">
+    <row r="33" spans="2:3">
+      <c r="B33" s="2" t="s">
         <v>1557</v>
       </c>
-      <c r="C20" s="189" t="s">
+      <c r="C33" s="189" t="s">
         <v>1555</v>
       </c>
     </row>
-    <row r="21" spans="2:4" ht="115.2">
-      <c r="C21" s="188" t="s">
+    <row r="34" spans="2:3" ht="115.2">
+      <c r="C34" s="188" t="s">
         <v>1556</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C4:D11">
-    <sortCondition ref="D4:D11"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C4:D24">
+    <sortCondition ref="D4:D24"/>
   </sortState>
-  <phoneticPr fontId="35" type="noConversion"/>
+  <phoneticPr fontId="36" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -43492,7 +43584,7 @@
     </row>
     <row r="40" spans="1:22" s="7" customFormat="1" ht="302.39999999999998">
       <c r="A40" s="91"/>
-      <c r="B40" s="68" t="s">
+      <c r="B40" s="200" t="s">
         <v>677</v>
       </c>
       <c r="C40" s="68" t="s">
@@ -47976,7 +48068,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="35" type="noConversion"/>
+  <phoneticPr fontId="36" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>

--- a/4 четверть_9_JavaScript_Vue 3 Composition API.xlsx
+++ b/4 четверть_9_JavaScript_Vue 3 Composition API.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89559D82-B49E-437D-928E-F1BA612CFE60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A960ECE9-4AC1-45F5-9D3A-267E3F402AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="1104" windowWidth="23016" windowHeight="11136" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Литература" sheetId="14" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2036" uniqueCount="1653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2046" uniqueCount="1660">
   <si>
     <t>Vue</t>
   </si>
@@ -19048,60 +19048,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">&lt;slot
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>text</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">="hello"
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:count</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>="1"
-/&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">&lt;BaseLayout&gt;
   &lt;template #header&gt;
     &lt;h1&gt;Here might be a page title&lt;/h1&gt;
@@ -40119,17 +40065,301 @@
   <si>
     <t>Библиотека компонентов</t>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>$attrs. ***</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> === </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>class</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;MyButton </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@click="onClick"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> /&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>ref</t>
+  </si>
+  <si>
+    <t>html</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;div class="col"&gt;
+  &lt;hwc-panel :title="$t('connection.connections')"
+              :caption="$t('connection.connectionNote')"
+              v-model:search="connection.search"
+              v-model:edit="connection.edit"
+              @add-item="addConnection"
+              icon="link"
+              searcheble
+              addable
+              expand&gt;
+    &lt;template v-slot:list&gt;
+      &lt;connection-list v-model:connection="connection.selected" :search="connection.search"/&gt;
+      &lt;tableselect v-model:opened="tableSelectShow" @select-table="createConnection"/&gt;
+    &lt;/template&gt;
+  &lt;/hwc-panel&gt;
+  &lt;template v-if="selectedConnection &amp;&amp; selectedConnection.id"&gt;
+    &lt;tablefields :selected-connection="connection.selected" </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ref="tablefieldsSection"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/&gt;
+    &lt;datashow :selected-connection="connection.selected" /&gt;
+  &lt;/template&gt;
+  &lt;q-inner-loading :showing="loading"&gt;
+    &lt;hwc-spinner-bar/&gt;
+  &lt;/q-inner-loading&gt;
+&lt;/div&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  setup() {
+    const </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tablefieldsSection</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = ref(null);
+    const </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>scrollToTablefields</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = async () =&gt; {
+      await nextTick();
+      </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tablefieldsSection.value?.$el?.scrollIntoView</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>({ behavior: 'smooth', block: 'start' });
+    };</t>
+    </r>
+  </si>
+  <si>
+    <t>$el - корневой DOM-узел шаблона tablefields (у вас это &lt;div&gt; из tablefields/index.html)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;slot
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>text</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">="hello"
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:count</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>="1"
+/&gt;</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="81">
+  <fonts count="83">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -40904,13 +41134,13 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="201">
+  <cellXfs count="204">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -40921,20 +41151,20 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="35" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -40943,13 +41173,7 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -40958,107 +41182,113 @@
     <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="27" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="49" fontId="42" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="23" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="53" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="57" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="62" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="64" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -41073,46 +41303,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="4" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="4" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -41121,77 +41351,77 @@
     <xf numFmtId="49" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="6" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="6" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="5" applyFill="1"/>
-    <xf numFmtId="49" fontId="17" fillId="7" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="5" applyFill="1"/>
+    <xf numFmtId="49" fontId="19" fillId="7" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="7" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="7" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="8" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="8" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="43" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="45" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="43" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -41200,97 +41430,97 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="16" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="16" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="16" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="16" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="43" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="37" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="37" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="37" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="37" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="37" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="8" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="8" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -41308,22 +41538,22 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -41335,71 +41565,71 @@
     <xf numFmtId="49" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="37" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="41" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="43" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="37" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="71" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="73" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -41408,59 +41638,77 @@
     <xf numFmtId="49" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="3" applyFill="1"/>
-    <xf numFmtId="49" fontId="73" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="43" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="37" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="3" applyFill="1"/>
+    <xf numFmtId="49" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -41469,37 +41717,28 @@
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -42132,7 +42371,7 @@
     </row>
     <row r="5" spans="1:22">
       <c r="B5" s="2" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="C5" s="183" t="s">
         <v>793</v>
@@ -42140,10 +42379,10 @@
     </row>
     <row r="6" spans="1:22">
       <c r="B6" s="2" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="C6" s="183" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -42157,40 +42396,40 @@
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="C11" s="183"/>
     </row>
     <row r="12" spans="1:22">
       <c r="B12" s="2" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="C12" s="199" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="B13" s="2" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="C13" s="200" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="14" spans="1:22">
       <c r="B14" s="2" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="C14" s="200" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="15" spans="1:22">
       <c r="B15" s="2" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="C15" s="200" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -42214,12 +42453,12 @@
         <v>791</v>
       </c>
       <c r="C21" s="189" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="22" spans="2:4">
       <c r="C22" s="110" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="24" spans="2:4">
@@ -42243,27 +42482,27 @@
         <v>791</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="33" spans="2:3">
       <c r="B33" s="2" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="C33" s="189" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="34" spans="2:3" ht="115.2">
       <c r="C34" s="188" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C4:D24">
     <sortCondition ref="D4:D24"/>
   </sortState>
-  <phoneticPr fontId="36" type="noConversion"/>
+  <phoneticPr fontId="38" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -42507,7 +42746,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="B3" s="153" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -42563,10 +42802,10 @@
         <v>725</v>
       </c>
       <c r="B14" s="150" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="C14" s="153" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D14" s="55" t="s">
         <v>398</v>
@@ -42577,7 +42816,7 @@
         <v>484</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="C15" s="103" t="s">
         <v>732</v>
@@ -42586,7 +42825,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="23" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B16" s="154" t="s">
         <v>172</v>
@@ -42594,19 +42833,19 @@
     </row>
     <row r="17" spans="1:4" ht="72">
       <c r="B17" s="155" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="72">
       <c r="A18" s="2" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B18" s="38"/>
       <c r="C18" s="2" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -42620,7 +42859,7 @@
         <v>817</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -43350,10 +43589,10 @@
         <v>668</v>
       </c>
       <c r="B31" s="111" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="C31" s="111" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="D31" s="68" t="s">
         <v>662</v>
@@ -43503,13 +43742,13 @@
     </row>
     <row r="37" spans="1:22" s="7" customFormat="1" ht="244.8">
       <c r="A37" s="22" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="B37" s="198" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="C37" s="198" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="D37" s="68"/>
       <c r="F37" s="1"/>
@@ -43530,13 +43769,13 @@
     </row>
     <row r="38" spans="1:22" s="7" customFormat="1" ht="273.60000000000002">
       <c r="A38" s="198" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="B38" s="198" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="C38" s="198" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="D38" s="68"/>
       <c r="F38" s="1"/>
@@ -44931,17 +45170,17 @@
         <v>181</v>
       </c>
       <c r="C2" s="92" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="3" spans="1:21">
       <c r="A3" s="20" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="4" spans="1:21">
       <c r="A4" s="20" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="5" spans="1:21">
@@ -44951,7 +45190,7 @@
     </row>
     <row r="6" spans="1:21">
       <c r="A6" s="10" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="8" spans="1:21" s="3" customFormat="1">
@@ -44978,7 +45217,7 @@
         <v>181</v>
       </c>
       <c r="B11" s="152" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="C11" s="115" t="s">
         <v>780</v>
@@ -44989,129 +45228,129 @@
     </row>
     <row r="12" spans="1:21" ht="273.60000000000002">
       <c r="B12" s="2" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="D12" s="140" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="13" spans="1:21">
       <c r="A13" s="23" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="C13" s="140"/>
     </row>
     <row r="14" spans="1:21">
       <c r="A14" s="140" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C14" s="140" t="s">
         <v>1005</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>1028</v>
-      </c>
-      <c r="C14" s="140" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="15" spans="1:21">
       <c r="A15" s="140" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="C15" s="140" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="16" spans="1:21">
       <c r="A16" s="140" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="C16" s="140" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="17" spans="1:20">
       <c r="A17" s="140" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="C17" s="140" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="18" spans="1:20">
       <c r="A18" s="140" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="C18" s="140" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="19" spans="1:20">
       <c r="A19" s="140" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="C19" s="140" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="20" spans="1:20">
       <c r="A20" s="140" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="C20" s="140" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="21" spans="1:20">
       <c r="A21" s="23" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
     </row>
     <row r="22" spans="1:20" ht="28.8">
       <c r="A22" s="142" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B22" s="145" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C22" s="142" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="D22" s="142"/>
     </row>
     <row r="23" spans="1:20" ht="86.4">
       <c r="A23" s="142" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B23" s="145" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="C23" s="142" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="D23" s="142" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="24" spans="1:20" ht="115.2">
@@ -45119,106 +45358,106 @@
         <v>645</v>
       </c>
       <c r="B24" s="141" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="C24" s="146" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="D24" s="141" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="28.8">
       <c r="A25" s="141" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B25" s="147" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C25" s="146" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="D25" s="141" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="26" spans="1:20">
       <c r="A26" s="141" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B26" s="141" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C26" s="146" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D26" s="141" t="s">
         <v>1016</v>
-      </c>
-      <c r="B26" s="141" t="s">
-        <v>1019</v>
-      </c>
-      <c r="C26" s="146" t="s">
-        <v>1018</v>
-      </c>
-      <c r="D26" s="141" t="s">
-        <v>1017</v>
       </c>
     </row>
     <row r="27" spans="1:20">
       <c r="A27" s="141" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B27" s="141" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C27" s="146" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D27" s="141" t="s">
         <v>1020</v>
-      </c>
-      <c r="B27" s="141" t="s">
-        <v>1023</v>
-      </c>
-      <c r="C27" s="146" t="s">
-        <v>1022</v>
-      </c>
-      <c r="D27" s="141" t="s">
-        <v>1021</v>
       </c>
     </row>
     <row r="28" spans="1:20" ht="187.2">
       <c r="A28" s="141" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B28" s="147" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C28" s="146" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D28" s="141" t="s">
         <v>1043</v>
-      </c>
-      <c r="D28" s="141" t="s">
-        <v>1044</v>
       </c>
     </row>
     <row r="29" spans="1:20" ht="28.8">
       <c r="A29" s="141" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B29" s="147" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C29" s="146" t="s">
         <v>1025</v>
       </c>
-      <c r="B29" s="147" t="s">
-        <v>1040</v>
-      </c>
-      <c r="C29" s="146" t="s">
-        <v>1026</v>
-      </c>
       <c r="D29" s="141" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="30" spans="1:20" ht="28.8">
       <c r="A30" s="143" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B30" s="145" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C30" s="144" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="D30" s="144"/>
     </row>
     <row r="31" spans="1:20" ht="28.8">
       <c r="A31" s="143" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B31" s="145" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C31" s="144" t="s">
         <v>1032</v>
-      </c>
-      <c r="B31" s="145" t="s">
-        <v>1040</v>
-      </c>
-      <c r="C31" s="144" t="s">
-        <v>1033</v>
       </c>
       <c r="D31" s="144"/>
     </row>
@@ -45240,7 +45479,7 @@
     <row r="33" spans="1:20" s="148" customFormat="1" ht="57.6">
       <c r="B33" s="133"/>
       <c r="C33" s="149" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="D33" s="150"/>
       <c r="E33" s="3"/>
@@ -45254,10 +45493,10 @@
     <row r="34" spans="1:20" s="148" customFormat="1" ht="186.6" customHeight="1">
       <c r="B34" s="133"/>
       <c r="C34" s="149" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="D34" s="149" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="133"/>
@@ -45269,7 +45508,7 @@
     </row>
     <row r="35" spans="1:20">
       <c r="A35" s="10" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>2</v>
@@ -45364,7 +45603,7 @@
         <v>355</v>
       </c>
       <c r="B42" s="55" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="C42" s="55" t="s">
         <v>528</v>
@@ -45517,25 +45756,25 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="138" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B2" s="88" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="53" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="53" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="53" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="39" customFormat="1">
@@ -45543,80 +45782,80 @@
     </row>
     <row r="9" spans="1:5" ht="28.8">
       <c r="A9" s="53" t="s">
+        <v>949</v>
+      </c>
+      <c r="B9" s="114" t="s">
         <v>950</v>
-      </c>
-      <c r="B9" s="114" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="144">
       <c r="C10" s="111" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="20" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="115.2">
       <c r="C12" s="2" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="30" customHeight="1">
       <c r="A13" s="138" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B13" s="114" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="20" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="28.8">
       <c r="B15" s="2" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="20" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="115.2">
       <c r="B17" s="2" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="20" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="57.6">
       <c r="B19" s="2" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="28.8">
       <c r="A20" s="20" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B20" s="114" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="C20" s="114" t="s">
         <v>62</v>
@@ -45627,106 +45866,106 @@
     </row>
     <row r="21" spans="1:4" ht="43.2">
       <c r="B21" s="2" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="20" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="20" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="115.2">
       <c r="B25" s="111" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="139" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B26" s="111" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="216">
       <c r="B27" s="111" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="53" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="72">
       <c r="B29" s="2" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="187.2">
       <c r="B30" s="2" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="20" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="86.4">
       <c r="A32" s="2" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B32" s="140" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="43.2">
       <c r="A33" s="2" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B33" s="140" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="331.2">
       <c r="A34" s="2" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B34" s="111" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
   </sheetData>
@@ -46105,7 +46344,7 @@
         <v>487</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -46268,16 +46507,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="53" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" ht="86.4">
       <c r="C15" s="88" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="D15" s="111" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="F15" s="2"/>
     </row>
@@ -46286,7 +46525,7 @@
         <v>651</v>
       </c>
       <c r="D16" s="111" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="F16" s="2"/>
     </row>
@@ -46431,19 +46670,19 @@
         <v>629</v>
       </c>
       <c r="D29" s="111" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="374.4">
       <c r="A30" s="58"/>
       <c r="C30" s="111" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="D30" s="111" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E30" s="111" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -47006,30 +47245,30 @@
   <sheetData>
     <row r="2" spans="1:6">
       <c r="A2" s="23" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="57.6">
       <c r="A3" s="53" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="57.6">
       <c r="A4" s="53" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="72">
       <c r="A5" s="53" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="53" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="39" customFormat="1">
@@ -47037,15 +47276,15 @@
     </row>
     <row r="9" spans="1:6" s="133" customFormat="1">
       <c r="A9" s="23" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="133" customFormat="1">
       <c r="A10" s="134" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="C10" s="133" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="11" spans="1:6" s="133" customFormat="1" ht="86.4">
@@ -47053,10 +47292,10 @@
         <v>828</v>
       </c>
       <c r="B11" s="135" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C11" s="133" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="133" customFormat="1" ht="57.6">
@@ -47064,64 +47303,64 @@
         <v>827</v>
       </c>
       <c r="C12" s="133" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="57.6">
       <c r="A13" s="53" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="C13" s="114" t="s">
+        <v>867</v>
+      </c>
+      <c r="D13" s="114" t="s">
         <v>868</v>
-      </c>
-      <c r="D13" s="114" t="s">
-        <v>869</v>
       </c>
       <c r="E13" s="130"/>
       <c r="F13" s="56"/>
     </row>
     <row r="14" spans="1:6" ht="144">
       <c r="B14" s="111" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="E14" s="130"/>
       <c r="F14" s="56"/>
     </row>
     <row r="15" spans="1:6" ht="231" customHeight="1">
       <c r="A15" s="22" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B15" s="111" t="s">
+        <v>889</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>890</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>891</v>
       </c>
       <c r="E15" s="130"/>
       <c r="F15" s="56"/>
     </row>
     <row r="16" spans="1:6" ht="86.4">
       <c r="A16" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B16" s="111" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="E16" s="130"/>
       <c r="F16" s="56"/>
     </row>
     <row r="17" spans="1:6" ht="172.8">
       <c r="A17" s="55" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B17" s="55"/>
       <c r="C17" s="55" t="s">
@@ -47133,13 +47372,13 @@
     </row>
     <row r="18" spans="1:6" ht="216">
       <c r="A18" s="55" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B18" s="113" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="C18" s="132" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="D18" s="55"/>
       <c r="E18" s="130"/>
@@ -47151,7 +47390,7 @@
         <v>827</v>
       </c>
       <c r="C19" s="132" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="D19" s="55"/>
       <c r="E19" s="130"/>
@@ -47159,14 +47398,14 @@
     </row>
     <row r="20" spans="1:6" ht="57.6">
       <c r="A20" s="53" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B20" s="55"/>
       <c r="C20" s="114" t="s">
+        <v>867</v>
+      </c>
+      <c r="D20" s="114" t="s">
         <v>868</v>
-      </c>
-      <c r="D20" s="114" t="s">
-        <v>869</v>
       </c>
       <c r="E20" s="130"/>
       <c r="F20" s="56"/>
@@ -47174,24 +47413,24 @@
     <row r="21" spans="1:6" ht="244.8">
       <c r="A21" s="55"/>
       <c r="B21" s="113" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C21" s="55" t="s">
+        <v>879</v>
+      </c>
+      <c r="D21" s="55" t="s">
         <v>880</v>
-      </c>
-      <c r="D21" s="55" t="s">
-        <v>881</v>
       </c>
       <c r="E21" s="130"/>
       <c r="F21" s="56"/>
     </row>
     <row r="22" spans="1:6" ht="72">
       <c r="A22" s="131" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B22" s="55"/>
       <c r="C22" s="113" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="D22" s="55"/>
       <c r="E22" s="130"/>
@@ -47215,7 +47454,7 @@
         <v>524</v>
       </c>
       <c r="C24" s="55" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="D24" s="55" t="s">
         <v>525</v>
@@ -47588,22 +47827,22 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="53" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="23" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="23" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="23" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="39" customFormat="1">
@@ -47611,7 +47850,7 @@
     </row>
     <row r="8" spans="1:5" s="54" customFormat="1">
       <c r="A8" s="53" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B8" s="55"/>
       <c r="C8" s="55"/>
@@ -47621,37 +47860,37 @@
       <c r="A9" s="55"/>
       <c r="B9" s="55"/>
       <c r="C9" s="184" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="E9" s="71"/>
     </row>
     <row r="10" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A10" s="55" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="B10" s="55" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C10" s="184" t="s">
         <v>1412</v>
-      </c>
-      <c r="C10" s="184" t="s">
-        <v>1413</v>
       </c>
       <c r="E10" s="71"/>
     </row>
     <row r="11" spans="1:5" s="54" customFormat="1" ht="43.2">
       <c r="A11" s="55" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B11" s="55" t="s">
         <v>1410</v>
       </c>
-      <c r="B11" s="55" t="s">
-        <v>1411</v>
-      </c>
       <c r="C11" s="55" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="E11" s="71"/>
     </row>
     <row r="12" spans="1:5" s="54" customFormat="1">
       <c r="A12" s="53" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="B12" s="55"/>
       <c r="C12" s="55"/>
@@ -47662,13 +47901,13 @@
         <v>62</v>
       </c>
       <c r="B13" s="55" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C13" s="54" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D13" s="54" t="s">
         <v>1415</v>
-      </c>
-      <c r="D13" s="54" t="s">
-        <v>1416</v>
       </c>
       <c r="E13" s="71"/>
     </row>
@@ -47677,18 +47916,18 @@
         <v>43</v>
       </c>
       <c r="B14" s="55" t="s">
+        <v>901</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>902</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>903</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="43.2">
       <c r="A15" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>900</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>901</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="244.8">
@@ -47696,109 +47935,109 @@
         <v>270</v>
       </c>
       <c r="B16" s="111" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="23" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="230.4">
       <c r="C18" s="2" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28.8">
       <c r="A19" s="23" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B19" s="183" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="20" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="100.8">
       <c r="B21" s="2" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="20" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="86.4">
       <c r="B23" s="2" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="20" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="100.8">
       <c r="B25" s="2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="20" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="100.8">
       <c r="B27" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="28.8">
       <c r="A28" s="20" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="345.6">
       <c r="C29" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="28.8">
       <c r="A30" s="23" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="43.2">
       <c r="C31" s="111" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
   </sheetData>
@@ -47848,32 +48087,32 @@
   <sheetData>
     <row r="2" spans="1:6">
       <c r="A2" s="23" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="23" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="B4" s="20" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="B5" s="20" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="B6" s="20" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="B7" s="20" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="39" customFormat="1">
@@ -47882,7 +48121,7 @@
     <row r="10" spans="1:6" s="133" customFormat="1"/>
     <row r="11" spans="1:6">
       <c r="A11" s="23" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="D11" s="40"/>
       <c r="E11" s="156"/>
@@ -47890,7 +48129,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="20" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="D12" s="40"/>
       <c r="E12" s="156"/>
@@ -47898,10 +48137,10 @@
     </row>
     <row r="13" spans="1:6" ht="72">
       <c r="B13" s="176" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="C13" s="169" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="D13" s="40"/>
       <c r="E13" s="156"/>
@@ -47909,7 +48148,7 @@
     </row>
     <row r="14" spans="1:6" ht="72">
       <c r="C14" s="169" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="D14" s="40"/>
       <c r="E14" s="156"/>
@@ -47917,13 +48156,13 @@
     </row>
     <row r="15" spans="1:6" ht="28.8">
       <c r="A15" s="2" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="C15" s="93" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="D15" s="40"/>
       <c r="E15" s="156"/>
@@ -47931,13 +48170,13 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C16" s="93" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="D16" s="40"/>
       <c r="E16" s="156"/>
@@ -47945,10 +48184,10 @@
     </row>
     <row r="17" spans="1:6" ht="100.8">
       <c r="B17" s="169" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C17" s="93" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="D17" s="40"/>
       <c r="E17" s="156"/>
@@ -47956,7 +48195,7 @@
     </row>
     <row r="18" spans="1:6" ht="100.8">
       <c r="C18" s="93" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="D18" s="40"/>
       <c r="E18" s="156"/>
@@ -47964,13 +48203,13 @@
     </row>
     <row r="19" spans="1:6" ht="28.8">
       <c r="A19" s="2" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B19" s="140" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="C19" s="93" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="D19" s="40"/>
       <c r="E19" s="156"/>
@@ -47978,13 +48217,13 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="C20" s="93" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="D20" s="40"/>
       <c r="E20" s="156"/>
@@ -47992,83 +48231,83 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="23" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="B22" s="2" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="72">
       <c r="B23" s="140" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="B24" s="2" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="172.8">
       <c r="C25" s="2" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="20" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="288">
       <c r="C27" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="20" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B28" s="114" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="331.2">
       <c r="B29" s="2" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="C29" s="140" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="20" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="158.4">
       <c r="B31" s="2" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="20" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="33" spans="3:3" ht="187.2">
       <c r="C33" s="2" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="36" type="noConversion"/>
+  <phoneticPr fontId="38" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -48115,50 +48354,50 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="23" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="23" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="23" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="23" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="175" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="175" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="175" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="D8" s="178" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="197" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="175" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="39" customFormat="1">
@@ -48166,14 +48405,14 @@
     </row>
     <row r="13" spans="1:5" s="133" customFormat="1">
       <c r="C13" s="168" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="D13" s="172"/>
       <c r="E13" s="70"/>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="23" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="B14" s="169"/>
     </row>
@@ -48183,7 +48422,7 @@
         <v>62</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -48191,7 +48430,7 @@
         <v>43</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -48199,25 +48438,25 @@
         <v>64</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="B18" s="2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>1286</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>1287</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="201.6">
       <c r="C19" s="2" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="175" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="B20" s="23" t="s">
         <v>62</v>
@@ -48227,80 +48466,80 @@
     </row>
     <row r="21" spans="1:4" ht="72">
       <c r="A21" s="2" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="72">
       <c r="A22" s="2" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="72">
       <c r="A23" s="2" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="168" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="28.8">
       <c r="B25" s="2" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>1297</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>1298</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="57.6">
       <c r="B26" s="2" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="115.2">
       <c r="A27" s="2" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>1301</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>1302</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="72">
       <c r="A28" s="2" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="168" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>43</v>
@@ -48308,63 +48547,63 @@
     </row>
     <row r="30" spans="1:4" ht="201.6">
       <c r="C30" s="2" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="23" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="B31" s="23"/>
       <c r="C31" s="23"/>
       <c r="D31" s="23" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="43.2">
       <c r="A32" s="2" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B32" s="169" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>1309</v>
-      </c>
-      <c r="B32" s="169" t="s">
-        <v>1315</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>1310</v>
       </c>
       <c r="D32" s="170"/>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="176" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="C34" s="2" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="23" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="302.39999999999998">
       <c r="A36" s="2" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="B36" s="189" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="28.8">
       <c r="A37" s="177" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="B37" s="169" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="C37" s="169"/>
     </row>
@@ -48372,212 +48611,212 @@
       <c r="A38" s="169"/>
       <c r="B38" s="169"/>
       <c r="C38" s="2" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="176" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="115.2">
       <c r="C40" s="2" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="176" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="100.8">
       <c r="C42" s="169" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="115.2">
       <c r="A43" s="2" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="115.2">
       <c r="A44" s="2" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="144">
       <c r="A45" s="2" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="57.6">
       <c r="A46" s="2" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="28.8">
       <c r="A47" s="177" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B47" s="169" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="187.2">
       <c r="A48" s="2" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="B48" s="169" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="86.4">
       <c r="A49" s="2" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B49" s="169" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>1337</v>
+      </c>
+      <c r="D49" s="2" t="s">
         <v>1335</v>
-      </c>
-      <c r="B49" s="169" t="s">
-        <v>1333</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>1338</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>1336</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="176" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>1330</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>1331</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="72">
       <c r="C51" s="2" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="176" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="187.2">
       <c r="C53" s="2" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="45" customHeight="1">
       <c r="A54" s="177" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="B54" s="169" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="144">
       <c r="A55" s="2" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="72">
       <c r="A56" s="2" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>1342</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>1341</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>1333</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>1343</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>1342</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="129.6">
       <c r="A57" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>1345</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>1333</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>1344</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>1346</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="244.8">
       <c r="B58" s="169" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="176" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="C60" s="2" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="176" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="172.8">
@@ -48585,7 +48824,7 @@
         <v>62</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="144">
@@ -48593,48 +48832,48 @@
         <v>43</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="28.8">
       <c r="A64" s="177" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B64" s="169" t="s">
         <v>1362</v>
       </c>
-      <c r="B64" s="169" t="s">
-        <v>1363</v>
-      </c>
       <c r="D64" s="2" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="216">
       <c r="A65" s="2" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="B65" s="2" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>1364</v>
+      </c>
+      <c r="D65" s="2" t="s">
         <v>1366</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>1365</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>1367</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="244.8">
       <c r="A66" s="2" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="176" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="172.8">
@@ -48642,7 +48881,7 @@
         <v>62</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="144">
@@ -48650,92 +48889,92 @@
         <v>43</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="23" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="172.8">
       <c r="A71" s="2" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B71" s="169" t="s">
         <v>1377</v>
       </c>
-      <c r="B71" s="169" t="s">
-        <v>1378</v>
-      </c>
       <c r="C71" s="2" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="244.8">
       <c r="B72" s="2" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="23" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="100.8">
       <c r="A74" s="2" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="115.2">
       <c r="A75" s="2" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="244.8">
       <c r="A76" s="2" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="43.2">
       <c r="A77" s="2" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="86.4">
       <c r="C78" s="2" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="175" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="216">
       <c r="B80" s="2" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="C80" s="2" t="s">
+        <v>1383</v>
+      </c>
+      <c r="D80" s="2" t="s">
         <v>1384</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>1385</v>
       </c>
     </row>
   </sheetData>
@@ -48785,7 +49024,7 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="23" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -48806,7 +49045,7 @@
     <row r="8" spans="1:5">
       <c r="A8" s="175"/>
       <c r="D8" s="178" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -48820,14 +49059,14 @@
     </row>
     <row r="13" spans="1:5" s="133" customFormat="1">
       <c r="C13" s="168" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="D13" s="172"/>
       <c r="E13" s="70"/>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="23" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
     </row>
   </sheetData>
@@ -48877,30 +49116,30 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="23" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="B3" s="168" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="C3" s="92" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="23" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="23" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="B6" s="23" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="39" customFormat="1">
@@ -48908,153 +49147,153 @@
     </row>
     <row r="12" spans="1:5" s="133" customFormat="1">
       <c r="C12" s="168" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="D12" s="172"/>
       <c r="E12" s="70"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="23" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="B13" s="169"/>
     </row>
     <row r="14" spans="1:5" ht="72">
       <c r="B14" s="169" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="C14" s="193"/>
     </row>
     <row r="15" spans="1:5" ht="302.39999999999998">
       <c r="A15" s="169" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>1279</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>1281</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>1280</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="23" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="230.4">
       <c r="A17" s="2" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="B17" s="183" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="201.6">
       <c r="A18" s="2" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B18" s="189" t="s">
+        <v>1604</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>1420</v>
       </c>
-      <c r="B18" s="189" t="s">
-        <v>1605</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>1421</v>
-      </c>
       <c r="D18" s="2" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="100.8">
       <c r="A19" s="2" t="s">
+        <v>1421</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>1423</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>1422</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>1424</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>1423</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="23" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="273.60000000000002">
       <c r="A21" s="2" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="B21" s="189" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="158.4">
       <c r="A22" s="2" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>1430</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>1431</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="100.8">
       <c r="A23" s="2" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="23" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="C24" s="114" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="D24" s="114" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="187.2">
       <c r="C25" s="2" t="s">
+        <v>1608</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>1609</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>1610</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="115.2">
       <c r="B26" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>1612</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>1613</v>
-      </c>
       <c r="D26" s="2" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="23" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="115.2">
       <c r="B28" s="189" t="s">
+        <v>1614</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>1615</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>1616</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="57.6">
       <c r="D29" s="110" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
     </row>
   </sheetData>
@@ -49084,84 +49323,84 @@
   <sheetData>
     <row r="2" spans="1:3">
       <c r="A2" s="177" t="s">
+        <v>1473</v>
+      </c>
+      <c r="B2" s="177" t="s">
         <v>1474</v>
-      </c>
-      <c r="B2" s="177" t="s">
-        <v>1475</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="B5" s="190" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="28.8">
       <c r="A6" s="2" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="B6" s="190" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="C6" s="92" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="B7" s="190" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="B8" s="190" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="B9" s="190" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="21" spans="1:29" s="39" customFormat="1">
@@ -49169,69 +49408,69 @@
     </row>
     <row r="22" spans="1:29" s="133" customFormat="1">
       <c r="C22" s="168" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="D22" s="172"/>
       <c r="E22" s="70"/>
     </row>
     <row r="23" spans="1:29">
       <c r="A23" s="177" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="B23" s="150"/>
       <c r="C23" s="150"/>
     </row>
     <row r="24" spans="1:29" ht="43.2">
       <c r="A24" s="114" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="B24" s="186" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="C24" s="189" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="25" spans="1:29">
       <c r="A25" s="2" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>1434</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>1463</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>1435</v>
-      </c>
       <c r="D25" s="2" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="26" spans="1:29">
       <c r="A26" s="2" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="27" spans="1:29" s="70" customFormat="1">
       <c r="A27" s="2" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -49260,16 +49499,16 @@
     </row>
     <row r="28" spans="1:29" s="70" customFormat="1">
       <c r="A28" s="2" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -49298,16 +49537,16 @@
     </row>
     <row r="29" spans="1:29" s="70" customFormat="1">
       <c r="A29" s="2" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -49336,16 +49575,16 @@
     </row>
     <row r="30" spans="1:29" s="70" customFormat="1">
       <c r="A30" s="2" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
@@ -49374,16 +49613,16 @@
     </row>
     <row r="31" spans="1:29" s="70" customFormat="1">
       <c r="A31" s="2" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
@@ -49412,16 +49651,16 @@
     </row>
     <row r="32" spans="1:29" s="70" customFormat="1" ht="72">
       <c r="A32" s="2" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -49450,16 +49689,16 @@
     </row>
     <row r="33" spans="1:29" s="70" customFormat="1">
       <c r="A33" s="2" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
@@ -49488,16 +49727,16 @@
     </row>
     <row r="34" spans="1:29" s="70" customFormat="1">
       <c r="A34" s="2" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -49526,7 +49765,7 @@
     </row>
     <row r="35" spans="1:29" s="70" customFormat="1">
       <c r="A35" s="177" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -49558,10 +49797,10 @@
     </row>
     <row r="36" spans="1:29" s="70" customFormat="1" ht="43.2">
       <c r="A36" s="114" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="B36" s="186" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -49592,7 +49831,7 @@
     </row>
     <row r="37" spans="1:29" s="70" customFormat="1">
       <c r="A37" s="23" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -49624,14 +49863,14 @@
     </row>
     <row r="38" spans="1:29" s="70" customFormat="1" ht="28.8">
       <c r="A38" s="186" t="s">
+        <v>1525</v>
+      </c>
+      <c r="B38" s="186" t="s">
         <v>1526</v>
-      </c>
-      <c r="B38" s="186" t="s">
-        <v>1527</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
@@ -49660,7 +49899,7 @@
     </row>
     <row r="39" spans="1:29" s="70" customFormat="1">
       <c r="A39" s="23" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -49692,16 +49931,16 @@
     </row>
     <row r="40" spans="1:29" s="70" customFormat="1">
       <c r="A40" s="2" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>1477</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="C40" s="2" t="s">
+        <v>1533</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>1478</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>1534</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>1479</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
@@ -49730,16 +49969,16 @@
     </row>
     <row r="41" spans="1:29" s="70" customFormat="1">
       <c r="A41" s="2" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>1480</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="C41" s="2" t="s">
         <v>1481</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>1482</v>
-      </c>
       <c r="D41" s="2" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -49768,16 +50007,16 @@
     </row>
     <row r="42" spans="1:29" s="70" customFormat="1">
       <c r="A42" s="2" t="s">
+        <v>1482</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>1483</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>1484</v>
-      </c>
       <c r="C42" s="2" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -49806,16 +50045,16 @@
     </row>
     <row r="43" spans="1:29" s="70" customFormat="1">
       <c r="A43" s="2" t="s">
+        <v>1484</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>1485</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="C43" s="2" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>1486</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>1536</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>1487</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
@@ -49844,16 +50083,16 @@
     </row>
     <row r="44" spans="1:29" s="70" customFormat="1">
       <c r="A44" s="2" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>1488</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="C44" s="2" t="s">
+        <v>1536</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>1489</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>1537</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>1490</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
@@ -49882,16 +50121,16 @@
     </row>
     <row r="45" spans="1:29" s="70" customFormat="1">
       <c r="A45" s="2" t="s">
+        <v>1530</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>1531</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>1532</v>
-      </c>
       <c r="C45" s="2" t="s">
+        <v>1537</v>
+      </c>
+      <c r="D45" s="183" t="s">
         <v>1538</v>
-      </c>
-      <c r="D45" s="183" t="s">
-        <v>1539</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
@@ -49920,7 +50159,7 @@
     </row>
     <row r="46" spans="1:29" s="70" customFormat="1">
       <c r="A46" s="190" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="B46" s="183"/>
       <c r="C46" s="2"/>
@@ -49952,10 +50191,10 @@
     </row>
     <row r="47" spans="1:29" s="70" customFormat="1">
       <c r="A47" s="114" t="s">
+        <v>1490</v>
+      </c>
+      <c r="B47" s="114" t="s">
         <v>1491</v>
-      </c>
-      <c r="B47" s="114" t="s">
-        <v>1492</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -49987,10 +50226,10 @@
     <row r="48" spans="1:29" s="70" customFormat="1">
       <c r="A48" s="133"/>
       <c r="B48" s="190" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C48" s="23" t="s">
         <v>1559</v>
-      </c>
-      <c r="C48" s="23" t="s">
-        <v>1560</v>
       </c>
       <c r="D48" s="2"/>
       <c r="F48" s="2"/>
@@ -50020,16 +50259,16 @@
     </row>
     <row r="49" spans="1:29" s="70" customFormat="1" ht="43.2">
       <c r="A49" s="183" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="B49" s="189" t="s">
+        <v>1541</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>1542</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>1543</v>
-      </c>
       <c r="D49" s="2" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -50058,7 +50297,7 @@
     </row>
     <row r="50" spans="1:29" s="70" customFormat="1">
       <c r="A50" s="191" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="B50" s="183"/>
       <c r="C50" s="2"/>
@@ -50090,13 +50329,13 @@
     </row>
     <row r="51" spans="1:29" s="70" customFormat="1">
       <c r="A51" s="2" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="D51" s="2"/>
       <c r="F51" s="2"/>
@@ -50126,16 +50365,16 @@
     </row>
     <row r="52" spans="1:29" s="70" customFormat="1" ht="28.8">
       <c r="A52" s="2" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="D52" s="189" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
@@ -50165,13 +50404,13 @@
     <row r="53" spans="1:29" s="70" customFormat="1" ht="57.6">
       <c r="A53" s="2"/>
       <c r="B53" s="189" t="s">
+        <v>1551</v>
+      </c>
+      <c r="C53" s="183" t="s">
         <v>1552</v>
       </c>
-      <c r="C53" s="183" t="s">
-        <v>1553</v>
-      </c>
       <c r="D53" s="189" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
@@ -50201,13 +50440,13 @@
     <row r="54" spans="1:29" s="70" customFormat="1" ht="72">
       <c r="A54" s="2"/>
       <c r="B54" s="59" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="C54" s="59" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="D54" s="189" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
@@ -50237,13 +50476,13 @@
     <row r="55" spans="1:29" s="70" customFormat="1" ht="86.4">
       <c r="A55" s="2"/>
       <c r="B55" s="59" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="C55" s="59" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="D55" s="189" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
@@ -50272,13 +50511,13 @@
     </row>
     <row r="56" spans="1:29" s="70" customFormat="1">
       <c r="A56" s="2" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="C56" s="22" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="D56" s="189"/>
       <c r="F56" s="2"/>
@@ -50308,7 +50547,7 @@
     </row>
     <row r="57" spans="1:29" s="70" customFormat="1">
       <c r="A57" s="191" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" s="22"/>
@@ -50340,13 +50579,13 @@
     </row>
     <row r="58" spans="1:29" s="70" customFormat="1">
       <c r="A58" s="2" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="C58" s="22" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="D58" s="2"/>
       <c r="F58" s="2"/>
@@ -50376,13 +50615,13 @@
     </row>
     <row r="59" spans="1:29" s="70" customFormat="1">
       <c r="A59" s="2" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="C59" s="22" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="D59" s="189"/>
       <c r="F59" s="2"/>
@@ -50412,16 +50651,16 @@
     </row>
     <row r="60" spans="1:29" s="70" customFormat="1">
       <c r="A60" s="2" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="C60" s="22" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="D60" s="189" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
@@ -50451,10 +50690,10 @@
     <row r="61" spans="1:29" s="70" customFormat="1" ht="57.6">
       <c r="A61" s="2"/>
       <c r="B61" s="189" t="s">
+        <v>1551</v>
+      </c>
+      <c r="C61" s="183" t="s">
         <v>1552</v>
-      </c>
-      <c r="C61" s="183" t="s">
-        <v>1553</v>
       </c>
       <c r="D61" s="189"/>
       <c r="F61" s="2"/>
@@ -50514,13 +50753,13 @@
     </row>
     <row r="63" spans="1:29" s="70" customFormat="1">
       <c r="A63" s="2" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="C63" s="22" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="D63" s="189"/>
       <c r="F63" s="2"/>
@@ -50551,13 +50790,13 @@
     <row r="64" spans="1:29" s="70" customFormat="1" ht="86.4">
       <c r="A64" s="2"/>
       <c r="B64" s="2" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="C64" s="22" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="D64" s="189" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
@@ -50586,10 +50825,10 @@
     </row>
     <row r="65" spans="1:29" s="70" customFormat="1">
       <c r="A65" s="114" t="s">
+        <v>1492</v>
+      </c>
+      <c r="B65" s="114" t="s">
         <v>1493</v>
-      </c>
-      <c r="B65" s="114" t="s">
-        <v>1494</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
@@ -50621,10 +50860,10 @@
     <row r="66" spans="1:29" s="70" customFormat="1">
       <c r="A66" s="192"/>
       <c r="B66" s="190" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C66" s="23" t="s">
         <v>1559</v>
-      </c>
-      <c r="C66" s="23" t="s">
-        <v>1560</v>
       </c>
       <c r="D66" s="2"/>
       <c r="F66" s="2"/>
@@ -50654,16 +50893,16 @@
     </row>
     <row r="67" spans="1:29" s="70" customFormat="1" ht="57.6">
       <c r="A67" s="183" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="B67" s="189" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C67" s="2" t="s">
         <v>1544</v>
       </c>
-      <c r="C67" s="2" t="s">
-        <v>1545</v>
-      </c>
       <c r="D67" s="2" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
@@ -50692,14 +50931,14 @@
     </row>
     <row r="68" spans="1:29" s="70" customFormat="1">
       <c r="A68" s="114" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B68" s="114" t="s">
         <v>1495</v>
-      </c>
-      <c r="B68" s="114" t="s">
-        <v>1496</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="2" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
@@ -50729,10 +50968,10 @@
     <row r="69" spans="1:29" s="70" customFormat="1" ht="172.8">
       <c r="A69" s="2"/>
       <c r="B69" s="189" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="D69" s="2"/>
       <c r="F69" s="2"/>
@@ -50762,16 +51001,16 @@
     </row>
     <row r="70" spans="1:29" s="70" customFormat="1">
       <c r="A70" s="114" t="s">
+        <v>1497</v>
+      </c>
+      <c r="B70" s="114" t="s">
         <v>1498</v>
       </c>
-      <c r="B70" s="114" t="s">
-        <v>1499</v>
-      </c>
       <c r="C70" s="2" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
@@ -50800,16 +51039,16 @@
     </row>
     <row r="71" spans="1:29" s="70" customFormat="1">
       <c r="A71" s="114" t="s">
+        <v>1499</v>
+      </c>
+      <c r="B71" s="114" t="s">
         <v>1500</v>
       </c>
-      <c r="B71" s="114" t="s">
-        <v>1501</v>
-      </c>
       <c r="C71" s="2" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
@@ -50838,7 +51077,7 @@
     </row>
     <row r="72" spans="1:29" s="70" customFormat="1" ht="28.8">
       <c r="A72" s="190" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -50870,14 +51109,14 @@
     </row>
     <row r="73" spans="1:29" s="70" customFormat="1">
       <c r="A73" s="114" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B73" s="114" t="s">
         <v>1504</v>
-      </c>
-      <c r="B73" s="114" t="s">
-        <v>1505</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" s="2" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
@@ -50906,13 +51145,13 @@
     </row>
     <row r="74" spans="1:29" s="70" customFormat="1" ht="115.2">
       <c r="A74" s="189" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B74" s="189" t="s">
         <v>1589</v>
       </c>
-      <c r="B74" s="189" t="s">
-        <v>1590</v>
-      </c>
       <c r="C74" s="2" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="D74" s="2"/>
       <c r="F74" s="2"/>
@@ -50942,7 +51181,7 @@
     </row>
     <row r="75" spans="1:29" s="70" customFormat="1">
       <c r="A75" s="190" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="B75" s="189"/>
       <c r="C75" s="2"/>
@@ -50974,124 +51213,124 @@
     </row>
     <row r="76" spans="1:29" ht="216">
       <c r="B76" s="59" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C76" s="189" t="s">
+        <v>1597</v>
+      </c>
+      <c r="D76" s="189" t="s">
         <v>1600</v>
-      </c>
-      <c r="C76" s="189" t="s">
-        <v>1598</v>
-      </c>
-      <c r="D76" s="189" t="s">
-        <v>1601</v>
       </c>
     </row>
     <row r="77" spans="1:29">
       <c r="A77" s="186" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B77" s="186" t="s">
         <v>1506</v>
       </c>
-      <c r="B77" s="186" t="s">
-        <v>1507</v>
-      </c>
       <c r="D77" s="2" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="78" spans="1:29">
       <c r="A78" s="190" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="79" spans="1:29">
       <c r="A79" s="186" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B79" s="186" t="s">
         <v>1508</v>
       </c>
-      <c r="B79" s="186" t="s">
+      <c r="D79" s="2" t="s">
         <v>1509</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>1510</v>
       </c>
     </row>
     <row r="80" spans="1:29">
       <c r="A80" s="190" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="186" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B81" s="186" t="s">
         <v>1511</v>
       </c>
-      <c r="B81" s="186" t="s">
+      <c r="D81" s="2" t="s">
         <v>1512</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>1513</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="185" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B82" s="186" t="s">
         <v>1502</v>
       </c>
-      <c r="B82" s="186" t="s">
-        <v>1503</v>
-      </c>
       <c r="D82" s="2" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="216">
       <c r="B83" s="2" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="190" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="186" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B85" s="186" t="s">
         <v>1514</v>
       </c>
-      <c r="B85" s="186" t="s">
+      <c r="D85" s="2" t="s">
         <v>1515</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>1516</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="186" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B86" s="186" t="s">
         <v>1517</v>
       </c>
-      <c r="B86" s="186" t="s">
+      <c r="D86" s="2" t="s">
         <v>1518</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>1519</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="186" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B87" s="186" t="s">
         <v>1520</v>
       </c>
-      <c r="B87" s="186" t="s">
+      <c r="D87" s="2" t="s">
         <v>1521</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>1522</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="186" t="s">
+        <v>1522</v>
+      </c>
+      <c r="B88" s="186" t="s">
         <v>1523</v>
       </c>
-      <c r="B88" s="186" t="s">
+      <c r="D88" s="2" t="s">
         <v>1524</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>1525</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -51146,71 +51385,71 @@
         <v>530</v>
       </c>
       <c r="B2" s="159" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>1117</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>1118</v>
-      </c>
       <c r="D2" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="B3" s="62" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="D3" s="110" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="B4" s="62" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="B5" s="62" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="B6" s="62" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="B7" s="62" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="62" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="B9" s="62" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="B10" s="62" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="B11" s="62" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="B12" s="62" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="B13" s="62" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -51220,17 +51459,17 @@
     </row>
     <row r="15" spans="1:4">
       <c r="B15" s="62" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="B16" s="62" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="B17" s="62" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="39" customFormat="1">
@@ -51257,7 +51496,7 @@
     </row>
     <row r="23" spans="1:5" s="54" customFormat="1">
       <c r="A23" s="62" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="C23" s="55"/>
       <c r="D23" s="55"/>
@@ -51265,19 +51504,19 @@
     </row>
     <row r="24" spans="1:5" s="54" customFormat="1" ht="129.6">
       <c r="B24" s="158" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C24" s="55" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D24" s="158" t="s">
         <v>1121</v>
-      </c>
-      <c r="C24" s="55" t="s">
-        <v>1095</v>
-      </c>
-      <c r="D24" s="158" t="s">
-        <v>1122</v>
       </c>
       <c r="E24" s="71"/>
     </row>
     <row r="25" spans="1:5" s="54" customFormat="1" ht="86.4">
       <c r="B25" s="158" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="C25" s="55"/>
       <c r="D25" s="158"/>
@@ -51285,7 +51524,7 @@
     </row>
     <row r="26" spans="1:5" s="54" customFormat="1">
       <c r="A26" s="62" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="B26" s="55"/>
       <c r="E26" s="71"/>
@@ -51293,16 +51532,16 @@
     <row r="27" spans="1:5" s="54" customFormat="1" ht="57.6">
       <c r="A27" s="55"/>
       <c r="B27" s="165" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C27" s="69" t="s">
         <v>1190</v>
-      </c>
-      <c r="C27" s="69" t="s">
-        <v>1191</v>
       </c>
       <c r="E27" s="71"/>
     </row>
     <row r="28" spans="1:5" s="54" customFormat="1">
       <c r="A28" s="62" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B28" s="55"/>
       <c r="C28" s="55"/>
@@ -51313,317 +51552,317 @@
       <c r="A29" s="55"/>
       <c r="B29" s="55"/>
       <c r="C29" s="153" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="D29" s="55"/>
       <c r="E29" s="71"/>
     </row>
     <row r="30" spans="1:5" s="54" customFormat="1">
       <c r="A30" s="166" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B30" s="166" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="C30" s="166" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="D30" s="55"/>
       <c r="E30" s="71"/>
     </row>
     <row r="31" spans="1:5" s="54" customFormat="1">
       <c r="A31" s="166" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B31" s="166" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="C31" s="166" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="D31" s="55"/>
       <c r="E31" s="71"/>
     </row>
     <row r="32" spans="1:5" s="54" customFormat="1" ht="129.6">
       <c r="A32" s="159" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="B32" s="140" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="C32" s="55" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D32" s="55"/>
       <c r="E32" s="71"/>
     </row>
     <row r="33" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A33" s="62" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="C33" s="55"/>
       <c r="D33" s="55" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="E33" s="71"/>
     </row>
     <row r="34" spans="1:5" s="54" customFormat="1" ht="43.2">
       <c r="A34" s="55" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="C34" s="137" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="D34" s="55"/>
       <c r="E34" s="71"/>
     </row>
     <row r="35" spans="1:5" s="54" customFormat="1" ht="72">
       <c r="A35" s="55" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="C35" s="137" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="D35" s="55"/>
       <c r="E35" s="71"/>
     </row>
     <row r="36" spans="1:5" s="54" customFormat="1" ht="57.6">
       <c r="A36" s="55" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="C36" s="137" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="D36" s="55"/>
       <c r="E36" s="71"/>
     </row>
     <row r="37" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A37" s="55" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="C37" s="137" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="D37" s="55"/>
       <c r="E37" s="71"/>
     </row>
     <row r="38" spans="1:5" s="54" customFormat="1" ht="72">
       <c r="A38" s="55" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="C38" s="137" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="D38" s="55"/>
       <c r="E38" s="71"/>
     </row>
     <row r="39" spans="1:5" s="54" customFormat="1" ht="57.6">
       <c r="A39" s="55" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C39" s="137" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="D39" s="55"/>
       <c r="E39" s="71"/>
     </row>
     <row r="40" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A40" s="62" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C40" s="55"/>
       <c r="D40" s="55" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="E40" s="71"/>
     </row>
     <row r="41" spans="1:5" s="54" customFormat="1" ht="129.6">
       <c r="A41" s="55"/>
       <c r="B41" s="54" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C41" s="153" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D41" s="55" t="s">
         <v>1110</v>
-      </c>
-      <c r="D41" s="55" t="s">
-        <v>1111</v>
       </c>
       <c r="E41" s="71"/>
     </row>
     <row r="42" spans="1:5" s="54" customFormat="1" ht="244.8">
       <c r="A42" s="55"/>
       <c r="B42" s="54" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C42" s="55" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="D42" s="55" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="E42" s="71"/>
     </row>
     <row r="43" spans="1:5" s="54" customFormat="1" ht="244.8">
       <c r="A43" s="55"/>
       <c r="B43" s="54" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C43" s="153" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D43" s="55" t="s">
         <v>1115</v>
-      </c>
-      <c r="D43" s="55" t="s">
-        <v>1116</v>
       </c>
       <c r="E43" s="71"/>
     </row>
     <row r="44" spans="1:5" s="54" customFormat="1" ht="43.2">
       <c r="A44" s="62" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D44" s="54" t="s">
         <v>1133</v>
-      </c>
-      <c r="D44" s="54" t="s">
-        <v>1134</v>
       </c>
       <c r="E44" s="71"/>
     </row>
     <row r="45" spans="1:5" s="54" customFormat="1" ht="144">
       <c r="B45" s="158" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="C45" s="54" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="E45" s="71"/>
     </row>
     <row r="46" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A46" s="62" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="B46" s="55"/>
       <c r="C46" s="55"/>
       <c r="D46" s="55" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="E46" s="71"/>
     </row>
     <row r="47" spans="1:5" s="54" customFormat="1" ht="302.39999999999998">
       <c r="A47" s="55"/>
       <c r="B47" s="153" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="C47" s="55" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E47" s="71"/>
     </row>
     <row r="48" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A48" s="62" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="B48" s="55"/>
       <c r="C48" s="55"/>
       <c r="D48" s="55" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="E48" s="71"/>
     </row>
     <row r="49" spans="1:5" s="54" customFormat="1" ht="43.2">
       <c r="A49" s="55"/>
       <c r="B49" s="153" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="C49" s="55" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="D49" s="55"/>
       <c r="E49" s="71"/>
     </row>
     <row r="50" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A50" s="62" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="C50" s="55"/>
       <c r="D50" s="55" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="E50" s="71"/>
     </row>
     <row r="51" spans="1:5" s="54" customFormat="1" ht="100.8">
       <c r="A51" s="160" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="B51" s="153" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="C51" s="55" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D51" s="55"/>
       <c r="E51" s="71"/>
     </row>
     <row r="52" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A52" s="62" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="B52" s="55"/>
       <c r="C52" s="55"/>
       <c r="D52" s="55" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="E52" s="71"/>
     </row>
     <row r="53" spans="1:5" s="54" customFormat="1" ht="144">
       <c r="A53" s="161" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B53" s="163" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="C53" s="163" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="D53" s="55"/>
       <c r="E53" s="71"/>
     </row>
     <row r="54" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A54" s="62" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B54" s="55"/>
       <c r="C54" s="55"/>
       <c r="D54" s="55" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="E54" s="71"/>
     </row>
     <row r="55" spans="1:5" s="54" customFormat="1" ht="43.2">
       <c r="A55" s="55"/>
       <c r="B55" s="55" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C55" s="55" t="s">
         <v>1154</v>
-      </c>
-      <c r="C55" s="55" t="s">
-        <v>1155</v>
       </c>
       <c r="D55" s="55"/>
       <c r="E55" s="71"/>
     </row>
     <row r="56" spans="1:5" s="54" customFormat="1" ht="43.2">
       <c r="A56" s="62" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B56" s="55"/>
       <c r="C56" s="55"/>
       <c r="D56" s="55" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="E56" s="71"/>
     </row>
     <row r="57" spans="1:5" s="54" customFormat="1" ht="172.8">
       <c r="A57" s="55"/>
       <c r="B57" s="55" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C57" s="55" t="s">
         <v>1157</v>
-      </c>
-      <c r="C57" s="55" t="s">
-        <v>1158</v>
       </c>
       <c r="D57" s="55"/>
       <c r="E57" s="71"/>
@@ -51635,17 +51874,17 @@
       <c r="B58" s="53"/>
       <c r="C58" s="53"/>
       <c r="D58" s="53" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="E58" s="71"/>
     </row>
     <row r="59" spans="1:5" s="54" customFormat="1" ht="43.2">
       <c r="A59" s="55"/>
       <c r="B59" s="163" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="C59" s="55" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="D59" s="55"/>
       <c r="E59" s="71"/>
@@ -51653,17 +51892,17 @@
     <row r="60" spans="1:5" s="54" customFormat="1" ht="100.8">
       <c r="A60" s="55"/>
       <c r="B60" s="165" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="C60" s="55" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="D60" s="55"/>
       <c r="E60" s="71"/>
     </row>
     <row r="61" spans="1:5" s="54" customFormat="1">
       <c r="A61" s="164" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="B61" s="55"/>
       <c r="C61" s="55"/>
@@ -51674,7 +51913,7 @@
       <c r="A62" s="55"/>
       <c r="B62" s="55"/>
       <c r="C62" s="55" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="D62" s="55"/>
       <c r="E62" s="71"/>
@@ -51683,7 +51922,7 @@
       <c r="A63" s="55"/>
       <c r="B63" s="55"/>
       <c r="C63" s="55" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="D63" s="55"/>
       <c r="E63" s="71"/>
@@ -51692,7 +51931,7 @@
       <c r="A64" s="55"/>
       <c r="B64" s="55"/>
       <c r="C64" s="55" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="D64" s="55"/>
       <c r="E64" s="71"/>
@@ -51705,10 +51944,10 @@
     </row>
     <row r="66" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A66" s="62" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B66" s="55" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="C66" s="55"/>
       <c r="D66" s="55"/>
@@ -51718,19 +51957,19 @@
       <c r="A67" s="55"/>
       <c r="B67" s="55"/>
       <c r="C67" s="55" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D67" s="55" t="s">
         <v>1169</v>
-      </c>
-      <c r="D67" s="55" t="s">
-        <v>1170</v>
       </c>
       <c r="E67" s="71"/>
     </row>
     <row r="68" spans="1:5" s="54" customFormat="1">
       <c r="A68" s="62" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="B68" s="55" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="E68" s="71"/>
     </row>
@@ -51739,29 +51978,29 @@
       <c r="B69" s="55"/>
       <c r="C69" s="55"/>
       <c r="D69" s="165" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="E69" s="71"/>
     </row>
     <row r="70" spans="1:5" s="54" customFormat="1" ht="16.2" customHeight="1">
       <c r="A70" s="62" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B70" s="54" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C70" s="164" t="s">
         <v>1175</v>
-      </c>
-      <c r="B70" s="54" t="s">
-        <v>1178</v>
-      </c>
-      <c r="C70" s="164" t="s">
-        <v>1176</v>
       </c>
       <c r="E70" s="71"/>
     </row>
     <row r="71" spans="1:5" s="54" customFormat="1" ht="216">
       <c r="A71" s="55"/>
       <c r="B71" s="55" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="C71" s="54" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="E71" s="71"/>
     </row>
@@ -51813,12 +52052,12 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="23" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="23" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -51828,22 +52067,22 @@
     </row>
     <row r="5" spans="1:5">
       <c r="C5" s="142" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="C6" s="142" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="B7" s="168" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="B8" s="168" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="39" customFormat="1">
@@ -51851,58 +52090,58 @@
     </row>
     <row r="12" spans="1:5" s="133" customFormat="1">
       <c r="C12" s="168" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="23" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="D13" s="170" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="100.8">
       <c r="B14" s="169" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="216.6" customHeight="1">
       <c r="B15" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>1194</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>1196</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>1195</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="23" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="D16" s="170" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="86.4">
       <c r="B17" s="169" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="129.6">
       <c r="B18" s="2" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28.8">
@@ -51910,71 +52149,71 @@
         <v>468</v>
       </c>
       <c r="B19" s="169" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="D19" s="170" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="142" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="115.2">
       <c r="B21" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>1216</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>1217</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="142" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="100.8">
       <c r="B23" s="2" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1">
       <c r="A24" s="168" t="s">
+        <v>1204</v>
+      </c>
+      <c r="D24" s="170" t="s">
         <v>1205</v>
-      </c>
-      <c r="D24" s="170" t="s">
-        <v>1206</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="201.6">
       <c r="A25" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="B25" s="169" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>1207</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>1208</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="168" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D26" s="170" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="43.2">
       <c r="B27" s="169" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>1211</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>1212</v>
       </c>
     </row>
   </sheetData>
@@ -52048,10 +52287,10 @@
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="P4" s="1"/>
       <c r="U4" s="1"/>
@@ -52078,7 +52317,7 @@
         <v>710</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="C7" s="99" t="s">
         <v>711</v>
@@ -52094,13 +52333,13 @@
     </row>
     <row r="9" spans="1:22" ht="28.8">
       <c r="A9" s="1" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1631</v>
+      </c>
+      <c r="C9" s="194" t="s">
         <v>1621</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>1632</v>
-      </c>
-      <c r="C9" s="194" t="s">
-        <v>1622</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -52113,65 +52352,65 @@
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="10" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="C13" s="1"/>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="C14" s="195" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="C15" s="195" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="10" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="C16" s="1"/>
     </row>
     <row r="17" spans="1:3" ht="28.8">
       <c r="A17" s="1" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="C17" s="196" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="C18" s="195" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="57.6">
       <c r="A19" s="10" t="s">
+        <v>1628</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>1629</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>1630</v>
-      </c>
       <c r="C19" s="195" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="10" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="C20" s="195" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -52228,20 +52467,20 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="23" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="B3" s="168" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="B4" s="168" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="39" customFormat="1">
@@ -52249,112 +52488,112 @@
     </row>
     <row r="7" spans="1:5" s="133" customFormat="1">
       <c r="C7" s="168" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="D7" s="171" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="E7" s="70"/>
     </row>
     <row r="8" spans="1:5" ht="28.8">
       <c r="A8" s="23" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B8" s="169" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="43.2">
       <c r="C9" s="169" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="158.4">
       <c r="B10" s="169" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="158.4">
       <c r="B11" s="169" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>1223</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>1224</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="168" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="72">
       <c r="B13" s="2" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="28.8">
       <c r="A14" s="168" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="B14" s="114" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="100.8">
       <c r="C15" s="169" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="86.4">
       <c r="A16" s="2" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>1230</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>1231</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="216">
       <c r="A17" s="2" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="C17" s="169" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="216">
       <c r="B18" s="2" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="C18" s="169" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="168" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="D19" s="170" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="86.4">
       <c r="B20" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>1241</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>1242</v>
       </c>
     </row>
   </sheetData>
@@ -52408,12 +52647,12 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="23" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="B3" s="168" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -52424,10 +52663,10 @@
     </row>
     <row r="7" spans="1:5" s="133" customFormat="1">
       <c r="C7" s="168" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="D7" s="172" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="E7" s="70"/>
     </row>
@@ -52438,108 +52677,108 @@
     </row>
     <row r="9" spans="1:5" ht="129.6">
       <c r="B9" s="169" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>1249</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>1250</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="168" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="57.6">
       <c r="B11" s="2" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28.8">
       <c r="B12" s="2" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>1252</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>1253</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="86.4">
       <c r="B13" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>1254</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>1255</v>
-      </c>
       <c r="D13" s="2" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="168" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="C15" s="2" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="30">
       <c r="A16" s="2" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="C16" s="173" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30">
       <c r="A17" s="2" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="C17" s="174" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="30">
       <c r="A18" s="2" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="C18" s="174" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="316.8">
       <c r="B19" s="2" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="168" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="144">
       <c r="B21" s="169" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="172.8">
       <c r="B22" s="169" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>1273</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>1274</v>
       </c>
     </row>
   </sheetData>
@@ -52595,25 +52834,25 @@
     <row r="3" spans="1:5">
       <c r="A3" s="131"/>
       <c r="B3" s="107" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="131"/>
       <c r="B4" s="107" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="131"/>
       <c r="B5" s="107" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="131"/>
       <c r="B6" s="107" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -52654,7 +52893,7 @@
         <v>502</v>
       </c>
       <c r="B13" s="55" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="C13" s="55" t="s">
         <v>503</v>
@@ -52664,7 +52903,7 @@
     </row>
     <row r="14" spans="1:5" s="54" customFormat="1">
       <c r="A14" s="62" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B14" s="55"/>
       <c r="C14" s="55"/>
@@ -52674,10 +52913,10 @@
     <row r="15" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A15" s="55"/>
       <c r="B15" s="55" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="C15" s="137" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="D15" s="55"/>
       <c r="E15" s="71"/>
@@ -52685,10 +52924,10 @@
     <row r="16" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A16" s="55"/>
       <c r="B16" s="55" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="C16" s="137" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="D16" s="55"/>
       <c r="E16" s="71"/>
@@ -52696,10 +52935,10 @@
     <row r="17" spans="1:5" s="54" customFormat="1" ht="57.6">
       <c r="A17" s="55"/>
       <c r="B17" s="55" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="C17" s="137" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="D17" s="55"/>
       <c r="E17" s="71"/>
@@ -52707,17 +52946,17 @@
     <row r="18" spans="1:5" s="54" customFormat="1" ht="43.2">
       <c r="A18" s="55"/>
       <c r="B18" s="55" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="C18" s="137" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="D18" s="55"/>
       <c r="E18" s="71"/>
     </row>
     <row r="19" spans="1:5" s="54" customFormat="1">
       <c r="A19" s="62" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B19" s="55"/>
       <c r="C19" s="55"/>
@@ -52727,10 +52966,10 @@
     <row r="20" spans="1:5" s="54" customFormat="1" ht="43.2">
       <c r="A20" s="55"/>
       <c r="B20" s="55" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="C20" s="137" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="D20" s="55"/>
       <c r="E20" s="71"/>
@@ -52738,10 +52977,10 @@
     <row r="21" spans="1:5" s="54" customFormat="1" ht="57.6">
       <c r="A21" s="55"/>
       <c r="B21" s="55" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="C21" s="137" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="D21" s="55"/>
       <c r="E21" s="71"/>
@@ -52749,10 +52988,10 @@
     <row r="22" spans="1:5" s="54" customFormat="1" ht="43.2">
       <c r="A22" s="55"/>
       <c r="B22" s="55" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="C22" s="137" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="D22" s="55"/>
       <c r="E22" s="71"/>
@@ -52762,7 +53001,7 @@
         <v>504</v>
       </c>
       <c r="B23" s="96" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="E23" s="71"/>
     </row>
@@ -53333,13 +53572,13 @@
     <tabColor theme="9"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:V28"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="36" style="73" customWidth="1"/>
     <col min="2" max="2" width="50.5546875" style="74" customWidth="1"/>
     <col min="3" max="3" width="53.77734375" style="74" customWidth="1"/>
-    <col min="4" max="4" width="29.33203125" style="73" customWidth="1"/>
+    <col min="4" max="4" width="53.6640625" style="73" customWidth="1"/>
     <col min="5" max="5" width="6.21875" style="72" customWidth="1"/>
     <col min="6" max="6" width="43.21875" style="73" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="55.109375" style="74" customWidth="1"/>
@@ -53372,168 +53611,248 @@
       <c r="D1" s="90"/>
     </row>
     <row r="2" spans="1:22">
-      <c r="A2" s="90"/>
+      <c r="A2" s="201" t="s">
+        <v>1652</v>
+      </c>
       <c r="B2" s="90"/>
       <c r="C2" s="90"/>
       <c r="D2" s="90"/>
     </row>
     <row r="3" spans="1:22">
-      <c r="A3" s="76"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="K3" s="76"/>
-      <c r="L3" s="76"/>
-      <c r="M3" s="76"/>
-      <c r="N3" s="76"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="U3" s="77"/>
-    </row>
-    <row r="4" spans="1:22" ht="57.6">
-      <c r="C4" s="128" t="s">
-        <v>857</v>
-      </c>
-      <c r="P4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="74"/>
+      <c r="A3" s="201" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B3" s="90"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
+    </row>
+    <row r="4" spans="1:22">
+      <c r="A4" s="90"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="104" t="s">
-        <v>774</v>
-      </c>
-      <c r="P5" s="73"/>
-      <c r="U5" s="73"/>
-      <c r="V5" s="74"/>
-    </row>
-    <row r="6" spans="1:22" ht="43.2">
-      <c r="C6" s="105" t="s">
-        <v>773</v>
-      </c>
-      <c r="P6" s="73"/>
-      <c r="U6" s="73"/>
-      <c r="V6" s="74"/>
-    </row>
-    <row r="7" spans="1:22" ht="43.2">
-      <c r="B7" s="105" t="s">
-        <v>777</v>
-      </c>
-      <c r="C7" s="105" t="s">
-        <v>776</v>
-      </c>
-      <c r="P7" s="73"/>
-      <c r="U7" s="73"/>
-      <c r="V7" s="74"/>
-    </row>
-    <row r="8" spans="1:22" ht="28.8">
-      <c r="B8" s="105" t="s">
-        <v>778</v>
-      </c>
-      <c r="C8" s="105" t="s">
-        <v>775</v>
-      </c>
-      <c r="P8" s="73"/>
-      <c r="U8" s="73"/>
-      <c r="V8" s="74"/>
+        <v>770</v>
+      </c>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+    </row>
+    <row r="6" spans="1:22">
+      <c r="A6" s="104" t="s">
+        <v>772</v>
+      </c>
+      <c r="B6" s="90"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="90"/>
+    </row>
+    <row r="7" spans="1:22">
+      <c r="A7" s="90"/>
+      <c r="B7" s="90"/>
+      <c r="C7" s="90"/>
+      <c r="D7" s="90"/>
+    </row>
+    <row r="8" spans="1:22">
+      <c r="A8" s="90"/>
+      <c r="B8" s="90"/>
+      <c r="C8" s="90"/>
+      <c r="D8" s="90"/>
     </row>
     <row r="9" spans="1:22">
-      <c r="A9" s="106" t="s">
-        <v>779</v>
-      </c>
-      <c r="B9" s="115" t="s">
-        <v>780</v>
-      </c>
-      <c r="C9" s="115" t="s">
-        <v>781</v>
-      </c>
-      <c r="P9" s="73"/>
-      <c r="U9" s="73"/>
-      <c r="V9" s="74"/>
-    </row>
-    <row r="10" spans="1:22" ht="86.4">
-      <c r="B10" s="116" t="s">
-        <v>931</v>
-      </c>
-      <c r="C10" s="116" t="s">
-        <v>930</v>
-      </c>
-      <c r="P10" s="73"/>
-      <c r="U10" s="73"/>
-      <c r="V10" s="74"/>
-    </row>
-    <row r="11" spans="1:22">
-      <c r="A11" s="104" t="s">
-        <v>767</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="73"/>
-      <c r="D11" s="2"/>
+      <c r="A9" s="90"/>
+      <c r="B9" s="90"/>
+      <c r="C9" s="90"/>
+      <c r="D9" s="90"/>
+    </row>
+    <row r="10" spans="1:22">
+      <c r="A10" s="76"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="76"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="76"/>
+      <c r="K10" s="76"/>
+      <c r="L10" s="76"/>
+      <c r="M10" s="76"/>
+      <c r="N10" s="76"/>
+      <c r="P10" s="77"/>
+      <c r="Q10" s="77"/>
+      <c r="R10" s="77"/>
+      <c r="S10" s="77"/>
+      <c r="U10" s="77"/>
+    </row>
+    <row r="11" spans="1:22" ht="57.6">
+      <c r="C11" s="128" t="s">
+        <v>856</v>
+      </c>
       <c r="P11" s="73"/>
       <c r="U11" s="73"/>
       <c r="V11" s="74"/>
     </row>
-    <row r="12" spans="1:22" ht="57.6">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="C12" s="111" t="s">
-        <v>585</v>
-      </c>
-      <c r="D12" s="2"/>
+    <row r="12" spans="1:22">
+      <c r="A12" s="201" t="s">
+        <v>774</v>
+      </c>
       <c r="P12" s="73"/>
       <c r="U12" s="73"/>
       <c r="V12" s="74"/>
     </row>
-    <row r="13" spans="1:22" ht="72">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="C13" s="100" t="s">
-        <v>584</v>
-      </c>
-      <c r="D13" s="2"/>
+    <row r="13" spans="1:22" ht="43.2">
+      <c r="C13" s="105" t="s">
+        <v>773</v>
+      </c>
       <c r="P13" s="73"/>
       <c r="U13" s="73"/>
       <c r="V13" s="74"/>
     </row>
-    <row r="14" spans="1:22">
-      <c r="A14" s="129" t="s">
+    <row r="14" spans="1:22" ht="43.2">
+      <c r="B14" s="105" t="s">
+        <v>777</v>
+      </c>
+      <c r="C14" s="105" t="s">
+        <v>776</v>
+      </c>
+      <c r="P14" s="73"/>
+      <c r="U14" s="73"/>
+      <c r="V14" s="74"/>
+    </row>
+    <row r="15" spans="1:22" ht="28.8">
+      <c r="B15" s="105" t="s">
+        <v>778</v>
+      </c>
+      <c r="C15" s="105" t="s">
+        <v>775</v>
+      </c>
+      <c r="P15" s="73"/>
+      <c r="U15" s="73"/>
+      <c r="V15" s="74"/>
+    </row>
+    <row r="16" spans="1:22">
+      <c r="A16" s="106" t="s">
+        <v>779</v>
+      </c>
+      <c r="B16" s="115" t="s">
+        <v>780</v>
+      </c>
+      <c r="C16" s="115" t="s">
+        <v>781</v>
+      </c>
+      <c r="P16" s="73"/>
+      <c r="U16" s="73"/>
+      <c r="V16" s="74"/>
+    </row>
+    <row r="17" spans="1:22" ht="86.4">
+      <c r="B17" s="116" t="s">
+        <v>930</v>
+      </c>
+      <c r="C17" s="116" t="s">
+        <v>929</v>
+      </c>
+      <c r="P17" s="73"/>
+      <c r="U17" s="73"/>
+      <c r="V17" s="74"/>
+    </row>
+    <row r="18" spans="1:22">
+      <c r="A18" s="106" t="s">
+        <v>767</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="73"/>
+      <c r="D18" s="2"/>
+      <c r="P18" s="73"/>
+      <c r="U18" s="73"/>
+      <c r="V18" s="74"/>
+    </row>
+    <row r="19" spans="1:22" ht="57.6">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="C19" s="111" t="s">
+        <v>585</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="P19" s="73"/>
+      <c r="U19" s="73"/>
+      <c r="V19" s="74"/>
+    </row>
+    <row r="20" spans="1:22" ht="72">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="C20" s="100" t="s">
+        <v>584</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="P20" s="73"/>
+      <c r="U20" s="73"/>
+      <c r="V20" s="74"/>
+    </row>
+    <row r="21" spans="1:22">
+      <c r="A21" s="23" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B21" s="185" t="s">
+        <v>1655</v>
+      </c>
+      <c r="C21" s="115" t="s">
+        <v>781</v>
+      </c>
+      <c r="D21" s="2"/>
+      <c r="P21" s="73"/>
+      <c r="U21" s="73"/>
+      <c r="V21" s="74"/>
+    </row>
+    <row r="22" spans="1:22" ht="409.6">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C22" s="202" t="s">
+        <v>1657</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>1658</v>
+      </c>
+      <c r="P22" s="73"/>
+      <c r="U22" s="73"/>
+      <c r="V22" s="74"/>
+    </row>
+    <row r="23" spans="1:22">
+      <c r="A23" s="129" t="s">
         <v>768</v>
       </c>
     </row>
-    <row r="15" spans="1:22" ht="28.8">
-      <c r="C15" s="105" t="s">
+    <row r="24" spans="1:22" ht="28.8">
+      <c r="C24" s="105" t="s">
         <v>769</v>
       </c>
     </row>
-    <row r="16" spans="1:22">
-      <c r="A16" s="104" t="s">
+    <row r="25" spans="1:22">
+      <c r="A25" s="104" t="s">
         <v>770</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="72">
-      <c r="C17" s="105" t="s">
+    <row r="26" spans="1:22" ht="72">
+      <c r="C26" s="105" t="s">
         <v>771</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="104" t="s">
+    <row r="27" spans="1:22">
+      <c r="A27" s="104" t="s">
         <v>772</v>
       </c>
-      <c r="B18" s="107" t="s">
+      <c r="B27" s="107" t="s">
         <v>780</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="86.4">
-      <c r="B19" s="105" t="s">
+    <row r="28" spans="1:22" ht="86.4">
+      <c r="B28" s="105" t="s">
         <v>782</v>
       </c>
     </row>
@@ -53621,7 +53940,7 @@
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="117" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B6" s="90"/>
       <c r="C6" s="90"/>
@@ -53629,7 +53948,7 @@
     </row>
     <row r="7" spans="1:22" ht="28.8">
       <c r="A7" s="117" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B7" s="90"/>
       <c r="C7" s="90"/>
@@ -53639,7 +53958,7 @@
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="117" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B8" s="90"/>
       <c r="C8" s="90"/>
@@ -53647,7 +53966,7 @@
     </row>
     <row r="9" spans="1:22" ht="28.8">
       <c r="A9" s="117" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B9" s="90"/>
       <c r="C9" s="90"/>
@@ -53703,7 +54022,7 @@
         <v>785</v>
       </c>
       <c r="B15" s="120" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="P15" s="73"/>
       <c r="U15" s="73"/>
@@ -53711,7 +54030,7 @@
     </row>
     <row r="16" spans="1:22" ht="104.4" customHeight="1">
       <c r="A16" s="116" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="P16" s="73"/>
       <c r="U16" s="73"/>
@@ -53758,7 +54077,7 @@
         <v>787</v>
       </c>
       <c r="B20" s="120" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="P20" s="73"/>
       <c r="U20" s="73"/>
@@ -53770,7 +54089,7 @@
         <v>827</v>
       </c>
       <c r="C21" s="116" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="D21" s="2"/>
       <c r="P21" s="73"/>
@@ -53782,7 +54101,7 @@
         <v>788</v>
       </c>
       <c r="B22" s="118" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -53793,13 +54112,13 @@
     <row r="23" spans="1:22">
       <c r="A23" s="179"/>
       <c r="B23" s="180" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="C23" s="181" t="s">
+        <v>1401</v>
+      </c>
+      <c r="D23" s="182" t="s">
         <v>1402</v>
-      </c>
-      <c r="D23" s="182" t="s">
-        <v>1403</v>
       </c>
       <c r="P23" s="73"/>
       <c r="U23" s="73"/>
@@ -53807,7 +54126,7 @@
     </row>
     <row r="24" spans="1:22" ht="201.6">
       <c r="A24" s="116" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B24" s="116" t="s">
         <v>790</v>
@@ -53816,7 +54135,7 @@
         <v>820</v>
       </c>
       <c r="D24" s="116" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="P24" s="73"/>
       <c r="U24" s="73"/>
@@ -53828,7 +54147,7 @@
         <v>827</v>
       </c>
       <c r="C25" s="116" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="28.8">
@@ -53836,7 +54155,7 @@
         <v>789</v>
       </c>
       <c r="B26" s="120" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C26" s="118" t="s">
         <v>825</v>
@@ -53858,15 +54177,15 @@
         <v>527</v>
       </c>
       <c r="C28" s="55" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="29" spans="1:22">
       <c r="A29" s="117" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B29" s="120" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C29" s="118" t="s">
         <v>822</v>
@@ -53889,21 +54208,21 @@
     </row>
     <row r="31" spans="1:22" ht="28.8">
       <c r="A31" s="117" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B31" s="120" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C31" s="126" t="s">
         <v>829</v>
       </c>
       <c r="D31" s="125" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="32" spans="1:22" ht="86.4">
       <c r="A32" s="116" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B32" s="116" t="s">
         <v>831</v>
@@ -53929,36 +54248,36 @@
       <c r="B34" s="116" t="s">
         <v>827</v>
       </c>
-      <c r="C34" s="116" t="s">
-        <v>834</v>
+      <c r="C34" s="203" t="s">
+        <v>1659</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="117" t="s">
+        <v>840</v>
+      </c>
+      <c r="B35" s="120" t="s">
         <v>841</v>
       </c>
-      <c r="B35" s="120" t="s">
-        <v>842</v>
-      </c>
       <c r="C35" s="119" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="D35" s="125" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="187.2">
       <c r="A36" s="116" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B36" s="123" t="s">
         <v>828</v>
       </c>
       <c r="C36" s="116" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="D36" s="116" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="57.6">
@@ -53967,12 +54286,12 @@
         <v>827</v>
       </c>
       <c r="C37" s="116" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="116" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C38" s="126" t="s">
         <v>828</v>
@@ -53984,21 +54303,21 @@
     <row r="39" spans="1:4" ht="115.2">
       <c r="A39" s="74"/>
       <c r="B39" s="116" t="s">
+        <v>854</v>
+      </c>
+      <c r="C39" s="116" t="s">
+        <v>853</v>
+      </c>
+      <c r="D39" s="116" t="s">
         <v>855</v>
-      </c>
-      <c r="C39" s="116" t="s">
-        <v>854</v>
-      </c>
-      <c r="D39" s="116" t="s">
-        <v>856</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="28.8">
       <c r="A40" s="117" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B40" s="126" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="C40" s="126" t="s">
         <v>828</v>
@@ -54009,13 +54328,13 @@
     </row>
     <row r="41" spans="1:4" ht="273.60000000000002">
       <c r="B41" s="116" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="C41" s="116" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="D41" s="116" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
   </sheetData>
@@ -54088,7 +54407,7 @@
         <v>367</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -54431,7 +54750,7 @@
         <v>316</v>
       </c>
       <c r="B33" s="162" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="C33" s="41" t="s">
         <v>370</v>

--- a/4 четверть_9_JavaScript_Vue 3 Composition API.xlsx
+++ b/4 четверть_9_JavaScript_Vue 3 Composition API.xlsx
@@ -8,44 +8,46 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A960ECE9-4AC1-45F5-9D3A-267E3F402AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A464A92F-3928-468A-8EB8-6605D20FB21A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="1104" windowWidth="23016" windowHeight="11136" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1995" yWindow="-18900" windowWidth="23010" windowHeight="16845" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Литература" sheetId="14" r:id="rId1"/>
     <sheet name="import require" sheetId="17" r:id="rId2"/>
-    <sheet name="VSCode" sheetId="43" r:id="rId3"/>
-    <sheet name="Templates" sheetId="42" r:id="rId4"/>
-    <sheet name="$attrs" sheetId="46" r:id="rId5"/>
-    <sheet name="slots" sheetId="47" r:id="rId6"/>
-    <sheet name="App" sheetId="25" r:id="rId7"/>
-    <sheet name="ref selector" sheetId="41" r:id="rId8"/>
-    <sheet name="ref" sheetId="31" r:id="rId9"/>
-    <sheet name="reactive" sheetId="38" r:id="rId10"/>
-    <sheet name="props" sheetId="44" r:id="rId11"/>
-    <sheet name="emit" sheetId="45" r:id="rId12"/>
-    <sheet name="value, v-model, @" sheetId="22" r:id="rId13"/>
-    <sheet name="{{ }}" sheetId="21" r:id="rId14"/>
-    <sheet name="Директивы" sheetId="16" r:id="rId15"/>
-    <sheet name="Composable" sheetId="49" r:id="rId16"/>
-    <sheet name="lifecycle" sheetId="29" r:id="rId17"/>
-    <sheet name="computed, readonly" sheetId="37" r:id="rId18"/>
-    <sheet name="watch" sheetId="36" r:id="rId19"/>
-    <sheet name="provide, inject" sheetId="33" r:id="rId20"/>
-    <sheet name="Vue Css" sheetId="39" r:id="rId21"/>
-    <sheet name="asyncComp" sheetId="48" r:id="rId22"/>
-    <sheet name="plugins" sheetId="50" r:id="rId23"/>
-    <sheet name="State" sheetId="55" r:id="rId24"/>
-    <sheet name="Pinia" sheetId="57" r:id="rId25"/>
-    <sheet name="Routing" sheetId="54" r:id="rId26"/>
-    <sheet name="$route" sheetId="56" r:id="rId27"/>
-    <sheet name="Transition, Animation" sheetId="35" r:id="rId28"/>
-    <sheet name="&lt;isComponent&gt;" sheetId="51" r:id="rId29"/>
-    <sheet name="Teleport" sheetId="52" r:id="rId30"/>
-    <sheet name="Suspense" sheetId="53" r:id="rId31"/>
-    <sheet name="Reactivity Advanced" sheetId="32" r:id="rId32"/>
-    <sheet name="batch" sheetId="40" r:id="rId33"/>
+    <sheet name="Анимации" sheetId="58" r:id="rId3"/>
+    <sheet name="VueUse" sheetId="59" r:id="rId4"/>
+    <sheet name="VSCode" sheetId="43" r:id="rId5"/>
+    <sheet name="Templates" sheetId="42" r:id="rId6"/>
+    <sheet name="$attrs" sheetId="46" r:id="rId7"/>
+    <sheet name="slots" sheetId="47" r:id="rId8"/>
+    <sheet name="App" sheetId="25" r:id="rId9"/>
+    <sheet name="ref selector" sheetId="41" r:id="rId10"/>
+    <sheet name="ref" sheetId="31" r:id="rId11"/>
+    <sheet name="reactive" sheetId="38" r:id="rId12"/>
+    <sheet name="props" sheetId="44" r:id="rId13"/>
+    <sheet name="emit" sheetId="45" r:id="rId14"/>
+    <sheet name="value, v-model, @" sheetId="22" r:id="rId15"/>
+    <sheet name="{{ }}" sheetId="21" r:id="rId16"/>
+    <sheet name="Директивы" sheetId="16" r:id="rId17"/>
+    <sheet name="Composable" sheetId="49" r:id="rId18"/>
+    <sheet name="lifecycle" sheetId="29" r:id="rId19"/>
+    <sheet name="computed, readonly" sheetId="37" r:id="rId20"/>
+    <sheet name="watch" sheetId="36" r:id="rId21"/>
+    <sheet name="provide, inject" sheetId="33" r:id="rId22"/>
+    <sheet name="Vue Css" sheetId="39" r:id="rId23"/>
+    <sheet name="asyncComp" sheetId="48" r:id="rId24"/>
+    <sheet name="plugins" sheetId="50" r:id="rId25"/>
+    <sheet name="State" sheetId="55" r:id="rId26"/>
+    <sheet name="Pinia" sheetId="57" r:id="rId27"/>
+    <sheet name="Routing" sheetId="54" r:id="rId28"/>
+    <sheet name="$route" sheetId="56" r:id="rId29"/>
+    <sheet name="Transition, Animation" sheetId="35" r:id="rId30"/>
+    <sheet name="&lt;isComponent&gt;" sheetId="51" r:id="rId31"/>
+    <sheet name="Teleport" sheetId="52" r:id="rId32"/>
+    <sheet name="Suspense" sheetId="53" r:id="rId33"/>
+    <sheet name="Reactivity Advanced" sheetId="32" r:id="rId34"/>
+    <sheet name="batch" sheetId="40" r:id="rId35"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -60,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2046" uniqueCount="1660">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2119" uniqueCount="1729">
   <si>
     <t>Vue</t>
   </si>
@@ -40333,17 +40335,328 @@
 /&gt;</t>
     </r>
   </si>
+  <si>
+    <t>анимации</t>
+  </si>
+  <si>
+    <t>`https://motion.vueuse.org/features/presets</t>
+  </si>
+  <si>
+    <t>огромная библиотека полезных функций</t>
+  </si>
+  <si>
+    <t>`https://vueuse.org/shared/createGlobalState/</t>
+  </si>
+  <si>
+    <t>Название</t>
+  </si>
+  <si>
+    <t>Пояснение</t>
+  </si>
+  <si>
+    <t>createGlobalState</t>
+  </si>
+  <si>
+    <t>Создаёт глобальное состояние, общее для всех экземпляров Vue в приложении. Фабрика состояния вызывается один раз, результат шарится между компонентами. Подходит для лёгкого shared store без Vuex/Pinia. Документация</t>
+  </si>
+  <si>
+    <t>createInjectionState</t>
+  </si>
+  <si>
+    <t>Оборачивает состояние в provide/inject с типобезопасным доступом. Состояние живёт в scope родителя, но доступно дочерним компонентам через composable. Удобно для модулей UI (фильтры, wizard) без глобального store.</t>
+  </si>
+  <si>
+    <t>createSharedComposable</t>
+  </si>
+  <si>
+    <t>Делает composable «singleton»: при множественных вызовах возвращает одно и то же состояние. Полезно для тяжёлых composables (WebSocket, геолокация). Отличается от createGlobalState уровнем изоляции.</t>
+  </si>
+  <si>
+    <t>injectLocal</t>
+  </si>
+  <si>
+    <t>provideLocal</t>
+  </si>
+  <si>
+    <t>Парный provide для injectLocal: данные доступны только потомкам. Не попадают в глобальный scope. Подходит для локальных контекстов (таблица, форма).</t>
+  </si>
+  <si>
+    <t>useAsyncState</t>
+  </si>
+  <si>
+    <t>useDebouncedRefHistory</t>
+  </si>
+  <si>
+    <t>История изменений ref с debounce перед записью в историю. Подходит для undo/redo в редакторе без спама записей при быстром вводе. Комбинирует ref history и debounce.</t>
+  </si>
+  <si>
+    <t>useLastChanged</t>
+  </si>
+  <si>
+    <t>Отслеживает время последнего изменения ref или reactive. Возвращает timestamp, полезно для «обновлено N секунд назад». Легковесная альтернатива ручным watch + Date.</t>
+  </si>
+  <si>
+    <t>useLocalStorage</t>
+  </si>
+  <si>
+    <t>useManualRefHistory</t>
+  </si>
+  <si>
+    <t>useRefHistory</t>
+  </si>
+  <si>
+    <t>Автоматическая история изменений ref: undo, redo, очистка. Каждое изменение — новый шаг. Упрощает прототипирование редакторов настроек.</t>
+  </si>
+  <si>
+    <t>useSessionStorage</t>
+  </si>
+  <si>
+    <t>useStorage</t>
+  </si>
+  <si>
+    <t>Универсальная реактивная обёртка: localStorage, sessionStorage или custom storage. Единый API для разных backend’ов. База для useLocalStorage/useSessionStorage.</t>
+  </si>
+  <si>
+    <t>useStorageAsync</t>
+  </si>
+  <si>
+    <t>Асинхронный storage (IndexedDB и др.) с реактивным ref. Для больших или нестроковых данных. Загрузка не блокирует первый рендер.</t>
+  </si>
+  <si>
+    <t>useThrottledRefHistory</t>
+  </si>
+  <si>
+    <t>История ref с throttle вместо debounce. Шаги не чаще заданного интервала. Для drag/slider, где debounce откладывает записи слишком долго.</t>
+  </si>
+  <si>
+    <t>Аналог inject, но только внутри текущего компонентного дерева. Не поднимается выше родителя, который сделал provide. Снижает случайные зависимости между далёкими частями приложения.</t>
+  </si>
+  <si>
+    <t>Оборачивает async-функцию в реактивный объект с state, isReady, isLoading, error. Упрощает загрузку данных в setup без ручных ref и try/catch. Можно перезапускать запрос через execute().</t>
+  </si>
+  <si>
+    <t>Реактивная связка ref с localStorage: чтение при init, записи при изменении. Сериализация JSON настраивается. Замена ручного getItem/setItem в store.</t>
+  </si>
+  <si>
+    <t>Undo/redo для ref с ручным commit() вместо авто на каждое изменение. Контролируете, когда шаг попадает в историю. Для форм «Сохранить» vs промежуточный ввод.</t>
+  </si>
+  <si>
+    <t>Как useLocalStorage, но для sessionStorage (до закрытия вкладки). Данные не переживают сессию браузера. Для временных UI-состояний.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Примечание!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+Работает</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> для нескольких </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ref</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Примечание!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+Работает </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>для одного</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ref</t>
+    </r>
+  </si>
+  <si>
+    <t>v-motion-fade</t>
+  </si>
+  <si>
+    <t>v-motion-fade-visible</t>
+  </si>
+  <si>
+    <t>v-motion-fade-visible-once</t>
+  </si>
+  <si>
+    <t>v-motion-roll-bottom</t>
+  </si>
+  <si>
+    <t>v-motion-roll-left</t>
+  </si>
+  <si>
+    <t>v-motion-roll-right</t>
+  </si>
+  <si>
+    <t>v-motion-roll-top</t>
+  </si>
+  <si>
+    <t>v-motion-roll-visible-bottom</t>
+  </si>
+  <si>
+    <t>v-motion-roll-visible-left</t>
+  </si>
+  <si>
+    <t>v-motion-roll-visible-right</t>
+  </si>
+  <si>
+    <t>v-motion-roll-visible-top</t>
+  </si>
+  <si>
+    <t>v-motion-roll-visible-once-bottom</t>
+  </si>
+  <si>
+    <t>v-motion-roll-visible-once-left</t>
+  </si>
+  <si>
+    <t>v-motion-roll-visible-once-right</t>
+  </si>
+  <si>
+    <t>v-motion-roll-visible-once-top</t>
+  </si>
+  <si>
+    <t>v-motion-pop</t>
+  </si>
+  <si>
+    <t>v-motion-pop-visible</t>
+  </si>
+  <si>
+    <t>v-motion-pop-visible-once</t>
+  </si>
+  <si>
+    <t>v-motion-slide-bottom</t>
+  </si>
+  <si>
+    <t>v-motion-slide-left</t>
+  </si>
+  <si>
+    <t>v-motion-slide-right</t>
+  </si>
+  <si>
+    <t>v-motion-slide-top</t>
+  </si>
+  <si>
+    <t>v-motion-slide-visible-bottom</t>
+  </si>
+  <si>
+    <t>v-motion-slide-visible-left</t>
+  </si>
+  <si>
+    <t>v-motion-slide-visible-right</t>
+  </si>
+  <si>
+    <t>v-motion-slide-visible-top</t>
+  </si>
+  <si>
+    <t>v-motion-slide-visible-once-bottom</t>
+  </si>
+  <si>
+    <t>v-motion-slide-visible-once-left</t>
+  </si>
+  <si>
+    <t>v-motion-slide-visible-once-right</t>
+  </si>
+  <si>
+    <t>v-motion-slide-visible-once-top</t>
+  </si>
+  <si>
+    <t>читай</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="83">
+  <fonts count="85">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -41134,13 +41447,13 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="204">
+  <cellXfs count="206">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -41151,20 +41464,20 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="37" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -41173,13 +41486,7 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -41188,107 +41495,113 @@
     <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="29" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="31" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="25" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="49" fontId="44" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="25" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="59" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="42" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="57" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="64" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="66" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="67" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -41303,46 +41616,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="4" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="4" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -41351,77 +41664,77 @@
     <xf numFmtId="49" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="6" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="6" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="5" applyFill="1"/>
-    <xf numFmtId="49" fontId="19" fillId="7" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" xfId="5" applyFill="1"/>
+    <xf numFmtId="49" fontId="21" fillId="7" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="7" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="7" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="8" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="8" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="48" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -41430,97 +41743,97 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="16" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="16" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="16" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="16" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="47" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="49" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="47" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="49" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="47" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="49" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="8" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="8" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -41538,22 +41851,22 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -41565,71 +41878,71 @@
     <xf numFmtId="49" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="43" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="48" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="60" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="73" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="75" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -41638,59 +41951,77 @@
     <xf numFmtId="49" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="50" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="50" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="3" applyFill="1"/>
-    <xf numFmtId="49" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="45" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="3" applyFill="1"/>
+    <xf numFmtId="49" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="47" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="47" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="47" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="49" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="49" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="49" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -41699,47 +42030,35 @@
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -42502,13 +42821,502 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C4:D24">
     <sortCondition ref="D4:D24"/>
   </sortState>
-  <phoneticPr fontId="38" type="noConversion"/>
+  <phoneticPr fontId="40" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98729587-661C-4647-8A0E-68347CF7376F}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:E16"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="39.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="59.21875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="55.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="53" style="2" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" style="70" customWidth="1"/>
+    <col min="6" max="6" width="67.88671875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="64.33203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7.77734375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="39.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="48.88671875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="72.6640625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="43.88671875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="7.77734375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="56.77734375" style="2" customWidth="1"/>
+    <col min="15" max="15" width="46.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="62.88671875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="49.21875" style="2" customWidth="1"/>
+    <col min="18" max="18" width="8.77734375" style="2" customWidth="1"/>
+    <col min="19" max="19" width="67.77734375" style="2" customWidth="1"/>
+    <col min="20" max="20" width="68.33203125" style="2" customWidth="1"/>
+    <col min="21" max="22" width="59.33203125" style="2" customWidth="1"/>
+    <col min="23" max="23" width="59.6640625" style="2" customWidth="1"/>
+    <col min="24" max="24" width="99.44140625" style="2" customWidth="1"/>
+    <col min="25" max="25" width="41.21875" style="2" customWidth="1"/>
+    <col min="26" max="26" width="8.77734375" style="2" customWidth="1"/>
+    <col min="27" max="16384" width="8.77734375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5">
+      <c r="A2" s="79"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="53"/>
+      <c r="C3" s="87"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="53"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="53"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="53"/>
+    </row>
+    <row r="8" spans="1:5" s="39" customFormat="1">
+      <c r="E8" s="70"/>
+    </row>
+    <row r="10" spans="1:5" s="54" customFormat="1">
+      <c r="A10" s="53" t="s">
+        <v>482</v>
+      </c>
+      <c r="E10" s="70"/>
+    </row>
+    <row r="11" spans="1:5" s="54" customFormat="1" ht="57.6">
+      <c r="C11" s="101" t="s">
+        <v>722</v>
+      </c>
+      <c r="E11" s="70"/>
+    </row>
+    <row r="12" spans="1:5" s="54" customFormat="1" ht="244.8">
+      <c r="A12" s="102" t="s">
+        <v>723</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="E12" s="70"/>
+    </row>
+    <row r="13" spans="1:5" s="54" customFormat="1">
+      <c r="B13" s="96" t="s">
+        <v>685</v>
+      </c>
+      <c r="C13" s="95" t="s">
+        <v>686</v>
+      </c>
+      <c r="E13" s="70"/>
+    </row>
+    <row r="14" spans="1:5" ht="187.2">
+      <c r="A14" s="22" t="s">
+        <v>719</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="273.60000000000002">
+      <c r="A15" s="100" t="s">
+        <v>718</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="409.6">
+      <c r="A16" s="22" t="s">
+        <v>694</v>
+      </c>
+      <c r="B16" s="100" t="s">
+        <v>721</v>
+      </c>
+      <c r="C16" s="100" t="s">
+        <v>720</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35186FB0-D6EE-48D6-AD0A-EC687D3766B2}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:V31"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="39.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="62" style="2" customWidth="1"/>
+    <col min="3" max="3" width="55.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="33.109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" style="70" customWidth="1"/>
+    <col min="6" max="6" width="67.88671875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="64.33203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7.77734375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="39.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="48.88671875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="72.6640625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="43.88671875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="7.77734375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="56.77734375" style="2" customWidth="1"/>
+    <col min="15" max="15" width="46.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="62.88671875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="49.21875" style="2" customWidth="1"/>
+    <col min="18" max="18" width="8.77734375" style="2" customWidth="1"/>
+    <col min="19" max="19" width="67.77734375" style="2" customWidth="1"/>
+    <col min="20" max="20" width="68.33203125" style="2" customWidth="1"/>
+    <col min="21" max="22" width="59.33203125" style="2" customWidth="1"/>
+    <col min="23" max="23" width="59.6640625" style="2" customWidth="1"/>
+    <col min="24" max="24" width="99.44140625" style="2" customWidth="1"/>
+    <col min="25" max="25" width="41.21875" style="2" customWidth="1"/>
+    <col min="26" max="26" width="8.77734375" style="2" customWidth="1"/>
+    <col min="27" max="16384" width="8.77734375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:22">
+      <c r="A2" s="79" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22">
+      <c r="A3" s="53" t="s">
+        <v>482</v>
+      </c>
+      <c r="C3" s="87" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22">
+      <c r="A4" s="53" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
+      <c r="A5" s="53" t="s">
+        <v>724</v>
+      </c>
+      <c r="C5" s="92" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
+      <c r="A6" s="53" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" s="39" customFormat="1">
+      <c r="E8" s="70"/>
+    </row>
+    <row r="9" spans="1:22">
+      <c r="A9" s="40" t="s">
+        <v>266</v>
+      </c>
+      <c r="B9" s="40" t="s">
+        <v>270</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>268</v>
+      </c>
+      <c r="D9" s="40"/>
+    </row>
+    <row r="10" spans="1:22" s="73" customFormat="1">
+      <c r="A10" s="79" t="s">
+        <v>580</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="72"/>
+      <c r="G10" s="74"/>
+      <c r="J10" s="72"/>
+      <c r="O10" s="72"/>
+      <c r="Q10" s="74"/>
+      <c r="R10" s="74"/>
+      <c r="T10" s="75"/>
+      <c r="V10" s="74"/>
+    </row>
+    <row r="11" spans="1:22" s="73" customFormat="1">
+      <c r="A11" s="1"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="D11" s="1"/>
+      <c r="E11" s="72"/>
+      <c r="G11" s="74"/>
+      <c r="J11" s="72"/>
+      <c r="O11" s="72"/>
+      <c r="Q11" s="74"/>
+      <c r="R11" s="74"/>
+      <c r="T11" s="75"/>
+      <c r="V11" s="74"/>
+    </row>
+    <row r="12" spans="1:22" s="73" customFormat="1">
+      <c r="A12" s="1"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="72"/>
+      <c r="G12" s="74"/>
+      <c r="J12" s="72"/>
+      <c r="O12" s="72"/>
+      <c r="Q12" s="74"/>
+      <c r="R12" s="74"/>
+      <c r="T12" s="75"/>
+      <c r="V12" s="74"/>
+    </row>
+    <row r="13" spans="1:22" s="73" customFormat="1">
+      <c r="A13" s="87" t="s">
+        <v>663</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="72"/>
+      <c r="G13" s="74"/>
+      <c r="J13" s="72"/>
+      <c r="O13" s="72"/>
+      <c r="Q13" s="74"/>
+      <c r="R13" s="74"/>
+      <c r="T13" s="75"/>
+      <c r="V13" s="74"/>
+    </row>
+    <row r="14" spans="1:22" s="73" customFormat="1" ht="72">
+      <c r="A14" s="87" t="s">
+        <v>663</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="72"/>
+      <c r="G14" s="74"/>
+      <c r="J14" s="72"/>
+      <c r="O14" s="72"/>
+      <c r="Q14" s="74"/>
+      <c r="R14" s="74"/>
+      <c r="T14" s="75"/>
+      <c r="V14" s="74"/>
+    </row>
+    <row r="15" spans="1:22" s="54" customFormat="1">
+      <c r="A15" s="53" t="s">
+        <v>482</v>
+      </c>
+      <c r="B15" s="65" t="s">
+        <v>554</v>
+      </c>
+      <c r="E15" s="71"/>
+    </row>
+    <row r="16" spans="1:22" s="54" customFormat="1" ht="100.8">
+      <c r="A16" s="55"/>
+      <c r="B16" s="55" t="s">
+        <v>483</v>
+      </c>
+      <c r="C16" s="55" t="s">
+        <v>566</v>
+      </c>
+      <c r="D16" s="56"/>
+      <c r="E16" s="71"/>
+    </row>
+    <row r="17" spans="1:5" s="54" customFormat="1" ht="43.2">
+      <c r="A17" s="55"/>
+      <c r="B17" s="55" t="s">
+        <v>490</v>
+      </c>
+      <c r="C17" s="61" t="s">
+        <v>547</v>
+      </c>
+      <c r="D17" s="56"/>
+      <c r="E17" s="71"/>
+    </row>
+    <row r="18" spans="1:5" s="54" customFormat="1">
+      <c r="A18" s="55"/>
+      <c r="B18" s="53" t="s">
+        <v>542</v>
+      </c>
+      <c r="C18" s="53" t="s">
+        <v>551</v>
+      </c>
+      <c r="D18" s="56"/>
+      <c r="E18" s="71"/>
+    </row>
+    <row r="19" spans="1:5" s="54" customFormat="1" ht="172.8">
+      <c r="B19" s="55" t="s">
+        <v>543</v>
+      </c>
+      <c r="C19" s="55" t="s">
+        <v>544</v>
+      </c>
+      <c r="D19" s="56"/>
+      <c r="E19" s="71"/>
+    </row>
+    <row r="20" spans="1:5" s="54" customFormat="1">
+      <c r="B20" s="64" t="s">
+        <v>552</v>
+      </c>
+      <c r="C20" s="53" t="s">
+        <v>539</v>
+      </c>
+      <c r="E20" s="71"/>
+    </row>
+    <row r="21" spans="1:5" s="54" customFormat="1" ht="273.60000000000002">
+      <c r="A21" s="61" t="s">
+        <v>556</v>
+      </c>
+      <c r="B21" s="55" t="s">
+        <v>540</v>
+      </c>
+      <c r="C21" s="61" t="s">
+        <v>541</v>
+      </c>
+      <c r="E21" s="71"/>
+    </row>
+    <row r="22" spans="1:5" s="54" customFormat="1" ht="72">
+      <c r="A22" s="61" t="s">
+        <v>560</v>
+      </c>
+      <c r="B22" s="55" t="s">
+        <v>557</v>
+      </c>
+      <c r="C22" s="55" t="s">
+        <v>555</v>
+      </c>
+      <c r="E22" s="71"/>
+    </row>
+    <row r="23" spans="1:5" s="54" customFormat="1">
+      <c r="A23" s="53" t="s">
+        <v>497</v>
+      </c>
+      <c r="B23" s="55"/>
+      <c r="C23" s="61"/>
+      <c r="E23" s="71"/>
+    </row>
+    <row r="24" spans="1:5" s="54" customFormat="1" ht="100.8">
+      <c r="A24" s="54" t="s">
+        <v>497</v>
+      </c>
+      <c r="B24" s="55" t="s">
+        <v>564</v>
+      </c>
+      <c r="C24" s="61"/>
+      <c r="E24" s="71"/>
+    </row>
+    <row r="25" spans="1:5" s="54" customFormat="1" ht="201.6">
+      <c r="A25" s="54" t="s">
+        <v>498</v>
+      </c>
+      <c r="B25" s="55" t="s">
+        <v>565</v>
+      </c>
+      <c r="C25" s="69" t="s">
+        <v>568</v>
+      </c>
+      <c r="E25" s="71"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="53" t="s">
+        <v>724</v>
+      </c>
+      <c r="B26" s="54"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="71"/>
+    </row>
+    <row r="27" spans="1:5" ht="100.8">
+      <c r="A27" s="55" t="s">
+        <v>803</v>
+      </c>
+      <c r="B27" s="113" t="s">
+        <v>814</v>
+      </c>
+      <c r="C27" s="55" t="s">
+        <v>569</v>
+      </c>
+      <c r="D27" s="56"/>
+    </row>
+    <row r="28" spans="1:5" ht="302.39999999999998">
+      <c r="A28" s="55" t="s">
+        <v>802</v>
+      </c>
+      <c r="B28" s="113" t="s">
+        <v>812</v>
+      </c>
+      <c r="C28" s="55" t="s">
+        <v>570</v>
+      </c>
+      <c r="D28" s="56"/>
+    </row>
+    <row r="29" spans="1:5" ht="172.8">
+      <c r="A29" s="55" t="s">
+        <v>806</v>
+      </c>
+      <c r="B29" s="113" t="s">
+        <v>813</v>
+      </c>
+      <c r="C29" s="113" t="s">
+        <v>809</v>
+      </c>
+      <c r="D29" s="56"/>
+    </row>
+    <row r="30" spans="1:5" ht="86.4">
+      <c r="A30" s="55" t="s">
+        <v>807</v>
+      </c>
+      <c r="B30" s="55" t="s">
+        <v>804</v>
+      </c>
+      <c r="C30" s="69" t="s">
+        <v>805</v>
+      </c>
+      <c r="D30" s="56"/>
+    </row>
+    <row r="31" spans="1:5" ht="216">
+      <c r="A31" s="55" t="s">
+        <v>810</v>
+      </c>
+      <c r="B31" s="69" t="s">
+        <v>811</v>
+      </c>
+      <c r="C31" s="113" t="s">
+        <v>808</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA21C6CE-E28C-44A8-8026-35145C4B3BB3}">
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
@@ -42699,7 +43507,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33802208-57A6-4A96-B3D6-9C8CAC2510A0}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -42983,7 +43791,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC5E3696-71DB-4B2D-8388-ED55357EFB2B}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -43073,7 +43881,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7BEB5B2-92F5-4415-BAF1-6F4428F63827}">
   <sheetPr codeName="Лист1">
     <tabColor rgb="FF0070C0"/>
@@ -44903,7 +45711,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1120C29B-A224-406A-9A85-6A1751B09B3B}">
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
@@ -45129,7 +45937,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2A651A-02D2-4C6D-91FC-2CBD73190D44}">
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
@@ -45717,7 +46525,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A61FC91-6FA9-4168-8E92-7EC4D5EDAEF7}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
@@ -45974,7 +46782,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7742DC2D-8356-42AF-A171-521A8B3CCEEA}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
@@ -46294,540 +47102,6 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId13"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A618EC0-3EC6-431F-A43F-335526068004}">
-  <sheetPr>
-    <tabColor rgb="FFFFC000"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A2:D11"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="39.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="59.21875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="55.33203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="43.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="55.109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="67.88671875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="64.33203125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="7.77734375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="39.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="48.88671875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="72.6640625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="43.88671875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="7.77734375" style="2" customWidth="1"/>
-    <col min="14" max="14" width="56.77734375" style="2" customWidth="1"/>
-    <col min="15" max="15" width="46.77734375" style="2" customWidth="1"/>
-    <col min="16" max="16" width="62.88671875" style="2" customWidth="1"/>
-    <col min="17" max="17" width="49.21875" style="2" customWidth="1"/>
-    <col min="18" max="18" width="8.77734375" style="2" customWidth="1"/>
-    <col min="19" max="19" width="67.77734375" style="2" customWidth="1"/>
-    <col min="20" max="20" width="68.33203125" style="2" customWidth="1"/>
-    <col min="21" max="22" width="59.33203125" style="2" customWidth="1"/>
-    <col min="23" max="23" width="59.6640625" style="2" customWidth="1"/>
-    <col min="24" max="24" width="99.44140625" style="2" customWidth="1"/>
-    <col min="25" max="25" width="41.21875" style="2" customWidth="1"/>
-    <col min="26" max="26" width="8.77734375" style="2" customWidth="1"/>
-    <col min="27" max="16384" width="8.77734375" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:4">
-      <c r="A2" s="53" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="53" t="s">
-        <v>487</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="53" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" s="39" customFormat="1"/>
-    <row r="7" spans="1:4">
-      <c r="A7" s="40" t="s">
-        <v>266</v>
-      </c>
-      <c r="B7" s="40" t="s">
-        <v>270</v>
-      </c>
-      <c r="C7" s="40" t="s">
-        <v>268</v>
-      </c>
-      <c r="D7" s="40" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" s="54" customFormat="1">
-      <c r="A8" s="53" t="s">
-        <v>484</v>
-      </c>
-      <c r="B8" s="55"/>
-      <c r="C8" s="55"/>
-      <c r="D8" s="56"/>
-    </row>
-    <row r="9" spans="1:4" s="54" customFormat="1" ht="265.2" customHeight="1">
-      <c r="B9" s="55" t="s">
-        <v>588</v>
-      </c>
-      <c r="C9" s="67" t="s">
-        <v>589</v>
-      </c>
-      <c r="D9" s="56" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" s="54" customFormat="1">
-      <c r="A10" s="53" t="s">
-        <v>487</v>
-      </c>
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="56"/>
-    </row>
-    <row r="11" spans="1:4" s="54" customFormat="1" ht="165" customHeight="1">
-      <c r="A11" s="54" t="s">
-        <v>500</v>
-      </c>
-      <c r="B11" s="55" t="s">
-        <v>575</v>
-      </c>
-      <c r="C11" s="55" t="s">
-        <v>579</v>
-      </c>
-      <c r="D11" s="56" t="s">
-        <v>274</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D9" r:id="rId1" xr:uid="{BCBCEA9E-F432-4A47-B60F-5B013B8D935F}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{699DA14B-4B03-4F00-B701-816422181365}">
-  <sheetPr>
-    <tabColor rgb="FFFFC000"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A2:F44"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="39.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="40.88671875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="59.21875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="55.33203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="69.6640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="8.44140625" style="70" customWidth="1"/>
-    <col min="7" max="7" width="67.88671875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="64.33203125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="7.77734375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="39.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="48.88671875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="72.6640625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="43.88671875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="7.77734375" style="2" customWidth="1"/>
-    <col min="15" max="15" width="56.77734375" style="2" customWidth="1"/>
-    <col min="16" max="16" width="46.77734375" style="2" customWidth="1"/>
-    <col min="17" max="17" width="62.88671875" style="2" customWidth="1"/>
-    <col min="18" max="18" width="49.21875" style="2" customWidth="1"/>
-    <col min="19" max="19" width="8.77734375" style="2" customWidth="1"/>
-    <col min="20" max="20" width="67.77734375" style="2" customWidth="1"/>
-    <col min="21" max="21" width="68.33203125" style="2" customWidth="1"/>
-    <col min="22" max="23" width="59.33203125" style="2" customWidth="1"/>
-    <col min="24" max="24" width="59.6640625" style="2" customWidth="1"/>
-    <col min="25" max="25" width="99.44140625" style="2" customWidth="1"/>
-    <col min="26" max="26" width="41.21875" style="2" customWidth="1"/>
-    <col min="27" max="27" width="8.77734375" style="2" customWidth="1"/>
-    <col min="28" max="16384" width="8.77734375" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:6">
-      <c r="A2" s="53" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="53" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="53" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="53" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="28.8">
-      <c r="A6" s="53" t="s">
-        <v>618</v>
-      </c>
-      <c r="B6" s="84" t="s">
-        <v>620</v>
-      </c>
-      <c r="E6" s="88" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="28.8">
-      <c r="A7" s="53" t="s">
-        <v>622</v>
-      </c>
-      <c r="B7" s="84" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="43.2">
-      <c r="A8" s="84" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" s="39" customFormat="1">
-      <c r="F12" s="70"/>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="53" t="s">
-        <v>960</v>
-      </c>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:6" ht="86.4">
-      <c r="C15" s="88" t="s">
-        <v>957</v>
-      </c>
-      <c r="D15" s="111" t="s">
-        <v>955</v>
-      </c>
-      <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="1:6" ht="86.4">
-      <c r="C16" s="88" t="s">
-        <v>651</v>
-      </c>
-      <c r="D16" s="111" t="s">
-        <v>956</v>
-      </c>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="1:6" s="54" customFormat="1">
-      <c r="A17" s="53" t="s">
-        <v>489</v>
-      </c>
-      <c r="B17" s="55"/>
-      <c r="C17" s="55" t="s">
-        <v>549</v>
-      </c>
-      <c r="D17" s="55"/>
-      <c r="E17" s="56" t="s">
-        <v>488</v>
-      </c>
-      <c r="F17" s="71"/>
-    </row>
-    <row r="18" spans="1:6" s="54" customFormat="1">
-      <c r="A18" s="62" t="s">
-        <v>562</v>
-      </c>
-      <c r="B18" s="55"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="56"/>
-      <c r="F18" s="71"/>
-    </row>
-    <row r="19" spans="1:6" s="54" customFormat="1" ht="100.8">
-      <c r="B19" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="C19" s="55" t="s">
-        <v>593</v>
-      </c>
-      <c r="D19" s="63" t="s">
-        <v>550</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="F19" s="71"/>
-    </row>
-    <row r="20" spans="1:6" s="54" customFormat="1" ht="28.8">
-      <c r="A20" s="80" t="s">
-        <v>563</v>
-      </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="63"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="71"/>
-    </row>
-    <row r="21" spans="1:6" s="54" customFormat="1" ht="129.6">
-      <c r="B21" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="D21" s="58" t="s">
-        <v>494</v>
-      </c>
-      <c r="E21" s="56"/>
-      <c r="F21" s="71"/>
-    </row>
-    <row r="22" spans="1:6" s="54" customFormat="1" ht="115.2">
-      <c r="A22" s="55"/>
-      <c r="B22" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="D22" s="58" t="s">
-        <v>495</v>
-      </c>
-      <c r="E22" s="56"/>
-      <c r="F22" s="71"/>
-    </row>
-    <row r="23" spans="1:6" s="54" customFormat="1">
-      <c r="A23" s="81" t="s">
-        <v>496</v>
-      </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="58"/>
-      <c r="E23" s="56"/>
-      <c r="F23" s="71"/>
-    </row>
-    <row r="24" spans="1:6" ht="86.4">
-      <c r="B24" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="C24" s="59" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="20" t="s">
-        <v>591</v>
-      </c>
-      <c r="C25" s="59"/>
-    </row>
-    <row r="26" spans="1:6" ht="43.2">
-      <c r="A26" s="58"/>
-      <c r="B26" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="C26" s="59" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="53" t="s">
-        <v>605</v>
-      </c>
-      <c r="B27" s="23" t="s">
-        <v>606</v>
-      </c>
-      <c r="C27" s="82" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="100.8">
-      <c r="A28" s="58"/>
-      <c r="C28" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="D28" s="111" t="s">
-        <v>603</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="115.2">
-      <c r="A29" s="58"/>
-      <c r="B29" s="86" t="s">
-        <v>628</v>
-      </c>
-      <c r="C29" s="111" t="s">
-        <v>629</v>
-      </c>
-      <c r="D29" s="111" t="s">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="374.4">
-      <c r="A30" s="58"/>
-      <c r="C30" s="111" t="s">
-        <v>951</v>
-      </c>
-      <c r="D30" s="111" t="s">
-        <v>954</v>
-      </c>
-      <c r="E30" s="111" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="53" t="s">
-        <v>601</v>
-      </c>
-      <c r="C31" s="59"/>
-    </row>
-    <row r="32" spans="1:6" ht="100.8">
-      <c r="A32" s="58"/>
-      <c r="C32" s="59" t="s">
-        <v>604</v>
-      </c>
-      <c r="D32" s="68" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="53" t="s">
-        <v>610</v>
-      </c>
-      <c r="B33" s="83" t="s">
-        <v>612</v>
-      </c>
-      <c r="C33" s="83" t="s">
-        <v>613</v>
-      </c>
-      <c r="D33" s="68"/>
-    </row>
-    <row r="34" spans="1:5" ht="216">
-      <c r="A34" s="68"/>
-      <c r="B34" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="C34" s="68" t="s">
-        <v>614</v>
-      </c>
-      <c r="D34" s="68" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="28.8">
-      <c r="A35" s="53" t="s">
-        <v>618</v>
-      </c>
-      <c r="C35" s="59"/>
-      <c r="D35" s="68"/>
-    </row>
-    <row r="36" spans="1:5" ht="187.2">
-      <c r="A36" s="58"/>
-      <c r="B36" s="58"/>
-      <c r="C36" s="59" t="s">
-        <v>626</v>
-      </c>
-      <c r="D36" s="68" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="72">
-      <c r="A37" s="58"/>
-      <c r="B37" s="86" t="s">
-        <v>627</v>
-      </c>
-      <c r="C37" s="59" t="s">
-        <v>625</v>
-      </c>
-      <c r="D37" s="68"/>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="53" t="s">
-        <v>622</v>
-      </c>
-      <c r="C38" s="59"/>
-      <c r="D38" s="68"/>
-    </row>
-    <row r="39" spans="1:5" ht="172.8">
-      <c r="A39" s="68"/>
-      <c r="B39" s="85" t="s">
-        <v>621</v>
-      </c>
-      <c r="C39" s="59" t="s">
-        <v>617</v>
-      </c>
-      <c r="D39" s="68" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="72">
-      <c r="B40" s="85" t="s">
-        <v>624</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="43.2">
-      <c r="A41" s="53" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="100.8">
-      <c r="A42" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>632</v>
-      </c>
-      <c r="D42" s="68" t="s">
-        <v>639</v>
-      </c>
-      <c r="E42" s="88" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" ht="345.6">
-      <c r="A43" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="57.6">
-      <c r="A44" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="D44" s="68" t="s">
-        <v>640</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="E17" r:id="rId1" xr:uid="{A78692EB-CF12-40DC-BDE2-751D89A74779}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -47206,6 +47480,549 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A618EC0-3EC6-431F-A43F-335526068004}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:D11"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="39.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="59.21875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="55.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="43.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="55.109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="67.88671875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="64.33203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7.77734375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="39.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="48.88671875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="72.6640625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="43.88671875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="7.77734375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="56.77734375" style="2" customWidth="1"/>
+    <col min="15" max="15" width="46.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="62.88671875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="49.21875" style="2" customWidth="1"/>
+    <col min="18" max="18" width="8.77734375" style="2" customWidth="1"/>
+    <col min="19" max="19" width="67.77734375" style="2" customWidth="1"/>
+    <col min="20" max="20" width="68.33203125" style="2" customWidth="1"/>
+    <col min="21" max="22" width="59.33203125" style="2" customWidth="1"/>
+    <col min="23" max="23" width="59.6640625" style="2" customWidth="1"/>
+    <col min="24" max="24" width="99.44140625" style="2" customWidth="1"/>
+    <col min="25" max="25" width="41.21875" style="2" customWidth="1"/>
+    <col min="26" max="26" width="8.77734375" style="2" customWidth="1"/>
+    <col min="27" max="16384" width="8.77734375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:4">
+      <c r="A2" s="53" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="53" t="s">
+        <v>487</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="53" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="39" customFormat="1"/>
+    <row r="7" spans="1:4">
+      <c r="A7" s="40" t="s">
+        <v>266</v>
+      </c>
+      <c r="B7" s="40" t="s">
+        <v>270</v>
+      </c>
+      <c r="C7" s="40" t="s">
+        <v>268</v>
+      </c>
+      <c r="D7" s="40" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="54" customFormat="1">
+      <c r="A8" s="53" t="s">
+        <v>484</v>
+      </c>
+      <c r="B8" s="55"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="56"/>
+    </row>
+    <row r="9" spans="1:4" s="54" customFormat="1" ht="265.2" customHeight="1">
+      <c r="B9" s="55" t="s">
+        <v>588</v>
+      </c>
+      <c r="C9" s="67" t="s">
+        <v>589</v>
+      </c>
+      <c r="D9" s="56" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" s="54" customFormat="1">
+      <c r="A10" s="53" t="s">
+        <v>487</v>
+      </c>
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="56"/>
+    </row>
+    <row r="11" spans="1:4" s="54" customFormat="1" ht="165" customHeight="1">
+      <c r="A11" s="54" t="s">
+        <v>500</v>
+      </c>
+      <c r="B11" s="55" t="s">
+        <v>575</v>
+      </c>
+      <c r="C11" s="55" t="s">
+        <v>579</v>
+      </c>
+      <c r="D11" s="56" t="s">
+        <v>274</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D9" r:id="rId1" xr:uid="{BCBCEA9E-F432-4A47-B60F-5B013B8D935F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{699DA14B-4B03-4F00-B701-816422181365}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:F44"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="39.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="40.88671875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="59.21875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="55.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="69.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="8.44140625" style="70" customWidth="1"/>
+    <col min="7" max="7" width="67.88671875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="64.33203125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="7.77734375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="39.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="48.88671875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="72.6640625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="43.88671875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="7.77734375" style="2" customWidth="1"/>
+    <col min="15" max="15" width="56.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="46.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="62.88671875" style="2" customWidth="1"/>
+    <col min="18" max="18" width="49.21875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="8.77734375" style="2" customWidth="1"/>
+    <col min="20" max="20" width="67.77734375" style="2" customWidth="1"/>
+    <col min="21" max="21" width="68.33203125" style="2" customWidth="1"/>
+    <col min="22" max="23" width="59.33203125" style="2" customWidth="1"/>
+    <col min="24" max="24" width="59.6640625" style="2" customWidth="1"/>
+    <col min="25" max="25" width="99.44140625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="41.21875" style="2" customWidth="1"/>
+    <col min="27" max="27" width="8.77734375" style="2" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6">
+      <c r="A2" s="53" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="53" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="53" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="53" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="28.8">
+      <c r="A6" s="53" t="s">
+        <v>618</v>
+      </c>
+      <c r="B6" s="84" t="s">
+        <v>620</v>
+      </c>
+      <c r="E6" s="88" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="28.8">
+      <c r="A7" s="53" t="s">
+        <v>622</v>
+      </c>
+      <c r="B7" s="84" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="43.2">
+      <c r="A8" s="84" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="39" customFormat="1">
+      <c r="F12" s="70"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="53" t="s">
+        <v>960</v>
+      </c>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:6" ht="86.4">
+      <c r="C15" s="88" t="s">
+        <v>957</v>
+      </c>
+      <c r="D15" s="111" t="s">
+        <v>955</v>
+      </c>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="1:6" ht="86.4">
+      <c r="C16" s="88" t="s">
+        <v>651</v>
+      </c>
+      <c r="D16" s="111" t="s">
+        <v>956</v>
+      </c>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="1:6" s="54" customFormat="1">
+      <c r="A17" s="53" t="s">
+        <v>489</v>
+      </c>
+      <c r="B17" s="55"/>
+      <c r="C17" s="55" t="s">
+        <v>549</v>
+      </c>
+      <c r="D17" s="55"/>
+      <c r="E17" s="56" t="s">
+        <v>488</v>
+      </c>
+      <c r="F17" s="71"/>
+    </row>
+    <row r="18" spans="1:6" s="54" customFormat="1">
+      <c r="A18" s="62" t="s">
+        <v>562</v>
+      </c>
+      <c r="B18" s="55"/>
+      <c r="C18" s="55"/>
+      <c r="D18" s="55"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="71"/>
+    </row>
+    <row r="19" spans="1:6" s="54" customFormat="1" ht="100.8">
+      <c r="A19" s="205" t="s">
+        <v>1697</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="C19" s="55" t="s">
+        <v>593</v>
+      </c>
+      <c r="D19" s="204" t="s">
+        <v>550</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="F19" s="71"/>
+    </row>
+    <row r="20" spans="1:6" s="54" customFormat="1" ht="28.8">
+      <c r="A20" s="80" t="s">
+        <v>563</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="63"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="71"/>
+    </row>
+    <row r="21" spans="1:6" s="54" customFormat="1" ht="129.6">
+      <c r="A21" s="205" t="s">
+        <v>1696</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="D21" s="58" t="s">
+        <v>494</v>
+      </c>
+      <c r="E21" s="56"/>
+      <c r="F21" s="71"/>
+    </row>
+    <row r="22" spans="1:6" s="54" customFormat="1" ht="115.2">
+      <c r="A22" s="55"/>
+      <c r="B22" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="D22" s="58" t="s">
+        <v>495</v>
+      </c>
+      <c r="E22" s="56"/>
+      <c r="F22" s="71"/>
+    </row>
+    <row r="23" spans="1:6" s="54" customFormat="1">
+      <c r="A23" s="81" t="s">
+        <v>496</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="58"/>
+      <c r="E23" s="56"/>
+      <c r="F23" s="71"/>
+    </row>
+    <row r="24" spans="1:6" ht="86.4">
+      <c r="A24" s="205" t="s">
+        <v>1696</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="C24" s="59" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="20" t="s">
+        <v>591</v>
+      </c>
+      <c r="C25" s="59"/>
+    </row>
+    <row r="26" spans="1:6" ht="43.2">
+      <c r="A26" s="58"/>
+      <c r="B26" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="C26" s="59" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="53" t="s">
+        <v>605</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>606</v>
+      </c>
+      <c r="C27" s="82" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="100.8">
+      <c r="A28" s="58"/>
+      <c r="C28" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="D28" s="111" t="s">
+        <v>603</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="115.2">
+      <c r="A29" s="58"/>
+      <c r="B29" s="86" t="s">
+        <v>628</v>
+      </c>
+      <c r="C29" s="111" t="s">
+        <v>629</v>
+      </c>
+      <c r="D29" s="111" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="374.4">
+      <c r="A30" s="58"/>
+      <c r="C30" s="111" t="s">
+        <v>951</v>
+      </c>
+      <c r="D30" s="111" t="s">
+        <v>954</v>
+      </c>
+      <c r="E30" s="111" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="53" t="s">
+        <v>601</v>
+      </c>
+      <c r="C31" s="59"/>
+    </row>
+    <row r="32" spans="1:6" ht="100.8">
+      <c r="A32" s="58"/>
+      <c r="C32" s="59" t="s">
+        <v>604</v>
+      </c>
+      <c r="D32" s="68" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="53" t="s">
+        <v>610</v>
+      </c>
+      <c r="B33" s="83" t="s">
+        <v>612</v>
+      </c>
+      <c r="C33" s="83" t="s">
+        <v>613</v>
+      </c>
+      <c r="D33" s="68"/>
+    </row>
+    <row r="34" spans="1:5" ht="216">
+      <c r="A34" s="68"/>
+      <c r="B34" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="C34" s="68" t="s">
+        <v>614</v>
+      </c>
+      <c r="D34" s="68" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="28.8">
+      <c r="A35" s="53" t="s">
+        <v>618</v>
+      </c>
+      <c r="C35" s="59"/>
+      <c r="D35" s="68"/>
+    </row>
+    <row r="36" spans="1:5" ht="187.2">
+      <c r="A36" s="58"/>
+      <c r="B36" s="58"/>
+      <c r="C36" s="59" t="s">
+        <v>626</v>
+      </c>
+      <c r="D36" s="68" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="72">
+      <c r="A37" s="58"/>
+      <c r="B37" s="86" t="s">
+        <v>627</v>
+      </c>
+      <c r="C37" s="59" t="s">
+        <v>625</v>
+      </c>
+      <c r="D37" s="68"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="53" t="s">
+        <v>622</v>
+      </c>
+      <c r="C38" s="59"/>
+      <c r="D38" s="68"/>
+    </row>
+    <row r="39" spans="1:5" ht="172.8">
+      <c r="A39" s="68"/>
+      <c r="B39" s="85" t="s">
+        <v>621</v>
+      </c>
+      <c r="C39" s="59" t="s">
+        <v>617</v>
+      </c>
+      <c r="D39" s="68" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="72">
+      <c r="B40" s="85" t="s">
+        <v>624</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="43.2">
+      <c r="A41" s="53" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="100.8">
+      <c r="A42" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="D42" s="68" t="s">
+        <v>639</v>
+      </c>
+      <c r="E42" s="88" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="345.6">
+      <c r="A43" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="57.6">
+      <c r="A44" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="D44" s="68" t="s">
+        <v>640</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E17" r:id="rId1" xr:uid="{A78692EB-CF12-40DC-BDE2-751D89A74779}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5196872-622E-452B-BF08-E278EFE9C4AC}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
@@ -47469,7 +48286,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC84526A-FEB5-4E92-A2D1-9E62E1253250}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -47789,7 +48606,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AED3772-2276-4A5B-8297-381C62F17A38}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
@@ -48046,7 +48863,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A76DD74-A7EF-46D8-857D-474EC57AEB74}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
@@ -48307,13 +49124,13 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="38" type="noConversion"/>
+  <phoneticPr fontId="40" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E54E95-45B1-4574-9D6D-878991F4CE0F}">
   <sheetPr>
     <tabColor theme="9" tint="-0.499984740745262"/>
@@ -48983,7 +49800,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB3FDEC5-323F-4EDF-BBD5-DDD411B00686}">
   <sheetPr>
     <tabColor theme="9" tint="-0.499984740745262"/>
@@ -49075,7 +49892,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4D1B500-F6F5-4CD5-8159-3B45448C9EA1}">
   <sheetPr>
     <tabColor theme="9" tint="-0.499984740745262"/>
@@ -49302,7 +50119,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{490F061F-854A-4B75-8430-04C1C2C326AC}">
   <sheetPr>
     <tabColor theme="9" tint="-0.499984740745262"/>
@@ -51345,7 +52162,229 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43CD9189-6831-4958-B83E-86B1AD49159E}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:V34"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="36" style="1" customWidth="1"/>
+    <col min="2" max="2" width="62.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="81.109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="43.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.5546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.88671875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="56.88671875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.6640625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.109375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="67.6640625" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.44140625" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.44140625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.5546875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.33203125" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.6640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:22" s="3" customFormat="1">
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
+      <c r="G2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="17"/>
+      <c r="U2" s="5"/>
+    </row>
+    <row r="3" spans="1:22">
+      <c r="C3" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="P3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="2"/>
+    </row>
+    <row r="4" spans="1:22">
+      <c r="A4" s="1" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B4" s="110" t="s">
+        <v>1728</v>
+      </c>
+      <c r="C4" s="204" t="s">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
+      <c r="C5" s="4" t="s">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
+      <c r="C6" s="4" t="s">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22">
+      <c r="C7" s="4" t="s">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22">
+      <c r="C8" s="4" t="s">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22">
+      <c r="C9" s="4" t="s">
+        <v>1702</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
+      <c r="C10" s="4" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22">
+      <c r="C11" s="4" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22">
+      <c r="C12" s="4" t="s">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22">
+      <c r="C13" s="4" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22">
+      <c r="C14" s="4" t="s">
+        <v>1707</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22">
+      <c r="C15" s="4" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22">
+      <c r="C16" s="4" t="s">
+        <v>1709</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" s="4" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" s="4" t="s">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3">
+      <c r="C19" s="4" t="s">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3">
+      <c r="C20" s="4" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="21" spans="3:3">
+      <c r="C21" s="4" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="22" spans="3:3">
+      <c r="C22" s="4" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="23" spans="3:3">
+      <c r="C23" s="4" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="24" spans="3:3">
+      <c r="C24" s="4" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="25" spans="3:3">
+      <c r="C25" s="4" t="s">
+        <v>1718</v>
+      </c>
+    </row>
+    <row r="26" spans="3:3">
+      <c r="C26" s="4" t="s">
+        <v>1719</v>
+      </c>
+    </row>
+    <row r="27" spans="3:3">
+      <c r="C27" s="4" t="s">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="28" spans="3:3">
+      <c r="C28" s="4" t="s">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="29" spans="3:3">
+      <c r="C29" s="4" t="s">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="30" spans="3:3">
+      <c r="C30" s="4" t="s">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="31" spans="3:3">
+      <c r="C31" s="4" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="32" spans="3:3">
+      <c r="C32" s="4" t="s">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="33" spans="3:3">
+      <c r="C33" s="4" t="s">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3">
+      <c r="C34" s="4" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1CE5012-6BDF-4D83-9304-D3C1725959C1}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -52011,7 +53050,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DB5FC45-CE13-43B4-B966-2D9F587DF48A}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -52229,7 +53268,1011 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0430A206-850D-44C6-89AD-2AAF1FF700E3}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:E20"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="39.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="42.88671875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="73.77734375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="30.88671875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="7.44140625" style="70" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="2" customWidth="1"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="2" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="2" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="2" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="2" customWidth="1"/>
+    <col min="28" max="28" width="8.77734375" style="2" customWidth="1"/>
+    <col min="29" max="16384" width="8.77734375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5">
+      <c r="A2" s="23" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="B3" s="168" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="B4" s="168" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="39" customFormat="1">
+      <c r="E6" s="70"/>
+    </row>
+    <row r="7" spans="1:5" s="133" customFormat="1">
+      <c r="C7" s="168" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D7" s="171" t="s">
+        <v>1205</v>
+      </c>
+      <c r="E7" s="70"/>
+    </row>
+    <row r="8" spans="1:5" ht="28.8">
+      <c r="A8" s="23" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B8" s="169" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="43.2">
+      <c r="C9" s="169" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="158.4">
+      <c r="B10" s="169" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="158.4">
+      <c r="B11" s="169" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="168" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="72">
+      <c r="B13" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="28.8">
+      <c r="A14" s="168" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B14" s="114" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="100.8">
+      <c r="C15" s="169" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="86.4">
+      <c r="A16" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="216">
+      <c r="A17" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C17" s="169" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="216">
+      <c r="B18" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C18" s="169" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="168" t="s">
+        <v>1238</v>
+      </c>
+      <c r="D19" s="170" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="86.4">
+      <c r="B20" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D7" r:id="rId1" location="teleport" xr:uid="{0E3B3246-2353-4504-A941-8F6807E7B81A}"/>
+    <hyperlink ref="D19" r:id="rId2" location="multiple-teleports-on-the-same-target" xr:uid="{53012BAD-A14C-4C99-818A-7EC8E407934F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBDC1ECC-7624-429D-BB98-76AA7F755485}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:E22"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="39.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="51.21875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="73.77734375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="55.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="7.44140625" style="70" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="2" customWidth="1"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="2" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="2" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="2" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="2" customWidth="1"/>
+    <col min="28" max="28" width="8.77734375" style="2" customWidth="1"/>
+    <col min="29" max="16384" width="8.77734375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5">
+      <c r="A2" s="23" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="B3" s="168" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="B4" s="168"/>
+    </row>
+    <row r="6" spans="1:5" s="39" customFormat="1">
+      <c r="E6" s="70"/>
+    </row>
+    <row r="7" spans="1:5" s="133" customFormat="1">
+      <c r="C7" s="168" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D7" s="172" t="s">
+        <v>1205</v>
+      </c>
+      <c r="E7" s="70"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="23" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="129.6">
+      <c r="B9" s="169" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="168" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="57.6">
+      <c r="B11" s="2" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="28.8">
+      <c r="B12" s="2" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="86.4">
+      <c r="B13" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="168" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="C15" s="2" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="30">
+      <c r="A16" s="2" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C16" s="173" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="30">
+      <c r="A17" s="2" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C17" s="174" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="30">
+      <c r="A18" s="2" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C18" s="174" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="316.8">
+      <c r="B19" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="168" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="144">
+      <c r="B21" s="169" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="172.8">
+      <c r="B22" s="169" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D7" r:id="rId1" xr:uid="{6A6FD24F-904C-4C95-BE3E-B72B8B6DD4CA}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A35D37AB-889F-4E36-AD27-D38FD2468E4E}">
+  <sheetPr>
+    <tabColor rgb="FF7030A0"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:E33"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="39.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="59.88671875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="59.21875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="55.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="10.21875" style="70" customWidth="1"/>
+    <col min="6" max="6" width="64.33203125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="7.77734375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="39.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="48.88671875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="72.6640625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="43.88671875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="7.77734375" style="2" customWidth="1"/>
+    <col min="13" max="13" width="56.77734375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="46.77734375" style="2" customWidth="1"/>
+    <col min="15" max="15" width="62.88671875" style="2" customWidth="1"/>
+    <col min="16" max="16" width="49.21875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="8.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="67.77734375" style="2" customWidth="1"/>
+    <col min="19" max="19" width="68.33203125" style="2" customWidth="1"/>
+    <col min="20" max="21" width="59.33203125" style="2" customWidth="1"/>
+    <col min="22" max="22" width="59.6640625" style="2" customWidth="1"/>
+    <col min="23" max="23" width="99.44140625" style="2" customWidth="1"/>
+    <col min="24" max="24" width="41.21875" style="2" customWidth="1"/>
+    <col min="25" max="25" width="8.77734375" style="2" customWidth="1"/>
+    <col min="26" max="16384" width="8.77734375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5">
+      <c r="A2" s="53" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="131"/>
+      <c r="B3" s="107" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="131"/>
+      <c r="B4" s="107" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="131"/>
+      <c r="B5" s="107" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="131"/>
+      <c r="B6" s="107" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="53" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="53" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="39" customFormat="1">
+      <c r="E10" s="70"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="40" t="s">
+        <v>266</v>
+      </c>
+      <c r="B11" s="40" t="s">
+        <v>267</v>
+      </c>
+      <c r="C11" s="40" t="s">
+        <v>270</v>
+      </c>
+      <c r="D11" s="40" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" s="54" customFormat="1">
+      <c r="A12" s="53" t="s">
+        <v>501</v>
+      </c>
+      <c r="E12" s="71"/>
+    </row>
+    <row r="13" spans="1:5" s="54" customFormat="1" ht="259.2">
+      <c r="A13" s="55" t="s">
+        <v>502</v>
+      </c>
+      <c r="B13" s="55" t="s">
+        <v>934</v>
+      </c>
+      <c r="C13" s="55" t="s">
+        <v>503</v>
+      </c>
+      <c r="D13" s="55"/>
+      <c r="E13" s="71"/>
+    </row>
+    <row r="14" spans="1:5" s="54" customFormat="1">
+      <c r="A14" s="62" t="s">
+        <v>935</v>
+      </c>
+      <c r="B14" s="55"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="71"/>
+    </row>
+    <row r="15" spans="1:5" s="54" customFormat="1" ht="28.8">
+      <c r="A15" s="55"/>
+      <c r="B15" s="55" t="s">
+        <v>936</v>
+      </c>
+      <c r="C15" s="137" t="s">
+        <v>941</v>
+      </c>
+      <c r="D15" s="55"/>
+      <c r="E15" s="71"/>
+    </row>
+    <row r="16" spans="1:5" s="54" customFormat="1" ht="28.8">
+      <c r="A16" s="55"/>
+      <c r="B16" s="55" t="s">
+        <v>937</v>
+      </c>
+      <c r="C16" s="137" t="s">
+        <v>940</v>
+      </c>
+      <c r="D16" s="55"/>
+      <c r="E16" s="71"/>
+    </row>
+    <row r="17" spans="1:5" s="54" customFormat="1" ht="57.6">
+      <c r="A17" s="55"/>
+      <c r="B17" s="55" t="s">
+        <v>938</v>
+      </c>
+      <c r="C17" s="137" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D17" s="55"/>
+      <c r="E17" s="71"/>
+    </row>
+    <row r="18" spans="1:5" s="54" customFormat="1" ht="43.2">
+      <c r="A18" s="55"/>
+      <c r="B18" s="55" t="s">
+        <v>939</v>
+      </c>
+      <c r="C18" s="137" t="s">
+        <v>1243</v>
+      </c>
+      <c r="D18" s="55"/>
+      <c r="E18" s="71"/>
+    </row>
+    <row r="19" spans="1:5" s="54" customFormat="1">
+      <c r="A19" s="62" t="s">
+        <v>942</v>
+      </c>
+      <c r="B19" s="55"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="71"/>
+    </row>
+    <row r="20" spans="1:5" s="54" customFormat="1" ht="43.2">
+      <c r="A20" s="55"/>
+      <c r="B20" s="55" t="s">
+        <v>943</v>
+      </c>
+      <c r="C20" s="137" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D20" s="55"/>
+      <c r="E20" s="71"/>
+    </row>
+    <row r="21" spans="1:5" s="54" customFormat="1" ht="57.6">
+      <c r="A21" s="55"/>
+      <c r="B21" s="55" t="s">
+        <v>944</v>
+      </c>
+      <c r="C21" s="137" t="s">
+        <v>1245</v>
+      </c>
+      <c r="D21" s="55"/>
+      <c r="E21" s="71"/>
+    </row>
+    <row r="22" spans="1:5" s="54" customFormat="1" ht="43.2">
+      <c r="A22" s="55"/>
+      <c r="B22" s="55" t="s">
+        <v>945</v>
+      </c>
+      <c r="C22" s="137" t="s">
+        <v>1246</v>
+      </c>
+      <c r="D22" s="55"/>
+      <c r="E22" s="71"/>
+    </row>
+    <row r="23" spans="1:5" s="54" customFormat="1">
+      <c r="A23" s="53" t="s">
+        <v>504</v>
+      </c>
+      <c r="B23" s="96" t="s">
+        <v>946</v>
+      </c>
+      <c r="E23" s="71"/>
+    </row>
+    <row r="24" spans="1:5" s="54" customFormat="1" ht="86.4">
+      <c r="A24" s="55" t="s">
+        <v>505</v>
+      </c>
+      <c r="B24" s="55" t="s">
+        <v>506</v>
+      </c>
+      <c r="C24" s="55" t="s">
+        <v>507</v>
+      </c>
+      <c r="D24" s="55"/>
+      <c r="E24" s="71"/>
+    </row>
+    <row r="25" spans="1:5" ht="100.8">
+      <c r="A25" s="55" t="s">
+        <v>508</v>
+      </c>
+      <c r="B25" s="55" t="s">
+        <v>509</v>
+      </c>
+      <c r="C25" s="55" t="s">
+        <v>510</v>
+      </c>
+      <c r="D25" s="55"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="53" t="s">
+        <v>511</v>
+      </c>
+      <c r="B26" s="54"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
+    </row>
+    <row r="27" spans="1:5" ht="230.4">
+      <c r="A27" s="55" t="s">
+        <v>512</v>
+      </c>
+      <c r="B27" s="55" t="s">
+        <v>513</v>
+      </c>
+      <c r="C27" s="55" t="s">
+        <v>514</v>
+      </c>
+      <c r="D27" s="55"/>
+    </row>
+    <row r="28" spans="1:5" ht="129.6">
+      <c r="A28" s="55" t="s">
+        <v>515</v>
+      </c>
+      <c r="B28" s="55" t="s">
+        <v>516</v>
+      </c>
+      <c r="C28" s="55" t="s">
+        <v>517</v>
+      </c>
+      <c r="D28" s="55"/>
+    </row>
+    <row r="29" spans="1:5" ht="129.6">
+      <c r="A29" s="55" t="s">
+        <v>518</v>
+      </c>
+      <c r="B29" s="55" t="s">
+        <v>519</v>
+      </c>
+      <c r="C29" s="55" t="s">
+        <v>520</v>
+      </c>
+      <c r="D29" s="55"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="55"/>
+      <c r="B30" s="55"/>
+      <c r="C30" s="55"/>
+      <c r="D30" s="57"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="55"/>
+      <c r="B31" s="55"/>
+      <c r="C31" s="55"/>
+      <c r="D31" s="55"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="55"/>
+      <c r="B32" s="55"/>
+      <c r="C32" s="55"/>
+      <c r="D32" s="55"/>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="55"/>
+      <c r="B33" s="55"/>
+      <c r="C33" s="55"/>
+      <c r="D33" s="55"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F21ADC02-F754-4C6C-B18D-281EDEC7371E}">
+  <sheetPr>
+    <tabColor rgb="FFC00000"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:E13"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="39.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="59.21875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="55.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="43.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" style="70" customWidth="1"/>
+    <col min="6" max="6" width="67.88671875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="64.33203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7.77734375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="39.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="48.88671875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="72.6640625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="43.88671875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="7.77734375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="56.77734375" style="2" customWidth="1"/>
+    <col min="15" max="15" width="46.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="62.88671875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="49.21875" style="2" customWidth="1"/>
+    <col min="18" max="18" width="8.77734375" style="2" customWidth="1"/>
+    <col min="19" max="19" width="67.77734375" style="2" customWidth="1"/>
+    <col min="20" max="20" width="68.33203125" style="2" customWidth="1"/>
+    <col min="21" max="22" width="59.33203125" style="2" customWidth="1"/>
+    <col min="23" max="23" width="59.6640625" style="2" customWidth="1"/>
+    <col min="24" max="24" width="99.44140625" style="2" customWidth="1"/>
+    <col min="25" max="25" width="41.21875" style="2" customWidth="1"/>
+    <col min="26" max="26" width="8.77734375" style="2" customWidth="1"/>
+    <col min="27" max="16384" width="8.77734375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5">
+      <c r="A2" s="53" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="53"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="53"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="53"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="53"/>
+    </row>
+    <row r="8" spans="1:5" s="39" customFormat="1">
+      <c r="E8" s="70"/>
+    </row>
+    <row r="9" spans="1:5" s="54" customFormat="1">
+      <c r="A9" s="53" t="s">
+        <v>545</v>
+      </c>
+      <c r="B9" s="55"/>
+      <c r="C9" s="55"/>
+      <c r="E9" s="71"/>
+    </row>
+    <row r="10" spans="1:5" s="54" customFormat="1" ht="115.2">
+      <c r="A10" s="55"/>
+      <c r="B10" s="55" t="s">
+        <v>546</v>
+      </c>
+      <c r="C10" s="61" t="s">
+        <v>558</v>
+      </c>
+      <c r="E10" s="71"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="53" t="s">
+        <v>622</v>
+      </c>
+      <c r="C11" s="59"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:5" ht="187.2">
+      <c r="A12" s="68"/>
+      <c r="B12" s="85" t="s">
+        <v>621</v>
+      </c>
+      <c r="C12" s="59" t="s">
+        <v>617</v>
+      </c>
+      <c r="D12" s="68" t="s">
+        <v>616</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5" ht="72">
+      <c r="B13" s="85" t="s">
+        <v>624</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A8B751A-9F7E-4F94-B3AC-58712593EA08}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:V20"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="36" style="1" customWidth="1"/>
+    <col min="2" max="2" width="62.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="81.109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="43.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.5546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.88671875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="56.88671875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.6640625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.109375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="67.6640625" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.44140625" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.44140625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.5546875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.33203125" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.6640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:22" s="3" customFormat="1">
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
+      <c r="G2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="17"/>
+      <c r="U2" s="5"/>
+    </row>
+    <row r="3" spans="1:22">
+      <c r="C3" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="P3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="2"/>
+    </row>
+    <row r="4" spans="1:22">
+      <c r="A4" s="1" t="s">
+        <v>1663</v>
+      </c>
+      <c r="C4" s="204" t="s">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
+      <c r="A5" s="10" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B5" s="93" t="s">
+        <v>1664</v>
+      </c>
+      <c r="C5" s="93" t="s">
+        <v>1665</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="43.2">
+      <c r="A6" s="93" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="93" t="s">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="43.2">
+      <c r="A7" s="93" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="93" t="s">
+        <v>1669</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="43.2">
+      <c r="A8" s="93" t="s">
+        <v>1670</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="93" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="43.2">
+      <c r="A9" s="93" t="s">
+        <v>1672</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="93" t="s">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="28.8">
+      <c r="A10" s="93" t="s">
+        <v>1673</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="93" t="s">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="43.2">
+      <c r="A11" s="93" t="s">
+        <v>1675</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="93" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="28.8">
+      <c r="A12" s="93" t="s">
+        <v>1676</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="93" t="s">
+        <v>1677</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="43.2">
+      <c r="A13" s="93" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="93" t="s">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" ht="28.8">
+      <c r="A14" s="93" t="s">
+        <v>1680</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="93" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" ht="28.8">
+      <c r="A15" s="93" t="s">
+        <v>1681</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="93" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="28.8">
+      <c r="A16" s="93" t="s">
+        <v>1682</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="93" t="s">
+        <v>1683</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="28.8">
+      <c r="A17" s="93" t="s">
+        <v>1684</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="93" t="s">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="28.8">
+      <c r="A18" s="93" t="s">
+        <v>1685</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="93" t="s">
+        <v>1686</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="28.8">
+      <c r="A19" s="93" t="s">
+        <v>1687</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="93" t="s">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="28.8">
+      <c r="A20" s="93" t="s">
+        <v>1689</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="93" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AC6B560-69D2-43B5-AB56-4CAC866C01FE}">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
@@ -52426,796 +54469,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0430A206-850D-44C6-89AD-2AAF1FF700E3}">
-  <sheetPr>
-    <tabColor rgb="FF00B050"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A2:E20"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="39.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="42.88671875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="73.77734375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="30.88671875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="7.44140625" style="70" customWidth="1"/>
-    <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="64.33203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="7.77734375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="39.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.88671875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="72.6640625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="43.88671875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="7.77734375" style="2" customWidth="1"/>
-    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
-    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
-    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
-    <col min="19" max="19" width="49.21875" style="2" customWidth="1"/>
-    <col min="20" max="20" width="8.77734375" style="2" customWidth="1"/>
-    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
-    <col min="22" max="22" width="68.33203125" style="2" customWidth="1"/>
-    <col min="23" max="24" width="59.33203125" style="2" customWidth="1"/>
-    <col min="25" max="25" width="59.6640625" style="2" customWidth="1"/>
-    <col min="26" max="26" width="99.44140625" style="2" customWidth="1"/>
-    <col min="27" max="27" width="41.21875" style="2" customWidth="1"/>
-    <col min="28" max="28" width="8.77734375" style="2" customWidth="1"/>
-    <col min="29" max="16384" width="8.77734375" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:5">
-      <c r="A2" s="23" t="s">
-        <v>1219</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="B3" s="168" t="s">
-        <v>1225</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="B4" s="168" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>1237</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" s="39" customFormat="1">
-      <c r="E6" s="70"/>
-    </row>
-    <row r="7" spans="1:5" s="133" customFormat="1">
-      <c r="C7" s="168" t="s">
-        <v>1219</v>
-      </c>
-      <c r="D7" s="171" t="s">
-        <v>1205</v>
-      </c>
-      <c r="E7" s="70"/>
-    </row>
-    <row r="8" spans="1:5" ht="28.8">
-      <c r="A8" s="23" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B8" s="169" t="s">
-        <v>1239</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="43.2">
-      <c r="C9" s="169" t="s">
-        <v>1220</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="158.4">
-      <c r="B10" s="169" t="s">
-        <v>1221</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>1224</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="158.4">
-      <c r="B11" s="169" t="s">
-        <v>1222</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>1223</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="168" t="s">
-        <v>1225</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="72">
-      <c r="B13" s="2" t="s">
-        <v>1227</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>1226</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="28.8">
-      <c r="A14" s="168" t="s">
-        <v>1228</v>
-      </c>
-      <c r="B14" s="114" t="s">
-        <v>1236</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="100.8">
-      <c r="C15" s="169" t="s">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="86.4">
-      <c r="A16" s="2" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>1229</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>1230</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="216">
-      <c r="A17" s="2" t="s">
-        <v>1064</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>1233</v>
-      </c>
-      <c r="C17" s="169" t="s">
-        <v>1231</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="216">
-      <c r="B18" s="2" t="s">
-        <v>1235</v>
-      </c>
-      <c r="C18" s="169" t="s">
-        <v>1232</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="168" t="s">
-        <v>1238</v>
-      </c>
-      <c r="D19" s="170" t="s">
-        <v>1205</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="86.4">
-      <c r="B20" s="2" t="s">
-        <v>1240</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>1241</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D7" r:id="rId1" location="teleport" xr:uid="{0E3B3246-2353-4504-A941-8F6807E7B81A}"/>
-    <hyperlink ref="D19" r:id="rId2" location="multiple-teleports-on-the-same-target" xr:uid="{53012BAD-A14C-4C99-818A-7EC8E407934F}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBDC1ECC-7624-429D-BB98-76AA7F755485}">
-  <sheetPr>
-    <tabColor rgb="FF00B050"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A2:E22"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="39.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="51.21875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="73.77734375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="55.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="7.44140625" style="70" customWidth="1"/>
-    <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="64.33203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="7.77734375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="39.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.88671875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="72.6640625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="43.88671875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="7.77734375" style="2" customWidth="1"/>
-    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
-    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
-    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
-    <col min="19" max="19" width="49.21875" style="2" customWidth="1"/>
-    <col min="20" max="20" width="8.77734375" style="2" customWidth="1"/>
-    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
-    <col min="22" max="22" width="68.33203125" style="2" customWidth="1"/>
-    <col min="23" max="24" width="59.33203125" style="2" customWidth="1"/>
-    <col min="25" max="25" width="59.6640625" style="2" customWidth="1"/>
-    <col min="26" max="26" width="99.44140625" style="2" customWidth="1"/>
-    <col min="27" max="27" width="41.21875" style="2" customWidth="1"/>
-    <col min="28" max="28" width="8.77734375" style="2" customWidth="1"/>
-    <col min="29" max="16384" width="8.77734375" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:5">
-      <c r="A2" s="23" t="s">
-        <v>1247</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="B3" s="168" t="s">
-        <v>1258</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="B4" s="168"/>
-    </row>
-    <row r="6" spans="1:5" s="39" customFormat="1">
-      <c r="E6" s="70"/>
-    </row>
-    <row r="7" spans="1:5" s="133" customFormat="1">
-      <c r="C7" s="168" t="s">
-        <v>1247</v>
-      </c>
-      <c r="D7" s="172" t="s">
-        <v>1205</v>
-      </c>
-      <c r="E7" s="70"/>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="23" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="129.6">
-      <c r="B9" s="169" t="s">
-        <v>1248</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>1249</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="168" t="s">
-        <v>1258</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="57.6">
-      <c r="B11" s="2" t="s">
-        <v>1250</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>1256</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>1255</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="28.8">
-      <c r="B12" s="2" t="s">
-        <v>1251</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>1252</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="86.4">
-      <c r="B13" s="2" t="s">
-        <v>1253</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>1257</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="168" t="s">
-        <v>1259</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="C15" s="2" t="s">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="30">
-      <c r="A16" s="2" t="s">
-        <v>1261</v>
-      </c>
-      <c r="C16" s="173" t="s">
-        <v>1264</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="30">
-      <c r="A17" s="2" t="s">
-        <v>1262</v>
-      </c>
-      <c r="C17" s="174" t="s">
-        <v>1265</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="30">
-      <c r="A18" s="2" t="s">
-        <v>1263</v>
-      </c>
-      <c r="C18" s="174" t="s">
-        <v>1266</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="316.8">
-      <c r="B19" s="2" t="s">
-        <v>1268</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>1267</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="168" t="s">
-        <v>1269</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="144">
-      <c r="B21" s="169" t="s">
-        <v>1271</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>1270</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="172.8">
-      <c r="B22" s="169" t="s">
-        <v>1272</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D7" r:id="rId1" xr:uid="{6A6FD24F-904C-4C95-BE3E-B72B8B6DD4CA}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A35D37AB-889F-4E36-AD27-D38FD2468E4E}">
-  <sheetPr>
-    <tabColor rgb="FF7030A0"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A2:E33"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="39.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="59.88671875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="59.21875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="55.33203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="10.21875" style="70" customWidth="1"/>
-    <col min="6" max="6" width="64.33203125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="7.77734375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="39.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="48.88671875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="72.6640625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="43.88671875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="7.77734375" style="2" customWidth="1"/>
-    <col min="13" max="13" width="56.77734375" style="2" customWidth="1"/>
-    <col min="14" max="14" width="46.77734375" style="2" customWidth="1"/>
-    <col min="15" max="15" width="62.88671875" style="2" customWidth="1"/>
-    <col min="16" max="16" width="49.21875" style="2" customWidth="1"/>
-    <col min="17" max="17" width="8.77734375" style="2" customWidth="1"/>
-    <col min="18" max="18" width="67.77734375" style="2" customWidth="1"/>
-    <col min="19" max="19" width="68.33203125" style="2" customWidth="1"/>
-    <col min="20" max="21" width="59.33203125" style="2" customWidth="1"/>
-    <col min="22" max="22" width="59.6640625" style="2" customWidth="1"/>
-    <col min="23" max="23" width="99.44140625" style="2" customWidth="1"/>
-    <col min="24" max="24" width="41.21875" style="2" customWidth="1"/>
-    <col min="25" max="25" width="8.77734375" style="2" customWidth="1"/>
-    <col min="26" max="16384" width="8.77734375" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:5">
-      <c r="A2" s="53" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="131"/>
-      <c r="B3" s="107" t="s">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="131"/>
-      <c r="B4" s="107" t="s">
-        <v>937</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="131"/>
-      <c r="B5" s="107" t="s">
-        <v>938</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="131"/>
-      <c r="B6" s="107" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="53" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="53" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" s="39" customFormat="1">
-      <c r="E10" s="70"/>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="40" t="s">
-        <v>266</v>
-      </c>
-      <c r="B11" s="40" t="s">
-        <v>267</v>
-      </c>
-      <c r="C11" s="40" t="s">
-        <v>270</v>
-      </c>
-      <c r="D11" s="40" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" s="54" customFormat="1">
-      <c r="A12" s="53" t="s">
-        <v>501</v>
-      </c>
-      <c r="E12" s="71"/>
-    </row>
-    <row r="13" spans="1:5" s="54" customFormat="1" ht="259.2">
-      <c r="A13" s="55" t="s">
-        <v>502</v>
-      </c>
-      <c r="B13" s="55" t="s">
-        <v>934</v>
-      </c>
-      <c r="C13" s="55" t="s">
-        <v>503</v>
-      </c>
-      <c r="D13" s="55"/>
-      <c r="E13" s="71"/>
-    </row>
-    <row r="14" spans="1:5" s="54" customFormat="1">
-      <c r="A14" s="62" t="s">
-        <v>935</v>
-      </c>
-      <c r="B14" s="55"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="55"/>
-      <c r="E14" s="71"/>
-    </row>
-    <row r="15" spans="1:5" s="54" customFormat="1" ht="28.8">
-      <c r="A15" s="55"/>
-      <c r="B15" s="55" t="s">
-        <v>936</v>
-      </c>
-      <c r="C15" s="137" t="s">
-        <v>941</v>
-      </c>
-      <c r="D15" s="55"/>
-      <c r="E15" s="71"/>
-    </row>
-    <row r="16" spans="1:5" s="54" customFormat="1" ht="28.8">
-      <c r="A16" s="55"/>
-      <c r="B16" s="55" t="s">
-        <v>937</v>
-      </c>
-      <c r="C16" s="137" t="s">
-        <v>940</v>
-      </c>
-      <c r="D16" s="55"/>
-      <c r="E16" s="71"/>
-    </row>
-    <row r="17" spans="1:5" s="54" customFormat="1" ht="57.6">
-      <c r="A17" s="55"/>
-      <c r="B17" s="55" t="s">
-        <v>938</v>
-      </c>
-      <c r="C17" s="137" t="s">
-        <v>1242</v>
-      </c>
-      <c r="D17" s="55"/>
-      <c r="E17" s="71"/>
-    </row>
-    <row r="18" spans="1:5" s="54" customFormat="1" ht="43.2">
-      <c r="A18" s="55"/>
-      <c r="B18" s="55" t="s">
-        <v>939</v>
-      </c>
-      <c r="C18" s="137" t="s">
-        <v>1243</v>
-      </c>
-      <c r="D18" s="55"/>
-      <c r="E18" s="71"/>
-    </row>
-    <row r="19" spans="1:5" s="54" customFormat="1">
-      <c r="A19" s="62" t="s">
-        <v>942</v>
-      </c>
-      <c r="B19" s="55"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="71"/>
-    </row>
-    <row r="20" spans="1:5" s="54" customFormat="1" ht="43.2">
-      <c r="A20" s="55"/>
-      <c r="B20" s="55" t="s">
-        <v>943</v>
-      </c>
-      <c r="C20" s="137" t="s">
-        <v>1244</v>
-      </c>
-      <c r="D20" s="55"/>
-      <c r="E20" s="71"/>
-    </row>
-    <row r="21" spans="1:5" s="54" customFormat="1" ht="57.6">
-      <c r="A21" s="55"/>
-      <c r="B21" s="55" t="s">
-        <v>944</v>
-      </c>
-      <c r="C21" s="137" t="s">
-        <v>1245</v>
-      </c>
-      <c r="D21" s="55"/>
-      <c r="E21" s="71"/>
-    </row>
-    <row r="22" spans="1:5" s="54" customFormat="1" ht="43.2">
-      <c r="A22" s="55"/>
-      <c r="B22" s="55" t="s">
-        <v>945</v>
-      </c>
-      <c r="C22" s="137" t="s">
-        <v>1246</v>
-      </c>
-      <c r="D22" s="55"/>
-      <c r="E22" s="71"/>
-    </row>
-    <row r="23" spans="1:5" s="54" customFormat="1">
-      <c r="A23" s="53" t="s">
-        <v>504</v>
-      </c>
-      <c r="B23" s="96" t="s">
-        <v>946</v>
-      </c>
-      <c r="E23" s="71"/>
-    </row>
-    <row r="24" spans="1:5" s="54" customFormat="1" ht="86.4">
-      <c r="A24" s="55" t="s">
-        <v>505</v>
-      </c>
-      <c r="B24" s="55" t="s">
-        <v>506</v>
-      </c>
-      <c r="C24" s="55" t="s">
-        <v>507</v>
-      </c>
-      <c r="D24" s="55"/>
-      <c r="E24" s="71"/>
-    </row>
-    <row r="25" spans="1:5" ht="100.8">
-      <c r="A25" s="55" t="s">
-        <v>508</v>
-      </c>
-      <c r="B25" s="55" t="s">
-        <v>509</v>
-      </c>
-      <c r="C25" s="55" t="s">
-        <v>510</v>
-      </c>
-      <c r="D25" s="55"/>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="53" t="s">
-        <v>511</v>
-      </c>
-      <c r="B26" s="54"/>
-      <c r="C26" s="54"/>
-      <c r="D26" s="54"/>
-    </row>
-    <row r="27" spans="1:5" ht="230.4">
-      <c r="A27" s="55" t="s">
-        <v>512</v>
-      </c>
-      <c r="B27" s="55" t="s">
-        <v>513</v>
-      </c>
-      <c r="C27" s="55" t="s">
-        <v>514</v>
-      </c>
-      <c r="D27" s="55"/>
-    </row>
-    <row r="28" spans="1:5" ht="129.6">
-      <c r="A28" s="55" t="s">
-        <v>515</v>
-      </c>
-      <c r="B28" s="55" t="s">
-        <v>516</v>
-      </c>
-      <c r="C28" s="55" t="s">
-        <v>517</v>
-      </c>
-      <c r="D28" s="55"/>
-    </row>
-    <row r="29" spans="1:5" ht="129.6">
-      <c r="A29" s="55" t="s">
-        <v>518</v>
-      </c>
-      <c r="B29" s="55" t="s">
-        <v>519</v>
-      </c>
-      <c r="C29" s="55" t="s">
-        <v>520</v>
-      </c>
-      <c r="D29" s="55"/>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="55"/>
-      <c r="B30" s="55"/>
-      <c r="C30" s="55"/>
-      <c r="D30" s="57"/>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="55"/>
-      <c r="B31" s="55"/>
-      <c r="C31" s="55"/>
-      <c r="D31" s="55"/>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="55"/>
-      <c r="B32" s="55"/>
-      <c r="C32" s="55"/>
-      <c r="D32" s="55"/>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="55"/>
-      <c r="B33" s="55"/>
-      <c r="C33" s="55"/>
-      <c r="D33" s="55"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F21ADC02-F754-4C6C-B18D-281EDEC7371E}">
-  <sheetPr>
-    <tabColor rgb="FFC00000"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A2:E13"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="39.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="59.21875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="55.33203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="43.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" style="70" customWidth="1"/>
-    <col min="6" max="6" width="67.88671875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="64.33203125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="7.77734375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="39.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="48.88671875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="72.6640625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="43.88671875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="7.77734375" style="2" customWidth="1"/>
-    <col min="14" max="14" width="56.77734375" style="2" customWidth="1"/>
-    <col min="15" max="15" width="46.77734375" style="2" customWidth="1"/>
-    <col min="16" max="16" width="62.88671875" style="2" customWidth="1"/>
-    <col min="17" max="17" width="49.21875" style="2" customWidth="1"/>
-    <col min="18" max="18" width="8.77734375" style="2" customWidth="1"/>
-    <col min="19" max="19" width="67.77734375" style="2" customWidth="1"/>
-    <col min="20" max="20" width="68.33203125" style="2" customWidth="1"/>
-    <col min="21" max="22" width="59.33203125" style="2" customWidth="1"/>
-    <col min="23" max="23" width="59.6640625" style="2" customWidth="1"/>
-    <col min="24" max="24" width="99.44140625" style="2" customWidth="1"/>
-    <col min="25" max="25" width="41.21875" style="2" customWidth="1"/>
-    <col min="26" max="26" width="8.77734375" style="2" customWidth="1"/>
-    <col min="27" max="16384" width="8.77734375" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:5">
-      <c r="A2" s="53" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="53"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="53"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="53"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="53"/>
-    </row>
-    <row r="8" spans="1:5" s="39" customFormat="1">
-      <c r="E8" s="70"/>
-    </row>
-    <row r="9" spans="1:5" s="54" customFormat="1">
-      <c r="A9" s="53" t="s">
-        <v>545</v>
-      </c>
-      <c r="B9" s="55"/>
-      <c r="C9" s="55"/>
-      <c r="E9" s="71"/>
-    </row>
-    <row r="10" spans="1:5" s="54" customFormat="1" ht="115.2">
-      <c r="A10" s="55"/>
-      <c r="B10" s="55" t="s">
-        <v>546</v>
-      </c>
-      <c r="C10" s="61" t="s">
-        <v>558</v>
-      </c>
-      <c r="E10" s="71"/>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="53" t="s">
-        <v>622</v>
-      </c>
-      <c r="C11" s="59"/>
-      <c r="D11" s="68"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:5" ht="187.2">
-      <c r="A12" s="68"/>
-      <c r="B12" s="85" t="s">
-        <v>621</v>
-      </c>
-      <c r="C12" s="59" t="s">
-        <v>617</v>
-      </c>
-      <c r="D12" s="68" t="s">
-        <v>616</v>
-      </c>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:5" ht="72">
-      <c r="B13" s="85" t="s">
-        <v>624</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="E13" s="2"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BCD0E6E-DD2E-4D2F-A721-3BEA42FDB1B7}">
   <sheetPr>
     <tabColor theme="9"/>
@@ -53566,7 +54820,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ED59116-A924-4966-A5C6-E1DAFCF03325}">
   <sheetPr>
     <tabColor theme="9"/>
@@ -53862,7 +55116,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F50744EB-70E7-48FB-BF33-F020F02BE9B4}">
   <sheetPr>
     <tabColor theme="9"/>
@@ -54344,7 +55598,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66028E03-DC1C-4884-967A-52D62E8CDBFA}">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
@@ -55012,493 +56266,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId14"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98729587-661C-4647-8A0E-68347CF7376F}">
-  <sheetPr>
-    <tabColor rgb="FF00B050"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A2:E16"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="39.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="59.21875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="55.33203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="53" style="2" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" style="70" customWidth="1"/>
-    <col min="6" max="6" width="67.88671875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="64.33203125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="7.77734375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="39.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="48.88671875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="72.6640625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="43.88671875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="7.77734375" style="2" customWidth="1"/>
-    <col min="14" max="14" width="56.77734375" style="2" customWidth="1"/>
-    <col min="15" max="15" width="46.77734375" style="2" customWidth="1"/>
-    <col min="16" max="16" width="62.88671875" style="2" customWidth="1"/>
-    <col min="17" max="17" width="49.21875" style="2" customWidth="1"/>
-    <col min="18" max="18" width="8.77734375" style="2" customWidth="1"/>
-    <col min="19" max="19" width="67.77734375" style="2" customWidth="1"/>
-    <col min="20" max="20" width="68.33203125" style="2" customWidth="1"/>
-    <col min="21" max="22" width="59.33203125" style="2" customWidth="1"/>
-    <col min="23" max="23" width="59.6640625" style="2" customWidth="1"/>
-    <col min="24" max="24" width="99.44140625" style="2" customWidth="1"/>
-    <col min="25" max="25" width="41.21875" style="2" customWidth="1"/>
-    <col min="26" max="26" width="8.77734375" style="2" customWidth="1"/>
-    <col min="27" max="16384" width="8.77734375" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:5">
-      <c r="A2" s="79"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="53"/>
-      <c r="C3" s="87"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="53"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="53"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="53"/>
-    </row>
-    <row r="8" spans="1:5" s="39" customFormat="1">
-      <c r="E8" s="70"/>
-    </row>
-    <row r="10" spans="1:5" s="54" customFormat="1">
-      <c r="A10" s="53" t="s">
-        <v>482</v>
-      </c>
-      <c r="E10" s="70"/>
-    </row>
-    <row r="11" spans="1:5" s="54" customFormat="1" ht="57.6">
-      <c r="C11" s="101" t="s">
-        <v>722</v>
-      </c>
-      <c r="E11" s="70"/>
-    </row>
-    <row r="12" spans="1:5" s="54" customFormat="1" ht="244.8">
-      <c r="A12" s="102" t="s">
-        <v>723</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>690</v>
-      </c>
-      <c r="E12" s="70"/>
-    </row>
-    <row r="13" spans="1:5" s="54" customFormat="1">
-      <c r="B13" s="96" t="s">
-        <v>685</v>
-      </c>
-      <c r="C13" s="95" t="s">
-        <v>686</v>
-      </c>
-      <c r="E13" s="70"/>
-    </row>
-    <row r="14" spans="1:5" ht="187.2">
-      <c r="A14" s="22" t="s">
-        <v>719</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>688</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="273.60000000000002">
-      <c r="A15" s="100" t="s">
-        <v>718</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>693</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="409.6">
-      <c r="A16" s="22" t="s">
-        <v>694</v>
-      </c>
-      <c r="B16" s="100" t="s">
-        <v>721</v>
-      </c>
-      <c r="C16" s="100" t="s">
-        <v>720</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35186FB0-D6EE-48D6-AD0A-EC687D3766B2}">
-  <sheetPr>
-    <tabColor rgb="FF00B050"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A2:V31"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="39.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="62" style="2" customWidth="1"/>
-    <col min="3" max="3" width="55.33203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="33.109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" style="70" customWidth="1"/>
-    <col min="6" max="6" width="67.88671875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="64.33203125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="7.77734375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="39.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="48.88671875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="72.6640625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="43.88671875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="7.77734375" style="2" customWidth="1"/>
-    <col min="14" max="14" width="56.77734375" style="2" customWidth="1"/>
-    <col min="15" max="15" width="46.77734375" style="2" customWidth="1"/>
-    <col min="16" max="16" width="62.88671875" style="2" customWidth="1"/>
-    <col min="17" max="17" width="49.21875" style="2" customWidth="1"/>
-    <col min="18" max="18" width="8.77734375" style="2" customWidth="1"/>
-    <col min="19" max="19" width="67.77734375" style="2" customWidth="1"/>
-    <col min="20" max="20" width="68.33203125" style="2" customWidth="1"/>
-    <col min="21" max="22" width="59.33203125" style="2" customWidth="1"/>
-    <col min="23" max="23" width="59.6640625" style="2" customWidth="1"/>
-    <col min="24" max="24" width="99.44140625" style="2" customWidth="1"/>
-    <col min="25" max="25" width="41.21875" style="2" customWidth="1"/>
-    <col min="26" max="26" width="8.77734375" style="2" customWidth="1"/>
-    <col min="27" max="16384" width="8.77734375" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:22">
-      <c r="A2" s="79" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22">
-      <c r="A3" s="53" t="s">
-        <v>482</v>
-      </c>
-      <c r="C3" s="87" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22">
-      <c r="A4" s="53" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22">
-      <c r="A5" s="53" t="s">
-        <v>724</v>
-      </c>
-      <c r="C5" s="92" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22">
-      <c r="A6" s="53" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" s="39" customFormat="1">
-      <c r="E8" s="70"/>
-    </row>
-    <row r="9" spans="1:22">
-      <c r="A9" s="40" t="s">
-        <v>266</v>
-      </c>
-      <c r="B9" s="40" t="s">
-        <v>270</v>
-      </c>
-      <c r="C9" s="40" t="s">
-        <v>268</v>
-      </c>
-      <c r="D9" s="40"/>
-    </row>
-    <row r="10" spans="1:22" s="73" customFormat="1">
-      <c r="A10" s="79" t="s">
-        <v>580</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="72"/>
-      <c r="G10" s="74"/>
-      <c r="J10" s="72"/>
-      <c r="O10" s="72"/>
-      <c r="Q10" s="74"/>
-      <c r="R10" s="74"/>
-      <c r="T10" s="75"/>
-      <c r="V10" s="74"/>
-    </row>
-    <row r="11" spans="1:22" s="73" customFormat="1">
-      <c r="A11" s="1"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="72"/>
-      <c r="G11" s="74"/>
-      <c r="J11" s="72"/>
-      <c r="O11" s="72"/>
-      <c r="Q11" s="74"/>
-      <c r="R11" s="74"/>
-      <c r="T11" s="75"/>
-      <c r="V11" s="74"/>
-    </row>
-    <row r="12" spans="1:22" s="73" customFormat="1">
-      <c r="A12" s="1"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="72"/>
-      <c r="G12" s="74"/>
-      <c r="J12" s="72"/>
-      <c r="O12" s="72"/>
-      <c r="Q12" s="74"/>
-      <c r="R12" s="74"/>
-      <c r="T12" s="75"/>
-      <c r="V12" s="74"/>
-    </row>
-    <row r="13" spans="1:22" s="73" customFormat="1">
-      <c r="A13" s="87" t="s">
-        <v>663</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="72"/>
-      <c r="G13" s="74"/>
-      <c r="J13" s="72"/>
-      <c r="O13" s="72"/>
-      <c r="Q13" s="74"/>
-      <c r="R13" s="74"/>
-      <c r="T13" s="75"/>
-      <c r="V13" s="74"/>
-    </row>
-    <row r="14" spans="1:22" s="73" customFormat="1" ht="72">
-      <c r="A14" s="87" t="s">
-        <v>663</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="D14" s="1"/>
-      <c r="E14" s="72"/>
-      <c r="G14" s="74"/>
-      <c r="J14" s="72"/>
-      <c r="O14" s="72"/>
-      <c r="Q14" s="74"/>
-      <c r="R14" s="74"/>
-      <c r="T14" s="75"/>
-      <c r="V14" s="74"/>
-    </row>
-    <row r="15" spans="1:22" s="54" customFormat="1">
-      <c r="A15" s="53" t="s">
-        <v>482</v>
-      </c>
-      <c r="B15" s="65" t="s">
-        <v>554</v>
-      </c>
-      <c r="E15" s="71"/>
-    </row>
-    <row r="16" spans="1:22" s="54" customFormat="1" ht="100.8">
-      <c r="A16" s="55"/>
-      <c r="B16" s="55" t="s">
-        <v>483</v>
-      </c>
-      <c r="C16" s="55" t="s">
-        <v>566</v>
-      </c>
-      <c r="D16" s="56"/>
-      <c r="E16" s="71"/>
-    </row>
-    <row r="17" spans="1:5" s="54" customFormat="1" ht="43.2">
-      <c r="A17" s="55"/>
-      <c r="B17" s="55" t="s">
-        <v>490</v>
-      </c>
-      <c r="C17" s="61" t="s">
-        <v>547</v>
-      </c>
-      <c r="D17" s="56"/>
-      <c r="E17" s="71"/>
-    </row>
-    <row r="18" spans="1:5" s="54" customFormat="1">
-      <c r="A18" s="55"/>
-      <c r="B18" s="53" t="s">
-        <v>542</v>
-      </c>
-      <c r="C18" s="53" t="s">
-        <v>551</v>
-      </c>
-      <c r="D18" s="56"/>
-      <c r="E18" s="71"/>
-    </row>
-    <row r="19" spans="1:5" s="54" customFormat="1" ht="172.8">
-      <c r="B19" s="55" t="s">
-        <v>543</v>
-      </c>
-      <c r="C19" s="55" t="s">
-        <v>544</v>
-      </c>
-      <c r="D19" s="56"/>
-      <c r="E19" s="71"/>
-    </row>
-    <row r="20" spans="1:5" s="54" customFormat="1">
-      <c r="B20" s="64" t="s">
-        <v>552</v>
-      </c>
-      <c r="C20" s="53" t="s">
-        <v>539</v>
-      </c>
-      <c r="E20" s="71"/>
-    </row>
-    <row r="21" spans="1:5" s="54" customFormat="1" ht="273.60000000000002">
-      <c r="A21" s="61" t="s">
-        <v>556</v>
-      </c>
-      <c r="B21" s="55" t="s">
-        <v>540</v>
-      </c>
-      <c r="C21" s="61" t="s">
-        <v>541</v>
-      </c>
-      <c r="E21" s="71"/>
-    </row>
-    <row r="22" spans="1:5" s="54" customFormat="1" ht="72">
-      <c r="A22" s="61" t="s">
-        <v>560</v>
-      </c>
-      <c r="B22" s="55" t="s">
-        <v>557</v>
-      </c>
-      <c r="C22" s="55" t="s">
-        <v>555</v>
-      </c>
-      <c r="E22" s="71"/>
-    </row>
-    <row r="23" spans="1:5" s="54" customFormat="1">
-      <c r="A23" s="53" t="s">
-        <v>497</v>
-      </c>
-      <c r="B23" s="55"/>
-      <c r="C23" s="61"/>
-      <c r="E23" s="71"/>
-    </row>
-    <row r="24" spans="1:5" s="54" customFormat="1" ht="100.8">
-      <c r="A24" s="54" t="s">
-        <v>497</v>
-      </c>
-      <c r="B24" s="55" t="s">
-        <v>564</v>
-      </c>
-      <c r="C24" s="61"/>
-      <c r="E24" s="71"/>
-    </row>
-    <row r="25" spans="1:5" s="54" customFormat="1" ht="201.6">
-      <c r="A25" s="54" t="s">
-        <v>498</v>
-      </c>
-      <c r="B25" s="55" t="s">
-        <v>565</v>
-      </c>
-      <c r="C25" s="69" t="s">
-        <v>568</v>
-      </c>
-      <c r="E25" s="71"/>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="53" t="s">
-        <v>724</v>
-      </c>
-      <c r="B26" s="54"/>
-      <c r="C26" s="54"/>
-      <c r="D26" s="54"/>
-      <c r="E26" s="71"/>
-    </row>
-    <row r="27" spans="1:5" ht="100.8">
-      <c r="A27" s="55" t="s">
-        <v>803</v>
-      </c>
-      <c r="B27" s="113" t="s">
-        <v>814</v>
-      </c>
-      <c r="C27" s="55" t="s">
-        <v>569</v>
-      </c>
-      <c r="D27" s="56"/>
-    </row>
-    <row r="28" spans="1:5" ht="302.39999999999998">
-      <c r="A28" s="55" t="s">
-        <v>802</v>
-      </c>
-      <c r="B28" s="113" t="s">
-        <v>812</v>
-      </c>
-      <c r="C28" s="55" t="s">
-        <v>570</v>
-      </c>
-      <c r="D28" s="56"/>
-    </row>
-    <row r="29" spans="1:5" ht="172.8">
-      <c r="A29" s="55" t="s">
-        <v>806</v>
-      </c>
-      <c r="B29" s="113" t="s">
-        <v>813</v>
-      </c>
-      <c r="C29" s="113" t="s">
-        <v>809</v>
-      </c>
-      <c r="D29" s="56"/>
-    </row>
-    <row r="30" spans="1:5" ht="86.4">
-      <c r="A30" s="55" t="s">
-        <v>807</v>
-      </c>
-      <c r="B30" s="55" t="s">
-        <v>804</v>
-      </c>
-      <c r="C30" s="69" t="s">
-        <v>805</v>
-      </c>
-      <c r="D30" s="56"/>
-    </row>
-    <row r="31" spans="1:5" ht="216">
-      <c r="A31" s="55" t="s">
-        <v>810</v>
-      </c>
-      <c r="B31" s="69" t="s">
-        <v>811</v>
-      </c>
-      <c r="C31" s="113" t="s">
-        <v>808</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
 </file>